--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6C649D-FF0D-3D45-A98B-9C0B87CF0292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8270C33-0AF7-E149-9EF7-457035E3A4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2656" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2661" uniqueCount="1179">
   <si>
     <t>id</t>
   </si>
@@ -3611,6 +3611,28 @@
   <si>
     <t>対 お城 与ダメx4
 100％の確率でLv4波動（射程 1067.5）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>devil,sage</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>black,floating</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>custom,floating,sage</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>enemy_images/enemy_530.jpg</t>
+  </si>
+  <si>
+    <t>聡慧の覇者ゼロムート</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -3704,7 +3726,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3724,6 +3746,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3958,7 +3981,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R530"/>
+  <dimension ref="A1:R531"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -27316,8 +27339,8 @@
       <c r="E520" t="s">
         <v>1115</v>
       </c>
-      <c r="F520" t="s">
-        <v>118</v>
+      <c r="F520" s="9" t="s">
+        <v>1175</v>
       </c>
       <c r="G520">
         <v>5000</v>
@@ -27691,8 +27714,8 @@
       <c r="E529" t="s">
         <v>1135</v>
       </c>
-      <c r="F529" t="s">
-        <v>1003</v>
+      <c r="F529" s="9" t="s">
+        <v>1174</v>
       </c>
       <c r="G529">
         <v>2100000</v>
@@ -27743,6 +27766,53 @@
       </c>
       <c r="G530">
         <v>10</v>
+      </c>
+    </row>
+    <row r="531" spans="1:15">
+      <c r="A531">
+        <v>530</v>
+      </c>
+      <c r="B531">
+        <v>530</v>
+      </c>
+      <c r="C531" s="9" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D531" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E531" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F531" s="9" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G531">
+        <v>4200000</v>
+      </c>
+      <c r="H531" s="11">
+        <v>290000</v>
+      </c>
+      <c r="I531">
+        <v>20</v>
+      </c>
+      <c r="J531">
+        <v>93</v>
+      </c>
+      <c r="K531">
+        <v>5</v>
+      </c>
+      <c r="L531">
+        <v>65</v>
+      </c>
+      <c r="M531">
+        <v>330</v>
+      </c>
+      <c r="N531" t="s">
+        <v>31</v>
+      </c>
+      <c r="O531">
+        <v>18900</v>
       </c>
     </row>
   </sheetData>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8270C33-0AF7-E149-9EF7-457035E3A4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265F3944-C485-394B-A322-F65F82C80123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2661" uniqueCount="1179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2703" uniqueCount="1217">
   <si>
     <t>id</t>
   </si>
@@ -3635,12 +3635,264 @@
     <t>聡慧の覇者ゼロムート</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>サウナが大好きなアラビア生まれの
+ラクダ。鼻の穴を閉じることができる
+特技を持っているが、ラクダの基本性能で
+あることを彼は知らない。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>対 お城 与ダメx4</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ルンルンの語源について日々研究をしている
+アヒル。あとルンルンとランラン、どちらが
+強いのかについても研究を進めている。
+あとフンフンとズンドコとデンデケ（割愛</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こう見えて実は78歳の老人である。
+健康のためにいつも歩いて移動しているが
+ややこしいので浮いてる敵扱いに
+されたことを毎日グチっている。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>イノシシのシシはライオンの獅子だと
+ずっと思いこんでいたが違うことを
+同僚に知らされ、あまりの恥ずかしさに
+赤くなったイノシシ。根はマジメ。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>木の上から降臨した最強の猛獣。
+…のはずだったが、地面に降りると移動が
+しんどすぎて早く木の上に帰りたがっている
+やる気の無いナマケモノ。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>歌唱力にはとっても自信のあるナカイくん。
+もちろん大の巨人ファンである。
+毛皮の中に誰かが入っているとの
+ウワサもあるが本人は否定している。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>TVで見た変てこなおじさんのものまねが
+したくて二足歩行までは何とかマスター。
+あとは手を突き出して、くるくる回して
+最後に自分の名前を言えば完成である。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>現役女子大生の彼女の午後はいつもの
+カフェでティータイム。友人たちと
+他愛の無い話で楽しむその時間は、
+正直みんなうんざりしている。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>俺は孤独な一匹オオカミさ・・・と
+ハイエナのくせに語る、残飯処理係。
+孤独を好み、近づく奴らを
+100％ふっとばす嫌なヤツ。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>100％の確率でふっとばす</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>33％の確率でLv3波動（射程 867.5）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>波動を放つ、13匹のお父さん。
+いつでもダンディなそのいでたちで
+7回の結婚と52回の浮気暦を持つ。
+黒に近いグレーだが黒くは無い。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こう見えてじつは都会育ちのウルルン。
+近所のペットショップでウルフを購入、
+中学校への登下校は、いつもウルフに
+またがって移動している。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ある日の折り込みチラシに書いてあった
+アルバイト募集で殺し屋のバイトを始めた
+黒いわんこ。日々、まじめに働いて
+予備校の学費を稼いでいる。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>連邦政府の改造手術により生まれ変わった
+ハガネの肉体を持った改造カバ。
+クリティカルな攻撃が弱点らしい。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ブタヤロウのご先祖様。
+そう、彼女こそはブタ小屋王国2代目女王
+エリザベス2世なのである！
+無菌豚として、近日出荷予定。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ぶんぶん先生の人生に多大な影響を与えた
+日本を代表する文豪。代表作は
+「体罰と散髪」(1868年)
+「パニッシュメンタル」(1875年)など</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>愛ゆえにおまえを天に返すのだ！と
+わけのわからない愛情で
+突然殴ってくる危険な先生。
+殴られるとあの世が見える。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ついにマジメに働き始めたニートゴリラ。
+ニート時代の自分と決別し、新しい人生の
+一歩を踏み出した誇り高き中年。
+別居中の家族も近々帰ってくるらしい。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「闇の世界ではライセンスなんかいらねぇ、
+殺しでさえも正当化されるのがこの世界さ」
+というセリフがお気に入りのカンガルー。
+袋の中の息子にとってはいい迷惑である。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>3連続攻撃 4,250 250 497（2F 4F 8F）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>世界的に有名な映画の巨匠
+を意識した泣かず飛ばずの映画監督
+いつも売れない作品ばかりを作るが
+作中のお色気要素には定評がある</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>覚えたてのファイル共有ソフトで、トロイの
+木馬とかいう謎の病原菌に侵されて暴走
+したカバちゃん。立ちふさがる敵はすべて
+ふっとばす。クリティカルな攻撃が弱点。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>もっと人助けをしたくて改造手術を
+施した一角くん。通報前に電話回線を
+傍受して出動できるが、足が遅いので
+現場にはやっぱり間に合わない。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>カオル君の家に居候してはや6年の
+着ぐるみクマ。ようやく重い腰を
+上げて外の世界へ出てきた。
+中身はサイボーグ化したクマ先生。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>30％の確率でふっとばす
+対 お城 与ダメx4
+90％の確率でLv8波動（射程 1867.5）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>人類の存亡をかけ開発された顔型決戦兵器。
+放たれる「波動」はすべてを無に帰す。
+浮いてるように見えるが光学迷彩仕様の
+12本足は肉眼で見ることが出来ない。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ちまたでウワサのアザラシに憧れて
+上京してきたアザラシ。
+なかなかチヤホヤされないので
+今度はサイボーグ化してみた。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>修正</t>
+    <rPh sb="0" eb="2">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>超高速回転による連続攻撃は
+いかなる者もよせつけない。
+動きを止めたり、押し返す手段があれば
+何とか攻略できるかも！？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>20％の確率でふっとばす</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>超高速回転による連続攻撃は
+いかなる者もよせつけない。
+サイクロン掃除機ブームのおかげで
+最近はどこに行っても人気者である。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>超高速回転による連続攻撃は
+いかなる者もよせつけない。
+さらに触れるものをたまに吹き飛ばす
+特性を持った恐ろしい敵。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>超高速回転による連続攻撃は
+いかなる者もよせつけない。
+鉄製であるがゆえに浮くことが出来ず
+鉄屑をまき散らしながら破壊を続ける。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>50％の確率で130F動きを止める</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>100％の確率でLv3波動（射程 867.5）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>％の確率でクリティカル</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3700,6 +3952,19 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFE0E0E0"/>
+      <name val="MS Mincho"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFF0C030"/>
+      <name val="Avenir"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3726,7 +3991,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3747,6 +4012,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -5427,7 +5693,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:17" ht="60">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5473,8 +5739,14 @@
       <c r="O30">
         <v>3555</v>
       </c>
-    </row>
-    <row r="31" spans="1:17">
+      <c r="P30" s="9" t="s">
+        <v>1180</v>
+      </c>
+      <c r="Q30" s="10" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="62">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5520,8 +5792,12 @@
       <c r="O31">
         <v>1580</v>
       </c>
-    </row>
-    <row r="32" spans="1:17">
+      <c r="P31" s="6"/>
+      <c r="Q31" s="10" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="60">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5567,8 +5843,11 @@
       <c r="O32">
         <v>3160</v>
       </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="Q32" s="10" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="60">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5614,8 +5893,11 @@
       <c r="O33">
         <v>8295</v>
       </c>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="Q33" s="10" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="60">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5661,8 +5943,11 @@
       <c r="O34">
         <v>7900</v>
       </c>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="Q34" s="10" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="60">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5708,8 +5993,11 @@
       <c r="O35">
         <v>3160</v>
       </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="Q35" s="10" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="60">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5755,8 +6043,11 @@
       <c r="O36">
         <v>2765</v>
       </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="Q36" s="10" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="60">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5802,8 +6093,11 @@
       <c r="O37">
         <v>2765</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" ht="20" customHeight="1">
+      <c r="Q37" s="10" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="60">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5849,8 +6143,14 @@
       <c r="O38">
         <v>4348</v>
       </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="P38" s="9" t="s">
+        <v>1189</v>
+      </c>
+      <c r="Q38" s="10" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="60">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5896,8 +6196,14 @@
       <c r="O39">
         <v>6320</v>
       </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="P39" s="9" t="s">
+        <v>1190</v>
+      </c>
+      <c r="Q39" s="10" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="60">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5943,8 +6249,11 @@
       <c r="O40">
         <v>5530</v>
       </c>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="Q40" s="10" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="60">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5990,8 +6299,11 @@
       <c r="O41">
         <v>1580</v>
       </c>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="Q41" s="10" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" ht="45">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6037,8 +6349,11 @@
       <c r="O42">
         <v>1580</v>
       </c>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="Q42" s="10" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="60">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6084,8 +6399,11 @@
       <c r="O43">
         <v>2370</v>
       </c>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="Q43" s="10" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="60">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6131,8 +6449,11 @@
       <c r="O44">
         <v>7900</v>
       </c>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="Q44" s="10" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="60">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6178,8 +6499,11 @@
       <c r="O45">
         <v>11850</v>
       </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="Q45" s="10" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="60">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6225,8 +6549,11 @@
       <c r="O46">
         <v>1975</v>
       </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="Q46" s="10" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="60">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6272,8 +6599,14 @@
       <c r="O47">
         <v>2370</v>
       </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="P47" s="9" t="s">
+        <v>1200</v>
+      </c>
+      <c r="Q47" s="10" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="60">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6319,8 +6652,11 @@
       <c r="O48">
         <v>3950</v>
       </c>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="Q48" s="10" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="60">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6366,8 +6702,14 @@
       <c r="O49">
         <v>3946</v>
       </c>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="P49" s="9" t="s">
+        <v>1189</v>
+      </c>
+      <c r="Q49" s="10" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="60">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6413,8 +6755,11 @@
       <c r="O50">
         <v>2370</v>
       </c>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="Q50" s="10" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" ht="60">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6460,8 +6805,11 @@
       <c r="O51">
         <v>2172</v>
       </c>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="Q51" s="10" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="60">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6507,8 +6855,14 @@
       <c r="O52">
         <v>2172</v>
       </c>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="P52" s="10" t="s">
+        <v>1205</v>
+      </c>
+      <c r="Q52" s="10" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="60">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6554,8 +6908,11 @@
       <c r="O53">
         <v>4562</v>
       </c>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="Q53" s="10" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6602,7 +6959,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:17" ht="17">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6648,8 +7005,12 @@
       <c r="O55">
         <v>23700</v>
       </c>
-    </row>
-    <row r="56" spans="1:15">
+      <c r="P55" s="12"/>
+      <c r="Q55" s="10" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="60">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6695,8 +7056,11 @@
       <c r="O56">
         <v>11850</v>
       </c>
-    </row>
-    <row r="57" spans="1:15">
+      <c r="Q56" s="10" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6742,8 +7106,11 @@
       <c r="O57">
         <v>1580</v>
       </c>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="P57" s="9" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6789,8 +7156,11 @@
       <c r="O58">
         <v>7900</v>
       </c>
-    </row>
-    <row r="59" spans="1:15">
+      <c r="P58" s="9" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="60">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6836,8 +7206,11 @@
       <c r="O59">
         <v>11850</v>
       </c>
-    </row>
-    <row r="60" spans="1:15">
+      <c r="Q59" s="10" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="60">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6883,8 +7256,14 @@
       <c r="O60">
         <v>11850</v>
       </c>
-    </row>
-    <row r="61" spans="1:15">
+      <c r="P60" s="9" t="s">
+        <v>1210</v>
+      </c>
+      <c r="Q60" s="10" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="60">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6930,8 +7309,11 @@
       <c r="O61">
         <v>11850</v>
       </c>
-    </row>
-    <row r="62" spans="1:15">
+      <c r="Q61" s="10" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6978,7 +7360,7 @@
         <v>11850</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:17">
       <c r="A63">
         <v>62</v>
       </c>
@@ -7024,8 +7406,11 @@
       <c r="O63">
         <v>7821</v>
       </c>
-    </row>
-    <row r="64" spans="1:15">
+      <c r="P63" s="9" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17">
       <c r="A64">
         <v>63</v>
       </c>
@@ -7071,8 +7456,11 @@
       <c r="O64">
         <v>9361</v>
       </c>
-    </row>
-    <row r="65" spans="1:15">
+      <c r="P64" s="9" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
       <c r="A65">
         <v>64</v>
       </c>
@@ -7118,8 +7506,11 @@
       <c r="O65">
         <v>7900</v>
       </c>
-    </row>
-    <row r="66" spans="1:15">
+      <c r="P65" s="9" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
       <c r="A66">
         <v>65</v>
       </c>
@@ -7166,7 +7557,7 @@
         <v>3199</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:16">
       <c r="A67">
         <v>66</v>
       </c>
@@ -7213,7 +7604,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:16" ht="17">
       <c r="A68">
         <v>67</v>
       </c>
@@ -7259,8 +7650,11 @@
       <c r="O68">
         <v>7896</v>
       </c>
-    </row>
-    <row r="69" spans="1:15">
+      <c r="P68" s="6" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
       <c r="A69">
         <v>68</v>
       </c>
@@ -7307,7 +7701,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="70" spans="1:15">
+    <row r="70" spans="1:16">
       <c r="A70">
         <v>69</v>
       </c>
@@ -7354,7 +7748,7 @@
         <v>5332</v>
       </c>
     </row>
-    <row r="71" spans="1:15">
+    <row r="71" spans="1:16">
       <c r="A71">
         <v>70</v>
       </c>
@@ -7401,7 +7795,7 @@
         <v>8393</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:16">
       <c r="A72">
         <v>71</v>
       </c>
@@ -7448,7 +7842,7 @@
         <v>7900</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:16">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7495,7 +7889,7 @@
         <v>6320</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:16">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7542,7 +7936,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:16">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7589,7 +7983,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:16">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7636,7 +8030,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:16">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7683,7 +8077,7 @@
         <v>3950</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:16">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7730,7 +8124,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="1:16">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7777,7 +8171,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:16">
       <c r="A80">
         <v>79</v>
       </c>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265F3944-C485-394B-A322-F65F82C80123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222656F4-70DE-574E-9E51-19FCAA9932DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2703" uniqueCount="1217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2729" uniqueCount="1240">
   <si>
     <t>id</t>
   </si>
@@ -3885,6 +3885,146 @@
       </rPr>
       <t>％の確率でクリティカル</t>
     </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>100％の確率でふっとばす
+40％の確率で200F動きを遅くする
+15％の確率でLv7波動（射程 1667.5）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>20％の確率で90F動きを遅くする</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>世の中を変わらない吸引力で
+浄化し続ける恐ろしい天使。
+また天使は浮いている敵属性の特殊攻撃を
+無効化するので注意が必要。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>天使になることを夢見たカバちゃん。
+毛はえ薬で羽が生えてきたので、
+憧れの動物のペガサスに八割ぐらい
+近づいたと思っている。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>わんこのご先祖様。
+いつも、わんこの背後で勉強を
+見守っている。勉強中に居眠りすると、
+具現化してわんこに噛み付く。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>顔がコワイ。という理由で天上界から
+たたき落とされた堕天使ゴリラ。
+堕天使になってからはパチプロで
+生計を立てている。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>天使の為に全財産を投じた実業家。
+天使には、天使属性以外の特殊攻撃が
+効かないということをレアガチャを
+やりまくることで発見した功労者。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ネコカベをライバル視して、負けじと
+自分もカベになってみたわんこ。
+たまに足らないドミノの代わりとして
+使われることもある。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>にょろのような形をしたヘビ。
+赤毛がにょろっと一本出ているため、
+どっかの学者が名づけた名前である。
+体の赤色はもちろん水彩絵の具。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>マンボウなのに本名は鈴木。
+ステルスつきのため魚群探知機に
+反応しない。姿を目撃したものは
+あの世に逝けるという。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>30％の確率で90F動きを遅くする</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>平和のシンボルとして、代々引き継が
+れてきた宿命を背負う17代目ハト。
+侵略してくるにゃんこに平和の頭突きが
+うなりを上げる！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>100％の確率でLv1波動（射程 467.5）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ラッコ一族に代々受け継がれる、
+「ただの石」で漬けた梅干しで
+ボコボコにしてくる。
+その酢っぱさは涙腺を刺激する。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>15％の確率でふっとばす</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>北欧神話に出てくる8本足の天馬。
+名前から連想するイメージとは
+若干違う気もするが、これが現実。
+趣味は家庭菜園</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>100％の確率で60F動きを止める
+無効 （波動 烈波 ふっとばす 止める 遅くする 攻撃力低下）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>50％の確率で60F動きを遅くする</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>50％の確率でふっとばす</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>日々の出来事を赤裸々に語っていた
+自身のブログ「本能のままに」が炎上。
+以来、仲間の誘いが激減したため
+ピンでの活動を余儀なくされている。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>予備校の帰り道、突如現れた巨大な円盤に
+吸い込まれていったわんこ。
+その間の記憶はないが手元に残された
+銀色のスーツはなんとなく毎日着ている。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>時空の歪みによって子供に戻ってしまった
+ニャンダム。顔が大人のままなことに
+ショックを受けキャンディで子供らしさを
+アピールするが電車は大人料金である。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>入手困難なセクシーなビデオを
+古今東西から収集している真っ黒のゾウ。
+没収されると大変困る物があるためか
+近づく者はみさかいなく蹴散らしてくる。</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -7160,7 +7300,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="60">
+    <row r="59" spans="1:17">
       <c r="A59">
         <v>58</v>
       </c>
@@ -7205,9 +7345,6 @@
       </c>
       <c r="O59">
         <v>11850</v>
-      </c>
-      <c r="Q59" s="10" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="60">
@@ -7256,11 +7393,8 @@
       <c r="O60">
         <v>11850</v>
       </c>
-      <c r="P60" s="9" t="s">
-        <v>1210</v>
-      </c>
       <c r="Q60" s="10" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="60">
@@ -7309,11 +7443,14 @@
       <c r="O61">
         <v>11850</v>
       </c>
+      <c r="P61" s="9" t="s">
+        <v>1210</v>
+      </c>
       <c r="Q61" s="10" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="60">
       <c r="A62">
         <v>61</v>
       </c>
@@ -7358,6 +7495,9 @@
       </c>
       <c r="O62">
         <v>11850</v>
+      </c>
+      <c r="Q62" s="10" t="s">
+        <v>1213</v>
       </c>
     </row>
     <row r="63" spans="1:17">
@@ -7654,7 +7794,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" ht="45">
       <c r="A69">
         <v>68</v>
       </c>
@@ -7699,6 +7839,9 @@
       </c>
       <c r="O69">
         <v>2449</v>
+      </c>
+      <c r="P69" s="10" t="s">
+        <v>1217</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -7747,6 +7890,9 @@
       <c r="O70">
         <v>5332</v>
       </c>
+      <c r="P70" s="9" t="s">
+        <v>1218</v>
+      </c>
     </row>
     <row r="71" spans="1:16">
       <c r="A71">
@@ -7794,6 +7940,9 @@
       <c r="O71">
         <v>8393</v>
       </c>
+      <c r="P71" s="9" t="s">
+        <v>1189</v>
+      </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72">
@@ -7982,6 +8131,9 @@
       <c r="O75">
         <v>790</v>
       </c>
+      <c r="P75" s="9" t="s">
+        <v>1180</v>
+      </c>
     </row>
     <row r="76" spans="1:16">
       <c r="A76">
@@ -8218,7 +8370,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="81" spans="1:15">
+    <row r="81" spans="1:17">
       <c r="A81">
         <v>80</v>
       </c>
@@ -8265,7 +8417,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="82" spans="1:15">
+    <row r="82" spans="1:17">
       <c r="A82">
         <v>81</v>
       </c>
@@ -8312,7 +8464,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="83" spans="1:15">
+    <row r="83" spans="1:17">
       <c r="A83">
         <v>82</v>
       </c>
@@ -8359,7 +8511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:15">
+    <row r="84" spans="1:17">
       <c r="A84">
         <v>83</v>
       </c>
@@ -8406,7 +8558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:15">
+    <row r="85" spans="1:17">
       <c r="A85">
         <v>84</v>
       </c>
@@ -8453,7 +8605,7 @@
         <v>7900</v>
       </c>
     </row>
-    <row r="86" spans="1:15">
+    <row r="86" spans="1:17">
       <c r="A86">
         <v>85</v>
       </c>
@@ -8500,7 +8652,7 @@
         <v>3950</v>
       </c>
     </row>
-    <row r="87" spans="1:15">
+    <row r="87" spans="1:17">
       <c r="A87">
         <v>86</v>
       </c>
@@ -8547,7 +8699,7 @@
         <v>5925</v>
       </c>
     </row>
-    <row r="88" spans="1:15">
+    <row r="88" spans="1:17">
       <c r="A88">
         <v>87</v>
       </c>
@@ -8594,7 +8746,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="89" spans="1:15">
+    <row r="89" spans="1:17" ht="60">
       <c r="A89">
         <v>88</v>
       </c>
@@ -8640,8 +8792,11 @@
       <c r="O89">
         <v>11850</v>
       </c>
-    </row>
-    <row r="90" spans="1:15">
+      <c r="Q89" s="10" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="60">
       <c r="A90">
         <v>89</v>
       </c>
@@ -8687,8 +8842,11 @@
       <c r="O90">
         <v>1777</v>
       </c>
-    </row>
-    <row r="91" spans="1:15">
+      <c r="Q90" s="10" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" ht="60">
       <c r="A91">
         <v>90</v>
       </c>
@@ -8734,8 +8892,11 @@
       <c r="O91">
         <v>987</v>
       </c>
-    </row>
-    <row r="92" spans="1:15">
+      <c r="Q91" s="10" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" ht="60">
       <c r="A92">
         <v>91</v>
       </c>
@@ -8781,8 +8942,11 @@
       <c r="O92">
         <v>1975</v>
       </c>
-    </row>
-    <row r="93" spans="1:15">
+      <c r="Q92" s="10" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" ht="60">
       <c r="A93">
         <v>92</v>
       </c>
@@ -8828,8 +8992,11 @@
       <c r="O93">
         <v>3</v>
       </c>
-    </row>
-    <row r="94" spans="1:15">
+      <c r="Q93" s="10" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" ht="60">
       <c r="A94">
         <v>93</v>
       </c>
@@ -8875,8 +9042,11 @@
       <c r="O94">
         <v>790</v>
       </c>
-    </row>
-    <row r="95" spans="1:15">
+      <c r="Q94" s="10" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" ht="60">
       <c r="A95">
         <v>94</v>
       </c>
@@ -8922,8 +9092,11 @@
       <c r="O95">
         <v>513</v>
       </c>
-    </row>
-    <row r="96" spans="1:15">
+      <c r="Q95" s="10" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" ht="60">
       <c r="A96">
         <v>95</v>
       </c>
@@ -8969,8 +9142,14 @@
       <c r="O96">
         <v>13165</v>
       </c>
-    </row>
-    <row r="97" spans="1:15">
+      <c r="P96" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="Q96" s="10" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17">
       <c r="A97">
         <v>96</v>
       </c>
@@ -8993,7 +9172,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="98" spans="1:15">
+    <row r="98" spans="1:17" ht="60">
       <c r="A98">
         <v>97</v>
       </c>
@@ -9039,8 +9218,14 @@
       <c r="O98">
         <v>1185</v>
       </c>
-    </row>
-    <row r="99" spans="1:15">
+      <c r="P98" s="9" t="s">
+        <v>1229</v>
+      </c>
+      <c r="Q98" s="10" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" ht="60">
       <c r="A99">
         <v>98</v>
       </c>
@@ -9086,8 +9271,11 @@
       <c r="O99">
         <v>987</v>
       </c>
-    </row>
-    <row r="100" spans="1:15">
+      <c r="Q99" s="10" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" ht="60">
       <c r="A100">
         <v>99</v>
       </c>
@@ -9133,8 +9321,14 @@
       <c r="O100">
         <v>3574</v>
       </c>
-    </row>
-    <row r="101" spans="1:15">
+      <c r="P100" s="9" t="s">
+        <v>1231</v>
+      </c>
+      <c r="Q100" s="10" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="45">
       <c r="A101">
         <v>100</v>
       </c>
@@ -9180,8 +9374,11 @@
       <c r="O101">
         <v>7959</v>
       </c>
-    </row>
-    <row r="102" spans="1:15">
+      <c r="P101" s="10" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17">
       <c r="A102">
         <v>101</v>
       </c>
@@ -9228,7 +9425,7 @@
         <v>35107</v>
       </c>
     </row>
-    <row r="103" spans="1:15">
+    <row r="103" spans="1:17">
       <c r="A103">
         <v>102</v>
       </c>
@@ -9275,7 +9472,7 @@
         <v>8769</v>
       </c>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:17">
       <c r="A104">
         <v>103</v>
       </c>
@@ -9322,7 +9519,7 @@
         <v>4345</v>
       </c>
     </row>
-    <row r="105" spans="1:15">
+    <row r="105" spans="1:17">
       <c r="A105">
         <v>104</v>
       </c>
@@ -9369,7 +9566,7 @@
         <v>3792</v>
       </c>
     </row>
-    <row r="106" spans="1:15">
+    <row r="106" spans="1:17">
       <c r="A106">
         <v>105</v>
       </c>
@@ -9416,7 +9613,7 @@
         <v>7584</v>
       </c>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:17">
       <c r="A107">
         <v>106</v>
       </c>
@@ -9463,7 +9660,7 @@
         <v>7702</v>
       </c>
     </row>
-    <row r="108" spans="1:15">
+    <row r="108" spans="1:17">
       <c r="A108">
         <v>107</v>
       </c>
@@ -9510,7 +9707,7 @@
         <v>6580</v>
       </c>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:17">
       <c r="A109">
         <v>108</v>
       </c>
@@ -9557,7 +9754,7 @@
         <v>4740</v>
       </c>
     </row>
-    <row r="110" spans="1:15">
+    <row r="110" spans="1:17">
       <c r="A110">
         <v>109</v>
       </c>
@@ -9604,7 +9801,7 @@
         <v>7821</v>
       </c>
     </row>
-    <row r="111" spans="1:15">
+    <row r="111" spans="1:17">
       <c r="A111">
         <v>110</v>
       </c>
@@ -9651,7 +9848,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="112" spans="1:15">
+    <row r="112" spans="1:17">
       <c r="A112">
         <v>111</v>
       </c>
@@ -9697,8 +9894,11 @@
       <c r="O112">
         <v>7505</v>
       </c>
-    </row>
-    <row r="113" spans="1:15">
+      <c r="P112" s="9" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17">
       <c r="A113">
         <v>112</v>
       </c>
@@ -9745,7 +9945,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="114" spans="1:15">
+    <row r="114" spans="1:17">
       <c r="A114">
         <v>113</v>
       </c>
@@ -9791,8 +9991,11 @@
       <c r="O114">
         <v>790</v>
       </c>
-    </row>
-    <row r="115" spans="1:15">
+      <c r="P114" s="9" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17">
       <c r="A115">
         <v>114</v>
       </c>
@@ -9839,7 +10042,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="116" spans="1:15">
+    <row r="116" spans="1:17" ht="60">
       <c r="A116">
         <v>115</v>
       </c>
@@ -9885,8 +10088,14 @@
       <c r="O116">
         <v>296</v>
       </c>
-    </row>
-    <row r="117" spans="1:15">
+      <c r="P116" s="9" t="s">
+        <v>1231</v>
+      </c>
+      <c r="Q116" s="10" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" ht="60">
       <c r="A117">
         <v>116</v>
       </c>
@@ -9932,8 +10141,11 @@
       <c r="O117">
         <v>1185</v>
       </c>
-    </row>
-    <row r="118" spans="1:15">
+      <c r="Q117" s="10" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="60">
       <c r="A118">
         <v>117</v>
       </c>
@@ -9979,8 +10191,11 @@
       <c r="O118">
         <v>8690</v>
       </c>
-    </row>
-    <row r="119" spans="1:15">
+      <c r="Q118" s="10" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" ht="60">
       <c r="A119">
         <v>118</v>
       </c>
@@ -10026,8 +10241,11 @@
       <c r="O119">
         <v>4740</v>
       </c>
-    </row>
-    <row r="120" spans="1:15">
+      <c r="Q119" s="10" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17">
       <c r="A120">
         <v>119</v>
       </c>
@@ -10074,7 +10292,7 @@
         <v>3555</v>
       </c>
     </row>
-    <row r="121" spans="1:15">
+    <row r="121" spans="1:17">
       <c r="A121">
         <v>120</v>
       </c>
@@ -10121,7 +10339,7 @@
         <v>3041</v>
       </c>
     </row>
-    <row r="122" spans="1:15">
+    <row r="122" spans="1:17">
       <c r="A122">
         <v>121</v>
       </c>
@@ -10168,7 +10386,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="123" spans="1:15">
+    <row r="123" spans="1:17">
       <c r="A123">
         <v>122</v>
       </c>
@@ -10215,7 +10433,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="124" spans="1:15">
+    <row r="124" spans="1:17">
       <c r="A124">
         <v>123</v>
       </c>
@@ -10262,7 +10480,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="125" spans="1:15">
+    <row r="125" spans="1:17">
       <c r="A125">
         <v>124</v>
       </c>
@@ -10309,7 +10527,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="126" spans="1:15">
+    <row r="126" spans="1:17">
       <c r="A126">
         <v>125</v>
       </c>
@@ -10356,7 +10574,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="127" spans="1:15">
+    <row r="127" spans="1:17">
       <c r="A127">
         <v>126</v>
       </c>
@@ -10403,7 +10621,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="128" spans="1:15">
+    <row r="128" spans="1:17">
       <c r="A128">
         <v>127</v>
       </c>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222656F4-70DE-574E-9E51-19FCAA9932DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48589D1E-0757-E043-8DE6-7087354ABFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE30C170-6DE5-C04C-B03E-207D112A0DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37353B1-A846-AB4B-9EEC-D31101279A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2729" uniqueCount="1240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="1241">
   <si>
     <t>id</t>
   </si>
@@ -4042,12 +4042,65 @@
 におぼれる日々が続く。</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>力持ちで体力にも自信があるカバ。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="Avenir"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一度に複数体をまとめて攻撃してくる危険なやつ。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="Avenir"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ちなみに、お姉キャラかどうかは不明。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4096,13 +4149,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FFE0E0E0"/>
-      <name val="Kozuka Gothic Pr6N B"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFE0E0E0"/>
       <name val="Avenir"/>
       <family val="2"/>
       <charset val="128"/>
@@ -4146,7 +4192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4160,14 +4206,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -4519,10 +4566,7 @@
       <c r="N2" t="s">
         <v>21</v>
       </c>
-      <c r="O2">
-        <v>59</v>
-      </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="8" t="s">
         <v>1236</v>
       </c>
       <c r="R2" s="4"/>
@@ -4570,10 +4614,7 @@
       <c r="N3" t="s">
         <v>21</v>
       </c>
-      <c r="O3">
-        <v>118</v>
-      </c>
-      <c r="Q3" s="10" t="s">
+      <c r="Q3" s="8" t="s">
         <v>1237</v>
       </c>
     </row>
@@ -4620,14 +4661,11 @@
       <c r="N4" t="s">
         <v>21</v>
       </c>
-      <c r="O4">
-        <v>296</v>
-      </c>
-      <c r="Q4" s="10" t="s">
+      <c r="Q4" s="8" t="s">
         <v>1238</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="24">
+    <row r="5" spans="1:18" ht="52">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4670,10 +4708,9 @@
       <c r="N5" t="s">
         <v>28</v>
       </c>
-      <c r="O5">
-        <v>1580</v>
-      </c>
-      <c r="Q5" s="7"/>
+      <c r="Q5" s="11" t="s">
+        <v>1240</v>
+      </c>
     </row>
     <row r="6" spans="1:18" ht="17">
       <c r="A6">
@@ -4718,12 +4755,9 @@
       <c r="N6" t="s">
         <v>28</v>
       </c>
-      <c r="O6">
-        <v>1580</v>
-      </c>
-      <c r="Q6" s="8"/>
-    </row>
-    <row r="7" spans="1:18" ht="24">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:18" ht="17">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4766,10 +4800,7 @@
       <c r="N7" t="s">
         <v>21</v>
       </c>
-      <c r="O7">
-        <v>1777</v>
-      </c>
-      <c r="Q7" s="7"/>
+      <c r="Q7" s="6"/>
     </row>
     <row r="8" spans="1:18" ht="60">
       <c r="A8">
@@ -4814,10 +4845,7 @@
       <c r="N8" t="s">
         <v>28</v>
       </c>
-      <c r="O8">
-        <v>2172</v>
-      </c>
-      <c r="Q8" s="10" t="s">
+      <c r="Q8" s="8" t="s">
         <v>1239</v>
       </c>
     </row>
@@ -4864,10 +4892,7 @@
       <c r="N9" t="s">
         <v>21</v>
       </c>
-      <c r="O9">
-        <v>592</v>
-      </c>
-      <c r="Q9" s="10" t="s">
+      <c r="Q9" s="8" t="s">
         <v>1150</v>
       </c>
     </row>
@@ -4914,10 +4939,7 @@
       <c r="N10" t="s">
         <v>28</v>
       </c>
-      <c r="O10">
-        <v>2567</v>
-      </c>
-      <c r="Q10" s="10" t="s">
+      <c r="Q10" s="8" t="s">
         <v>1151</v>
       </c>
     </row>
@@ -4964,10 +4986,7 @@
       <c r="N11" t="s">
         <v>28</v>
       </c>
-      <c r="O11">
-        <v>5135</v>
-      </c>
-      <c r="Q11" s="10" t="s">
+      <c r="Q11" s="8" t="s">
         <v>1152</v>
       </c>
     </row>
@@ -5014,13 +5033,10 @@
       <c r="N12" t="s">
         <v>21</v>
       </c>
-      <c r="O12">
-        <v>5530</v>
-      </c>
-      <c r="P12" s="9" t="s">
+      <c r="P12" s="7" t="s">
         <v>1154</v>
       </c>
-      <c r="Q12" s="10" t="s">
+      <c r="Q12" s="8" t="s">
         <v>1153</v>
       </c>
     </row>
@@ -5067,10 +5083,7 @@
       <c r="N13" t="s">
         <v>28</v>
       </c>
-      <c r="O13">
-        <v>9875</v>
-      </c>
-      <c r="Q13" s="10" t="s">
+      <c r="Q13" s="8" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -5117,10 +5130,7 @@
       <c r="N14" t="s">
         <v>28</v>
       </c>
-      <c r="O14">
-        <v>7900</v>
-      </c>
-      <c r="Q14" s="10" t="s">
+      <c r="Q14" s="8" t="s">
         <v>1156</v>
       </c>
     </row>
@@ -5167,10 +5177,7 @@
       <c r="N15" t="s">
         <v>21</v>
       </c>
-      <c r="O15">
-        <v>197</v>
-      </c>
-      <c r="Q15" s="10" t="s">
+      <c r="Q15" s="8" t="s">
         <v>1157</v>
       </c>
     </row>
@@ -5217,9 +5224,6 @@
       <c r="N16" t="s">
         <v>21</v>
       </c>
-      <c r="O16">
-        <v>711</v>
-      </c>
       <c r="Q16" s="6"/>
     </row>
     <row r="17" spans="1:17" ht="17">
@@ -5265,9 +5269,6 @@
       <c r="N17" t="s">
         <v>21</v>
       </c>
-      <c r="O17">
-        <v>395</v>
-      </c>
       <c r="Q17" s="6"/>
     </row>
     <row r="18" spans="1:17" ht="17">
@@ -5313,9 +5314,6 @@
       <c r="N18" t="s">
         <v>28</v>
       </c>
-      <c r="O18">
-        <v>3</v>
-      </c>
       <c r="Q18" s="6"/>
     </row>
     <row r="19" spans="1:17" ht="17">
@@ -5360,9 +5358,6 @@
       </c>
       <c r="N19" t="s">
         <v>28</v>
-      </c>
-      <c r="O19">
-        <v>5925</v>
       </c>
       <c r="Q19" s="6"/>
     </row>
@@ -5409,10 +5404,7 @@
       <c r="N20" t="s">
         <v>28</v>
       </c>
-      <c r="O20">
-        <v>15800</v>
-      </c>
-      <c r="Q20" s="10" t="s">
+      <c r="Q20" s="8" t="s">
         <v>1158</v>
       </c>
     </row>
@@ -5485,10 +5477,7 @@
       <c r="N22" t="s">
         <v>21</v>
       </c>
-      <c r="O22">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="10" t="s">
+      <c r="Q22" s="8" t="s">
         <v>1159</v>
       </c>
     </row>
@@ -5535,10 +5524,7 @@
       <c r="N23" t="s">
         <v>28</v>
       </c>
-      <c r="O23">
-        <v>7110</v>
-      </c>
-      <c r="Q23" s="10" t="s">
+      <c r="Q23" s="8" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -5585,10 +5571,7 @@
       <c r="N24" t="s">
         <v>28</v>
       </c>
-      <c r="O24">
-        <v>23700</v>
-      </c>
-      <c r="Q24" s="10" t="s">
+      <c r="Q24" s="8" t="s">
         <v>1161</v>
       </c>
     </row>
@@ -5635,10 +5618,7 @@
       <c r="N25" t="s">
         <v>28</v>
       </c>
-      <c r="O25">
-        <v>31600</v>
-      </c>
-      <c r="Q25" s="10" t="s">
+      <c r="Q25" s="8" t="s">
         <v>1162</v>
       </c>
     </row>
@@ -5685,10 +5665,7 @@
       <c r="N26" t="s">
         <v>28</v>
       </c>
-      <c r="O26">
-        <v>7900</v>
-      </c>
-      <c r="Q26" s="10" t="s">
+      <c r="Q26" s="8" t="s">
         <v>1163</v>
       </c>
     </row>
@@ -5735,13 +5712,10 @@
       <c r="N27" t="s">
         <v>28</v>
       </c>
-      <c r="O27">
-        <v>4266</v>
-      </c>
-      <c r="P27" s="9" t="s">
+      <c r="P27" s="7" t="s">
         <v>1165</v>
       </c>
-      <c r="Q27" s="10" t="s">
+      <c r="Q27" s="8" t="s">
         <v>1164</v>
       </c>
     </row>
@@ -5788,10 +5762,7 @@
       <c r="N28" t="s">
         <v>28</v>
       </c>
-      <c r="O28">
-        <v>790</v>
-      </c>
-      <c r="Q28" s="10" t="s">
+      <c r="Q28" s="8" t="s">
         <v>1166</v>
       </c>
     </row>
@@ -5838,13 +5809,10 @@
       <c r="N29" t="s">
         <v>28</v>
       </c>
-      <c r="O29">
-        <v>3555</v>
-      </c>
-      <c r="P29" s="10" t="s">
+      <c r="P29" s="8" t="s">
         <v>1168</v>
       </c>
-      <c r="Q29" s="10" t="s">
+      <c r="Q29" s="8" t="s">
         <v>1167</v>
       </c>
     </row>
@@ -5891,13 +5859,10 @@
       <c r="N30" t="s">
         <v>28</v>
       </c>
-      <c r="O30">
-        <v>3555</v>
-      </c>
-      <c r="P30" s="9" t="s">
+      <c r="P30" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="Q30" s="10" t="s">
+      <c r="Q30" s="8" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -5944,11 +5909,8 @@
       <c r="N31" t="s">
         <v>28</v>
       </c>
-      <c r="O31">
-        <v>1580</v>
-      </c>
       <c r="P31" s="6"/>
-      <c r="Q31" s="10" t="s">
+      <c r="Q31" s="8" t="s">
         <v>1177</v>
       </c>
     </row>
@@ -5995,10 +5957,7 @@
       <c r="N32" t="s">
         <v>28</v>
       </c>
-      <c r="O32">
-        <v>3160</v>
-      </c>
-      <c r="Q32" s="10" t="s">
+      <c r="Q32" s="8" t="s">
         <v>1178</v>
       </c>
     </row>
@@ -6045,10 +6004,7 @@
       <c r="N33" t="s">
         <v>28</v>
       </c>
-      <c r="O33">
-        <v>8295</v>
-      </c>
-      <c r="Q33" s="10" t="s">
+      <c r="Q33" s="8" t="s">
         <v>1179</v>
       </c>
     </row>
@@ -6095,10 +6051,7 @@
       <c r="N34" t="s">
         <v>28</v>
       </c>
-      <c r="O34">
-        <v>7900</v>
-      </c>
-      <c r="Q34" s="10" t="s">
+      <c r="Q34" s="8" t="s">
         <v>1180</v>
       </c>
     </row>
@@ -6145,10 +6098,7 @@
       <c r="N35" t="s">
         <v>28</v>
       </c>
-      <c r="O35">
-        <v>3160</v>
-      </c>
-      <c r="Q35" s="10" t="s">
+      <c r="Q35" s="8" t="s">
         <v>1181</v>
       </c>
     </row>
@@ -6195,10 +6145,7 @@
       <c r="N36" t="s">
         <v>28</v>
       </c>
-      <c r="O36">
-        <v>2765</v>
-      </c>
-      <c r="Q36" s="10" t="s">
+      <c r="Q36" s="8" t="s">
         <v>1182</v>
       </c>
     </row>
@@ -6245,10 +6192,7 @@
       <c r="N37" t="s">
         <v>21</v>
       </c>
-      <c r="O37">
-        <v>2765</v>
-      </c>
-      <c r="Q37" s="10" t="s">
+      <c r="Q37" s="8" t="s">
         <v>1183</v>
       </c>
     </row>
@@ -6295,13 +6239,10 @@
       <c r="N38" t="s">
         <v>28</v>
       </c>
-      <c r="O38">
-        <v>4348</v>
-      </c>
-      <c r="P38" s="9" t="s">
+      <c r="P38" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="Q38" s="10" t="s">
+      <c r="Q38" s="8" t="s">
         <v>1184</v>
       </c>
     </row>
@@ -6348,13 +6289,10 @@
       <c r="N39" t="s">
         <v>28</v>
       </c>
-      <c r="O39">
-        <v>6320</v>
-      </c>
-      <c r="P39" s="9" t="s">
+      <c r="P39" s="7" t="s">
         <v>1186</v>
       </c>
-      <c r="Q39" s="10" t="s">
+      <c r="Q39" s="8" t="s">
         <v>1187</v>
       </c>
     </row>
@@ -6401,10 +6339,7 @@
       <c r="N40" t="s">
         <v>28</v>
       </c>
-      <c r="O40">
-        <v>5530</v>
-      </c>
-      <c r="Q40" s="10" t="s">
+      <c r="Q40" s="8" t="s">
         <v>1188</v>
       </c>
     </row>
@@ -6451,10 +6386,7 @@
       <c r="N41" t="s">
         <v>21</v>
       </c>
-      <c r="O41">
-        <v>1580</v>
-      </c>
-      <c r="Q41" s="10" t="s">
+      <c r="Q41" s="8" t="s">
         <v>1189</v>
       </c>
     </row>
@@ -6501,10 +6433,7 @@
       <c r="N42" t="s">
         <v>28</v>
       </c>
-      <c r="O42">
-        <v>1580</v>
-      </c>
-      <c r="Q42" s="10" t="s">
+      <c r="Q42" s="8" t="s">
         <v>1190</v>
       </c>
     </row>
@@ -6551,10 +6480,7 @@
       <c r="N43" t="s">
         <v>28</v>
       </c>
-      <c r="O43">
-        <v>2370</v>
-      </c>
-      <c r="Q43" s="10" t="s">
+      <c r="Q43" s="8" t="s">
         <v>1191</v>
       </c>
     </row>
@@ -6601,10 +6527,7 @@
       <c r="N44" t="s">
         <v>28</v>
       </c>
-      <c r="O44">
-        <v>7900</v>
-      </c>
-      <c r="Q44" s="10" t="s">
+      <c r="Q44" s="8" t="s">
         <v>1192</v>
       </c>
     </row>
@@ -6651,10 +6574,7 @@
       <c r="N45" t="s">
         <v>28</v>
       </c>
-      <c r="O45">
-        <v>11850</v>
-      </c>
-      <c r="Q45" s="10" t="s">
+      <c r="Q45" s="8" t="s">
         <v>1193</v>
       </c>
     </row>
@@ -6701,10 +6621,7 @@
       <c r="N46" t="s">
         <v>28</v>
       </c>
-      <c r="O46">
-        <v>1975</v>
-      </c>
-      <c r="Q46" s="10" t="s">
+      <c r="Q46" s="8" t="s">
         <v>1194</v>
       </c>
     </row>
@@ -6751,13 +6668,10 @@
       <c r="N47" t="s">
         <v>28</v>
       </c>
-      <c r="O47">
-        <v>2370</v>
-      </c>
-      <c r="P47" s="9" t="s">
+      <c r="P47" s="7" t="s">
         <v>1196</v>
       </c>
-      <c r="Q47" s="10" t="s">
+      <c r="Q47" s="8" t="s">
         <v>1195</v>
       </c>
     </row>
@@ -6804,10 +6718,7 @@
       <c r="N48" t="s">
         <v>28</v>
       </c>
-      <c r="O48">
-        <v>3950</v>
-      </c>
-      <c r="Q48" s="10" t="s">
+      <c r="Q48" s="8" t="s">
         <v>1197</v>
       </c>
     </row>
@@ -6854,13 +6765,10 @@
       <c r="N49" t="s">
         <v>28</v>
       </c>
-      <c r="O49">
-        <v>3946</v>
-      </c>
-      <c r="P49" s="9" t="s">
+      <c r="P49" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="Q49" s="10" t="s">
+      <c r="Q49" s="8" t="s">
         <v>1198</v>
       </c>
     </row>
@@ -6907,10 +6815,7 @@
       <c r="N50" t="s">
         <v>28</v>
       </c>
-      <c r="O50">
-        <v>2370</v>
-      </c>
-      <c r="Q50" s="10" t="s">
+      <c r="Q50" s="8" t="s">
         <v>1199</v>
       </c>
     </row>
@@ -6957,10 +6862,7 @@
       <c r="N51" t="s">
         <v>21</v>
       </c>
-      <c r="O51">
-        <v>2172</v>
-      </c>
-      <c r="Q51" s="10" t="s">
+      <c r="Q51" s="8" t="s">
         <v>1200</v>
       </c>
     </row>
@@ -7007,13 +6909,10 @@
       <c r="N52" t="s">
         <v>28</v>
       </c>
-      <c r="O52">
-        <v>2172</v>
-      </c>
-      <c r="P52" s="10" t="s">
+      <c r="P52" s="8" t="s">
         <v>1201</v>
       </c>
-      <c r="Q52" s="10" t="s">
+      <c r="Q52" s="8" t="s">
         <v>1202</v>
       </c>
     </row>
@@ -7060,10 +6959,7 @@
       <c r="N53" t="s">
         <v>28</v>
       </c>
-      <c r="O53">
-        <v>4562</v>
-      </c>
-      <c r="Q53" s="10" t="s">
+      <c r="Q53" s="8" t="s">
         <v>1203</v>
       </c>
     </row>
@@ -7110,9 +7006,6 @@
       <c r="N54" t="s">
         <v>28</v>
       </c>
-      <c r="O54">
-        <v>1777</v>
-      </c>
     </row>
     <row r="55" spans="1:17" ht="17">
       <c r="A55">
@@ -7157,11 +7050,8 @@
       <c r="N55" t="s">
         <v>28</v>
       </c>
-      <c r="O55">
-        <v>23700</v>
-      </c>
-      <c r="P55" s="12"/>
-      <c r="Q55" s="10" t="s">
+      <c r="P55" s="10"/>
+      <c r="Q55" s="8" t="s">
         <v>1204</v>
       </c>
     </row>
@@ -7208,10 +7098,7 @@
       <c r="N56" t="s">
         <v>28</v>
       </c>
-      <c r="O56">
-        <v>11850</v>
-      </c>
-      <c r="Q56" s="10" t="s">
+      <c r="Q56" s="8" t="s">
         <v>1205</v>
       </c>
     </row>
@@ -7258,10 +7145,7 @@
       <c r="N57" t="s">
         <v>28</v>
       </c>
-      <c r="O57">
-        <v>1580</v>
-      </c>
-      <c r="P57" s="9" t="s">
+      <c r="P57" s="7" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -7308,10 +7192,7 @@
       <c r="N58" t="s">
         <v>28</v>
       </c>
-      <c r="O58">
-        <v>7900</v>
-      </c>
-      <c r="P58" s="9" t="s">
+      <c r="P58" s="7" t="s">
         <v>1185</v>
       </c>
     </row>
@@ -7358,9 +7239,6 @@
       <c r="N59" t="s">
         <v>28</v>
       </c>
-      <c r="O59">
-        <v>11850</v>
-      </c>
     </row>
     <row r="60" spans="1:17" ht="60">
       <c r="A60">
@@ -7405,10 +7283,7 @@
       <c r="N60" t="s">
         <v>28</v>
       </c>
-      <c r="O60">
-        <v>11850</v>
-      </c>
-      <c r="Q60" s="10" t="s">
+      <c r="Q60" s="8" t="s">
         <v>1207</v>
       </c>
     </row>
@@ -7455,13 +7330,10 @@
       <c r="N61" t="s">
         <v>28</v>
       </c>
-      <c r="O61">
-        <v>11850</v>
-      </c>
-      <c r="P61" s="9" t="s">
+      <c r="P61" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="Q61" s="10" t="s">
+      <c r="Q61" s="8" t="s">
         <v>1208</v>
       </c>
     </row>
@@ -7508,10 +7380,7 @@
       <c r="N62" t="s">
         <v>28</v>
       </c>
-      <c r="O62">
-        <v>11850</v>
-      </c>
-      <c r="Q62" s="10" t="s">
+      <c r="Q62" s="8" t="s">
         <v>1209</v>
       </c>
     </row>
@@ -7558,10 +7427,7 @@
       <c r="N63" t="s">
         <v>28</v>
       </c>
-      <c r="O63">
-        <v>7821</v>
-      </c>
-      <c r="P63" s="9" t="s">
+      <c r="P63" s="7" t="s">
         <v>1176</v>
       </c>
     </row>
@@ -7608,10 +7474,7 @@
       <c r="N64" t="s">
         <v>28</v>
       </c>
-      <c r="O64">
-        <v>9361</v>
-      </c>
-      <c r="P64" s="9" t="s">
+      <c r="P64" s="7" t="s">
         <v>1210</v>
       </c>
     </row>
@@ -7658,10 +7521,7 @@
       <c r="N65" t="s">
         <v>28</v>
       </c>
-      <c r="O65">
-        <v>7900</v>
-      </c>
-      <c r="P65" s="9" t="s">
+      <c r="P65" s="7" t="s">
         <v>1211</v>
       </c>
     </row>
@@ -7708,9 +7568,6 @@
       <c r="N66" t="s">
         <v>28</v>
       </c>
-      <c r="O66">
-        <v>3199</v>
-      </c>
     </row>
     <row r="67" spans="1:16">
       <c r="A67">
@@ -7755,9 +7612,6 @@
       <c r="N67" t="s">
         <v>21</v>
       </c>
-      <c r="O67">
-        <v>1975</v>
-      </c>
     </row>
     <row r="68" spans="1:16" ht="17">
       <c r="A68">
@@ -7802,9 +7656,6 @@
       <c r="N68" t="s">
         <v>28</v>
       </c>
-      <c r="O68">
-        <v>7896</v>
-      </c>
       <c r="P68" s="6" t="s">
         <v>1212</v>
       </c>
@@ -7852,10 +7703,7 @@
       <c r="N69" t="s">
         <v>28</v>
       </c>
-      <c r="O69">
-        <v>2449</v>
-      </c>
-      <c r="P69" s="10" t="s">
+      <c r="P69" s="8" t="s">
         <v>1213</v>
       </c>
     </row>
@@ -7902,10 +7750,7 @@
       <c r="N70" t="s">
         <v>28</v>
       </c>
-      <c r="O70">
-        <v>5332</v>
-      </c>
-      <c r="P70" s="9" t="s">
+      <c r="P70" s="7" t="s">
         <v>1214</v>
       </c>
     </row>
@@ -7952,10 +7797,7 @@
       <c r="N71" t="s">
         <v>28</v>
       </c>
-      <c r="O71">
-        <v>8393</v>
-      </c>
-      <c r="P71" s="9" t="s">
+      <c r="P71" s="7" t="s">
         <v>1185</v>
       </c>
     </row>
@@ -8002,9 +7844,6 @@
       <c r="N72" t="s">
         <v>28</v>
       </c>
-      <c r="O72">
-        <v>7900</v>
-      </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73">
@@ -8049,9 +7888,6 @@
       <c r="N73" t="s">
         <v>28</v>
       </c>
-      <c r="O73">
-        <v>6320</v>
-      </c>
     </row>
     <row r="74" spans="1:16">
       <c r="A74">
@@ -8096,9 +7932,6 @@
       <c r="N74" t="s">
         <v>28</v>
       </c>
-      <c r="O74">
-        <v>1185</v>
-      </c>
     </row>
     <row r="75" spans="1:16">
       <c r="A75">
@@ -8143,10 +7976,7 @@
       <c r="N75" t="s">
         <v>28</v>
       </c>
-      <c r="O75">
-        <v>790</v>
-      </c>
-      <c r="P75" s="9" t="s">
+      <c r="P75" s="7" t="s">
         <v>1176</v>
       </c>
     </row>
@@ -8193,9 +8023,6 @@
       <c r="N76" t="s">
         <v>28</v>
       </c>
-      <c r="O76">
-        <v>1975</v>
-      </c>
     </row>
     <row r="77" spans="1:16">
       <c r="A77">
@@ -8240,9 +8067,6 @@
       <c r="N77" t="s">
         <v>28</v>
       </c>
-      <c r="O77">
-        <v>3950</v>
-      </c>
     </row>
     <row r="78" spans="1:16">
       <c r="A78">
@@ -8287,9 +8111,6 @@
       <c r="N78" t="s">
         <v>28</v>
       </c>
-      <c r="O78">
-        <v>987</v>
-      </c>
     </row>
     <row r="79" spans="1:16">
       <c r="A79">
@@ -8334,9 +8155,6 @@
       <c r="N79" t="s">
         <v>28</v>
       </c>
-      <c r="O79">
-        <v>1777</v>
-      </c>
     </row>
     <row r="80" spans="1:16">
       <c r="A80">
@@ -8381,9 +8199,6 @@
       <c r="N80" t="s">
         <v>21</v>
       </c>
-      <c r="O80">
-        <v>118</v>
-      </c>
     </row>
     <row r="81" spans="1:17">
       <c r="A81">
@@ -8428,9 +8243,6 @@
       <c r="N81" t="s">
         <v>21</v>
       </c>
-      <c r="O81">
-        <v>237</v>
-      </c>
     </row>
     <row r="82" spans="1:17">
       <c r="A82">
@@ -8475,9 +8287,6 @@
       <c r="N82" t="s">
         <v>21</v>
       </c>
-      <c r="O82">
-        <v>1185</v>
-      </c>
     </row>
     <row r="83" spans="1:17">
       <c r="A83">
@@ -8522,9 +8331,6 @@
       <c r="N83" t="s">
         <v>21</v>
       </c>
-      <c r="O83">
-        <v>3</v>
-      </c>
     </row>
     <row r="84" spans="1:17">
       <c r="A84">
@@ -8569,9 +8375,6 @@
       <c r="N84" t="s">
         <v>21</v>
       </c>
-      <c r="O84">
-        <v>3</v>
-      </c>
     </row>
     <row r="85" spans="1:17">
       <c r="A85">
@@ -8616,9 +8419,6 @@
       <c r="N85" t="s">
         <v>28</v>
       </c>
-      <c r="O85">
-        <v>7900</v>
-      </c>
     </row>
     <row r="86" spans="1:17">
       <c r="A86">
@@ -8663,9 +8463,6 @@
       <c r="N86" t="s">
         <v>28</v>
       </c>
-      <c r="O86">
-        <v>3950</v>
-      </c>
     </row>
     <row r="87" spans="1:17">
       <c r="A87">
@@ -8710,9 +8507,6 @@
       <c r="N87" t="s">
         <v>28</v>
       </c>
-      <c r="O87">
-        <v>5925</v>
-      </c>
     </row>
     <row r="88" spans="1:17">
       <c r="A88">
@@ -8757,9 +8551,6 @@
       <c r="N88" t="s">
         <v>28</v>
       </c>
-      <c r="O88">
-        <v>1975</v>
-      </c>
     </row>
     <row r="89" spans="1:17" ht="60">
       <c r="A89">
@@ -8804,10 +8595,7 @@
       <c r="N89" t="s">
         <v>28</v>
       </c>
-      <c r="O89">
-        <v>11850</v>
-      </c>
-      <c r="Q89" s="10" t="s">
+      <c r="Q89" s="8" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -8854,10 +8642,7 @@
       <c r="N90" t="s">
         <v>28</v>
       </c>
-      <c r="O90">
-        <v>1777</v>
-      </c>
-      <c r="Q90" s="10" t="s">
+      <c r="Q90" s="8" t="s">
         <v>1216</v>
       </c>
     </row>
@@ -8904,10 +8689,7 @@
       <c r="N91" t="s">
         <v>28</v>
       </c>
-      <c r="O91">
-        <v>987</v>
-      </c>
-      <c r="Q91" s="10" t="s">
+      <c r="Q91" s="8" t="s">
         <v>1217</v>
       </c>
     </row>
@@ -8954,10 +8736,7 @@
       <c r="N92" t="s">
         <v>28</v>
       </c>
-      <c r="O92">
-        <v>1975</v>
-      </c>
-      <c r="Q92" s="10" t="s">
+      <c r="Q92" s="8" t="s">
         <v>1218</v>
       </c>
     </row>
@@ -9004,10 +8783,7 @@
       <c r="N93" t="s">
         <v>21</v>
       </c>
-      <c r="O93">
-        <v>3</v>
-      </c>
-      <c r="Q93" s="10" t="s">
+      <c r="Q93" s="8" t="s">
         <v>1219</v>
       </c>
     </row>
@@ -9054,10 +8830,7 @@
       <c r="N94" t="s">
         <v>28</v>
       </c>
-      <c r="O94">
-        <v>790</v>
-      </c>
-      <c r="Q94" s="10" t="s">
+      <c r="Q94" s="8" t="s">
         <v>1220</v>
       </c>
     </row>
@@ -9104,10 +8877,7 @@
       <c r="N95" t="s">
         <v>21</v>
       </c>
-      <c r="O95">
-        <v>513</v>
-      </c>
-      <c r="Q95" s="10" t="s">
+      <c r="Q95" s="8" t="s">
         <v>1221</v>
       </c>
     </row>
@@ -9154,13 +8924,10 @@
       <c r="N96" t="s">
         <v>28</v>
       </c>
-      <c r="O96">
-        <v>13165</v>
-      </c>
-      <c r="P96" s="9" t="s">
+      <c r="P96" s="7" t="s">
         <v>1223</v>
       </c>
-      <c r="Q96" s="10" t="s">
+      <c r="Q96" s="8" t="s">
         <v>1222</v>
       </c>
     </row>
@@ -9230,13 +8997,10 @@
       <c r="N98" t="s">
         <v>21</v>
       </c>
-      <c r="O98">
-        <v>1185</v>
-      </c>
-      <c r="P98" s="9" t="s">
+      <c r="P98" s="7" t="s">
         <v>1225</v>
       </c>
-      <c r="Q98" s="10" t="s">
+      <c r="Q98" s="8" t="s">
         <v>1224</v>
       </c>
     </row>
@@ -9283,10 +9047,7 @@
       <c r="N99" t="s">
         <v>28</v>
       </c>
-      <c r="O99">
-        <v>987</v>
-      </c>
-      <c r="Q99" s="10" t="s">
+      <c r="Q99" s="8" t="s">
         <v>1226</v>
       </c>
     </row>
@@ -9333,13 +9094,10 @@
       <c r="N100" t="s">
         <v>28</v>
       </c>
-      <c r="O100">
-        <v>3574</v>
-      </c>
-      <c r="P100" s="9" t="s">
+      <c r="P100" s="7" t="s">
         <v>1227</v>
       </c>
-      <c r="Q100" s="10" t="s">
+      <c r="Q100" s="8" t="s">
         <v>1228</v>
       </c>
     </row>
@@ -9386,10 +9144,7 @@
       <c r="N101" t="s">
         <v>28</v>
       </c>
-      <c r="O101">
-        <v>7959</v>
-      </c>
-      <c r="P101" s="10" t="s">
+      <c r="P101" s="8" t="s">
         <v>1229</v>
       </c>
     </row>
@@ -9436,9 +9191,6 @@
       <c r="N102" t="s">
         <v>28</v>
       </c>
-      <c r="O102">
-        <v>35107</v>
-      </c>
     </row>
     <row r="103" spans="1:17">
       <c r="A103">
@@ -9483,9 +9235,6 @@
       <c r="N103" t="s">
         <v>28</v>
       </c>
-      <c r="O103">
-        <v>8769</v>
-      </c>
     </row>
     <row r="104" spans="1:17">
       <c r="A104">
@@ -9530,9 +9279,6 @@
       <c r="N104" t="s">
         <v>28</v>
       </c>
-      <c r="O104">
-        <v>4345</v>
-      </c>
     </row>
     <row r="105" spans="1:17">
       <c r="A105">
@@ -9577,9 +9323,6 @@
       <c r="N105" t="s">
         <v>28</v>
       </c>
-      <c r="O105">
-        <v>3792</v>
-      </c>
     </row>
     <row r="106" spans="1:17">
       <c r="A106">
@@ -9624,9 +9367,6 @@
       <c r="N106" t="s">
         <v>28</v>
       </c>
-      <c r="O106">
-        <v>7584</v>
-      </c>
     </row>
     <row r="107" spans="1:17">
       <c r="A107">
@@ -9671,9 +9411,6 @@
       <c r="N107" t="s">
         <v>28</v>
       </c>
-      <c r="O107">
-        <v>7702</v>
-      </c>
     </row>
     <row r="108" spans="1:17">
       <c r="A108">
@@ -9718,9 +9455,6 @@
       <c r="N108" t="s">
         <v>28</v>
       </c>
-      <c r="O108">
-        <v>6580</v>
-      </c>
     </row>
     <row r="109" spans="1:17">
       <c r="A109">
@@ -9765,9 +9499,6 @@
       <c r="N109" t="s">
         <v>28</v>
       </c>
-      <c r="O109">
-        <v>4740</v>
-      </c>
     </row>
     <row r="110" spans="1:17">
       <c r="A110">
@@ -9812,9 +9543,6 @@
       <c r="N110" t="s">
         <v>28</v>
       </c>
-      <c r="O110">
-        <v>7821</v>
-      </c>
     </row>
     <row r="111" spans="1:17">
       <c r="A111">
@@ -9859,9 +9587,6 @@
       <c r="N111" t="s">
         <v>28</v>
       </c>
-      <c r="O111">
-        <v>987</v>
-      </c>
     </row>
     <row r="112" spans="1:17">
       <c r="A112">
@@ -9906,10 +9631,7 @@
       <c r="N112" t="s">
         <v>28</v>
       </c>
-      <c r="O112">
-        <v>7505</v>
-      </c>
-      <c r="P112" s="9" t="s">
+      <c r="P112" s="7" t="s">
         <v>1230</v>
       </c>
     </row>
@@ -9956,9 +9678,6 @@
       <c r="N113" t="s">
         <v>28</v>
       </c>
-      <c r="O113">
-        <v>1975</v>
-      </c>
     </row>
     <row r="114" spans="1:17">
       <c r="A114">
@@ -10003,10 +9722,7 @@
       <c r="N114" t="s">
         <v>28</v>
       </c>
-      <c r="O114">
-        <v>790</v>
-      </c>
-      <c r="P114" s="9" t="s">
+      <c r="P114" s="7" t="s">
         <v>1231</v>
       </c>
     </row>
@@ -10053,9 +9769,6 @@
       <c r="N115" t="s">
         <v>28</v>
       </c>
-      <c r="O115">
-        <v>950</v>
-      </c>
     </row>
     <row r="116" spans="1:17" ht="60">
       <c r="A116">
@@ -10100,13 +9813,10 @@
       <c r="N116" t="s">
         <v>28</v>
       </c>
-      <c r="O116">
-        <v>296</v>
-      </c>
-      <c r="P116" s="9" t="s">
+      <c r="P116" s="7" t="s">
         <v>1227</v>
       </c>
-      <c r="Q116" s="10" t="s">
+      <c r="Q116" s="8" t="s">
         <v>1232</v>
       </c>
     </row>
@@ -10153,10 +9863,7 @@
       <c r="N117" t="s">
         <v>28</v>
       </c>
-      <c r="O117">
-        <v>1185</v>
-      </c>
-      <c r="Q117" s="10" t="s">
+      <c r="Q117" s="8" t="s">
         <v>1233</v>
       </c>
     </row>
@@ -10203,10 +9910,7 @@
       <c r="N118" t="s">
         <v>28</v>
       </c>
-      <c r="O118">
-        <v>8690</v>
-      </c>
-      <c r="Q118" s="10" t="s">
+      <c r="Q118" s="8" t="s">
         <v>1234</v>
       </c>
     </row>
@@ -10253,10 +9957,7 @@
       <c r="N119" t="s">
         <v>28</v>
       </c>
-      <c r="O119">
-        <v>4740</v>
-      </c>
-      <c r="Q119" s="10" t="s">
+      <c r="Q119" s="8" t="s">
         <v>1235</v>
       </c>
     </row>
@@ -10303,9 +10004,6 @@
       <c r="N120" t="s">
         <v>28</v>
       </c>
-      <c r="O120">
-        <v>3555</v>
-      </c>
     </row>
     <row r="121" spans="1:17">
       <c r="A121">
@@ -10350,9 +10048,6 @@
       <c r="N121" t="s">
         <v>28</v>
       </c>
-      <c r="O121">
-        <v>3041</v>
-      </c>
     </row>
     <row r="122" spans="1:17">
       <c r="A122">
@@ -10397,9 +10092,6 @@
       <c r="N122" t="s">
         <v>21</v>
       </c>
-      <c r="O122">
-        <v>90</v>
-      </c>
     </row>
     <row r="123" spans="1:17">
       <c r="A123">
@@ -10444,9 +10136,6 @@
       <c r="N123" t="s">
         <v>21</v>
       </c>
-      <c r="O123">
-        <v>130</v>
-      </c>
     </row>
     <row r="124" spans="1:17">
       <c r="A124">
@@ -10491,9 +10180,6 @@
       <c r="N124" t="s">
         <v>28</v>
       </c>
-      <c r="O124">
-        <v>350</v>
-      </c>
     </row>
     <row r="125" spans="1:17">
       <c r="A125">
@@ -10538,9 +10224,6 @@
       <c r="N125" t="s">
         <v>28</v>
       </c>
-      <c r="O125">
-        <v>500</v>
-      </c>
     </row>
     <row r="126" spans="1:17">
       <c r="A126">
@@ -10585,9 +10268,6 @@
       <c r="N126" t="s">
         <v>28</v>
       </c>
-      <c r="O126">
-        <v>1555</v>
-      </c>
     </row>
     <row r="127" spans="1:17">
       <c r="A127">
@@ -10632,9 +10312,6 @@
       <c r="N127" t="s">
         <v>21</v>
       </c>
-      <c r="O127">
-        <v>250</v>
-      </c>
     </row>
     <row r="128" spans="1:17">
       <c r="A128">
@@ -10679,11 +10356,8 @@
       <c r="N128" t="s">
         <v>28</v>
       </c>
-      <c r="O128">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15">
+    </row>
+    <row r="129" spans="1:14">
       <c r="A129">
         <v>128</v>
       </c>
@@ -10726,11 +10400,8 @@
       <c r="N129" t="s">
         <v>28</v>
       </c>
-      <c r="O129">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15">
+    </row>
+    <row r="130" spans="1:14">
       <c r="A130">
         <v>129</v>
       </c>
@@ -10773,11 +10444,8 @@
       <c r="N130" t="s">
         <v>28</v>
       </c>
-      <c r="O130">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15">
+    </row>
+    <row r="131" spans="1:14">
       <c r="A131">
         <v>130</v>
       </c>
@@ -10820,11 +10488,8 @@
       <c r="N131" t="s">
         <v>28</v>
       </c>
-      <c r="O131">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15">
+    </row>
+    <row r="132" spans="1:14">
       <c r="A132">
         <v>131</v>
       </c>
@@ -10867,11 +10532,8 @@
       <c r="N132" t="s">
         <v>28</v>
       </c>
-      <c r="O132">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15">
+    </row>
+    <row r="133" spans="1:14">
       <c r="A133">
         <v>132</v>
       </c>
@@ -10914,11 +10576,8 @@
       <c r="N133" t="s">
         <v>28</v>
       </c>
-      <c r="O133">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="134" spans="1:15">
+    </row>
+    <row r="134" spans="1:14">
       <c r="A134">
         <v>133</v>
       </c>
@@ -10961,11 +10620,8 @@
       <c r="N134" t="s">
         <v>28</v>
       </c>
-      <c r="O134">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15">
+    </row>
+    <row r="135" spans="1:14">
       <c r="A135">
         <v>134</v>
       </c>
@@ -11008,11 +10664,8 @@
       <c r="N135" t="s">
         <v>28</v>
       </c>
-      <c r="O135">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15">
+    </row>
+    <row r="136" spans="1:14">
       <c r="A136">
         <v>135</v>
       </c>
@@ -11055,11 +10708,8 @@
       <c r="N136" t="s">
         <v>28</v>
       </c>
-      <c r="O136">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15">
+    </row>
+    <row r="137" spans="1:14">
       <c r="A137">
         <v>136</v>
       </c>
@@ -11102,11 +10752,8 @@
       <c r="N137" t="s">
         <v>28</v>
       </c>
-      <c r="O137">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="138" spans="1:15">
+    </row>
+    <row r="138" spans="1:14">
       <c r="A138">
         <v>137</v>
       </c>
@@ -11149,11 +10796,8 @@
       <c r="N138" t="s">
         <v>28</v>
       </c>
-      <c r="O138">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="139" spans="1:15">
+    </row>
+    <row r="139" spans="1:14">
       <c r="A139">
         <v>138</v>
       </c>
@@ -11196,11 +10840,8 @@
       <c r="N139" t="s">
         <v>21</v>
       </c>
-      <c r="O139">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15">
+    </row>
+    <row r="140" spans="1:14">
       <c r="A140">
         <v>139</v>
       </c>
@@ -11243,11 +10884,8 @@
       <c r="N140" t="s">
         <v>28</v>
       </c>
-      <c r="O140">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15">
+    </row>
+    <row r="141" spans="1:14">
       <c r="A141">
         <v>140</v>
       </c>
@@ -11270,7 +10908,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="142" spans="1:15">
+    <row r="142" spans="1:14">
       <c r="A142">
         <v>141</v>
       </c>
@@ -11313,11 +10951,8 @@
       <c r="N142" t="s">
         <v>21</v>
       </c>
-      <c r="O142">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15">
+    </row>
+    <row r="143" spans="1:14">
       <c r="A143">
         <v>142</v>
       </c>
@@ -11360,11 +10995,8 @@
       <c r="N143" t="s">
         <v>28</v>
       </c>
-      <c r="O143">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15">
+    </row>
+    <row r="144" spans="1:14">
       <c r="A144">
         <v>143</v>
       </c>
@@ -11407,11 +11039,8 @@
       <c r="N144" t="s">
         <v>28</v>
       </c>
-      <c r="O144">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15">
+    </row>
+    <row r="145" spans="1:14">
       <c r="A145">
         <v>144</v>
       </c>
@@ -11454,11 +11083,8 @@
       <c r="N145" t="s">
         <v>21</v>
       </c>
-      <c r="O145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15">
+    </row>
+    <row r="146" spans="1:14">
       <c r="A146">
         <v>145</v>
       </c>
@@ -11501,11 +11127,8 @@
       <c r="N146" t="s">
         <v>28</v>
       </c>
-      <c r="O146">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15">
+    </row>
+    <row r="147" spans="1:14">
       <c r="A147">
         <v>146</v>
       </c>
@@ -11548,11 +11171,8 @@
       <c r="N147" t="s">
         <v>28</v>
       </c>
-      <c r="O147">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15">
+    </row>
+    <row r="148" spans="1:14">
       <c r="A148">
         <v>147</v>
       </c>
@@ -11595,11 +11215,8 @@
       <c r="N148" t="s">
         <v>28</v>
       </c>
-      <c r="O148">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15">
+    </row>
+    <row r="149" spans="1:14">
       <c r="A149">
         <v>148</v>
       </c>
@@ -11642,11 +11259,8 @@
       <c r="N149" t="s">
         <v>28</v>
       </c>
-      <c r="O149">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15">
+    </row>
+    <row r="150" spans="1:14">
       <c r="A150">
         <v>149</v>
       </c>
@@ -11689,11 +11303,8 @@
       <c r="N150" t="s">
         <v>28</v>
       </c>
-      <c r="O150">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15">
+    </row>
+    <row r="151" spans="1:14">
       <c r="A151">
         <v>150</v>
       </c>
@@ -11736,11 +11347,8 @@
       <c r="N151" t="s">
         <v>28</v>
       </c>
-      <c r="O151">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15">
+    </row>
+    <row r="152" spans="1:14">
       <c r="A152">
         <v>151</v>
       </c>
@@ -11783,11 +11391,8 @@
       <c r="N152" t="s">
         <v>28</v>
       </c>
-      <c r="O152">
-        <v>4444</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15">
+    </row>
+    <row r="153" spans="1:14">
       <c r="A153">
         <v>152</v>
       </c>
@@ -11830,11 +11435,8 @@
       <c r="N153" t="s">
         <v>28</v>
       </c>
-      <c r="O153">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15">
+    </row>
+    <row r="154" spans="1:14">
       <c r="A154">
         <v>153</v>
       </c>
@@ -11877,11 +11479,8 @@
       <c r="N154" t="s">
         <v>28</v>
       </c>
-      <c r="O154">
-        <v>1555</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15">
+    </row>
+    <row r="155" spans="1:14">
       <c r="A155">
         <v>154</v>
       </c>
@@ -11924,11 +11523,8 @@
       <c r="N155" t="s">
         <v>28</v>
       </c>
-      <c r="O155">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15">
+    </row>
+    <row r="156" spans="1:14">
       <c r="A156">
         <v>155</v>
       </c>
@@ -11971,11 +11567,8 @@
       <c r="N156" t="s">
         <v>28</v>
       </c>
-      <c r="O156">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15">
+    </row>
+    <row r="157" spans="1:14">
       <c r="A157">
         <v>156</v>
       </c>
@@ -12018,11 +11611,8 @@
       <c r="N157" t="s">
         <v>28</v>
       </c>
-      <c r="O157">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15">
+    </row>
+    <row r="158" spans="1:14">
       <c r="A158">
         <v>157</v>
       </c>
@@ -12065,11 +11655,8 @@
       <c r="N158" t="s">
         <v>21</v>
       </c>
-      <c r="O158">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="159" spans="1:15">
+    </row>
+    <row r="159" spans="1:14">
       <c r="A159">
         <v>158</v>
       </c>
@@ -12112,11 +11699,8 @@
       <c r="N159" t="s">
         <v>28</v>
       </c>
-      <c r="O159">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15">
+    </row>
+    <row r="160" spans="1:14">
       <c r="A160">
         <v>159</v>
       </c>
@@ -12159,11 +11743,8 @@
       <c r="N160" t="s">
         <v>28</v>
       </c>
-      <c r="O160">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15">
+    </row>
+    <row r="161" spans="1:14">
       <c r="A161">
         <v>160</v>
       </c>
@@ -12206,11 +11787,8 @@
       <c r="N161" t="s">
         <v>28</v>
       </c>
-      <c r="O161">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="162" spans="1:15">
+    </row>
+    <row r="162" spans="1:14">
       <c r="A162">
         <v>161</v>
       </c>
@@ -12253,11 +11831,8 @@
       <c r="N162" t="s">
         <v>28</v>
       </c>
-      <c r="O162">
-        <v>2370</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15">
+    </row>
+    <row r="163" spans="1:14">
       <c r="A163">
         <v>162</v>
       </c>
@@ -12300,11 +11875,8 @@
       <c r="N163" t="s">
         <v>28</v>
       </c>
-      <c r="O163">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15">
+    </row>
+    <row r="164" spans="1:14">
       <c r="A164">
         <v>163</v>
       </c>
@@ -12347,11 +11919,8 @@
       <c r="N164" t="s">
         <v>28</v>
       </c>
-      <c r="O164">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15">
+    </row>
+    <row r="165" spans="1:14">
       <c r="A165">
         <v>164</v>
       </c>
@@ -12394,11 +11963,8 @@
       <c r="N165" t="s">
         <v>21</v>
       </c>
-      <c r="O165">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15">
+    </row>
+    <row r="166" spans="1:14">
       <c r="A166">
         <v>165</v>
       </c>
@@ -12441,11 +12007,8 @@
       <c r="N166" t="s">
         <v>28</v>
       </c>
-      <c r="O166">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15">
+    </row>
+    <row r="167" spans="1:14">
       <c r="A167">
         <v>166</v>
       </c>
@@ -12488,11 +12051,8 @@
       <c r="N167" t="s">
         <v>28</v>
       </c>
-      <c r="O167">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15">
+    </row>
+    <row r="168" spans="1:14">
       <c r="A168">
         <v>167</v>
       </c>
@@ -12535,11 +12095,8 @@
       <c r="N168" t="s">
         <v>28</v>
       </c>
-      <c r="O168">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="169" spans="1:15">
+    </row>
+    <row r="169" spans="1:14">
       <c r="A169">
         <v>168</v>
       </c>
@@ -12582,11 +12139,8 @@
       <c r="N169" t="s">
         <v>28</v>
       </c>
-      <c r="O169">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15">
+    </row>
+    <row r="170" spans="1:14">
       <c r="A170">
         <v>169</v>
       </c>
@@ -12629,11 +12183,8 @@
       <c r="N170" t="s">
         <v>28</v>
       </c>
-      <c r="O170">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15">
+    </row>
+    <row r="171" spans="1:14">
       <c r="A171">
         <v>170</v>
       </c>
@@ -12676,11 +12227,8 @@
       <c r="N171" t="s">
         <v>28</v>
       </c>
-      <c r="O171">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15">
+    </row>
+    <row r="172" spans="1:14">
       <c r="A172">
         <v>171</v>
       </c>
@@ -12723,11 +12271,8 @@
       <c r="N172" t="s">
         <v>28</v>
       </c>
-      <c r="O172">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15">
+    </row>
+    <row r="173" spans="1:14">
       <c r="A173">
         <v>172</v>
       </c>
@@ -12770,11 +12315,8 @@
       <c r="N173" t="s">
         <v>28</v>
       </c>
-      <c r="O173">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15">
+    </row>
+    <row r="174" spans="1:14">
       <c r="A174">
         <v>173</v>
       </c>
@@ -12817,11 +12359,8 @@
       <c r="N174" t="s">
         <v>21</v>
       </c>
-      <c r="O174">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="175" spans="1:15">
+    </row>
+    <row r="175" spans="1:14">
       <c r="A175">
         <v>174</v>
       </c>
@@ -12864,11 +12403,8 @@
       <c r="N175" t="s">
         <v>28</v>
       </c>
-      <c r="O175">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15">
+    </row>
+    <row r="176" spans="1:14">
       <c r="A176">
         <v>175</v>
       </c>
@@ -12911,11 +12447,8 @@
       <c r="N176" t="s">
         <v>28</v>
       </c>
-      <c r="O176">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="177" spans="1:15">
+    </row>
+    <row r="177" spans="1:14">
       <c r="A177">
         <v>176</v>
       </c>
@@ -12958,11 +12491,8 @@
       <c r="N177" t="s">
         <v>28</v>
       </c>
-      <c r="O177">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="178" spans="1:15">
+    </row>
+    <row r="178" spans="1:14">
       <c r="A178">
         <v>177</v>
       </c>
@@ -13005,11 +12535,8 @@
       <c r="N178" t="s">
         <v>28</v>
       </c>
-      <c r="O178">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="179" spans="1:15">
+    </row>
+    <row r="179" spans="1:14">
       <c r="A179">
         <v>178</v>
       </c>
@@ -13052,11 +12579,8 @@
       <c r="N179" t="s">
         <v>28</v>
       </c>
-      <c r="O179">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="180" spans="1:15">
+    </row>
+    <row r="180" spans="1:14">
       <c r="A180">
         <v>179</v>
       </c>
@@ -13099,11 +12623,8 @@
       <c r="N180" t="s">
         <v>28</v>
       </c>
-      <c r="O180">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="181" spans="1:15">
+    </row>
+    <row r="181" spans="1:14">
       <c r="A181">
         <v>180</v>
       </c>
@@ -13146,11 +12667,8 @@
       <c r="N181" t="s">
         <v>28</v>
       </c>
-      <c r="O181">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="182" spans="1:15">
+    </row>
+    <row r="182" spans="1:14">
       <c r="A182">
         <v>181</v>
       </c>
@@ -13193,11 +12711,8 @@
       <c r="N182" t="s">
         <v>21</v>
       </c>
-      <c r="O182">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="183" spans="1:15">
+    </row>
+    <row r="183" spans="1:14">
       <c r="A183">
         <v>182</v>
       </c>
@@ -13240,11 +12755,8 @@
       <c r="N183" t="s">
         <v>28</v>
       </c>
-      <c r="O183">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="184" spans="1:15">
+    </row>
+    <row r="184" spans="1:14">
       <c r="A184">
         <v>183</v>
       </c>
@@ -13287,11 +12799,8 @@
       <c r="N184" t="s">
         <v>28</v>
       </c>
-      <c r="O184">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="185" spans="1:15">
+    </row>
+    <row r="185" spans="1:14">
       <c r="A185">
         <v>184</v>
       </c>
@@ -13334,11 +12843,8 @@
       <c r="N185" t="s">
         <v>21</v>
       </c>
-      <c r="O185">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="186" spans="1:15">
+    </row>
+    <row r="186" spans="1:14">
       <c r="A186">
         <v>185</v>
       </c>
@@ -13381,11 +12887,8 @@
       <c r="N186" t="s">
         <v>28</v>
       </c>
-      <c r="O186">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="187" spans="1:15">
+    </row>
+    <row r="187" spans="1:14">
       <c r="A187">
         <v>186</v>
       </c>
@@ -13428,11 +12931,8 @@
       <c r="N187" t="s">
         <v>28</v>
       </c>
-      <c r="O187">
-        <v>4444</v>
-      </c>
-    </row>
-    <row r="188" spans="1:15">
+    </row>
+    <row r="188" spans="1:14">
       <c r="A188">
         <v>187</v>
       </c>
@@ -13475,11 +12975,8 @@
       <c r="N188" t="s">
         <v>28</v>
       </c>
-      <c r="O188">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="189" spans="1:15">
+    </row>
+    <row r="189" spans="1:14">
       <c r="A189">
         <v>188</v>
       </c>
@@ -13522,11 +13019,8 @@
       <c r="N189" t="s">
         <v>28</v>
       </c>
-      <c r="O189">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="190" spans="1:15">
+    </row>
+    <row r="190" spans="1:14">
       <c r="A190">
         <v>189</v>
       </c>
@@ -13569,11 +13063,8 @@
       <c r="N190" t="s">
         <v>28</v>
       </c>
-      <c r="O190">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="191" spans="1:15">
+    </row>
+    <row r="191" spans="1:14">
       <c r="A191">
         <v>190</v>
       </c>
@@ -13616,11 +13107,8 @@
       <c r="N191" t="s">
         <v>28</v>
       </c>
-      <c r="O191">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="192" spans="1:15">
+    </row>
+    <row r="192" spans="1:14">
       <c r="A192">
         <v>191</v>
       </c>
@@ -13663,11 +13151,8 @@
       <c r="N192" t="s">
         <v>28</v>
       </c>
-      <c r="O192">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="193" spans="1:15">
+    </row>
+    <row r="193" spans="1:14">
       <c r="A193">
         <v>192</v>
       </c>
@@ -13690,7 +13175,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="194" spans="1:15">
+    <row r="194" spans="1:14">
       <c r="A194">
         <v>193</v>
       </c>
@@ -13733,11 +13218,8 @@
       <c r="N194" t="s">
         <v>28</v>
       </c>
-      <c r="O194">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="195" spans="1:15">
+    </row>
+    <row r="195" spans="1:14">
       <c r="A195">
         <v>194</v>
       </c>
@@ -13780,11 +13262,8 @@
       <c r="N195" t="s">
         <v>28</v>
       </c>
-      <c r="O195">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="196" spans="1:15">
+    </row>
+    <row r="196" spans="1:14">
       <c r="A196">
         <v>195</v>
       </c>
@@ -13827,11 +13306,8 @@
       <c r="N196" t="s">
         <v>28</v>
       </c>
-      <c r="O196">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="197" spans="1:15">
+    </row>
+    <row r="197" spans="1:14">
       <c r="A197">
         <v>196</v>
       </c>
@@ -13874,11 +13350,8 @@
       <c r="N197" t="s">
         <v>28</v>
       </c>
-      <c r="O197">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="198" spans="1:15">
+    </row>
+    <row r="198" spans="1:14">
       <c r="A198">
         <v>197</v>
       </c>
@@ -13921,11 +13394,8 @@
       <c r="N198" t="s">
         <v>21</v>
       </c>
-      <c r="O198">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="199" spans="1:15">
+    </row>
+    <row r="199" spans="1:14">
       <c r="A199">
         <v>198</v>
       </c>
@@ -13968,11 +13438,8 @@
       <c r="N199" t="s">
         <v>28</v>
       </c>
-      <c r="O199">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="200" spans="1:15">
+    </row>
+    <row r="200" spans="1:14">
       <c r="A200">
         <v>199</v>
       </c>
@@ -14015,11 +13482,8 @@
       <c r="N200" t="s">
         <v>28</v>
       </c>
-      <c r="O200">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="201" spans="1:15">
+    </row>
+    <row r="201" spans="1:14">
       <c r="A201">
         <v>200</v>
       </c>
@@ -14062,11 +13526,8 @@
       <c r="N201" t="s">
         <v>28</v>
       </c>
-      <c r="O201">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="202" spans="1:15">
+    </row>
+    <row r="202" spans="1:14">
       <c r="A202">
         <v>201</v>
       </c>
@@ -14109,11 +13570,8 @@
       <c r="N202" t="s">
         <v>21</v>
       </c>
-      <c r="O202">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="203" spans="1:15">
+    </row>
+    <row r="203" spans="1:14">
       <c r="A203">
         <v>202</v>
       </c>
@@ -14156,11 +13614,8 @@
       <c r="N203" t="s">
         <v>28</v>
       </c>
-      <c r="O203">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="204" spans="1:15">
+    </row>
+    <row r="204" spans="1:14">
       <c r="A204">
         <v>203</v>
       </c>
@@ -14203,11 +13658,8 @@
       <c r="N204" t="s">
         <v>28</v>
       </c>
-      <c r="O204">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="205" spans="1:15">
+    </row>
+    <row r="205" spans="1:14">
       <c r="A205">
         <v>204</v>
       </c>
@@ -14250,11 +13702,8 @@
       <c r="N205" t="s">
         <v>28</v>
       </c>
-      <c r="O205">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="206" spans="1:15">
+    </row>
+    <row r="206" spans="1:14">
       <c r="A206">
         <v>205</v>
       </c>
@@ -14297,11 +13746,8 @@
       <c r="N206" t="s">
         <v>28</v>
       </c>
-      <c r="O206">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="207" spans="1:15">
+    </row>
+    <row r="207" spans="1:14">
       <c r="A207">
         <v>206</v>
       </c>
@@ -14324,7 +13770,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="208" spans="1:15">
+    <row r="208" spans="1:14">
       <c r="A208">
         <v>207</v>
       </c>
@@ -14367,11 +13813,8 @@
       <c r="N208" t="s">
         <v>28</v>
       </c>
-      <c r="O208">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="209" spans="1:15">
+    </row>
+    <row r="209" spans="1:14">
       <c r="A209">
         <v>208</v>
       </c>
@@ -14414,11 +13857,8 @@
       <c r="N209" t="s">
         <v>28</v>
       </c>
-      <c r="O209">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="210" spans="1:15">
+    </row>
+    <row r="210" spans="1:14">
       <c r="A210">
         <v>209</v>
       </c>
@@ -14461,11 +13901,8 @@
       <c r="N210" t="s">
         <v>28</v>
       </c>
-      <c r="O210">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="211" spans="1:15">
+    </row>
+    <row r="211" spans="1:14">
       <c r="A211">
         <v>210</v>
       </c>
@@ -14508,11 +13945,8 @@
       <c r="N211" t="s">
         <v>28</v>
       </c>
-      <c r="O211">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="212" spans="1:15">
+    </row>
+    <row r="212" spans="1:14">
       <c r="A212">
         <v>211</v>
       </c>
@@ -14555,11 +13989,8 @@
       <c r="N212" t="s">
         <v>21</v>
       </c>
-      <c r="O212">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="213" spans="1:15">
+    </row>
+    <row r="213" spans="1:14">
       <c r="A213">
         <v>212</v>
       </c>
@@ -14602,11 +14033,8 @@
       <c r="N213" t="s">
         <v>28</v>
       </c>
-      <c r="O213">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="214" spans="1:15">
+    </row>
+    <row r="214" spans="1:14">
       <c r="A214">
         <v>213</v>
       </c>
@@ -14649,11 +14077,8 @@
       <c r="N214" t="s">
         <v>28</v>
       </c>
-      <c r="O214">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="215" spans="1:15">
+    </row>
+    <row r="215" spans="1:14">
       <c r="A215">
         <v>214</v>
       </c>
@@ -14696,11 +14121,8 @@
       <c r="N215" t="s">
         <v>21</v>
       </c>
-      <c r="O215">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="216" spans="1:15">
+    </row>
+    <row r="216" spans="1:14">
       <c r="A216">
         <v>215</v>
       </c>
@@ -14723,7 +14145,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="217" spans="1:15">
+    <row r="217" spans="1:14">
       <c r="A217">
         <v>216</v>
       </c>
@@ -14746,7 +14168,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="218" spans="1:15">
+    <row r="218" spans="1:14">
       <c r="A218">
         <v>217</v>
       </c>
@@ -14789,11 +14211,8 @@
       <c r="N218" t="s">
         <v>28</v>
       </c>
-      <c r="O218">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="219" spans="1:15">
+    </row>
+    <row r="219" spans="1:14">
       <c r="A219">
         <v>218</v>
       </c>
@@ -14836,11 +14255,8 @@
       <c r="N219" t="s">
         <v>28</v>
       </c>
-      <c r="O219">
-        <v>4444</v>
-      </c>
-    </row>
-    <row r="220" spans="1:15">
+    </row>
+    <row r="220" spans="1:14">
       <c r="A220">
         <v>219</v>
       </c>
@@ -14883,11 +14299,8 @@
       <c r="N220" t="s">
         <v>28</v>
       </c>
-      <c r="O220">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="221" spans="1:15">
+    </row>
+    <row r="221" spans="1:14">
       <c r="A221">
         <v>220</v>
       </c>
@@ -14930,11 +14343,8 @@
       <c r="N221" t="s">
         <v>28</v>
       </c>
-      <c r="O221">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="222" spans="1:15">
+    </row>
+    <row r="222" spans="1:14">
       <c r="A222">
         <v>221</v>
       </c>
@@ -14977,11 +14387,8 @@
       <c r="N222" t="s">
         <v>28</v>
       </c>
-      <c r="O222">
-        <v>2370</v>
-      </c>
-    </row>
-    <row r="223" spans="1:15">
+    </row>
+    <row r="223" spans="1:14">
       <c r="A223">
         <v>222</v>
       </c>
@@ -15024,11 +14431,8 @@
       <c r="N223" t="s">
         <v>28</v>
       </c>
-      <c r="O223">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="224" spans="1:15">
+    </row>
+    <row r="224" spans="1:14">
       <c r="A224">
         <v>223</v>
       </c>
@@ -15071,11 +14475,8 @@
       <c r="N224" t="s">
         <v>28</v>
       </c>
-      <c r="O224">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="225" spans="1:15">
+    </row>
+    <row r="225" spans="1:14">
       <c r="A225">
         <v>224</v>
       </c>
@@ -15118,11 +14519,8 @@
       <c r="N225" t="s">
         <v>21</v>
       </c>
-      <c r="O225">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="226" spans="1:15">
+    </row>
+    <row r="226" spans="1:14">
       <c r="A226">
         <v>225</v>
       </c>
@@ -15165,11 +14563,8 @@
       <c r="N226" t="s">
         <v>28</v>
       </c>
-      <c r="O226">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="227" spans="1:15">
+    </row>
+    <row r="227" spans="1:14">
       <c r="A227">
         <v>226</v>
       </c>
@@ -15212,11 +14607,8 @@
       <c r="N227" t="s">
         <v>28</v>
       </c>
-      <c r="O227">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="228" spans="1:15">
+    </row>
+    <row r="228" spans="1:14">
       <c r="A228">
         <v>227</v>
       </c>
@@ -15259,11 +14651,8 @@
       <c r="N228" t="s">
         <v>28</v>
       </c>
-      <c r="O228">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="229" spans="1:15">
+    </row>
+    <row r="229" spans="1:14">
       <c r="A229">
         <v>228</v>
       </c>
@@ -15306,11 +14695,8 @@
       <c r="N229" t="s">
         <v>28</v>
       </c>
-      <c r="O229">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="230" spans="1:15">
+    </row>
+    <row r="230" spans="1:14">
       <c r="A230">
         <v>229</v>
       </c>
@@ -15353,11 +14739,8 @@
       <c r="N230" t="s">
         <v>28</v>
       </c>
-      <c r="O230">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="231" spans="1:15">
+    </row>
+    <row r="231" spans="1:14">
       <c r="A231">
         <v>230</v>
       </c>
@@ -15400,11 +14783,8 @@
       <c r="N231" t="s">
         <v>21</v>
       </c>
-      <c r="O231">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="232" spans="1:15">
+    </row>
+    <row r="232" spans="1:14">
       <c r="A232">
         <v>231</v>
       </c>
@@ -15427,7 +14807,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="233" spans="1:15">
+    <row r="233" spans="1:14">
       <c r="A233">
         <v>232</v>
       </c>
@@ -15470,11 +14850,8 @@
       <c r="N233" t="s">
         <v>21</v>
       </c>
-      <c r="O233">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="234" spans="1:15">
+    </row>
+    <row r="234" spans="1:14">
       <c r="A234">
         <v>233</v>
       </c>
@@ -15517,11 +14894,8 @@
       <c r="N234" t="s">
         <v>28</v>
       </c>
-      <c r="O234">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="235" spans="1:15">
+    </row>
+    <row r="235" spans="1:14">
       <c r="A235">
         <v>234</v>
       </c>
@@ -15564,11 +14938,8 @@
       <c r="N235" t="s">
         <v>28</v>
       </c>
-      <c r="O235">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="236" spans="1:15">
+    </row>
+    <row r="236" spans="1:14">
       <c r="A236">
         <v>235</v>
       </c>
@@ -15611,11 +14982,8 @@
       <c r="N236" t="s">
         <v>21</v>
       </c>
-      <c r="O236">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="237" spans="1:15">
+    </row>
+    <row r="237" spans="1:14">
       <c r="A237">
         <v>236</v>
       </c>
@@ -15658,11 +15026,8 @@
       <c r="N237" t="s">
         <v>21</v>
       </c>
-      <c r="O237">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="238" spans="1:15">
+    </row>
+    <row r="238" spans="1:14">
       <c r="A238">
         <v>237</v>
       </c>
@@ -15705,11 +15070,8 @@
       <c r="N238" t="s">
         <v>28</v>
       </c>
-      <c r="O238">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="239" spans="1:15">
+    </row>
+    <row r="239" spans="1:14">
       <c r="A239">
         <v>238</v>
       </c>
@@ -15752,11 +15114,8 @@
       <c r="N239" t="s">
         <v>28</v>
       </c>
-      <c r="O239">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="240" spans="1:15">
+    </row>
+    <row r="240" spans="1:14">
       <c r="A240">
         <v>239</v>
       </c>
@@ -15779,7 +15138,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="241" spans="1:15">
+    <row r="241" spans="1:14">
       <c r="A241">
         <v>240</v>
       </c>
@@ -15822,11 +15181,8 @@
       <c r="N241" t="s">
         <v>28</v>
       </c>
-      <c r="O241">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="242" spans="1:15">
+    </row>
+    <row r="242" spans="1:14">
       <c r="A242">
         <v>241</v>
       </c>
@@ -15869,11 +15225,8 @@
       <c r="N242" t="s">
         <v>28</v>
       </c>
-      <c r="O242">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="243" spans="1:15">
+    </row>
+    <row r="243" spans="1:14">
       <c r="A243">
         <v>242</v>
       </c>
@@ -15916,11 +15269,8 @@
       <c r="N243" t="s">
         <v>28</v>
       </c>
-      <c r="O243">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="244" spans="1:15">
+    </row>
+    <row r="244" spans="1:14">
       <c r="A244">
         <v>243</v>
       </c>
@@ -15963,11 +15313,8 @@
       <c r="N244" t="s">
         <v>28</v>
       </c>
-      <c r="O244">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="245" spans="1:15">
+    </row>
+    <row r="245" spans="1:14">
       <c r="A245">
         <v>244</v>
       </c>
@@ -16010,11 +15357,8 @@
       <c r="N245" t="s">
         <v>21</v>
       </c>
-      <c r="O245">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="246" spans="1:15">
+    </row>
+    <row r="246" spans="1:14">
       <c r="A246">
         <v>245</v>
       </c>
@@ -16057,11 +15401,8 @@
       <c r="N246" t="s">
         <v>28</v>
       </c>
-      <c r="O246">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="247" spans="1:15">
+    </row>
+    <row r="247" spans="1:14">
       <c r="A247">
         <v>246</v>
       </c>
@@ -16104,11 +15445,8 @@
       <c r="N247" t="s">
         <v>21</v>
       </c>
-      <c r="O247">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="248" spans="1:15">
+    </row>
+    <row r="248" spans="1:14">
       <c r="A248">
         <v>247</v>
       </c>
@@ -16151,11 +15489,8 @@
       <c r="N248" t="s">
         <v>21</v>
       </c>
-      <c r="O248">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="249" spans="1:15">
+    </row>
+    <row r="249" spans="1:14">
       <c r="A249">
         <v>248</v>
       </c>
@@ -16198,11 +15533,8 @@
       <c r="N249" t="s">
         <v>28</v>
       </c>
-      <c r="O249">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="250" spans="1:15">
+    </row>
+    <row r="250" spans="1:14">
       <c r="A250">
         <v>249</v>
       </c>
@@ -16245,11 +15577,8 @@
       <c r="N250" t="s">
         <v>28</v>
       </c>
-      <c r="O250">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="251" spans="1:15">
+    </row>
+    <row r="251" spans="1:14">
       <c r="A251">
         <v>250</v>
       </c>
@@ -16292,11 +15621,8 @@
       <c r="N251" t="s">
         <v>28</v>
       </c>
-      <c r="O251">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="252" spans="1:15">
+    </row>
+    <row r="252" spans="1:14">
       <c r="A252">
         <v>251</v>
       </c>
@@ -16339,11 +15665,8 @@
       <c r="N252" t="s">
         <v>28</v>
       </c>
-      <c r="O252">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="253" spans="1:15">
+    </row>
+    <row r="253" spans="1:14">
       <c r="A253">
         <v>252</v>
       </c>
@@ -16386,11 +15709,8 @@
       <c r="N253" t="s">
         <v>28</v>
       </c>
-      <c r="O253">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="254" spans="1:15">
+    </row>
+    <row r="254" spans="1:14">
       <c r="A254">
         <v>253</v>
       </c>
@@ -16433,11 +15753,8 @@
       <c r="N254" t="s">
         <v>28</v>
       </c>
-      <c r="O254">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="255" spans="1:15">
+    </row>
+    <row r="255" spans="1:14">
       <c r="A255">
         <v>254</v>
       </c>
@@ -16480,11 +15797,8 @@
       <c r="N255" t="s">
         <v>28</v>
       </c>
-      <c r="O255">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="256" spans="1:15">
+    </row>
+    <row r="256" spans="1:14">
       <c r="A256">
         <v>255</v>
       </c>
@@ -16507,7 +15821,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="257" spans="1:15">
+    <row r="257" spans="1:14">
       <c r="A257">
         <v>256</v>
       </c>
@@ -16550,11 +15864,8 @@
       <c r="N257" t="s">
         <v>28</v>
       </c>
-      <c r="O257">
-        <v>3333</v>
-      </c>
-    </row>
-    <row r="258" spans="1:15">
+    </row>
+    <row r="258" spans="1:14">
       <c r="A258">
         <v>257</v>
       </c>
@@ -16577,7 +15888,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="259" spans="1:15">
+    <row r="259" spans="1:14">
       <c r="A259">
         <v>258</v>
       </c>
@@ -16620,11 +15931,8 @@
       <c r="N259" t="s">
         <v>28</v>
       </c>
-      <c r="O259">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="260" spans="1:15">
+    </row>
+    <row r="260" spans="1:14">
       <c r="A260">
         <v>259</v>
       </c>
@@ -16667,11 +15975,8 @@
       <c r="N260" t="s">
         <v>28</v>
       </c>
-      <c r="O260">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="261" spans="1:15">
+    </row>
+    <row r="261" spans="1:14">
       <c r="A261">
         <v>260</v>
       </c>
@@ -16714,11 +16019,8 @@
       <c r="N261" t="s">
         <v>28</v>
       </c>
-      <c r="O261">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="262" spans="1:15">
+    </row>
+    <row r="262" spans="1:14">
       <c r="A262">
         <v>261</v>
       </c>
@@ -16761,11 +16063,8 @@
       <c r="N262" t="s">
         <v>21</v>
       </c>
-      <c r="O262">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="263" spans="1:15">
+    </row>
+    <row r="263" spans="1:14">
       <c r="A263">
         <v>262</v>
       </c>
@@ -16808,11 +16107,8 @@
       <c r="N263" t="s">
         <v>28</v>
       </c>
-      <c r="O263">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="264" spans="1:15">
+    </row>
+    <row r="264" spans="1:14">
       <c r="A264">
         <v>263</v>
       </c>
@@ -16855,11 +16151,8 @@
       <c r="N264" t="s">
         <v>28</v>
       </c>
-      <c r="O264">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="265" spans="1:15">
+    </row>
+    <row r="265" spans="1:14">
       <c r="A265">
         <v>264</v>
       </c>
@@ -16902,11 +16195,8 @@
       <c r="N265" t="s">
         <v>28</v>
       </c>
-      <c r="O265">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="266" spans="1:15">
+    </row>
+    <row r="266" spans="1:14">
       <c r="A266">
         <v>265</v>
       </c>
@@ -16949,11 +16239,8 @@
       <c r="N266" t="s">
         <v>28</v>
       </c>
-      <c r="O266">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="267" spans="1:15">
+    </row>
+    <row r="267" spans="1:14">
       <c r="A267">
         <v>266</v>
       </c>
@@ -16996,11 +16283,8 @@
       <c r="N267" t="s">
         <v>21</v>
       </c>
-      <c r="O267">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="268" spans="1:15">
+    </row>
+    <row r="268" spans="1:14">
       <c r="A268">
         <v>267</v>
       </c>
@@ -17043,11 +16327,8 @@
       <c r="N268" t="s">
         <v>28</v>
       </c>
-      <c r="O268">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="269" spans="1:15">
+    </row>
+    <row r="269" spans="1:14">
       <c r="A269">
         <v>268</v>
       </c>
@@ -17090,11 +16371,8 @@
       <c r="N269" t="s">
         <v>28</v>
       </c>
-      <c r="O269">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="270" spans="1:15">
+    </row>
+    <row r="270" spans="1:14">
       <c r="A270">
         <v>269</v>
       </c>
@@ -17137,11 +16415,8 @@
       <c r="N270" t="s">
         <v>28</v>
       </c>
-      <c r="O270">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="271" spans="1:15">
+    </row>
+    <row r="271" spans="1:14">
       <c r="A271">
         <v>270</v>
       </c>
@@ -17184,11 +16459,8 @@
       <c r="N271" t="s">
         <v>28</v>
       </c>
-      <c r="O271">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="272" spans="1:15">
+    </row>
+    <row r="272" spans="1:14">
       <c r="A272">
         <v>271</v>
       </c>
@@ -17231,11 +16503,8 @@
       <c r="N272" t="s">
         <v>21</v>
       </c>
-      <c r="O272">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="273" spans="1:15">
+    </row>
+    <row r="273" spans="1:14">
       <c r="A273">
         <v>272</v>
       </c>
@@ -17278,11 +16547,8 @@
       <c r="N273" t="s">
         <v>28</v>
       </c>
-      <c r="O273">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="274" spans="1:15">
+    </row>
+    <row r="274" spans="1:14">
       <c r="A274">
         <v>273</v>
       </c>
@@ -17325,11 +16591,8 @@
       <c r="N274" t="s">
         <v>28</v>
       </c>
-      <c r="O274">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="275" spans="1:15">
+    </row>
+    <row r="275" spans="1:14">
       <c r="A275">
         <v>274</v>
       </c>
@@ -17372,11 +16635,8 @@
       <c r="N275" t="s">
         <v>28</v>
       </c>
-      <c r="O275">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="276" spans="1:15">
+    </row>
+    <row r="276" spans="1:14">
       <c r="A276">
         <v>275</v>
       </c>
@@ -17419,11 +16679,8 @@
       <c r="N276" t="s">
         <v>28</v>
       </c>
-      <c r="O276">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="277" spans="1:15">
+    </row>
+    <row r="277" spans="1:14">
       <c r="A277">
         <v>276</v>
       </c>
@@ -17466,11 +16723,8 @@
       <c r="N277" t="s">
         <v>28</v>
       </c>
-      <c r="O277">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="278" spans="1:15">
+    </row>
+    <row r="278" spans="1:14">
       <c r="A278">
         <v>277</v>
       </c>
@@ -17513,11 +16767,8 @@
       <c r="N278" t="s">
         <v>28</v>
       </c>
-      <c r="O278">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="279" spans="1:15">
+    </row>
+    <row r="279" spans="1:14">
       <c r="A279">
         <v>278</v>
       </c>
@@ -17560,11 +16811,8 @@
       <c r="N279" t="s">
         <v>28</v>
       </c>
-      <c r="O279">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="280" spans="1:15">
+    </row>
+    <row r="280" spans="1:14">
       <c r="A280">
         <v>279</v>
       </c>
@@ -17607,11 +16855,8 @@
       <c r="N280" t="s">
         <v>28</v>
       </c>
-      <c r="O280">
-        <v>4590</v>
-      </c>
-    </row>
-    <row r="281" spans="1:15">
+    </row>
+    <row r="281" spans="1:14">
       <c r="A281">
         <v>280</v>
       </c>
@@ -17654,11 +16899,8 @@
       <c r="N281" t="s">
         <v>28</v>
       </c>
-      <c r="O281">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="282" spans="1:15">
+    </row>
+    <row r="282" spans="1:14">
       <c r="A282">
         <v>281</v>
       </c>
@@ -17701,11 +16943,8 @@
       <c r="N282" t="s">
         <v>28</v>
       </c>
-      <c r="O282">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="283" spans="1:15">
+    </row>
+    <row r="283" spans="1:14">
       <c r="A283">
         <v>282</v>
       </c>
@@ -17748,11 +16987,8 @@
       <c r="N283" t="s">
         <v>28</v>
       </c>
-      <c r="O283">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="284" spans="1:15">
+    </row>
+    <row r="284" spans="1:14">
       <c r="A284">
         <v>283</v>
       </c>
@@ -17795,11 +17031,8 @@
       <c r="N284" t="s">
         <v>28</v>
       </c>
-      <c r="O284">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="285" spans="1:15">
+    </row>
+    <row r="285" spans="1:14">
       <c r="A285">
         <v>284</v>
       </c>
@@ -17842,11 +17075,8 @@
       <c r="N285" t="s">
         <v>28</v>
       </c>
-      <c r="O285">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="286" spans="1:15">
+    </row>
+    <row r="286" spans="1:14">
       <c r="A286">
         <v>285</v>
       </c>
@@ -17889,11 +17119,8 @@
       <c r="N286" t="s">
         <v>28</v>
       </c>
-      <c r="O286">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="287" spans="1:15">
+    </row>
+    <row r="287" spans="1:14">
       <c r="A287">
         <v>286</v>
       </c>
@@ -17936,11 +17163,8 @@
       <c r="N287" t="s">
         <v>28</v>
       </c>
-      <c r="O287">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="288" spans="1:15">
+    </row>
+    <row r="288" spans="1:14">
       <c r="A288">
         <v>287</v>
       </c>
@@ -17983,11 +17207,8 @@
       <c r="N288" t="s">
         <v>28</v>
       </c>
-      <c r="O288">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="289" spans="1:15">
+    </row>
+    <row r="289" spans="1:14">
       <c r="A289">
         <v>288</v>
       </c>
@@ -18030,11 +17251,8 @@
       <c r="N289" t="s">
         <v>28</v>
       </c>
-      <c r="O289">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="290" spans="1:15">
+    </row>
+    <row r="290" spans="1:14">
       <c r="A290">
         <v>289</v>
       </c>
@@ -18077,11 +17295,8 @@
       <c r="N290" t="s">
         <v>28</v>
       </c>
-      <c r="O290">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="291" spans="1:15">
+    </row>
+    <row r="291" spans="1:14">
       <c r="A291">
         <v>290</v>
       </c>
@@ -18124,11 +17339,8 @@
       <c r="N291" t="s">
         <v>28</v>
       </c>
-      <c r="O291">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="292" spans="1:15">
+    </row>
+    <row r="292" spans="1:14">
       <c r="A292">
         <v>291</v>
       </c>
@@ -18171,11 +17383,8 @@
       <c r="N292" t="s">
         <v>28</v>
       </c>
-      <c r="O292">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="293" spans="1:15">
+    </row>
+    <row r="293" spans="1:14">
       <c r="A293">
         <v>292</v>
       </c>
@@ -18198,7 +17407,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="294" spans="1:15">
+    <row r="294" spans="1:14">
       <c r="A294">
         <v>293</v>
       </c>
@@ -18221,7 +17430,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="295" spans="1:15">
+    <row r="295" spans="1:14">
       <c r="A295">
         <v>294</v>
       </c>
@@ -18264,11 +17473,8 @@
       <c r="N295" t="s">
         <v>21</v>
       </c>
-      <c r="O295">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="296" spans="1:15">
+    </row>
+    <row r="296" spans="1:14">
       <c r="A296">
         <v>295</v>
       </c>
@@ -18311,11 +17517,8 @@
       <c r="N296" t="s">
         <v>28</v>
       </c>
-      <c r="O296">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="297" spans="1:15">
+    </row>
+    <row r="297" spans="1:14">
       <c r="A297">
         <v>296</v>
       </c>
@@ -18358,11 +17561,8 @@
       <c r="N297" t="s">
         <v>28</v>
       </c>
-      <c r="O297">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="298" spans="1:15">
+    </row>
+    <row r="298" spans="1:14">
       <c r="A298">
         <v>297</v>
       </c>
@@ -18405,11 +17605,8 @@
       <c r="N298" t="s">
         <v>28</v>
       </c>
-      <c r="O298">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="299" spans="1:15">
+    </row>
+    <row r="299" spans="1:14">
       <c r="A299">
         <v>298</v>
       </c>
@@ -18452,11 +17649,8 @@
       <c r="N299" t="s">
         <v>28</v>
       </c>
-      <c r="O299">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="300" spans="1:15">
+    </row>
+    <row r="300" spans="1:14">
       <c r="A300">
         <v>299</v>
       </c>
@@ -18499,11 +17693,8 @@
       <c r="N300" t="s">
         <v>28</v>
       </c>
-      <c r="O300">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="301" spans="1:15">
+    </row>
+    <row r="301" spans="1:14">
       <c r="A301">
         <v>300</v>
       </c>
@@ -18546,11 +17737,8 @@
       <c r="N301" t="s">
         <v>28</v>
       </c>
-      <c r="O301">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="302" spans="1:15">
+    </row>
+    <row r="302" spans="1:14">
       <c r="A302">
         <v>301</v>
       </c>
@@ -18593,11 +17781,8 @@
       <c r="N302" t="s">
         <v>28</v>
       </c>
-      <c r="O302">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="303" spans="1:15">
+    </row>
+    <row r="303" spans="1:14">
       <c r="A303">
         <v>302</v>
       </c>
@@ -18640,11 +17825,8 @@
       <c r="N303" t="s">
         <v>28</v>
       </c>
-      <c r="O303">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="304" spans="1:15">
+    </row>
+    <row r="304" spans="1:14">
       <c r="A304">
         <v>303</v>
       </c>
@@ -18687,11 +17869,8 @@
       <c r="N304" t="s">
         <v>28</v>
       </c>
-      <c r="O304">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="305" spans="1:15">
+    </row>
+    <row r="305" spans="1:14">
       <c r="A305">
         <v>304</v>
       </c>
@@ -18734,11 +17913,8 @@
       <c r="N305" t="s">
         <v>21</v>
       </c>
-      <c r="O305">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="306" spans="1:15">
+    </row>
+    <row r="306" spans="1:14">
       <c r="A306">
         <v>305</v>
       </c>
@@ -18781,11 +17957,8 @@
       <c r="N306" t="s">
         <v>28</v>
       </c>
-      <c r="O306">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="307" spans="1:15">
+    </row>
+    <row r="307" spans="1:14">
       <c r="A307">
         <v>306</v>
       </c>
@@ -18828,11 +18001,8 @@
       <c r="N307" t="s">
         <v>21</v>
       </c>
-      <c r="O307">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="308" spans="1:15">
+    </row>
+    <row r="308" spans="1:14">
       <c r="A308">
         <v>307</v>
       </c>
@@ -18875,11 +18045,8 @@
       <c r="N308" t="s">
         <v>28</v>
       </c>
-      <c r="O308">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="309" spans="1:15">
+    </row>
+    <row r="309" spans="1:14">
       <c r="A309">
         <v>308</v>
       </c>
@@ -18922,11 +18089,8 @@
       <c r="N309" t="s">
         <v>21</v>
       </c>
-      <c r="O309">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="310" spans="1:15">
+    </row>
+    <row r="310" spans="1:14">
       <c r="A310">
         <v>309</v>
       </c>
@@ -18969,11 +18133,8 @@
       <c r="N310" t="s">
         <v>28</v>
       </c>
-      <c r="O310">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="311" spans="1:15">
+    </row>
+    <row r="311" spans="1:14">
       <c r="A311">
         <v>310</v>
       </c>
@@ -19016,11 +18177,8 @@
       <c r="N311" t="s">
         <v>21</v>
       </c>
-      <c r="O311">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="312" spans="1:15">
+    </row>
+    <row r="312" spans="1:14">
       <c r="A312">
         <v>311</v>
       </c>
@@ -19063,11 +18221,8 @@
       <c r="N312" t="s">
         <v>28</v>
       </c>
-      <c r="O312">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="313" spans="1:15">
+    </row>
+    <row r="313" spans="1:14">
       <c r="A313">
         <v>312</v>
       </c>
@@ -19090,7 +18245,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="314" spans="1:15">
+    <row r="314" spans="1:14">
       <c r="A314">
         <v>313</v>
       </c>
@@ -19113,7 +18268,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="315" spans="1:15">
+    <row r="315" spans="1:14">
       <c r="A315">
         <v>314</v>
       </c>
@@ -19156,11 +18311,8 @@
       <c r="N315" t="s">
         <v>28</v>
       </c>
-      <c r="O315">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="316" spans="1:15">
+    </row>
+    <row r="316" spans="1:14">
       <c r="A316">
         <v>315</v>
       </c>
@@ -19203,11 +18355,8 @@
       <c r="N316" t="s">
         <v>28</v>
       </c>
-      <c r="O316">
-        <v>4444</v>
-      </c>
-    </row>
-    <row r="317" spans="1:15">
+    </row>
+    <row r="317" spans="1:14">
       <c r="A317">
         <v>316</v>
       </c>
@@ -19250,11 +18399,8 @@
       <c r="N317" t="s">
         <v>28</v>
       </c>
-      <c r="O317">
-        <v>6666</v>
-      </c>
-    </row>
-    <row r="318" spans="1:15">
+    </row>
+    <row r="318" spans="1:14">
       <c r="A318">
         <v>317</v>
       </c>
@@ -19297,11 +18443,8 @@
       <c r="N318" t="s">
         <v>21</v>
       </c>
-      <c r="O318">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="319" spans="1:15">
+    </row>
+    <row r="319" spans="1:14">
       <c r="A319">
         <v>318</v>
       </c>
@@ -19344,11 +18487,8 @@
       <c r="N319" t="s">
         <v>28</v>
       </c>
-      <c r="O319">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="320" spans="1:15">
+    </row>
+    <row r="320" spans="1:14">
       <c r="A320">
         <v>319</v>
       </c>
@@ -19391,11 +18531,8 @@
       <c r="N320" t="s">
         <v>28</v>
       </c>
-      <c r="O320">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="321" spans="1:15">
+    </row>
+    <row r="321" spans="1:14">
       <c r="A321">
         <v>320</v>
       </c>
@@ -19438,11 +18575,8 @@
       <c r="N321" t="s">
         <v>21</v>
       </c>
-      <c r="O321">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="322" spans="1:15">
+    </row>
+    <row r="322" spans="1:14">
       <c r="A322">
         <v>321</v>
       </c>
@@ -19485,11 +18619,8 @@
       <c r="N322" t="s">
         <v>28</v>
       </c>
-      <c r="O322">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="323" spans="1:15">
+    </row>
+    <row r="323" spans="1:14">
       <c r="A323">
         <v>322</v>
       </c>
@@ -19532,11 +18663,8 @@
       <c r="N323" t="s">
         <v>28</v>
       </c>
-      <c r="O323">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="324" spans="1:15">
+    </row>
+    <row r="324" spans="1:14">
       <c r="A324">
         <v>323</v>
       </c>
@@ -19579,11 +18707,8 @@
       <c r="N324" t="s">
         <v>28</v>
       </c>
-      <c r="O324">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="325" spans="1:15">
+    </row>
+    <row r="325" spans="1:14">
       <c r="A325">
         <v>324</v>
       </c>
@@ -19626,11 +18751,8 @@
       <c r="N325" t="s">
         <v>28</v>
       </c>
-      <c r="O325">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="326" spans="1:15">
+    </row>
+    <row r="326" spans="1:14">
       <c r="A326">
         <v>325</v>
       </c>
@@ -19673,11 +18795,8 @@
       <c r="N326" t="s">
         <v>28</v>
       </c>
-      <c r="O326">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="327" spans="1:15">
+    </row>
+    <row r="327" spans="1:14">
       <c r="A327">
         <v>326</v>
       </c>
@@ -19720,11 +18839,8 @@
       <c r="N327" t="s">
         <v>28</v>
       </c>
-      <c r="O327">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="328" spans="1:15">
+    </row>
+    <row r="328" spans="1:14">
       <c r="A328">
         <v>327</v>
       </c>
@@ -19767,11 +18883,8 @@
       <c r="N328" t="s">
         <v>28</v>
       </c>
-      <c r="O328">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="329" spans="1:15">
+    </row>
+    <row r="329" spans="1:14">
       <c r="A329">
         <v>328</v>
       </c>
@@ -19814,11 +18927,8 @@
       <c r="N329" t="s">
         <v>28</v>
       </c>
-      <c r="O329">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="330" spans="1:15">
+    </row>
+    <row r="330" spans="1:14">
       <c r="A330">
         <v>329</v>
       </c>
@@ -19861,11 +18971,8 @@
       <c r="N330" t="s">
         <v>28</v>
       </c>
-      <c r="O330">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="331" spans="1:15">
+    </row>
+    <row r="331" spans="1:14">
       <c r="A331">
         <v>330</v>
       </c>
@@ -19908,11 +19015,8 @@
       <c r="N331" t="s">
         <v>28</v>
       </c>
-      <c r="O331">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="332" spans="1:15">
+    </row>
+    <row r="332" spans="1:14">
       <c r="A332">
         <v>331</v>
       </c>
@@ -19955,11 +19059,8 @@
       <c r="N332" t="s">
         <v>28</v>
       </c>
-      <c r="O332">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="333" spans="1:15">
+    </row>
+    <row r="333" spans="1:14">
       <c r="A333">
         <v>332</v>
       </c>
@@ -20002,11 +19103,8 @@
       <c r="N333" t="s">
         <v>28</v>
       </c>
-      <c r="O333">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="334" spans="1:15">
+    </row>
+    <row r="334" spans="1:14">
       <c r="A334">
         <v>333</v>
       </c>
@@ -20029,7 +19127,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="335" spans="1:15">
+    <row r="335" spans="1:14">
       <c r="A335">
         <v>334</v>
       </c>
@@ -20052,7 +19150,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="336" spans="1:15">
+    <row r="336" spans="1:14">
       <c r="A336">
         <v>335</v>
       </c>
@@ -20075,7 +19173,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="337" spans="1:15">
+    <row r="337" spans="1:14">
       <c r="A337">
         <v>336</v>
       </c>
@@ -20118,11 +19216,8 @@
       <c r="N337" t="s">
         <v>28</v>
       </c>
-      <c r="O337">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="338" spans="1:15">
+    </row>
+    <row r="338" spans="1:14">
       <c r="A338">
         <v>337</v>
       </c>
@@ -20165,11 +19260,8 @@
       <c r="N338" t="s">
         <v>28</v>
       </c>
-      <c r="O338">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="339" spans="1:15">
+    </row>
+    <row r="339" spans="1:14">
       <c r="A339">
         <v>338</v>
       </c>
@@ -20212,11 +19304,8 @@
       <c r="N339" t="s">
         <v>28</v>
       </c>
-      <c r="O339">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="340" spans="1:15">
+    </row>
+    <row r="340" spans="1:14">
       <c r="A340">
         <v>339</v>
       </c>
@@ -20239,7 +19328,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="341" spans="1:15">
+    <row r="341" spans="1:14">
       <c r="A341">
         <v>340</v>
       </c>
@@ -20262,7 +19351,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="342" spans="1:15">
+    <row r="342" spans="1:14">
       <c r="A342">
         <v>341</v>
       </c>
@@ -20305,11 +19394,8 @@
       <c r="N342" t="s">
         <v>28</v>
       </c>
-      <c r="O342">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="343" spans="1:15">
+    </row>
+    <row r="343" spans="1:14">
       <c r="A343">
         <v>342</v>
       </c>
@@ -20352,11 +19438,8 @@
       <c r="N343" t="s">
         <v>21</v>
       </c>
-      <c r="O343">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="344" spans="1:15">
+    </row>
+    <row r="344" spans="1:14">
       <c r="A344">
         <v>343</v>
       </c>
@@ -20399,11 +19482,8 @@
       <c r="N344" t="s">
         <v>28</v>
       </c>
-      <c r="O344">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="345" spans="1:15">
+    </row>
+    <row r="345" spans="1:14">
       <c r="A345">
         <v>344</v>
       </c>
@@ -20446,11 +19526,8 @@
       <c r="N345" t="s">
         <v>28</v>
       </c>
-      <c r="O345">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="346" spans="1:15">
+    </row>
+    <row r="346" spans="1:14">
       <c r="A346">
         <v>345</v>
       </c>
@@ -20493,11 +19570,8 @@
       <c r="N346" t="s">
         <v>28</v>
       </c>
-      <c r="O346">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="347" spans="1:15">
+    </row>
+    <row r="347" spans="1:14">
       <c r="A347">
         <v>346</v>
       </c>
@@ -20540,11 +19614,8 @@
       <c r="N347" t="s">
         <v>28</v>
       </c>
-      <c r="O347">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="348" spans="1:15">
+    </row>
+    <row r="348" spans="1:14">
       <c r="A348">
         <v>347</v>
       </c>
@@ -20584,11 +19655,8 @@
       <c r="N348" t="s">
         <v>28</v>
       </c>
-      <c r="O348">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="349" spans="1:15">
+    </row>
+    <row r="349" spans="1:14">
       <c r="A349">
         <v>348</v>
       </c>
@@ -20631,11 +19699,8 @@
       <c r="N349" t="s">
         <v>28</v>
       </c>
-      <c r="O349">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="350" spans="1:15">
+    </row>
+    <row r="350" spans="1:14">
       <c r="A350">
         <v>349</v>
       </c>
@@ -20675,11 +19740,8 @@
       <c r="N350" t="s">
         <v>28</v>
       </c>
-      <c r="O350">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="351" spans="1:15">
+    </row>
+    <row r="351" spans="1:14">
       <c r="A351">
         <v>350</v>
       </c>
@@ -20722,11 +19784,8 @@
       <c r="N351" t="s">
         <v>21</v>
       </c>
-      <c r="O351">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="352" spans="1:15">
+    </row>
+    <row r="352" spans="1:14">
       <c r="A352">
         <v>351</v>
       </c>
@@ -20769,11 +19828,8 @@
       <c r="N352" t="s">
         <v>28</v>
       </c>
-      <c r="O352">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="353" spans="1:15">
+    </row>
+    <row r="353" spans="1:14">
       <c r="A353">
         <v>352</v>
       </c>
@@ -20816,11 +19872,8 @@
       <c r="N353" t="s">
         <v>21</v>
       </c>
-      <c r="O353">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="354" spans="1:15">
+    </row>
+    <row r="354" spans="1:14">
       <c r="A354">
         <v>353</v>
       </c>
@@ -20863,11 +19916,8 @@
       <c r="N354" t="s">
         <v>28</v>
       </c>
-      <c r="O354">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="355" spans="1:15">
+    </row>
+    <row r="355" spans="1:14">
       <c r="A355">
         <v>354</v>
       </c>
@@ -20910,11 +19960,8 @@
       <c r="N355" t="s">
         <v>28</v>
       </c>
-      <c r="O355">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="356" spans="1:15">
+    </row>
+    <row r="356" spans="1:14">
       <c r="A356">
         <v>355</v>
       </c>
@@ -20957,11 +20004,8 @@
       <c r="N356" t="s">
         <v>28</v>
       </c>
-      <c r="O356">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="357" spans="1:15">
+    </row>
+    <row r="357" spans="1:14">
       <c r="A357">
         <v>356</v>
       </c>
@@ -21004,11 +20048,8 @@
       <c r="N357" t="s">
         <v>28</v>
       </c>
-      <c r="O357">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="358" spans="1:15">
+    </row>
+    <row r="358" spans="1:14">
       <c r="A358">
         <v>357</v>
       </c>
@@ -21051,11 +20092,8 @@
       <c r="N358" t="s">
         <v>28</v>
       </c>
-      <c r="O358">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="359" spans="1:15">
+    </row>
+    <row r="359" spans="1:14">
       <c r="A359">
         <v>358</v>
       </c>
@@ -21098,11 +20136,8 @@
       <c r="N359" t="s">
         <v>28</v>
       </c>
-      <c r="O359">
-        <v>6666</v>
-      </c>
-    </row>
-    <row r="360" spans="1:15">
+    </row>
+    <row r="360" spans="1:14">
       <c r="A360">
         <v>359</v>
       </c>
@@ -21145,11 +20180,8 @@
       <c r="N360" t="s">
         <v>28</v>
       </c>
-      <c r="O360">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="361" spans="1:15">
+    </row>
+    <row r="361" spans="1:14">
       <c r="A361">
         <v>360</v>
       </c>
@@ -21192,11 +20224,8 @@
       <c r="N361" t="s">
         <v>28</v>
       </c>
-      <c r="O361">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="362" spans="1:15">
+    </row>
+    <row r="362" spans="1:14">
       <c r="A362">
         <v>361</v>
       </c>
@@ -21239,11 +20268,8 @@
       <c r="N362" t="s">
         <v>28</v>
       </c>
-      <c r="O362">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="363" spans="1:15">
+    </row>
+    <row r="363" spans="1:14">
       <c r="A363">
         <v>362</v>
       </c>
@@ -21266,7 +20292,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="364" spans="1:15">
+    <row r="364" spans="1:14">
       <c r="A364">
         <v>363</v>
       </c>
@@ -21309,11 +20335,8 @@
       <c r="N364" t="s">
         <v>28</v>
       </c>
-      <c r="O364">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="365" spans="1:15">
+    </row>
+    <row r="365" spans="1:14">
       <c r="A365">
         <v>364</v>
       </c>
@@ -21356,11 +20379,8 @@
       <c r="N365" t="s">
         <v>28</v>
       </c>
-      <c r="O365">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="366" spans="1:15">
+    </row>
+    <row r="366" spans="1:14">
       <c r="A366">
         <v>365</v>
       </c>
@@ -21403,11 +20423,8 @@
       <c r="N366" t="s">
         <v>28</v>
       </c>
-      <c r="O366">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="367" spans="1:15">
+    </row>
+    <row r="367" spans="1:14">
       <c r="A367">
         <v>366</v>
       </c>
@@ -21450,11 +20467,8 @@
       <c r="N367" t="s">
         <v>28</v>
       </c>
-      <c r="O367">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="368" spans="1:15">
+    </row>
+    <row r="368" spans="1:14">
       <c r="A368">
         <v>367</v>
       </c>
@@ -21477,7 +20491,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="369" spans="1:15">
+    <row r="369" spans="1:14">
       <c r="A369">
         <v>368</v>
       </c>
@@ -21500,7 +20514,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="370" spans="1:15">
+    <row r="370" spans="1:14">
       <c r="A370">
         <v>369</v>
       </c>
@@ -21543,11 +20557,8 @@
       <c r="N370" t="s">
         <v>28</v>
       </c>
-      <c r="O370">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="371" spans="1:15">
+    </row>
+    <row r="371" spans="1:14">
       <c r="A371">
         <v>370</v>
       </c>
@@ -21590,11 +20601,8 @@
       <c r="N371" t="s">
         <v>28</v>
       </c>
-      <c r="O371">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="372" spans="1:15">
+    </row>
+    <row r="372" spans="1:14">
       <c r="A372">
         <v>371</v>
       </c>
@@ -21637,11 +20645,8 @@
       <c r="N372" t="s">
         <v>28</v>
       </c>
-      <c r="O372">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="373" spans="1:15">
+    </row>
+    <row r="373" spans="1:14">
       <c r="A373">
         <v>372</v>
       </c>
@@ -21684,11 +20689,8 @@
       <c r="N373" t="s">
         <v>28</v>
       </c>
-      <c r="O373">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="374" spans="1:15">
+    </row>
+    <row r="374" spans="1:14">
       <c r="A374">
         <v>373</v>
       </c>
@@ -21731,11 +20733,8 @@
       <c r="N374" t="s">
         <v>28</v>
       </c>
-      <c r="O374">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="375" spans="1:15">
+    </row>
+    <row r="375" spans="1:14">
       <c r="A375">
         <v>374</v>
       </c>
@@ -21778,11 +20777,8 @@
       <c r="N375" t="s">
         <v>28</v>
       </c>
-      <c r="O375">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="376" spans="1:15">
+    </row>
+    <row r="376" spans="1:14">
       <c r="A376">
         <v>375</v>
       </c>
@@ -21825,11 +20821,8 @@
       <c r="N376" t="s">
         <v>28</v>
       </c>
-      <c r="O376">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="377" spans="1:15">
+    </row>
+    <row r="377" spans="1:14">
       <c r="A377">
         <v>376</v>
       </c>
@@ -21872,11 +20865,8 @@
       <c r="N377" t="s">
         <v>28</v>
       </c>
-      <c r="O377">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="378" spans="1:15">
+    </row>
+    <row r="378" spans="1:14">
       <c r="A378">
         <v>377</v>
       </c>
@@ -21919,11 +20909,8 @@
       <c r="N378" t="s">
         <v>28</v>
       </c>
-      <c r="O378">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="379" spans="1:15">
+    </row>
+    <row r="379" spans="1:14">
       <c r="A379">
         <v>378</v>
       </c>
@@ -21966,11 +20953,8 @@
       <c r="N379" t="s">
         <v>28</v>
       </c>
-      <c r="O379">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="380" spans="1:15">
+    </row>
+    <row r="380" spans="1:14">
       <c r="A380">
         <v>379</v>
       </c>
@@ -22013,11 +20997,8 @@
       <c r="N380" t="s">
         <v>28</v>
       </c>
-      <c r="O380">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="381" spans="1:15">
+    </row>
+    <row r="381" spans="1:14">
       <c r="A381">
         <v>380</v>
       </c>
@@ -22060,11 +21041,8 @@
       <c r="N381" t="s">
         <v>28</v>
       </c>
-      <c r="O381">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="382" spans="1:15">
+    </row>
+    <row r="382" spans="1:14">
       <c r="A382">
         <v>381</v>
       </c>
@@ -22107,11 +21085,8 @@
       <c r="N382" t="s">
         <v>28</v>
       </c>
-      <c r="O382">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="383" spans="1:15">
+    </row>
+    <row r="383" spans="1:14">
       <c r="A383">
         <v>382</v>
       </c>
@@ -22134,7 +21109,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="384" spans="1:15">
+    <row r="384" spans="1:14">
       <c r="A384">
         <v>383</v>
       </c>
@@ -22157,7 +21132,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="385" spans="1:15">
+    <row r="385" spans="1:14">
       <c r="A385">
         <v>384</v>
       </c>
@@ -22200,11 +21175,8 @@
       <c r="N385" t="s">
         <v>28</v>
       </c>
-      <c r="O385">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="386" spans="1:15">
+    </row>
+    <row r="386" spans="1:14">
       <c r="A386">
         <v>385</v>
       </c>
@@ -22247,11 +21219,8 @@
       <c r="N386" t="s">
         <v>28</v>
       </c>
-      <c r="O386">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="387" spans="1:15">
+    </row>
+    <row r="387" spans="1:14">
       <c r="A387">
         <v>386</v>
       </c>
@@ -22294,11 +21263,8 @@
       <c r="N387" t="s">
         <v>28</v>
       </c>
-      <c r="O387">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="388" spans="1:15">
+    </row>
+    <row r="388" spans="1:14">
       <c r="A388">
         <v>387</v>
       </c>
@@ -22321,7 +21287,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="389" spans="1:15">
+    <row r="389" spans="1:14">
       <c r="A389">
         <v>388</v>
       </c>
@@ -22364,11 +21330,8 @@
       <c r="N389" t="s">
         <v>28</v>
       </c>
-      <c r="O389">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="390" spans="1:15">
+    </row>
+    <row r="390" spans="1:14">
       <c r="A390">
         <v>389</v>
       </c>
@@ -22411,11 +21374,8 @@
       <c r="N390" t="s">
         <v>28</v>
       </c>
-      <c r="O390">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="391" spans="1:15">
+    </row>
+    <row r="391" spans="1:14">
       <c r="A391">
         <v>390</v>
       </c>
@@ -22458,11 +21418,8 @@
       <c r="N391" t="s">
         <v>21</v>
       </c>
-      <c r="O391">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="392" spans="1:15">
+    </row>
+    <row r="392" spans="1:14">
       <c r="A392">
         <v>391</v>
       </c>
@@ -22485,7 +21442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="393" spans="1:15">
+    <row r="393" spans="1:14">
       <c r="A393">
         <v>392</v>
       </c>
@@ -22508,7 +21465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="394" spans="1:15">
+    <row r="394" spans="1:14">
       <c r="A394">
         <v>393</v>
       </c>
@@ -22551,11 +21508,8 @@
       <c r="N394" t="s">
         <v>28</v>
       </c>
-      <c r="O394">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="395" spans="1:15">
+    </row>
+    <row r="395" spans="1:14">
       <c r="A395">
         <v>394</v>
       </c>
@@ -22598,11 +21552,8 @@
       <c r="N395" t="s">
         <v>28</v>
       </c>
-      <c r="O395">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="396" spans="1:15">
+    </row>
+    <row r="396" spans="1:14">
       <c r="A396">
         <v>395</v>
       </c>
@@ -22645,11 +21596,8 @@
       <c r="N396" t="s">
         <v>28</v>
       </c>
-      <c r="O396">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="397" spans="1:15">
+    </row>
+    <row r="397" spans="1:14">
       <c r="A397">
         <v>396</v>
       </c>
@@ -22692,11 +21640,8 @@
       <c r="N397" t="s">
         <v>28</v>
       </c>
-      <c r="O397">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="398" spans="1:15">
+    </row>
+    <row r="398" spans="1:14">
       <c r="A398">
         <v>397</v>
       </c>
@@ -22739,11 +21684,8 @@
       <c r="N398" t="s">
         <v>28</v>
       </c>
-      <c r="O398">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="399" spans="1:15">
+    </row>
+    <row r="399" spans="1:14">
       <c r="A399">
         <v>398</v>
       </c>
@@ -22786,11 +21728,8 @@
       <c r="N399" t="s">
         <v>21</v>
       </c>
-      <c r="O399">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="400" spans="1:15">
+    </row>
+    <row r="400" spans="1:14">
       <c r="A400">
         <v>399</v>
       </c>
@@ -22833,11 +21772,8 @@
       <c r="N400" t="s">
         <v>28</v>
       </c>
-      <c r="O400">
-        <v>3333</v>
-      </c>
-    </row>
-    <row r="401" spans="1:15">
+    </row>
+    <row r="401" spans="1:14">
       <c r="A401">
         <v>400</v>
       </c>
@@ -22880,11 +21816,8 @@
       <c r="N401" t="s">
         <v>28</v>
       </c>
-      <c r="O401">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="402" spans="1:15">
+    </row>
+    <row r="402" spans="1:14">
       <c r="A402">
         <v>401</v>
       </c>
@@ -22927,11 +21860,8 @@
       <c r="N402" t="s">
         <v>28</v>
       </c>
-      <c r="O402">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="403" spans="1:15">
+    </row>
+    <row r="403" spans="1:14">
       <c r="A403">
         <v>402</v>
       </c>
@@ -22974,11 +21904,8 @@
       <c r="N403" t="s">
         <v>21</v>
       </c>
-      <c r="O403">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="404" spans="1:15">
+    </row>
+    <row r="404" spans="1:14">
       <c r="A404">
         <v>403</v>
       </c>
@@ -23021,11 +21948,8 @@
       <c r="N404" t="s">
         <v>28</v>
       </c>
-      <c r="O404">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="405" spans="1:15">
+    </row>
+    <row r="405" spans="1:14">
       <c r="A405">
         <v>404</v>
       </c>
@@ -23068,11 +21992,8 @@
       <c r="N405" t="s">
         <v>28</v>
       </c>
-      <c r="O405">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="406" spans="1:15">
+    </row>
+    <row r="406" spans="1:14">
       <c r="A406">
         <v>405</v>
       </c>
@@ -23115,11 +22036,8 @@
       <c r="N406" t="s">
         <v>28</v>
       </c>
-      <c r="O406">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="407" spans="1:15">
+    </row>
+    <row r="407" spans="1:14">
       <c r="A407">
         <v>406</v>
       </c>
@@ -23162,11 +22080,8 @@
       <c r="N407" t="s">
         <v>28</v>
       </c>
-      <c r="O407">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="408" spans="1:15">
+    </row>
+    <row r="408" spans="1:14">
       <c r="A408">
         <v>407</v>
       </c>
@@ -23209,11 +22124,8 @@
       <c r="N408" t="s">
         <v>28</v>
       </c>
-      <c r="O408">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="409" spans="1:15">
+    </row>
+    <row r="409" spans="1:14">
       <c r="A409">
         <v>408</v>
       </c>
@@ -23236,7 +22148,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="410" spans="1:15">
+    <row r="410" spans="1:14">
       <c r="A410">
         <v>409</v>
       </c>
@@ -23259,7 +22171,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="411" spans="1:15">
+    <row r="411" spans="1:14">
       <c r="A411">
         <v>410</v>
       </c>
@@ -23302,11 +22214,8 @@
       <c r="N411" t="s">
         <v>28</v>
       </c>
-      <c r="O411">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="412" spans="1:15">
+    </row>
+    <row r="412" spans="1:14">
       <c r="A412">
         <v>411</v>
       </c>
@@ -23349,11 +22258,8 @@
       <c r="N412" t="s">
         <v>28</v>
       </c>
-      <c r="O412">
-        <v>5555</v>
-      </c>
-    </row>
-    <row r="413" spans="1:15">
+    </row>
+    <row r="413" spans="1:14">
       <c r="A413">
         <v>412</v>
       </c>
@@ -23396,11 +22302,8 @@
       <c r="N413" t="s">
         <v>28</v>
       </c>
-      <c r="O413">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="414" spans="1:15">
+    </row>
+    <row r="414" spans="1:14">
       <c r="A414">
         <v>413</v>
       </c>
@@ -23443,11 +22346,8 @@
       <c r="N414" t="s">
         <v>28</v>
       </c>
-      <c r="O414">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="415" spans="1:15">
+    </row>
+    <row r="415" spans="1:14">
       <c r="A415">
         <v>414</v>
       </c>
@@ -23470,7 +22370,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="416" spans="1:15">
+    <row r="416" spans="1:14">
       <c r="A416">
         <v>415</v>
       </c>
@@ -23493,7 +22393,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="417" spans="1:15">
+    <row r="417" spans="1:14">
       <c r="A417">
         <v>416</v>
       </c>
@@ -23536,11 +22436,8 @@
       <c r="N417" t="s">
         <v>28</v>
       </c>
-      <c r="O417">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="418" spans="1:15">
+    </row>
+    <row r="418" spans="1:14">
       <c r="A418">
         <v>417</v>
       </c>
@@ -23583,11 +22480,8 @@
       <c r="N418" t="s">
         <v>28</v>
       </c>
-      <c r="O418">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="419" spans="1:15">
+    </row>
+    <row r="419" spans="1:14">
       <c r="A419">
         <v>418</v>
       </c>
@@ -23630,11 +22524,8 @@
       <c r="N419" t="s">
         <v>28</v>
       </c>
-      <c r="O419">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="420" spans="1:15">
+    </row>
+    <row r="420" spans="1:14">
       <c r="A420">
         <v>419</v>
       </c>
@@ -23677,11 +22568,8 @@
       <c r="N420" t="s">
         <v>21</v>
       </c>
-      <c r="O420">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="421" spans="1:15">
+    </row>
+    <row r="421" spans="1:14">
       <c r="A421">
         <v>420</v>
       </c>
@@ -23724,11 +22612,8 @@
       <c r="N421" t="s">
         <v>28</v>
       </c>
-      <c r="O421">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="422" spans="1:15">
+    </row>
+    <row r="422" spans="1:14">
       <c r="A422">
         <v>421</v>
       </c>
@@ -23771,11 +22656,8 @@
       <c r="N422" t="s">
         <v>21</v>
       </c>
-      <c r="O422">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="423" spans="1:15">
+    </row>
+    <row r="423" spans="1:14">
       <c r="A423">
         <v>422</v>
       </c>
@@ -23818,11 +22700,8 @@
       <c r="N423" t="s">
         <v>28</v>
       </c>
-      <c r="O423">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="424" spans="1:15">
+    </row>
+    <row r="424" spans="1:14">
       <c r="A424">
         <v>423</v>
       </c>
@@ -23865,11 +22744,8 @@
       <c r="N424" t="s">
         <v>28</v>
       </c>
-      <c r="O424">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="425" spans="1:15">
+    </row>
+    <row r="425" spans="1:14">
       <c r="A425">
         <v>424</v>
       </c>
@@ -23912,11 +22788,8 @@
       <c r="N425" t="s">
         <v>28</v>
       </c>
-      <c r="O425">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="426" spans="1:15">
+    </row>
+    <row r="426" spans="1:14">
       <c r="A426">
         <v>425</v>
       </c>
@@ -23959,11 +22832,8 @@
       <c r="N426" t="s">
         <v>28</v>
       </c>
-      <c r="O426">
-        <v>6666</v>
-      </c>
-    </row>
-    <row r="427" spans="1:15">
+    </row>
+    <row r="427" spans="1:14">
       <c r="A427">
         <v>426</v>
       </c>
@@ -24006,11 +22876,8 @@
       <c r="N427" t="s">
         <v>28</v>
       </c>
-      <c r="O427">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="428" spans="1:15">
+    </row>
+    <row r="428" spans="1:14">
       <c r="A428">
         <v>427</v>
       </c>
@@ -24033,7 +22900,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="429" spans="1:15">
+    <row r="429" spans="1:14">
       <c r="A429">
         <v>428</v>
       </c>
@@ -24056,7 +22923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="430" spans="1:15">
+    <row r="430" spans="1:14">
       <c r="A430">
         <v>429</v>
       </c>
@@ -24099,11 +22966,8 @@
       <c r="N430" t="s">
         <v>28</v>
       </c>
-      <c r="O430">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="431" spans="1:15">
+    </row>
+    <row r="431" spans="1:14">
       <c r="A431">
         <v>430</v>
       </c>
@@ -24146,11 +23010,8 @@
       <c r="N431" t="s">
         <v>28</v>
       </c>
-      <c r="O431">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="432" spans="1:15">
+    </row>
+    <row r="432" spans="1:14">
       <c r="A432">
         <v>431</v>
       </c>
@@ -24193,11 +23054,8 @@
       <c r="N432" t="s">
         <v>28</v>
       </c>
-      <c r="O432">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="433" spans="1:15">
+    </row>
+    <row r="433" spans="1:14">
       <c r="A433">
         <v>432</v>
       </c>
@@ -24240,11 +23098,8 @@
       <c r="N433" t="s">
         <v>28</v>
       </c>
-      <c r="O433">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="434" spans="1:15">
+    </row>
+    <row r="434" spans="1:14">
       <c r="A434">
         <v>433</v>
       </c>
@@ -24287,11 +23142,8 @@
       <c r="N434" t="s">
         <v>21</v>
       </c>
-      <c r="O434">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="435" spans="1:15">
+    </row>
+    <row r="435" spans="1:14">
       <c r="A435">
         <v>434</v>
       </c>
@@ -24334,11 +23186,8 @@
       <c r="N435" t="s">
         <v>28</v>
       </c>
-      <c r="O435">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="436" spans="1:15">
+    </row>
+    <row r="436" spans="1:14">
       <c r="A436">
         <v>435</v>
       </c>
@@ -24381,11 +23230,8 @@
       <c r="N436" t="s">
         <v>28</v>
       </c>
-      <c r="O436">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="437" spans="1:15">
+    </row>
+    <row r="437" spans="1:14">
       <c r="A437">
         <v>436</v>
       </c>
@@ -24428,11 +23274,8 @@
       <c r="N437" t="s">
         <v>28</v>
       </c>
-      <c r="O437">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="438" spans="1:15">
+    </row>
+    <row r="438" spans="1:14">
       <c r="A438">
         <v>437</v>
       </c>
@@ -24475,11 +23318,8 @@
       <c r="N438" t="s">
         <v>28</v>
       </c>
-      <c r="O438">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="439" spans="1:15">
+    </row>
+    <row r="439" spans="1:14">
       <c r="A439">
         <v>438</v>
       </c>
@@ -24522,11 +23362,8 @@
       <c r="N439" t="s">
         <v>28</v>
       </c>
-      <c r="O439">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="440" spans="1:15">
+    </row>
+    <row r="440" spans="1:14">
       <c r="A440">
         <v>439</v>
       </c>
@@ -24569,11 +23406,8 @@
       <c r="N440" t="s">
         <v>28</v>
       </c>
-      <c r="O440">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="441" spans="1:15">
+    </row>
+    <row r="441" spans="1:14">
       <c r="A441">
         <v>440</v>
       </c>
@@ -24616,11 +23450,8 @@
       <c r="N441" t="s">
         <v>28</v>
       </c>
-      <c r="O441">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="442" spans="1:15">
+    </row>
+    <row r="442" spans="1:14">
       <c r="A442">
         <v>441</v>
       </c>
@@ -24663,11 +23494,8 @@
       <c r="N442" t="s">
         <v>21</v>
       </c>
-      <c r="O442">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="443" spans="1:15">
+    </row>
+    <row r="443" spans="1:14">
       <c r="A443">
         <v>442</v>
       </c>
@@ -24710,11 +23538,8 @@
       <c r="N443" t="s">
         <v>28</v>
       </c>
-      <c r="O443">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="444" spans="1:15">
+    </row>
+    <row r="444" spans="1:14">
       <c r="A444">
         <v>443</v>
       </c>
@@ -24757,11 +23582,8 @@
       <c r="N444" t="s">
         <v>28</v>
       </c>
-      <c r="O444">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="445" spans="1:15">
+    </row>
+    <row r="445" spans="1:14">
       <c r="A445">
         <v>444</v>
       </c>
@@ -24804,11 +23626,8 @@
       <c r="N445" t="s">
         <v>28</v>
       </c>
-      <c r="O445">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="446" spans="1:15">
+    </row>
+    <row r="446" spans="1:14">
       <c r="A446">
         <v>445</v>
       </c>
@@ -24851,11 +23670,8 @@
       <c r="N446" t="s">
         <v>28</v>
       </c>
-      <c r="O446">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="447" spans="1:15">
+    </row>
+    <row r="447" spans="1:14">
       <c r="A447">
         <v>446</v>
       </c>
@@ -24878,7 +23694,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="448" spans="1:15">
+    <row r="448" spans="1:14">
       <c r="A448">
         <v>447</v>
       </c>
@@ -24921,11 +23737,8 @@
       <c r="N448" t="s">
         <v>28</v>
       </c>
-      <c r="O448">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="449" spans="1:15">
+    </row>
+    <row r="449" spans="1:14">
       <c r="A449">
         <v>448</v>
       </c>
@@ -24968,11 +23781,8 @@
       <c r="N449" t="s">
         <v>28</v>
       </c>
-      <c r="O449">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="450" spans="1:15">
+    </row>
+    <row r="450" spans="1:14">
       <c r="A450">
         <v>449</v>
       </c>
@@ -24995,7 +23805,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="451" spans="1:15">
+    <row r="451" spans="1:14">
       <c r="A451">
         <v>450</v>
       </c>
@@ -25018,7 +23828,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="452" spans="1:15">
+    <row r="452" spans="1:14">
       <c r="A452">
         <v>451</v>
       </c>
@@ -25061,11 +23871,8 @@
       <c r="N452" t="s">
         <v>28</v>
       </c>
-      <c r="O452">
-        <v>3333</v>
-      </c>
-    </row>
-    <row r="453" spans="1:15">
+    </row>
+    <row r="453" spans="1:14">
       <c r="A453">
         <v>452</v>
       </c>
@@ -25088,7 +23895,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="454" spans="1:15">
+    <row r="454" spans="1:14">
       <c r="A454">
         <v>453</v>
       </c>
@@ -25131,11 +23938,8 @@
       <c r="N454" t="s">
         <v>28</v>
       </c>
-      <c r="O454">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="455" spans="1:15">
+    </row>
+    <row r="455" spans="1:14">
       <c r="A455">
         <v>454</v>
       </c>
@@ -25158,7 +23962,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="456" spans="1:15">
+    <row r="456" spans="1:14">
       <c r="A456">
         <v>455</v>
       </c>
@@ -25201,11 +24005,8 @@
       <c r="N456" t="s">
         <v>28</v>
       </c>
-      <c r="O456">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="457" spans="1:15">
+    </row>
+    <row r="457" spans="1:14">
       <c r="A457">
         <v>456</v>
       </c>
@@ -25248,11 +24049,8 @@
       <c r="N457" t="s">
         <v>28</v>
       </c>
-      <c r="O457">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="458" spans="1:15">
+    </row>
+    <row r="458" spans="1:14">
       <c r="A458">
         <v>457</v>
       </c>
@@ -25275,7 +24073,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="459" spans="1:15">
+    <row r="459" spans="1:14">
       <c r="A459">
         <v>458</v>
       </c>
@@ -25318,11 +24116,8 @@
       <c r="N459" t="s">
         <v>28</v>
       </c>
-      <c r="O459">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="460" spans="1:15">
+    </row>
+    <row r="460" spans="1:14">
       <c r="A460">
         <v>459</v>
       </c>
@@ -25365,11 +24160,8 @@
       <c r="N460" t="s">
         <v>28</v>
       </c>
-      <c r="O460">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="461" spans="1:15">
+    </row>
+    <row r="461" spans="1:14">
       <c r="A461">
         <v>460</v>
       </c>
@@ -25412,11 +24204,8 @@
       <c r="N461" t="s">
         <v>28</v>
       </c>
-      <c r="O461">
-        <v>11115</v>
-      </c>
-    </row>
-    <row r="462" spans="1:15">
+    </row>
+    <row r="462" spans="1:14">
       <c r="A462">
         <v>461</v>
       </c>
@@ -25459,11 +24248,8 @@
       <c r="N462" t="s">
         <v>28</v>
       </c>
-      <c r="O462">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="463" spans="1:15">
+    </row>
+    <row r="463" spans="1:14">
       <c r="A463">
         <v>462</v>
       </c>
@@ -25506,11 +24292,8 @@
       <c r="N463" t="s">
         <v>28</v>
       </c>
-      <c r="O463">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="464" spans="1:15">
+    </row>
+    <row r="464" spans="1:14">
       <c r="A464">
         <v>463</v>
       </c>
@@ -25533,7 +24316,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="465" spans="1:15">
+    <row r="465" spans="1:14">
       <c r="A465">
         <v>464</v>
       </c>
@@ -25576,11 +24359,8 @@
       <c r="N465" t="s">
         <v>28</v>
       </c>
-      <c r="O465">
-        <v>1505</v>
-      </c>
-    </row>
-    <row r="466" spans="1:15">
+    </row>
+    <row r="466" spans="1:14">
       <c r="A466">
         <v>465</v>
       </c>
@@ -25623,11 +24403,8 @@
       <c r="N466" t="s">
         <v>28</v>
       </c>
-      <c r="O466">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="467" spans="1:15">
+    </row>
+    <row r="467" spans="1:14">
       <c r="A467">
         <v>466</v>
       </c>
@@ -25670,11 +24447,8 @@
       <c r="N467" t="s">
         <v>28</v>
       </c>
-      <c r="O467">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="468" spans="1:15">
+    </row>
+    <row r="468" spans="1:14">
       <c r="A468">
         <v>467</v>
       </c>
@@ -25717,11 +24491,8 @@
       <c r="N468" t="s">
         <v>28</v>
       </c>
-      <c r="O468">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="469" spans="1:15">
+    </row>
+    <row r="469" spans="1:14">
       <c r="A469">
         <v>468</v>
       </c>
@@ -25764,11 +24535,8 @@
       <c r="N469" t="s">
         <v>28</v>
       </c>
-      <c r="O469">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="470" spans="1:15">
+    </row>
+    <row r="470" spans="1:14">
       <c r="A470">
         <v>469</v>
       </c>
@@ -25811,11 +24579,8 @@
       <c r="N470" t="s">
         <v>28</v>
       </c>
-      <c r="O470">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="471" spans="1:15">
+    </row>
+    <row r="471" spans="1:14">
       <c r="A471">
         <v>470</v>
       </c>
@@ -25858,11 +24623,8 @@
       <c r="N471" t="s">
         <v>28</v>
       </c>
-      <c r="O471">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="472" spans="1:15">
+    </row>
+    <row r="472" spans="1:14">
       <c r="A472">
         <v>471</v>
       </c>
@@ -25905,11 +24667,8 @@
       <c r="N472" t="s">
         <v>28</v>
       </c>
-      <c r="O472">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="473" spans="1:15">
+    </row>
+    <row r="473" spans="1:14">
       <c r="A473">
         <v>472</v>
       </c>
@@ -25952,11 +24711,8 @@
       <c r="N473" t="s">
         <v>21</v>
       </c>
-      <c r="O473">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="474" spans="1:15">
+    </row>
+    <row r="474" spans="1:14">
       <c r="A474">
         <v>473</v>
       </c>
@@ -25999,11 +24755,8 @@
       <c r="N474" t="s">
         <v>28</v>
       </c>
-      <c r="O474">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="475" spans="1:15">
+    </row>
+    <row r="475" spans="1:14">
       <c r="A475">
         <v>474</v>
       </c>
@@ -26046,11 +24799,8 @@
       <c r="N475" t="s">
         <v>28</v>
       </c>
-      <c r="O475">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="476" spans="1:15">
+    </row>
+    <row r="476" spans="1:14">
       <c r="A476">
         <v>475</v>
       </c>
@@ -26093,11 +24843,8 @@
       <c r="N476" t="s">
         <v>28</v>
       </c>
-      <c r="O476">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="477" spans="1:15">
+    </row>
+    <row r="477" spans="1:14">
       <c r="A477">
         <v>476</v>
       </c>
@@ -26140,11 +24887,8 @@
       <c r="N477" t="s">
         <v>28</v>
       </c>
-      <c r="O477">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="478" spans="1:15">
+    </row>
+    <row r="478" spans="1:14">
       <c r="A478">
         <v>477</v>
       </c>
@@ -26187,11 +24931,8 @@
       <c r="N478" t="s">
         <v>28</v>
       </c>
-      <c r="O478">
-        <v>4350</v>
-      </c>
-    </row>
-    <row r="479" spans="1:15">
+    </row>
+    <row r="479" spans="1:14">
       <c r="A479">
         <v>478</v>
       </c>
@@ -26214,7 +24955,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="480" spans="1:15">
+    <row r="480" spans="1:14">
       <c r="A480">
         <v>479</v>
       </c>
@@ -26237,7 +24978,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="481" spans="1:15">
+    <row r="481" spans="1:14">
       <c r="A481">
         <v>480</v>
       </c>
@@ -26260,7 +25001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="482" spans="1:15">
+    <row r="482" spans="1:14">
       <c r="A482">
         <v>481</v>
       </c>
@@ -26303,11 +25044,8 @@
       <c r="N482" t="s">
         <v>21</v>
       </c>
-      <c r="O482">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="483" spans="1:15">
+    </row>
+    <row r="483" spans="1:14">
       <c r="A483">
         <v>482</v>
       </c>
@@ -26350,11 +25088,8 @@
       <c r="N483" t="s">
         <v>28</v>
       </c>
-      <c r="O483">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="484" spans="1:15">
+    </row>
+    <row r="484" spans="1:14">
       <c r="A484">
         <v>483</v>
       </c>
@@ -26397,11 +25132,8 @@
       <c r="N484" t="s">
         <v>28</v>
       </c>
-      <c r="O484">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="485" spans="1:15">
+    </row>
+    <row r="485" spans="1:14">
       <c r="A485">
         <v>484</v>
       </c>
@@ -26444,11 +25176,8 @@
       <c r="N485" t="s">
         <v>28</v>
       </c>
-      <c r="O485">
-        <v>5050</v>
-      </c>
-    </row>
-    <row r="486" spans="1:15">
+    </row>
+    <row r="486" spans="1:14">
       <c r="A486">
         <v>485</v>
       </c>
@@ -26491,11 +25220,8 @@
       <c r="N486" t="s">
         <v>28</v>
       </c>
-      <c r="O486">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="487" spans="1:15">
+    </row>
+    <row r="487" spans="1:14">
       <c r="A487">
         <v>486</v>
       </c>
@@ -26538,11 +25264,8 @@
       <c r="N487" t="s">
         <v>28</v>
       </c>
-      <c r="O487">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="488" spans="1:15">
+    </row>
+    <row r="488" spans="1:14">
       <c r="A488">
         <v>487</v>
       </c>
@@ -26585,11 +25308,8 @@
       <c r="N488" t="s">
         <v>28</v>
       </c>
-      <c r="O488">
-        <v>4444</v>
-      </c>
-    </row>
-    <row r="489" spans="1:15">
+    </row>
+    <row r="489" spans="1:14">
       <c r="A489">
         <v>488</v>
       </c>
@@ -26632,11 +25352,8 @@
       <c r="N489" t="s">
         <v>21</v>
       </c>
-      <c r="O489">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="490" spans="1:15">
+    </row>
+    <row r="490" spans="1:14">
       <c r="A490">
         <v>489</v>
       </c>
@@ -26679,11 +25396,8 @@
       <c r="N490" t="s">
         <v>21</v>
       </c>
-      <c r="O490">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="491" spans="1:15">
+    </row>
+    <row r="491" spans="1:14">
       <c r="A491">
         <v>490</v>
       </c>
@@ -26706,7 +25420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="492" spans="1:15">
+    <row r="492" spans="1:14">
       <c r="A492">
         <v>491</v>
       </c>
@@ -26749,11 +25463,8 @@
       <c r="N492" t="s">
         <v>28</v>
       </c>
-      <c r="O492">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="493" spans="1:15">
+    </row>
+    <row r="493" spans="1:14">
       <c r="A493">
         <v>492</v>
       </c>
@@ -26796,11 +25507,8 @@
       <c r="N493" t="s">
         <v>28</v>
       </c>
-      <c r="O493">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="494" spans="1:15">
+    </row>
+    <row r="494" spans="1:14">
       <c r="A494">
         <v>493</v>
       </c>
@@ -26843,11 +25551,8 @@
       <c r="N494" t="s">
         <v>28</v>
       </c>
-      <c r="O494">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="495" spans="1:15">
+    </row>
+    <row r="495" spans="1:14">
       <c r="A495">
         <v>494</v>
       </c>
@@ -26890,11 +25595,8 @@
       <c r="N495" t="s">
         <v>28</v>
       </c>
-      <c r="O495">
-        <v>8888</v>
-      </c>
-    </row>
-    <row r="496" spans="1:15">
+    </row>
+    <row r="496" spans="1:14">
       <c r="A496">
         <v>495</v>
       </c>
@@ -26937,11 +25639,8 @@
       <c r="N496" t="s">
         <v>28</v>
       </c>
-      <c r="O496">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="497" spans="1:15">
+    </row>
+    <row r="497" spans="1:14">
       <c r="A497">
         <v>496</v>
       </c>
@@ -26984,11 +25683,8 @@
       <c r="N497" t="s">
         <v>21</v>
       </c>
-      <c r="O497">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="498" spans="1:15">
+    </row>
+    <row r="498" spans="1:14">
       <c r="A498">
         <v>497</v>
       </c>
@@ -27031,11 +25727,8 @@
       <c r="N498" t="s">
         <v>28</v>
       </c>
-      <c r="O498">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="499" spans="1:15">
+    </row>
+    <row r="499" spans="1:14">
       <c r="A499">
         <v>498</v>
       </c>
@@ -27058,7 +25751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="500" spans="1:15">
+    <row r="500" spans="1:14">
       <c r="A500">
         <v>499</v>
       </c>
@@ -27081,7 +25774,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="501" spans="1:15">
+    <row r="501" spans="1:14">
       <c r="A501">
         <v>500</v>
       </c>
@@ -27124,11 +25817,8 @@
       <c r="N501" t="s">
         <v>28</v>
       </c>
-      <c r="O501">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="502" spans="1:15">
+    </row>
+    <row r="502" spans="1:14">
       <c r="A502">
         <v>501</v>
       </c>
@@ -27171,11 +25861,8 @@
       <c r="N502" t="s">
         <v>28</v>
       </c>
-      <c r="O502">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="503" spans="1:15">
+    </row>
+    <row r="503" spans="1:14">
       <c r="A503">
         <v>502</v>
       </c>
@@ -27218,11 +25905,8 @@
       <c r="N503" t="s">
         <v>28</v>
       </c>
-      <c r="O503">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="504" spans="1:15">
+    </row>
+    <row r="504" spans="1:14">
       <c r="A504">
         <v>503</v>
       </c>
@@ -27265,11 +25949,8 @@
       <c r="N504" t="s">
         <v>28</v>
       </c>
-      <c r="O504">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="505" spans="1:15">
+    </row>
+    <row r="505" spans="1:14">
       <c r="A505">
         <v>504</v>
       </c>
@@ -27312,11 +25993,8 @@
       <c r="N505" t="s">
         <v>28</v>
       </c>
-      <c r="O505">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="506" spans="1:15">
+    </row>
+    <row r="506" spans="1:14">
       <c r="A506">
         <v>505</v>
       </c>
@@ -27359,11 +26037,8 @@
       <c r="N506" t="s">
         <v>28</v>
       </c>
-      <c r="O506">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="507" spans="1:15">
+    </row>
+    <row r="507" spans="1:14">
       <c r="A507">
         <v>506</v>
       </c>
@@ -27406,11 +26081,8 @@
       <c r="N507" t="s">
         <v>21</v>
       </c>
-      <c r="O507">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="508" spans="1:15">
+    </row>
+    <row r="508" spans="1:14">
       <c r="A508">
         <v>507</v>
       </c>
@@ -27453,11 +26125,8 @@
       <c r="N508" t="s">
         <v>28</v>
       </c>
-      <c r="O508">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="509" spans="1:15">
+    </row>
+    <row r="509" spans="1:14">
       <c r="A509">
         <v>508</v>
       </c>
@@ -27500,11 +26169,8 @@
       <c r="N509" t="s">
         <v>28</v>
       </c>
-      <c r="O509">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="510" spans="1:15">
+    </row>
+    <row r="510" spans="1:14">
       <c r="A510">
         <v>509</v>
       </c>
@@ -27547,11 +26213,8 @@
       <c r="N510" t="s">
         <v>28</v>
       </c>
-      <c r="O510">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="511" spans="1:15">
+    </row>
+    <row r="511" spans="1:14">
       <c r="A511">
         <v>510</v>
       </c>
@@ -27594,11 +26257,8 @@
       <c r="N511" t="s">
         <v>28</v>
       </c>
-      <c r="O511">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="512" spans="1:15">
+    </row>
+    <row r="512" spans="1:14">
       <c r="A512">
         <v>511</v>
       </c>
@@ -27641,11 +26301,8 @@
       <c r="N512" t="s">
         <v>28</v>
       </c>
-      <c r="O512">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="513" spans="1:15">
+    </row>
+    <row r="513" spans="1:14">
       <c r="A513">
         <v>512</v>
       </c>
@@ -27688,11 +26345,8 @@
       <c r="N513" t="s">
         <v>28</v>
       </c>
-      <c r="O513">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="514" spans="1:15">
+    </row>
+    <row r="514" spans="1:14">
       <c r="A514">
         <v>513</v>
       </c>
@@ -27735,11 +26389,8 @@
       <c r="N514" t="s">
         <v>28</v>
       </c>
-      <c r="O514">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="515" spans="1:15">
+    </row>
+    <row r="515" spans="1:14">
       <c r="A515">
         <v>514</v>
       </c>
@@ -27782,11 +26433,8 @@
       <c r="N515" t="s">
         <v>28</v>
       </c>
-      <c r="O515">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="516" spans="1:15">
+    </row>
+    <row r="516" spans="1:14">
       <c r="A516">
         <v>515</v>
       </c>
@@ -27809,7 +26457,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="517" spans="1:15">
+    <row r="517" spans="1:14">
       <c r="A517">
         <v>516</v>
       </c>
@@ -27852,11 +26500,8 @@
       <c r="N517" t="s">
         <v>21</v>
       </c>
-      <c r="O517">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="518" spans="1:15">
+    </row>
+    <row r="518" spans="1:14">
       <c r="A518">
         <v>517</v>
       </c>
@@ -27899,11 +26544,8 @@
       <c r="N518" t="s">
         <v>28</v>
       </c>
-      <c r="O518">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="519" spans="1:15">
+    </row>
+    <row r="519" spans="1:14">
       <c r="A519">
         <v>518</v>
       </c>
@@ -27946,11 +26588,8 @@
       <c r="N519" t="s">
         <v>28</v>
       </c>
-      <c r="O519">
-        <v>4320</v>
-      </c>
-    </row>
-    <row r="520" spans="1:15">
+    </row>
+    <row r="520" spans="1:14">
       <c r="A520">
         <v>519</v>
       </c>
@@ -27966,7 +26605,7 @@
       <c r="E520" t="s">
         <v>1112</v>
       </c>
-      <c r="F520" s="9" t="s">
+      <c r="F520" s="7" t="s">
         <v>1171</v>
       </c>
       <c r="G520">
@@ -27993,11 +26632,8 @@
       <c r="N520" t="s">
         <v>21</v>
       </c>
-      <c r="O520">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="521" spans="1:15">
+    </row>
+    <row r="521" spans="1:14">
       <c r="A521">
         <v>520</v>
       </c>
@@ -28040,11 +26676,8 @@
       <c r="N521" t="s">
         <v>28</v>
       </c>
-      <c r="O521">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="522" spans="1:15">
+    </row>
+    <row r="522" spans="1:14">
       <c r="A522">
         <v>521</v>
       </c>
@@ -28087,11 +26720,8 @@
       <c r="N522" t="s">
         <v>28</v>
       </c>
-      <c r="O522">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="523" spans="1:15">
+    </row>
+    <row r="523" spans="1:14">
       <c r="A523">
         <v>522</v>
       </c>
@@ -28134,11 +26764,8 @@
       <c r="N523" t="s">
         <v>21</v>
       </c>
-      <c r="O523">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="524" spans="1:15">
+    </row>
+    <row r="524" spans="1:14">
       <c r="A524">
         <v>523</v>
       </c>
@@ -28161,7 +26788,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="525" spans="1:15">
+    <row r="525" spans="1:14">
       <c r="A525">
         <v>524</v>
       </c>
@@ -28204,11 +26831,8 @@
       <c r="N525" t="s">
         <v>28</v>
       </c>
-      <c r="O525">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="526" spans="1:15">
+    </row>
+    <row r="526" spans="1:14">
       <c r="A526">
         <v>525</v>
       </c>
@@ -28251,11 +26875,8 @@
       <c r="N526" t="s">
         <v>28</v>
       </c>
-      <c r="O526">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="527" spans="1:15">
+    </row>
+    <row r="527" spans="1:14">
       <c r="A527">
         <v>526</v>
       </c>
@@ -28298,11 +26919,8 @@
       <c r="N527" t="s">
         <v>28</v>
       </c>
-      <c r="O527">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="528" spans="1:15">
+    </row>
+    <row r="528" spans="1:14">
       <c r="A528">
         <v>527</v>
       </c>
@@ -28341,7 +26959,7 @@
       <c r="E529" t="s">
         <v>1132</v>
       </c>
-      <c r="F529" s="9" t="s">
+      <c r="F529" s="7" t="s">
         <v>1170</v>
       </c>
       <c r="G529">
@@ -28367,9 +26985,6 @@
       </c>
       <c r="N529" t="s">
         <v>28</v>
-      </c>
-      <c r="O529">
-        <v>5000</v>
       </c>
     </row>
     <row r="530" spans="1:15">
@@ -28402,7 +27017,7 @@
       <c r="B531">
         <v>530</v>
       </c>
-      <c r="C531" s="9" t="s">
+      <c r="C531" s="7" t="s">
         <v>1174</v>
       </c>
       <c r="D531" t="s">
@@ -28411,13 +27026,13 @@
       <c r="E531" t="s">
         <v>1173</v>
       </c>
-      <c r="F531" s="9" t="s">
+      <c r="F531" s="7" t="s">
         <v>1172</v>
       </c>
       <c r="G531">
         <v>4200000</v>
       </c>
-      <c r="H531" s="11">
+      <c r="H531" s="9">
         <v>290000</v>
       </c>
       <c r="I531">
@@ -28445,7 +27060,7 @@
   </sheetData>
   <autoFilter ref="A1:Q530" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" sqref="D2:D1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"official,custom"</formula1>
     </dataValidation>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4D5B35-0744-CB46-9743-982DDFC3713A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CE81A1-09B6-7D48-8F05-C621314BDB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7890" uniqueCount="2158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7422" uniqueCount="2169">
   <si>
     <t>id</t>
   </si>
@@ -7110,10 +7110,6 @@
     <t>指定条件により説明入力対象外</t>
   </si>
   <si>
-    <t>https://battlecats-db.com/enemy/078.html</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>大空へ羽ばたくため高台を目指して旅を
 続ける生後2日の新米天使。8回目の旅に
 友達のアヒルンルンを誘ったが断られた。
@@ -7458,6 +7454,86 @@
   </si>
   <si>
     <t xml:space="preserve">100%の確率 45F動きを止める </t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ネコアレルギー持ちの宇宙サンショウウオ
+くしゃみが止まらないので、ネコには
+なるべく近寄らないようにしている。
+UFOの近くで目撃されることが多い。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>会うのは3回目だね、神さまです！
+宇宙は無事、侵略できたかな？
+突然だけどなぞなぞ出しまーす！
+めっちゃカッコよくって皆に好かれて……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>星々の間を彷徨いながら
+破壊を繰り返す謎の生命体。
+その凄まじき超絶破壊力は
+宇宙の構造すら書き換える。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お尻に火を付けて自分の能力の限界に挑む
+不毛な研究の末に命を落としたニワトリ。
+死してなお限界突破に挑み、天国に
+羽ばたけることを夢見て走り続ける。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大天使を目指して今日も猛勉強の女の子。
+彼女の分厚い本にはお勉強のための心得と
+他人を蹴落とす真っ黒な裏技が書かれている。
+会得した毒撃で静かに確実に仕留める。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>芸歴888年、演歌歌手専属のバックダンサー。
+ダンスのキレは衰えたが特技の呪い針は健在で
+新人歌手の能力を潰しては大御所シンガーから
+高額の報酬をせしめているとの噂が耐えない。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>キュウリの舌ざわりが気に入り
+四六時中無心でくわえ続けている妖怪の子。
+穏やかに過ごしていたかと思うと突然、
+烈火のごとく怒り「烈波」を放つ。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>輝く星々をも魅了する宇宙No.1ホスト。
+あざとさに磨きをかけたトーク力と
+輝く瞳でマダムの心は無重力状態。
+キラ星キッスで異空間へご招待。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>古代の呪い（100％の確率で300F特殊能力封印）
+無効 （波動 ふっとばす 止める 遅くする 攻撃力低下）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>100％の確率でLv3烈波（80F 射程 150～2000）
+無効 （波動 ふっとばす 止める 遅くする 攻撃力低下）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>古代研究所の極秘技術によってゲノム改造され
+超生命体へと生まれ変わったカーバチャン。
+必ず動きを遅くする力を得た巨大な侵略者は
+戦うごとに凶暴性を増していく。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>毎年お盆になると三途の川を越えて
+故郷に帰ってくるタフな渡り鳥。
+険しい道中で全身の肉をもがれた痛みに
+酸性の涙を流しながら帰省する。</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -7932,9 +8008,7 @@
       <c r="Q2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="4" t="s">
-        <v>1595</v>
-      </c>
+      <c r="R2" s="4"/>
     </row>
     <row r="3" spans="1:18" ht="60">
       <c r="A3">
@@ -7986,9 +8060,6 @@
       <c r="Q3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="R3" t="s">
-        <v>1596</v>
-      </c>
     </row>
     <row r="4" spans="1:18" ht="60">
       <c r="A4">
@@ -8040,9 +8111,6 @@
       <c r="Q4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="R4" t="s">
-        <v>1597</v>
-      </c>
     </row>
     <row r="5" spans="1:18" ht="45">
       <c r="A5">
@@ -8094,9 +8162,6 @@
       <c r="Q5" s="10" t="s">
         <v>2098</v>
       </c>
-      <c r="R5" t="s">
-        <v>1598</v>
-      </c>
     </row>
     <row r="6" spans="1:18" ht="60">
       <c r="A6">
@@ -8148,9 +8213,6 @@
       <c r="Q6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R6" t="s">
-        <v>1599</v>
-      </c>
     </row>
     <row r="7" spans="1:18" ht="60">
       <c r="A7">
@@ -8202,9 +8264,6 @@
       <c r="Q7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R7" t="s">
-        <v>1600</v>
-      </c>
     </row>
     <row r="8" spans="1:18" ht="60">
       <c r="A8">
@@ -8256,9 +8315,6 @@
       <c r="Q8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="R8" t="s">
-        <v>1601</v>
-      </c>
     </row>
     <row r="9" spans="1:18" ht="60">
       <c r="A9">
@@ -8310,9 +8366,6 @@
       <c r="Q9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="R9" t="s">
-        <v>1602</v>
-      </c>
     </row>
     <row r="10" spans="1:18" ht="60">
       <c r="A10">
@@ -8364,9 +8417,6 @@
       <c r="Q10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="R10" t="s">
-        <v>1603</v>
-      </c>
     </row>
     <row r="11" spans="1:18" ht="60">
       <c r="A11">
@@ -8418,9 +8468,6 @@
       <c r="Q11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="R11" t="s">
-        <v>1604</v>
-      </c>
     </row>
     <row r="12" spans="1:18" ht="60">
       <c r="A12">
@@ -8474,9 +8521,6 @@
       <c r="Q12" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="R12" t="s">
-        <v>1605</v>
-      </c>
     </row>
     <row r="13" spans="1:18" ht="60">
       <c r="A13">
@@ -8528,9 +8572,6 @@
       <c r="Q13" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="R13" t="s">
-        <v>1606</v>
-      </c>
     </row>
     <row r="14" spans="1:18" ht="60">
       <c r="A14">
@@ -8582,9 +8623,6 @@
       <c r="Q14" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="R14" t="s">
-        <v>1607</v>
-      </c>
     </row>
     <row r="15" spans="1:18" ht="60">
       <c r="A15">
@@ -8636,9 +8674,6 @@
       <c r="Q15" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="R15" t="s">
-        <v>1608</v>
-      </c>
     </row>
     <row r="16" spans="1:18" ht="60">
       <c r="A16">
@@ -8690,11 +8725,8 @@
       <c r="Q16" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="R16" t="s">
-        <v>1609</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="60">
+    </row>
+    <row r="17" spans="1:17" ht="60">
       <c r="A17">
         <v>16</v>
       </c>
@@ -8744,11 +8776,8 @@
       <c r="Q17" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="R17" t="s">
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="60">
+    </row>
+    <row r="18" spans="1:17" ht="60">
       <c r="A18">
         <v>17</v>
       </c>
@@ -8798,11 +8827,8 @@
       <c r="Q18" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R18" t="s">
-        <v>1611</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="60">
+    </row>
+    <row r="19" spans="1:17" ht="60">
       <c r="A19">
         <v>18</v>
       </c>
@@ -8852,11 +8878,8 @@
       <c r="Q19" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="R19" t="s">
-        <v>1612</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="60">
+    </row>
+    <row r="20" spans="1:17" ht="60">
       <c r="A20">
         <v>19</v>
       </c>
@@ -8906,11 +8929,8 @@
       <c r="Q20" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="R20" t="s">
-        <v>1613</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21">
         <v>20</v>
       </c>
@@ -8939,7 +8959,7 @@
       <c r="P21" s="10"/>
       <c r="Q21" s="10"/>
     </row>
-    <row r="22" spans="1:18" ht="60">
+    <row r="22" spans="1:17" ht="60">
       <c r="A22">
         <v>21</v>
       </c>
@@ -8989,11 +9009,8 @@
       <c r="Q22" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="R22" t="s">
-        <v>1614</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="60">
+    </row>
+    <row r="23" spans="1:17" ht="60">
       <c r="A23">
         <v>22</v>
       </c>
@@ -9043,11 +9060,8 @@
       <c r="Q23" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="R23" t="s">
-        <v>1615</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="60">
+    </row>
+    <row r="24" spans="1:17" ht="60">
       <c r="A24">
         <v>23</v>
       </c>
@@ -9097,11 +9111,8 @@
       <c r="Q24" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="R24" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="60">
+    </row>
+    <row r="25" spans="1:17" ht="60">
       <c r="A25">
         <v>24</v>
       </c>
@@ -9151,11 +9162,8 @@
       <c r="Q25" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="R25" t="s">
-        <v>1617</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="60">
+    </row>
+    <row r="26" spans="1:17" ht="60">
       <c r="A26">
         <v>25</v>
       </c>
@@ -9205,11 +9213,8 @@
       <c r="Q26" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="R26" t="s">
-        <v>1618</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="60">
+    </row>
+    <row r="27" spans="1:17" ht="60">
       <c r="A27">
         <v>26</v>
       </c>
@@ -9261,11 +9266,8 @@
       <c r="Q27" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="R27" t="s">
-        <v>1619</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="60">
+    </row>
+    <row r="28" spans="1:17" ht="60">
       <c r="A28">
         <v>27</v>
       </c>
@@ -9315,11 +9317,8 @@
       <c r="Q28" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="R28" t="s">
-        <v>1620</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="60">
+    </row>
+    <row r="29" spans="1:17" ht="60">
       <c r="A29">
         <v>28</v>
       </c>
@@ -9371,11 +9370,8 @@
       <c r="Q29" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="R29" t="s">
-        <v>1621</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="60">
+    </row>
+    <row r="30" spans="1:17" ht="60">
       <c r="A30">
         <v>29</v>
       </c>
@@ -9427,11 +9423,8 @@
       <c r="Q30" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="R30" t="s">
-        <v>1622</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="60">
+    </row>
+    <row r="31" spans="1:17" ht="60">
       <c r="A31">
         <v>30</v>
       </c>
@@ -9483,11 +9476,8 @@
       <c r="Q31" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="R31" t="s">
-        <v>1623</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="60">
+    </row>
+    <row r="32" spans="1:17" ht="60">
       <c r="A32">
         <v>31</v>
       </c>
@@ -9537,11 +9527,8 @@
       <c r="Q32" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="R32" t="s">
-        <v>1624</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="60">
+    </row>
+    <row r="33" spans="1:17" ht="60">
       <c r="A33">
         <v>32</v>
       </c>
@@ -9591,11 +9578,8 @@
       <c r="Q33" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="R33" t="s">
-        <v>1625</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="60">
+    </row>
+    <row r="34" spans="1:17" ht="60">
       <c r="A34">
         <v>33</v>
       </c>
@@ -9645,11 +9629,8 @@
       <c r="Q34" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="R34" t="s">
-        <v>1626</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="60">
+    </row>
+    <row r="35" spans="1:17" ht="60">
       <c r="A35">
         <v>34</v>
       </c>
@@ -9699,11 +9680,8 @@
       <c r="Q35" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="R35" t="s">
-        <v>1627</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="60">
+    </row>
+    <row r="36" spans="1:17" ht="60">
       <c r="A36">
         <v>35</v>
       </c>
@@ -9753,11 +9731,8 @@
       <c r="Q36" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="R36" t="s">
-        <v>1628</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="60">
+    </row>
+    <row r="37" spans="1:17" ht="60">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9807,11 +9782,8 @@
       <c r="Q37" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="R37" t="s">
-        <v>1629</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="60">
+    </row>
+    <row r="38" spans="1:17" ht="60">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9863,11 +9835,8 @@
       <c r="Q38" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="R38" t="s">
-        <v>1630</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="60">
+    </row>
+    <row r="39" spans="1:17" ht="60">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9919,11 +9888,8 @@
       <c r="Q39" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="R39" t="s">
-        <v>1631</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="60">
+    </row>
+    <row r="40" spans="1:17" ht="60">
       <c r="A40">
         <v>39</v>
       </c>
@@ -9973,11 +9939,8 @@
       <c r="Q40" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="R40" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" ht="60">
+    </row>
+    <row r="41" spans="1:17" ht="60">
       <c r="A41">
         <v>40</v>
       </c>
@@ -10027,11 +9990,8 @@
       <c r="Q41" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="R41" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="45">
+    </row>
+    <row r="42" spans="1:17" ht="45">
       <c r="A42">
         <v>41</v>
       </c>
@@ -10081,11 +10041,8 @@
       <c r="Q42" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="R42" t="s">
-        <v>1634</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="60">
+    </row>
+    <row r="43" spans="1:17" ht="60">
       <c r="A43">
         <v>42</v>
       </c>
@@ -10135,11 +10092,8 @@
       <c r="Q43" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="R43" t="s">
-        <v>1635</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="60">
+    </row>
+    <row r="44" spans="1:17" ht="60">
       <c r="A44">
         <v>43</v>
       </c>
@@ -10189,11 +10143,8 @@
       <c r="Q44" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="R44" t="s">
-        <v>1636</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" ht="60">
+    </row>
+    <row r="45" spans="1:17" ht="60">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10243,11 +10194,8 @@
       <c r="Q45" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="R45" t="s">
-        <v>1637</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" ht="60">
+    </row>
+    <row r="46" spans="1:17" ht="60">
       <c r="A46">
         <v>45</v>
       </c>
@@ -10297,11 +10245,8 @@
       <c r="Q46" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="R46" t="s">
-        <v>1638</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="60">
+    </row>
+    <row r="47" spans="1:17" ht="60">
       <c r="A47">
         <v>46</v>
       </c>
@@ -10353,11 +10298,8 @@
       <c r="Q47" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="R47" t="s">
-        <v>1639</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="60">
+    </row>
+    <row r="48" spans="1:17" ht="60">
       <c r="A48">
         <v>47</v>
       </c>
@@ -10407,9 +10349,6 @@
       <c r="Q48" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="R48" t="s">
-        <v>1640</v>
-      </c>
     </row>
     <row r="49" spans="1:18" ht="60">
       <c r="A49">
@@ -10463,9 +10402,6 @@
       <c r="Q49" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="R49" t="s">
-        <v>1641</v>
-      </c>
     </row>
     <row r="50" spans="1:18" ht="60">
       <c r="A50">
@@ -10517,9 +10453,6 @@
       <c r="Q50" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="R50" t="s">
-        <v>1642</v>
-      </c>
     </row>
     <row r="51" spans="1:18" ht="60">
       <c r="A51">
@@ -10571,9 +10504,6 @@
       <c r="Q51" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="R51" t="s">
-        <v>1643</v>
-      </c>
     </row>
     <row r="52" spans="1:18" ht="60">
       <c r="A52">
@@ -10627,9 +10557,6 @@
       <c r="Q52" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="R52" t="s">
-        <v>1644</v>
-      </c>
     </row>
     <row r="53" spans="1:18" ht="60">
       <c r="A53">
@@ -10681,9 +10608,6 @@
       <c r="Q53" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="R53" t="s">
-        <v>1645</v>
-      </c>
     </row>
     <row r="54" spans="1:18">
       <c r="A54">
@@ -10733,9 +10657,6 @@
       </c>
       <c r="P54" s="10"/>
       <c r="Q54" s="10"/>
-      <c r="R54" t="s">
-        <v>1646</v>
-      </c>
     </row>
     <row r="55" spans="1:18" ht="15">
       <c r="A55">
@@ -10789,9 +10710,6 @@
       <c r="Q55" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="R55" t="s">
-        <v>1647</v>
-      </c>
     </row>
     <row r="56" spans="1:18" ht="60">
       <c r="A56">
@@ -10843,9 +10761,6 @@
       <c r="Q56" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="R56" t="s">
-        <v>1648</v>
-      </c>
     </row>
     <row r="57" spans="1:18" ht="15">
       <c r="A57">
@@ -10897,9 +10812,6 @@
         <v>203</v>
       </c>
       <c r="Q57" s="10"/>
-      <c r="R57" t="s">
-        <v>1649</v>
-      </c>
     </row>
     <row r="58" spans="1:18" ht="15">
       <c r="A58">
@@ -10951,9 +10863,6 @@
         <v>138</v>
       </c>
       <c r="Q58" s="10"/>
-      <c r="R58" t="s">
-        <v>1650</v>
-      </c>
     </row>
     <row r="59" spans="1:18" ht="15">
       <c r="A59">
@@ -11005,9 +10914,6 @@
         <v>138</v>
       </c>
       <c r="Q59" s="10"/>
-      <c r="R59" t="s">
-        <v>1651</v>
-      </c>
     </row>
     <row r="60" spans="1:18" ht="60">
       <c r="A60">
@@ -11059,9 +10965,6 @@
       <c r="Q60" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="R60" t="s">
-        <v>1652</v>
-      </c>
     </row>
     <row r="61" spans="1:18" ht="60">
       <c r="A61">
@@ -11115,9 +11018,6 @@
       <c r="Q61" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="R61" t="s">
-        <v>1653</v>
-      </c>
     </row>
     <row r="62" spans="1:18" ht="60">
       <c r="A62">
@@ -11169,9 +11069,6 @@
       <c r="Q62" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="R62" t="s">
-        <v>1654</v>
-      </c>
     </row>
     <row r="63" spans="1:18" ht="15">
       <c r="A63">
@@ -11223,9 +11120,6 @@
         <v>112</v>
       </c>
       <c r="Q63" s="10"/>
-      <c r="R63" t="s">
-        <v>1655</v>
-      </c>
     </row>
     <row r="64" spans="1:18" ht="15">
       <c r="A64">
@@ -11277,11 +11171,9 @@
         <v>221</v>
       </c>
       <c r="Q64" s="10"/>
-      <c r="R64" s="12" t="s">
-        <v>2105</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" ht="15">
+      <c r="R64" s="12"/>
+    </row>
+    <row r="65" spans="1:17" ht="15">
       <c r="A65">
         <v>64</v>
       </c>
@@ -11331,11 +11223,8 @@
         <v>224</v>
       </c>
       <c r="Q65" s="10"/>
-      <c r="R65" t="s">
-        <v>1657</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" ht="15">
+    </row>
+    <row r="66" spans="1:17" ht="15">
       <c r="A66">
         <v>65</v>
       </c>
@@ -11385,11 +11274,8 @@
         <v>224</v>
       </c>
       <c r="Q66" s="10"/>
-      <c r="R66" t="s">
-        <v>1658</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18">
+    </row>
+    <row r="67" spans="1:17">
       <c r="A67">
         <v>66</v>
       </c>
@@ -11437,11 +11323,8 @@
       </c>
       <c r="P67" s="10"/>
       <c r="Q67" s="10"/>
-      <c r="R67" t="s">
-        <v>1659</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" ht="15">
+    </row>
+    <row r="68" spans="1:17" ht="15">
       <c r="A68">
         <v>67</v>
       </c>
@@ -11491,11 +11374,8 @@
         <v>492</v>
       </c>
       <c r="Q68" s="10"/>
-      <c r="R68" t="s">
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" ht="45">
+    </row>
+    <row r="69" spans="1:17" ht="45">
       <c r="A69">
         <v>68</v>
       </c>
@@ -11545,11 +11425,8 @@
         <v>233</v>
       </c>
       <c r="Q69" s="10"/>
-      <c r="R69" t="s">
-        <v>1661</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" ht="15">
+    </row>
+    <row r="70" spans="1:17" ht="15">
       <c r="A70">
         <v>69</v>
       </c>
@@ -11599,11 +11476,8 @@
         <v>236</v>
       </c>
       <c r="Q70" s="10"/>
-      <c r="R70" t="s">
-        <v>1662</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" ht="15">
+    </row>
+    <row r="71" spans="1:17" ht="15">
       <c r="A71">
         <v>70</v>
       </c>
@@ -11653,11 +11527,8 @@
         <v>138</v>
       </c>
       <c r="Q71" s="10"/>
-      <c r="R71" t="s">
-        <v>1663</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" ht="15">
+    </row>
+    <row r="72" spans="1:17" ht="15">
       <c r="A72">
         <v>71</v>
       </c>
@@ -11707,11 +11578,8 @@
         <v>236</v>
       </c>
       <c r="Q72" s="10"/>
-      <c r="R72" t="s">
-        <v>1664</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" ht="15">
+    </row>
+    <row r="73" spans="1:17" ht="15">
       <c r="A73">
         <v>72</v>
       </c>
@@ -11761,11 +11629,8 @@
         <v>138</v>
       </c>
       <c r="Q73" s="10"/>
-      <c r="R73" t="s">
-        <v>1665</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18">
+    </row>
+    <row r="74" spans="1:17">
       <c r="A74">
         <v>73</v>
       </c>
@@ -11813,11 +11678,8 @@
       </c>
       <c r="P74" s="10"/>
       <c r="Q74" s="10"/>
-      <c r="R74" t="s">
-        <v>1666</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" ht="15">
+    </row>
+    <row r="75" spans="1:17" ht="15">
       <c r="A75">
         <v>74</v>
       </c>
@@ -11867,11 +11729,8 @@
         <v>112</v>
       </c>
       <c r="Q75" s="10"/>
-      <c r="R75" t="s">
-        <v>1667</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18">
+    </row>
+    <row r="76" spans="1:17">
       <c r="A76">
         <v>75</v>
       </c>
@@ -11919,11 +11778,8 @@
       </c>
       <c r="P76" s="10"/>
       <c r="Q76" s="10"/>
-      <c r="R76" t="s">
-        <v>1668</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18">
+    </row>
+    <row r="77" spans="1:17">
       <c r="A77">
         <v>76</v>
       </c>
@@ -11971,11 +11827,8 @@
       </c>
       <c r="P77" s="10"/>
       <c r="Q77" s="10"/>
-      <c r="R77" t="s">
-        <v>1669</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18">
+    </row>
+    <row r="78" spans="1:17">
       <c r="A78">
         <v>77</v>
       </c>
@@ -12023,11 +11876,8 @@
       </c>
       <c r="P78" s="10"/>
       <c r="Q78" s="10"/>
-      <c r="R78" t="s">
-        <v>1670</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18">
+    </row>
+    <row r="79" spans="1:17">
       <c r="A79">
         <v>78</v>
       </c>
@@ -12075,11 +11925,8 @@
       </c>
       <c r="P79" s="10"/>
       <c r="Q79" s="10"/>
-      <c r="R79" t="s">
-        <v>1671</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18">
+    </row>
+    <row r="80" spans="1:17">
       <c r="A80">
         <v>79</v>
       </c>
@@ -12127,11 +11974,8 @@
       </c>
       <c r="P80" s="10"/>
       <c r="Q80" s="10"/>
-      <c r="R80" t="s">
-        <v>1672</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18">
+    </row>
+    <row r="81" spans="1:17">
       <c r="A81">
         <v>80</v>
       </c>
@@ -12179,11 +12023,8 @@
       </c>
       <c r="P81" s="10"/>
       <c r="Q81" s="10"/>
-      <c r="R81" t="s">
-        <v>1673</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18">
+    </row>
+    <row r="82" spans="1:17">
       <c r="A82">
         <v>81</v>
       </c>
@@ -12231,11 +12072,8 @@
       </c>
       <c r="P82" s="10"/>
       <c r="Q82" s="10"/>
-      <c r="R82" t="s">
-        <v>1674</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18">
+    </row>
+    <row r="83" spans="1:17">
       <c r="A83">
         <v>82</v>
       </c>
@@ -12283,11 +12121,8 @@
       </c>
       <c r="P83" s="10"/>
       <c r="Q83" s="10"/>
-      <c r="R83" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18">
+    </row>
+    <row r="84" spans="1:17">
       <c r="A84">
         <v>83</v>
       </c>
@@ -12335,11 +12170,8 @@
       </c>
       <c r="P84" s="10"/>
       <c r="Q84" s="10"/>
-      <c r="R84" t="s">
-        <v>1676</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18">
+    </row>
+    <row r="85" spans="1:17">
       <c r="A85">
         <v>84</v>
       </c>
@@ -12387,11 +12219,8 @@
       </c>
       <c r="P85" s="10"/>
       <c r="Q85" s="10"/>
-      <c r="R85" t="s">
-        <v>1677</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18">
+    </row>
+    <row r="86" spans="1:17">
       <c r="A86">
         <v>85</v>
       </c>
@@ -12439,11 +12268,8 @@
       </c>
       <c r="P86" s="10"/>
       <c r="Q86" s="10"/>
-      <c r="R86" t="s">
-        <v>1678</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18">
+    </row>
+    <row r="87" spans="1:17">
       <c r="A87">
         <v>86</v>
       </c>
@@ -12491,11 +12317,8 @@
       </c>
       <c r="P87" s="10"/>
       <c r="Q87" s="10"/>
-      <c r="R87" t="s">
-        <v>1679</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18">
+    </row>
+    <row r="88" spans="1:17">
       <c r="A88">
         <v>87</v>
       </c>
@@ -12543,11 +12366,8 @@
       </c>
       <c r="P88" s="10"/>
       <c r="Q88" s="10"/>
-      <c r="R88" t="s">
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" ht="60">
+    </row>
+    <row r="89" spans="1:17" ht="60">
       <c r="A89">
         <v>88</v>
       </c>
@@ -12597,11 +12417,8 @@
       <c r="Q89" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="R89" t="s">
-        <v>1681</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18" ht="60">
+    </row>
+    <row r="90" spans="1:17" ht="60">
       <c r="A90">
         <v>89</v>
       </c>
@@ -12651,11 +12468,8 @@
       <c r="Q90" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="R90" t="s">
-        <v>1682</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" ht="60">
+    </row>
+    <row r="91" spans="1:17" ht="60">
       <c r="A91">
         <v>90</v>
       </c>
@@ -12705,11 +12519,8 @@
       <c r="Q91" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="R91" t="s">
-        <v>1683</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" ht="60">
+    </row>
+    <row r="92" spans="1:17" ht="60">
       <c r="A92">
         <v>91</v>
       </c>
@@ -12759,11 +12570,8 @@
       <c r="Q92" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="R92" t="s">
-        <v>1684</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" ht="60">
+    </row>
+    <row r="93" spans="1:17" ht="60">
       <c r="A93">
         <v>92</v>
       </c>
@@ -12813,11 +12621,8 @@
       <c r="Q93" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="R93" t="s">
-        <v>1685</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18" ht="60">
+    </row>
+    <row r="94" spans="1:17" ht="60">
       <c r="A94">
         <v>93</v>
       </c>
@@ -12867,11 +12672,8 @@
       <c r="Q94" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="R94" t="s">
-        <v>1686</v>
-      </c>
-    </row>
-    <row r="95" spans="1:18" ht="60">
+    </row>
+    <row r="95" spans="1:17" ht="60">
       <c r="A95">
         <v>94</v>
       </c>
@@ -12921,11 +12723,8 @@
       <c r="Q95" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="R95" t="s">
-        <v>1687</v>
-      </c>
-    </row>
-    <row r="96" spans="1:18" ht="60">
+    </row>
+    <row r="96" spans="1:17" ht="60">
       <c r="A96">
         <v>95</v>
       </c>
@@ -12977,11 +12776,8 @@
       <c r="Q96" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="R96" t="s">
-        <v>1688</v>
-      </c>
-    </row>
-    <row r="97" spans="1:18">
+    </row>
+    <row r="97" spans="1:17">
       <c r="A97">
         <v>96</v>
       </c>
@@ -13007,7 +12803,7 @@
       <c r="P97" s="10"/>
       <c r="Q97" s="10"/>
     </row>
-    <row r="98" spans="1:18" ht="60">
+    <row r="98" spans="1:17" ht="60">
       <c r="A98">
         <v>97</v>
       </c>
@@ -13059,11 +12855,8 @@
       <c r="Q98" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="R98" t="s">
-        <v>1689</v>
-      </c>
-    </row>
-    <row r="99" spans="1:18" ht="60">
+    </row>
+    <row r="99" spans="1:17" ht="60">
       <c r="A99">
         <v>98</v>
       </c>
@@ -13113,11 +12906,8 @@
       <c r="Q99" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="R99" t="s">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="100" spans="1:18" ht="60">
+    </row>
+    <row r="100" spans="1:17" ht="60">
       <c r="A100">
         <v>99</v>
       </c>
@@ -13169,11 +12959,8 @@
       <c r="Q100" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="R100" t="s">
-        <v>1691</v>
-      </c>
-    </row>
-    <row r="101" spans="1:18" ht="45">
+    </row>
+    <row r="101" spans="1:17" ht="45">
       <c r="A101">
         <v>100</v>
       </c>
@@ -13223,11 +13010,8 @@
         <v>315</v>
       </c>
       <c r="Q101" s="10"/>
-      <c r="R101" t="s">
-        <v>1692</v>
-      </c>
-    </row>
-    <row r="102" spans="1:18">
+    </row>
+    <row r="102" spans="1:17">
       <c r="A102">
         <v>101</v>
       </c>
@@ -13275,11 +13059,8 @@
       </c>
       <c r="P102" s="10"/>
       <c r="Q102" s="10"/>
-      <c r="R102" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="103" spans="1:18">
+    </row>
+    <row r="103" spans="1:17">
       <c r="A103">
         <v>102</v>
       </c>
@@ -13327,11 +13108,8 @@
       </c>
       <c r="P103" s="10"/>
       <c r="Q103" s="10"/>
-      <c r="R103" t="s">
-        <v>1694</v>
-      </c>
-    </row>
-    <row r="104" spans="1:18">
+    </row>
+    <row r="104" spans="1:17">
       <c r="A104">
         <v>103</v>
       </c>
@@ -13379,11 +13157,8 @@
       </c>
       <c r="P104" s="10"/>
       <c r="Q104" s="10"/>
-      <c r="R104" t="s">
-        <v>1695</v>
-      </c>
-    </row>
-    <row r="105" spans="1:18">
+    </row>
+    <row r="105" spans="1:17">
       <c r="A105">
         <v>104</v>
       </c>
@@ -13431,11 +13206,8 @@
       </c>
       <c r="P105" s="10"/>
       <c r="Q105" s="10"/>
-      <c r="R105" t="s">
-        <v>1696</v>
-      </c>
-    </row>
-    <row r="106" spans="1:18">
+    </row>
+    <row r="106" spans="1:17">
       <c r="A106">
         <v>105</v>
       </c>
@@ -13483,11 +13255,8 @@
       </c>
       <c r="P106" s="10"/>
       <c r="Q106" s="10"/>
-      <c r="R106" t="s">
-        <v>1697</v>
-      </c>
-    </row>
-    <row r="107" spans="1:18">
+    </row>
+    <row r="107" spans="1:17">
       <c r="A107">
         <v>106</v>
       </c>
@@ -13535,11 +13304,8 @@
       </c>
       <c r="P107" s="10"/>
       <c r="Q107" s="10"/>
-      <c r="R107" t="s">
-        <v>1698</v>
-      </c>
-    </row>
-    <row r="108" spans="1:18">
+    </row>
+    <row r="108" spans="1:17">
       <c r="A108">
         <v>107</v>
       </c>
@@ -13587,11 +13353,8 @@
       </c>
       <c r="P108" s="10"/>
       <c r="Q108" s="10"/>
-      <c r="R108" t="s">
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="109" spans="1:18">
+    </row>
+    <row r="109" spans="1:17">
       <c r="A109">
         <v>108</v>
       </c>
@@ -13639,11 +13402,8 @@
       </c>
       <c r="P109" s="10"/>
       <c r="Q109" s="10"/>
-      <c r="R109" t="s">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="110" spans="1:18">
+    </row>
+    <row r="110" spans="1:17">
       <c r="A110">
         <v>109</v>
       </c>
@@ -13691,11 +13451,8 @@
       </c>
       <c r="P110" s="10"/>
       <c r="Q110" s="10"/>
-      <c r="R110" t="s">
-        <v>1701</v>
-      </c>
-    </row>
-    <row r="111" spans="1:18">
+    </row>
+    <row r="111" spans="1:17">
       <c r="A111">
         <v>110</v>
       </c>
@@ -13743,11 +13500,8 @@
       </c>
       <c r="P111" s="10"/>
       <c r="Q111" s="10"/>
-      <c r="R111" t="s">
-        <v>1702</v>
-      </c>
-    </row>
-    <row r="112" spans="1:18" ht="15">
+    </row>
+    <row r="112" spans="1:17" ht="15">
       <c r="A112">
         <v>111</v>
       </c>
@@ -13797,11 +13551,8 @@
         <v>338</v>
       </c>
       <c r="Q112" s="10"/>
-      <c r="R112" t="s">
-        <v>1703</v>
-      </c>
-    </row>
-    <row r="113" spans="1:18" ht="30">
+    </row>
+    <row r="113" spans="1:17" ht="30">
       <c r="A113">
         <v>112</v>
       </c>
@@ -13851,11 +13602,8 @@
         <v>341</v>
       </c>
       <c r="Q113" s="10"/>
-      <c r="R113" t="s">
-        <v>1704</v>
-      </c>
-    </row>
-    <row r="114" spans="1:18" ht="15">
+    </row>
+    <row r="114" spans="1:17" ht="15">
       <c r="A114">
         <v>113</v>
       </c>
@@ -13905,11 +13653,8 @@
         <v>344</v>
       </c>
       <c r="Q114" s="10"/>
-      <c r="R114" t="s">
-        <v>1705</v>
-      </c>
-    </row>
-    <row r="115" spans="1:18">
+    </row>
+    <row r="115" spans="1:17">
       <c r="A115">
         <v>114</v>
       </c>
@@ -13957,11 +13702,8 @@
       </c>
       <c r="P115" s="10"/>
       <c r="Q115" s="10"/>
-      <c r="R115" t="s">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="116" spans="1:18" ht="60">
+    </row>
+    <row r="116" spans="1:17" ht="60">
       <c r="A116">
         <v>115</v>
       </c>
@@ -14013,11 +13755,8 @@
       <c r="Q116" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="R116" t="s">
-        <v>1707</v>
-      </c>
-    </row>
-    <row r="117" spans="1:18" ht="60">
+    </row>
+    <row r="117" spans="1:17" ht="60">
       <c r="A117">
         <v>116</v>
       </c>
@@ -14067,11 +13806,8 @@
       <c r="Q117" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="R117" t="s">
-        <v>1708</v>
-      </c>
-    </row>
-    <row r="118" spans="1:18" ht="60">
+    </row>
+    <row r="118" spans="1:17" ht="60">
       <c r="A118">
         <v>117</v>
       </c>
@@ -14121,11 +13857,8 @@
       <c r="Q118" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="R118" t="s">
-        <v>1709</v>
-      </c>
-    </row>
-    <row r="119" spans="1:18" ht="60">
+    </row>
+    <row r="119" spans="1:17" ht="60">
       <c r="A119">
         <v>118</v>
       </c>
@@ -14175,11 +13908,8 @@
       <c r="Q119" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="R119" t="s">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="120" spans="1:18">
+    </row>
+    <row r="120" spans="1:17">
       <c r="A120">
         <v>119</v>
       </c>
@@ -14227,11 +13957,8 @@
       </c>
       <c r="P120" s="10"/>
       <c r="Q120" s="10"/>
-      <c r="R120" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="121" spans="1:18" ht="60">
+    </row>
+    <row r="121" spans="1:17" ht="60">
       <c r="A121">
         <v>120</v>
       </c>
@@ -14281,13 +14008,10 @@
         <v>363</v>
       </c>
       <c r="Q121" s="10" t="s">
-        <v>2106</v>
-      </c>
-      <c r="R121" t="s">
-        <v>1712</v>
-      </c>
-    </row>
-    <row r="122" spans="1:18" ht="60">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" ht="60">
       <c r="A122">
         <v>121</v>
       </c>
@@ -14335,13 +14059,10 @@
       </c>
       <c r="P122" s="10"/>
       <c r="Q122" s="10" t="s">
-        <v>2107</v>
-      </c>
-      <c r="R122" t="s">
-        <v>1713</v>
-      </c>
-    </row>
-    <row r="123" spans="1:18" ht="60">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" ht="60">
       <c r="A123">
         <v>122</v>
       </c>
@@ -14389,13 +14110,10 @@
       </c>
       <c r="P123" s="10"/>
       <c r="Q123" s="10" t="s">
-        <v>2108</v>
-      </c>
-      <c r="R123" t="s">
-        <v>1714</v>
-      </c>
-    </row>
-    <row r="124" spans="1:18" ht="60">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" ht="60">
       <c r="A124">
         <v>123</v>
       </c>
@@ -14443,13 +14161,10 @@
       </c>
       <c r="P124" s="10"/>
       <c r="Q124" s="10" t="s">
-        <v>2109</v>
-      </c>
-      <c r="R124" t="s">
-        <v>1715</v>
-      </c>
-    </row>
-    <row r="125" spans="1:18" ht="60">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" ht="60">
       <c r="A125">
         <v>124</v>
       </c>
@@ -14499,13 +14214,10 @@
         <v>374</v>
       </c>
       <c r="Q125" s="10" t="s">
-        <v>2110</v>
-      </c>
-      <c r="R125" t="s">
-        <v>1716</v>
-      </c>
-    </row>
-    <row r="126" spans="1:18" ht="60">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="60">
       <c r="A126">
         <v>125</v>
       </c>
@@ -14555,13 +14267,10 @@
         <v>377</v>
       </c>
       <c r="Q126" s="10" t="s">
-        <v>2111</v>
-      </c>
-      <c r="R126" t="s">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="127" spans="1:18" ht="60">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" ht="60">
       <c r="A127">
         <v>126</v>
       </c>
@@ -14611,13 +14320,10 @@
         <v>380</v>
       </c>
       <c r="Q127" s="10" t="s">
-        <v>2112</v>
-      </c>
-      <c r="R127" t="s">
-        <v>1718</v>
-      </c>
-    </row>
-    <row r="128" spans="1:18" ht="60">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" ht="60">
       <c r="A128">
         <v>127</v>
       </c>
@@ -14667,13 +14373,10 @@
         <v>383</v>
       </c>
       <c r="Q128" s="10" t="s">
-        <v>2113</v>
-      </c>
-      <c r="R128" t="s">
-        <v>1719</v>
-      </c>
-    </row>
-    <row r="129" spans="1:18" ht="60">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" ht="60">
       <c r="A129">
         <v>128</v>
       </c>
@@ -14725,11 +14428,8 @@
       <c r="Q129" s="10" t="s">
         <v>386</v>
       </c>
-      <c r="R129" t="s">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="130" spans="1:18" ht="60">
+    </row>
+    <row r="130" spans="1:17" ht="60">
       <c r="A130">
         <v>129</v>
       </c>
@@ -14781,11 +14481,8 @@
       <c r="Q130" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="R130" t="s">
-        <v>1721</v>
-      </c>
-    </row>
-    <row r="131" spans="1:18" ht="60">
+    </row>
+    <row r="131" spans="1:17" ht="60">
       <c r="A131">
         <v>130</v>
       </c>
@@ -14837,11 +14534,8 @@
       <c r="Q131" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="R131" t="s">
-        <v>1722</v>
-      </c>
-    </row>
-    <row r="132" spans="1:18" ht="60">
+    </row>
+    <row r="132" spans="1:17" ht="60">
       <c r="A132">
         <v>131</v>
       </c>
@@ -14893,11 +14587,8 @@
       <c r="Q132" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="R132" t="s">
-        <v>1723</v>
-      </c>
-    </row>
-    <row r="133" spans="1:18" ht="60">
+    </row>
+    <row r="133" spans="1:17" ht="60">
       <c r="A133">
         <v>132</v>
       </c>
@@ -14947,13 +14638,10 @@
         <v>224</v>
       </c>
       <c r="Q133" s="10" t="s">
-        <v>2114</v>
-      </c>
-      <c r="R133" t="s">
-        <v>1724</v>
-      </c>
-    </row>
-    <row r="134" spans="1:18" ht="60">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" ht="60">
       <c r="A134">
         <v>133</v>
       </c>
@@ -15005,11 +14693,8 @@
       <c r="Q134" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="R134" t="s">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="135" spans="1:18" ht="60">
+    </row>
+    <row r="135" spans="1:17" ht="60">
       <c r="A135">
         <v>134</v>
       </c>
@@ -15061,11 +14746,8 @@
       <c r="Q135" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="R135" t="s">
-        <v>1726</v>
-      </c>
-    </row>
-    <row r="136" spans="1:18" ht="60">
+    </row>
+    <row r="136" spans="1:17" ht="60">
       <c r="A136">
         <v>135</v>
       </c>
@@ -15117,11 +14799,8 @@
       <c r="Q136" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="R136" t="s">
-        <v>1727</v>
-      </c>
-    </row>
-    <row r="137" spans="1:18" ht="60">
+    </row>
+    <row r="137" spans="1:17" ht="60">
       <c r="A137">
         <v>136</v>
       </c>
@@ -15173,11 +14852,8 @@
       <c r="Q137" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="R137" t="s">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="138" spans="1:18" ht="60">
+    </row>
+    <row r="138" spans="1:17" ht="60">
       <c r="A138">
         <v>137</v>
       </c>
@@ -15227,11 +14903,8 @@
       <c r="Q138" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="R138" t="s">
-        <v>1729</v>
-      </c>
-    </row>
-    <row r="139" spans="1:18" ht="60">
+    </row>
+    <row r="139" spans="1:17" ht="60">
       <c r="A139">
         <v>138</v>
       </c>
@@ -15283,11 +14956,8 @@
       <c r="Q139" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="R139" t="s">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="140" spans="1:18" ht="60">
+    </row>
+    <row r="140" spans="1:17" ht="60">
       <c r="A140">
         <v>139</v>
       </c>
@@ -15337,13 +15007,10 @@
         <v>374</v>
       </c>
       <c r="Q140" s="10" t="s">
-        <v>2115</v>
-      </c>
-      <c r="R140" t="s">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="141" spans="1:18">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17">
       <c r="A141">
         <v>140</v>
       </c>
@@ -15351,7 +15018,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="D141" t="s">
         <v>18</v>
@@ -15389,7 +15056,7 @@
       <c r="P141" s="10"/>
       <c r="Q141" s="10"/>
     </row>
-    <row r="142" spans="1:18">
+    <row r="142" spans="1:17">
       <c r="A142">
         <v>141</v>
       </c>
@@ -15437,11 +15104,8 @@
       </c>
       <c r="P142" s="10"/>
       <c r="Q142" s="10"/>
-      <c r="R142" t="s">
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="143" spans="1:18" ht="30">
+    </row>
+    <row r="143" spans="1:17" ht="30">
       <c r="A143">
         <v>142</v>
       </c>
@@ -15491,11 +15155,8 @@
         <v>430</v>
       </c>
       <c r="Q143" s="10"/>
-      <c r="R143" t="s">
-        <v>1733</v>
-      </c>
-    </row>
-    <row r="144" spans="1:18">
+    </row>
+    <row r="144" spans="1:17">
       <c r="A144">
         <v>143</v>
       </c>
@@ -15543,11 +15204,8 @@
       </c>
       <c r="P144" s="10"/>
       <c r="Q144" s="10"/>
-      <c r="R144" t="s">
-        <v>1734</v>
-      </c>
-    </row>
-    <row r="145" spans="1:18" ht="60">
+    </row>
+    <row r="145" spans="1:17" ht="60">
       <c r="A145">
         <v>144</v>
       </c>
@@ -15597,13 +15255,10 @@
         <v>435</v>
       </c>
       <c r="Q145" s="10" t="s">
-        <v>2117</v>
-      </c>
-      <c r="R145" t="s">
-        <v>1735</v>
-      </c>
-    </row>
-    <row r="146" spans="1:18" ht="60">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" ht="60">
       <c r="A146">
         <v>145</v>
       </c>
@@ -15653,13 +15308,10 @@
         <v>438</v>
       </c>
       <c r="Q146" s="10" t="s">
-        <v>2118</v>
-      </c>
-      <c r="R146" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="147" spans="1:18" ht="60">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" ht="60">
       <c r="A147">
         <v>146</v>
       </c>
@@ -15707,13 +15359,10 @@
       </c>
       <c r="P147" s="10"/>
       <c r="Q147" s="10" t="s">
-        <v>2119</v>
-      </c>
-      <c r="R147" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="148" spans="1:18" ht="60">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" ht="60">
       <c r="A148">
         <v>147</v>
       </c>
@@ -15763,13 +15412,10 @@
         <v>443</v>
       </c>
       <c r="Q148" s="10" t="s">
-        <v>2120</v>
-      </c>
-      <c r="R148" t="s">
-        <v>1738</v>
-      </c>
-    </row>
-    <row r="149" spans="1:18" ht="60">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" ht="60">
       <c r="A149">
         <v>148</v>
       </c>
@@ -15819,13 +15465,10 @@
         <v>446</v>
       </c>
       <c r="Q149" s="10" t="s">
-        <v>2121</v>
-      </c>
-      <c r="R149" t="s">
-        <v>1739</v>
-      </c>
-    </row>
-    <row r="150" spans="1:18" ht="60">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" ht="60">
       <c r="A150">
         <v>149</v>
       </c>
@@ -15875,13 +15518,10 @@
         <v>138</v>
       </c>
       <c r="Q150" s="10" t="s">
-        <v>2122</v>
-      </c>
-      <c r="R150" t="s">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="151" spans="1:18" ht="60">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" ht="60">
       <c r="A151">
         <v>150</v>
       </c>
@@ -15931,13 +15571,10 @@
         <v>451</v>
       </c>
       <c r="Q151" s="10" t="s">
-        <v>2123</v>
-      </c>
-      <c r="R151" t="s">
-        <v>1741</v>
-      </c>
-    </row>
-    <row r="152" spans="1:18" ht="60">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" ht="60">
       <c r="A152">
         <v>151</v>
       </c>
@@ -15984,16 +15621,13 @@
         <v>17553</v>
       </c>
       <c r="P152" s="10" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="Q152" s="10" t="s">
-        <v>2124</v>
-      </c>
-      <c r="R152" t="s">
-        <v>1742</v>
-      </c>
-    </row>
-    <row r="153" spans="1:18" ht="15">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" ht="15">
       <c r="A153">
         <v>152</v>
       </c>
@@ -16043,11 +15677,8 @@
         <v>456</v>
       </c>
       <c r="Q153" s="10"/>
-      <c r="R153" t="s">
-        <v>1743</v>
-      </c>
-    </row>
-    <row r="154" spans="1:18" ht="15">
+    </row>
+    <row r="154" spans="1:17" ht="15">
       <c r="A154">
         <v>153</v>
       </c>
@@ -16097,11 +15728,8 @@
         <v>459</v>
       </c>
       <c r="Q154" s="10"/>
-      <c r="R154" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="155" spans="1:18" ht="15">
+    </row>
+    <row r="155" spans="1:17" ht="15">
       <c r="A155">
         <v>154</v>
       </c>
@@ -16151,11 +15779,8 @@
         <v>462</v>
       </c>
       <c r="Q155" s="10"/>
-      <c r="R155" t="s">
-        <v>1745</v>
-      </c>
-    </row>
-    <row r="156" spans="1:18" ht="60">
+    </row>
+    <row r="156" spans="1:17" ht="60">
       <c r="A156">
         <v>155</v>
       </c>
@@ -16205,13 +15830,10 @@
         <v>465</v>
       </c>
       <c r="Q156" s="10" t="s">
-        <v>2126</v>
-      </c>
-      <c r="R156" t="s">
-        <v>1746</v>
-      </c>
-    </row>
-    <row r="157" spans="1:18" ht="15">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" ht="15">
       <c r="A157">
         <v>156</v>
       </c>
@@ -16261,11 +15883,8 @@
         <v>304</v>
       </c>
       <c r="Q157" s="10"/>
-      <c r="R157" t="s">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="158" spans="1:18">
+    </row>
+    <row r="158" spans="1:17">
       <c r="A158">
         <v>157</v>
       </c>
@@ -16313,11 +15932,8 @@
       </c>
       <c r="P158" s="10"/>
       <c r="Q158" s="10"/>
-      <c r="R158" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="159" spans="1:18" ht="60">
+    </row>
+    <row r="159" spans="1:17" ht="60">
       <c r="A159">
         <v>158</v>
       </c>
@@ -16367,13 +15983,10 @@
         <v>472</v>
       </c>
       <c r="Q159" s="10" t="s">
-        <v>2127</v>
-      </c>
-      <c r="R159" t="s">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="160" spans="1:18" ht="60">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" ht="60">
       <c r="A160">
         <v>159</v>
       </c>
@@ -16423,13 +16036,10 @@
         <v>475</v>
       </c>
       <c r="Q160" s="10" t="s">
-        <v>2128</v>
-      </c>
-      <c r="R160" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="161" spans="1:18">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17">
       <c r="A161">
         <v>160</v>
       </c>
@@ -16477,11 +16087,8 @@
       </c>
       <c r="P161" s="10"/>
       <c r="Q161" s="10"/>
-      <c r="R161" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="162" spans="1:18" ht="15">
+    </row>
+    <row r="162" spans="1:17" ht="15">
       <c r="A162">
         <v>161</v>
       </c>
@@ -16531,11 +16138,8 @@
         <v>112</v>
       </c>
       <c r="Q162" s="10"/>
-      <c r="R162" t="s">
-        <v>1752</v>
-      </c>
-    </row>
-    <row r="163" spans="1:18" ht="15">
+    </row>
+    <row r="163" spans="1:17" ht="15">
       <c r="A163">
         <v>162</v>
       </c>
@@ -16585,11 +16189,8 @@
         <v>482</v>
       </c>
       <c r="Q163" s="10"/>
-      <c r="R163" t="s">
-        <v>1753</v>
-      </c>
-    </row>
-    <row r="164" spans="1:18" ht="15">
+    </row>
+    <row r="164" spans="1:17" ht="15">
       <c r="A164">
         <v>163</v>
       </c>
@@ -16639,11 +16240,8 @@
         <v>485</v>
       </c>
       <c r="Q164" s="10"/>
-      <c r="R164" t="s">
-        <v>1754</v>
-      </c>
-    </row>
-    <row r="165" spans="1:18">
+    </row>
+    <row r="165" spans="1:17">
       <c r="A165">
         <v>164</v>
       </c>
@@ -16691,11 +16289,8 @@
       </c>
       <c r="P165" s="10"/>
       <c r="Q165" s="10"/>
-      <c r="R165" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="166" spans="1:18">
+    </row>
+    <row r="166" spans="1:17">
       <c r="A166">
         <v>165</v>
       </c>
@@ -16743,11 +16338,8 @@
       </c>
       <c r="P166" s="10"/>
       <c r="Q166" s="10"/>
-      <c r="R166" t="s">
-        <v>1756</v>
-      </c>
-    </row>
-    <row r="167" spans="1:18" ht="15">
+    </row>
+    <row r="167" spans="1:17" ht="15">
       <c r="A167">
         <v>166</v>
       </c>
@@ -16797,11 +16389,8 @@
         <v>492</v>
       </c>
       <c r="Q167" s="10"/>
-      <c r="R167" t="s">
-        <v>1757</v>
-      </c>
-    </row>
-    <row r="168" spans="1:18">
+    </row>
+    <row r="168" spans="1:17">
       <c r="A168">
         <v>167</v>
       </c>
@@ -16849,11 +16438,8 @@
       </c>
       <c r="P168" s="10"/>
       <c r="Q168" s="10"/>
-      <c r="R168" t="s">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="169" spans="1:18" ht="45">
+    </row>
+    <row r="169" spans="1:17" ht="45">
       <c r="A169">
         <v>168</v>
       </c>
@@ -16903,11 +16489,8 @@
         <v>497</v>
       </c>
       <c r="Q169" s="10"/>
-      <c r="R169" t="s">
-        <v>1759</v>
-      </c>
-    </row>
-    <row r="170" spans="1:18">
+    </row>
+    <row r="170" spans="1:17">
       <c r="A170">
         <v>169</v>
       </c>
@@ -16955,11 +16538,8 @@
       </c>
       <c r="P170" s="10"/>
       <c r="Q170" s="10"/>
-      <c r="R170" t="s">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="171" spans="1:18" ht="45">
+    </row>
+    <row r="171" spans="1:17" ht="45">
       <c r="A171">
         <v>170</v>
       </c>
@@ -17009,11 +16589,8 @@
         <v>502</v>
       </c>
       <c r="Q171" s="10"/>
-      <c r="R171" t="s">
-        <v>1761</v>
-      </c>
-    </row>
-    <row r="172" spans="1:18" ht="15">
+    </row>
+    <row r="172" spans="1:17" ht="15">
       <c r="A172">
         <v>171</v>
       </c>
@@ -17063,11 +16640,8 @@
         <v>344</v>
       </c>
       <c r="Q172" s="10"/>
-      <c r="R172" t="s">
-        <v>1762</v>
-      </c>
-    </row>
-    <row r="173" spans="1:18" ht="60">
+    </row>
+    <row r="173" spans="1:17" ht="60">
       <c r="A173">
         <v>172</v>
       </c>
@@ -17119,11 +16693,8 @@
       <c r="Q173" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="R173" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="174" spans="1:18" ht="60">
+    </row>
+    <row r="174" spans="1:17" ht="60">
       <c r="A174">
         <v>173</v>
       </c>
@@ -17175,11 +16746,8 @@
       <c r="Q174" s="10" t="s">
         <v>512</v>
       </c>
-      <c r="R174" t="s">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="175" spans="1:18" ht="60">
+    </row>
+    <row r="175" spans="1:17" ht="60">
       <c r="A175">
         <v>174</v>
       </c>
@@ -17231,11 +16799,8 @@
       <c r="Q175" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="R175" t="s">
-        <v>1765</v>
-      </c>
-    </row>
-    <row r="176" spans="1:18" ht="60">
+    </row>
+    <row r="176" spans="1:17" ht="60">
       <c r="A176">
         <v>175</v>
       </c>
@@ -17287,11 +16852,8 @@
       <c r="Q176" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="R176" t="s">
-        <v>1766</v>
-      </c>
-    </row>
-    <row r="177" spans="1:18" ht="60">
+    </row>
+    <row r="177" spans="1:17" ht="60">
       <c r="A177">
         <v>176</v>
       </c>
@@ -17343,11 +16905,8 @@
       <c r="Q177" s="10" t="s">
         <v>524</v>
       </c>
-      <c r="R177" t="s">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="178" spans="1:18" ht="15">
+    </row>
+    <row r="178" spans="1:17" ht="15">
       <c r="A178">
         <v>177</v>
       </c>
@@ -17397,11 +16956,8 @@
         <v>527</v>
       </c>
       <c r="Q178" s="10"/>
-      <c r="R178" t="s">
-        <v>1768</v>
-      </c>
-    </row>
-    <row r="179" spans="1:18" ht="60">
+    </row>
+    <row r="179" spans="1:17" ht="60">
       <c r="A179">
         <v>178</v>
       </c>
@@ -17451,11 +17007,8 @@
       <c r="Q179" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="R179" t="s">
-        <v>1769</v>
-      </c>
-    </row>
-    <row r="180" spans="1:18" ht="15">
+    </row>
+    <row r="180" spans="1:17" ht="15">
       <c r="A180">
         <v>179</v>
       </c>
@@ -17505,11 +17058,8 @@
         <v>533</v>
       </c>
       <c r="Q180" s="10"/>
-      <c r="R180" t="s">
-        <v>1770</v>
-      </c>
-    </row>
-    <row r="181" spans="1:18" ht="15">
+    </row>
+    <row r="181" spans="1:17" ht="15">
       <c r="A181">
         <v>180</v>
       </c>
@@ -17559,11 +17109,8 @@
         <v>344</v>
       </c>
       <c r="Q181" s="10"/>
-      <c r="R181" t="s">
-        <v>1771</v>
-      </c>
-    </row>
-    <row r="182" spans="1:18" ht="45">
+    </row>
+    <row r="182" spans="1:17" ht="45">
       <c r="A182">
         <v>181</v>
       </c>
@@ -17613,11 +17160,8 @@
         <v>538</v>
       </c>
       <c r="Q182" s="10"/>
-      <c r="R182" t="s">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="183" spans="1:18" ht="60">
+    </row>
+    <row r="183" spans="1:17" ht="60">
       <c r="A183">
         <v>182</v>
       </c>
@@ -17669,11 +17213,8 @@
       <c r="Q183" s="10" t="s">
         <v>542</v>
       </c>
-      <c r="R183" t="s">
-        <v>1773</v>
-      </c>
-    </row>
-    <row r="184" spans="1:18" ht="60">
+    </row>
+    <row r="184" spans="1:17" ht="60">
       <c r="A184">
         <v>183</v>
       </c>
@@ -17725,11 +17266,8 @@
       <c r="Q184" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="R184" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="185" spans="1:18">
+    </row>
+    <row r="185" spans="1:17">
       <c r="A185">
         <v>184</v>
       </c>
@@ -17777,11 +17315,8 @@
       </c>
       <c r="P185" s="10"/>
       <c r="Q185" s="10"/>
-      <c r="R185" t="s">
-        <v>1775</v>
-      </c>
-    </row>
-    <row r="186" spans="1:18">
+    </row>
+    <row r="186" spans="1:17">
       <c r="A186">
         <v>185</v>
       </c>
@@ -17829,11 +17364,8 @@
       </c>
       <c r="P186" s="10"/>
       <c r="Q186" s="10"/>
-      <c r="R186" t="s">
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="187" spans="1:18" ht="60">
+    </row>
+    <row r="187" spans="1:17" ht="60">
       <c r="A187">
         <v>186</v>
       </c>
@@ -17883,13 +17415,10 @@
         <v>553</v>
       </c>
       <c r="Q187" s="10" t="s">
-        <v>2129</v>
-      </c>
-      <c r="R187" t="s">
-        <v>1777</v>
-      </c>
-    </row>
-    <row r="188" spans="1:18" ht="60">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" ht="60">
       <c r="A188">
         <v>187</v>
       </c>
@@ -17937,13 +17466,10 @@
       </c>
       <c r="P188" s="10"/>
       <c r="Q188" s="10" t="s">
-        <v>2130</v>
-      </c>
-      <c r="R188" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="189" spans="1:18" ht="15">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" ht="15">
       <c r="A189">
         <v>188</v>
       </c>
@@ -17993,11 +17519,8 @@
         <v>389</v>
       </c>
       <c r="Q189" s="10"/>
-      <c r="R189" t="s">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="190" spans="1:18" ht="60">
+    </row>
+    <row r="190" spans="1:17" ht="60">
       <c r="A190">
         <v>189</v>
       </c>
@@ -18047,13 +17570,10 @@
         <v>560</v>
       </c>
       <c r="Q190" s="10" t="s">
-        <v>2131</v>
-      </c>
-      <c r="R190" t="s">
-        <v>1780</v>
-      </c>
-    </row>
-    <row r="191" spans="1:18">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17">
       <c r="A191">
         <v>190</v>
       </c>
@@ -18101,11 +17621,8 @@
       </c>
       <c r="P191" s="10"/>
       <c r="Q191" s="10"/>
-      <c r="R191" t="s">
-        <v>1781</v>
-      </c>
-    </row>
-    <row r="192" spans="1:18" ht="15">
+    </row>
+    <row r="192" spans="1:17" ht="15">
       <c r="A192">
         <v>191</v>
       </c>
@@ -18155,11 +17672,8 @@
         <v>565</v>
       </c>
       <c r="Q192" s="10"/>
-      <c r="R192" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="193" spans="1:18" ht="30">
+    </row>
+    <row r="193" spans="1:17" ht="30">
       <c r="A193">
         <v>192</v>
       </c>
@@ -18206,11 +17720,11 @@
         <v>0</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="Q193" s="10"/>
     </row>
-    <row r="194" spans="1:18" ht="60">
+    <row r="194" spans="1:17" ht="60">
       <c r="A194">
         <v>193</v>
       </c>
@@ -18260,13 +17774,10 @@
         <v>571</v>
       </c>
       <c r="Q194" s="10" t="s">
-        <v>2133</v>
-      </c>
-      <c r="R194" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="195" spans="1:18" ht="60">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" ht="60">
       <c r="A195">
         <v>194</v>
       </c>
@@ -18316,13 +17827,10 @@
         <v>574</v>
       </c>
       <c r="Q195" s="10" t="s">
-        <v>2134</v>
-      </c>
-      <c r="R195" t="s">
-        <v>1784</v>
-      </c>
-    </row>
-    <row r="196" spans="1:18" ht="60">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" ht="60">
       <c r="A196">
         <v>195</v>
       </c>
@@ -18372,13 +17880,10 @@
         <v>577</v>
       </c>
       <c r="Q196" s="10" t="s">
-        <v>2135</v>
-      </c>
-      <c r="R196" t="s">
-        <v>1785</v>
-      </c>
-    </row>
-    <row r="197" spans="1:18" ht="60">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" ht="60">
       <c r="A197">
         <v>196</v>
       </c>
@@ -18428,13 +17933,10 @@
         <v>580</v>
       </c>
       <c r="Q197" s="10" t="s">
-        <v>2136</v>
-      </c>
-      <c r="R197" t="s">
-        <v>1786</v>
-      </c>
-    </row>
-    <row r="198" spans="1:18" ht="60">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" ht="60">
       <c r="A198">
         <v>197</v>
       </c>
@@ -18484,13 +17986,10 @@
         <v>583</v>
       </c>
       <c r="Q198" s="10" t="s">
-        <v>2137</v>
-      </c>
-      <c r="R198" t="s">
-        <v>1787</v>
-      </c>
-    </row>
-    <row r="199" spans="1:18" ht="60">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" ht="60">
       <c r="A199">
         <v>198</v>
       </c>
@@ -18540,13 +18039,10 @@
         <v>586</v>
       </c>
       <c r="Q199" s="10" t="s">
-        <v>2138</v>
-      </c>
-      <c r="R199" t="s">
-        <v>1788</v>
-      </c>
-    </row>
-    <row r="200" spans="1:18" ht="60">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" ht="60">
       <c r="A200">
         <v>199</v>
       </c>
@@ -18596,13 +18092,10 @@
         <v>589</v>
       </c>
       <c r="Q200" s="10" t="s">
-        <v>2139</v>
-      </c>
-      <c r="R200" t="s">
-        <v>1789</v>
-      </c>
-    </row>
-    <row r="201" spans="1:18" ht="60">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" ht="60">
       <c r="A201">
         <v>200</v>
       </c>
@@ -18654,11 +18147,8 @@
       <c r="Q201" s="10" t="s">
         <v>593</v>
       </c>
-      <c r="R201" t="s">
-        <v>1790</v>
-      </c>
-    </row>
-    <row r="202" spans="1:18" ht="60">
+    </row>
+    <row r="202" spans="1:17" ht="60">
       <c r="A202">
         <v>201</v>
       </c>
@@ -18710,11 +18200,8 @@
       <c r="Q202" s="10" t="s">
         <v>597</v>
       </c>
-      <c r="R202" t="s">
-        <v>1791</v>
-      </c>
-    </row>
-    <row r="203" spans="1:18" ht="60">
+    </row>
+    <row r="203" spans="1:17" ht="60">
       <c r="A203">
         <v>202</v>
       </c>
@@ -18766,11 +18253,8 @@
       <c r="Q203" s="10" t="s">
         <v>601</v>
       </c>
-      <c r="R203" t="s">
-        <v>1792</v>
-      </c>
-    </row>
-    <row r="204" spans="1:18" ht="60">
+    </row>
+    <row r="204" spans="1:17" ht="60">
       <c r="A204">
         <v>203</v>
       </c>
@@ -18822,11 +18306,8 @@
       <c r="Q204" s="10" t="s">
         <v>605</v>
       </c>
-      <c r="R204" t="s">
-        <v>1793</v>
-      </c>
-    </row>
-    <row r="205" spans="1:18">
+    </row>
+    <row r="205" spans="1:17">
       <c r="A205">
         <v>204</v>
       </c>
@@ -18874,11 +18355,8 @@
       </c>
       <c r="P205" s="10"/>
       <c r="Q205" s="10"/>
-      <c r="R205" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="206" spans="1:18">
+    </row>
+    <row r="206" spans="1:17">
       <c r="A206">
         <v>205</v>
       </c>
@@ -18926,11 +18404,8 @@
       </c>
       <c r="P206" s="10"/>
       <c r="Q206" s="10"/>
-      <c r="R206" t="s">
-        <v>1795</v>
-      </c>
-    </row>
-    <row r="207" spans="1:18">
+    </row>
+    <row r="207" spans="1:17">
       <c r="A207">
         <v>206</v>
       </c>
@@ -18978,11 +18453,8 @@
       </c>
       <c r="P207" s="10"/>
       <c r="Q207" s="10"/>
-      <c r="R207" t="s">
-        <v>1796</v>
-      </c>
-    </row>
-    <row r="208" spans="1:18" ht="60">
+    </row>
+    <row r="208" spans="1:17" ht="60">
       <c r="A208">
         <v>207</v>
       </c>
@@ -19034,11 +18506,8 @@
       <c r="Q208" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="R208" t="s">
-        <v>1797</v>
-      </c>
-    </row>
-    <row r="209" spans="1:18" ht="60">
+    </row>
+    <row r="209" spans="1:17" ht="60">
       <c r="A209">
         <v>208</v>
       </c>
@@ -19090,11 +18559,8 @@
       <c r="Q209" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="R209" t="s">
-        <v>1798</v>
-      </c>
-    </row>
-    <row r="210" spans="1:18" ht="15">
+    </row>
+    <row r="210" spans="1:17" ht="15">
       <c r="A210">
         <v>209</v>
       </c>
@@ -19144,11 +18610,8 @@
         <v>224</v>
       </c>
       <c r="Q210" s="10"/>
-      <c r="R210" t="s">
-        <v>1799</v>
-      </c>
-    </row>
-    <row r="211" spans="1:18">
+    </row>
+    <row r="211" spans="1:17">
       <c r="A211">
         <v>210</v>
       </c>
@@ -19196,11 +18659,8 @@
       </c>
       <c r="P211" s="10"/>
       <c r="Q211" s="10"/>
-      <c r="R211" t="s">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="212" spans="1:18">
+    </row>
+    <row r="212" spans="1:17">
       <c r="A212">
         <v>211</v>
       </c>
@@ -19248,11 +18708,8 @@
       </c>
       <c r="P212" s="10"/>
       <c r="Q212" s="10"/>
-      <c r="R212" t="s">
-        <v>1801</v>
-      </c>
-    </row>
-    <row r="213" spans="1:18" ht="60">
+    </row>
+    <row r="213" spans="1:17" ht="60">
       <c r="A213">
         <v>212</v>
       </c>
@@ -19304,11 +18761,8 @@
       <c r="Q213" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="R213" t="s">
-        <v>1802</v>
-      </c>
-    </row>
-    <row r="214" spans="1:18" ht="60">
+    </row>
+    <row r="214" spans="1:17" ht="60">
       <c r="A214">
         <v>213</v>
       </c>
@@ -19360,11 +18814,8 @@
       <c r="Q214" s="10" t="s">
         <v>633</v>
       </c>
-      <c r="R214" t="s">
-        <v>1803</v>
-      </c>
-    </row>
-    <row r="215" spans="1:18">
+    </row>
+    <row r="215" spans="1:17">
       <c r="A215">
         <v>214</v>
       </c>
@@ -19412,11 +18863,8 @@
       </c>
       <c r="P215" s="10"/>
       <c r="Q215" s="10"/>
-      <c r="R215" t="s">
-        <v>1804</v>
-      </c>
-    </row>
-    <row r="216" spans="1:18" ht="45">
+    </row>
+    <row r="216" spans="1:17" ht="45">
       <c r="A216">
         <v>215</v>
       </c>
@@ -19463,11 +18911,11 @@
         <v>0</v>
       </c>
       <c r="P216" s="10" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="Q216" s="10"/>
     </row>
-    <row r="217" spans="1:18" ht="45">
+    <row r="217" spans="1:17" ht="45">
       <c r="A217">
         <v>216</v>
       </c>
@@ -19514,11 +18962,11 @@
         <v>0</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="Q217" s="10"/>
     </row>
-    <row r="218" spans="1:18" ht="60">
+    <row r="218" spans="1:17" ht="60">
       <c r="A218">
         <v>217</v>
       </c>
@@ -19570,11 +19018,8 @@
       <c r="Q218" s="10" t="s">
         <v>643</v>
       </c>
-      <c r="R218" t="s">
-        <v>1805</v>
-      </c>
-    </row>
-    <row r="219" spans="1:18" ht="75">
+    </row>
+    <row r="219" spans="1:17" ht="75">
       <c r="A219">
         <v>218</v>
       </c>
@@ -19624,13 +19069,10 @@
         <v>646</v>
       </c>
       <c r="Q219" s="10" t="s">
-        <v>2141</v>
-      </c>
-      <c r="R219" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="220" spans="1:18" ht="60">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" ht="60">
       <c r="A220">
         <v>219</v>
       </c>
@@ -19680,13 +19122,10 @@
         <v>649</v>
       </c>
       <c r="Q220" s="10" t="s">
-        <v>2142</v>
-      </c>
-      <c r="R220" t="s">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="221" spans="1:18">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17">
       <c r="A221">
         <v>220</v>
       </c>
@@ -19734,11 +19173,8 @@
       </c>
       <c r="P221" s="10"/>
       <c r="Q221" s="10"/>
-      <c r="R221" t="s">
-        <v>1808</v>
-      </c>
-    </row>
-    <row r="222" spans="1:18">
+    </row>
+    <row r="222" spans="1:17">
       <c r="A222">
         <v>221</v>
       </c>
@@ -19786,11 +19222,8 @@
       </c>
       <c r="P222" s="10"/>
       <c r="Q222" s="10"/>
-      <c r="R222" t="s">
-        <v>1809</v>
-      </c>
-    </row>
-    <row r="223" spans="1:18" ht="15">
+    </row>
+    <row r="223" spans="1:17" ht="15">
       <c r="A223">
         <v>222</v>
       </c>
@@ -19840,11 +19273,8 @@
         <v>656</v>
       </c>
       <c r="Q223" s="10"/>
-      <c r="R223" t="s">
-        <v>1810</v>
-      </c>
-    </row>
-    <row r="224" spans="1:18" ht="15">
+    </row>
+    <row r="224" spans="1:17" ht="15">
       <c r="A224">
         <v>223</v>
       </c>
@@ -19894,11 +19324,8 @@
         <v>224</v>
       </c>
       <c r="Q224" s="10"/>
-      <c r="R224" t="s">
-        <v>1811</v>
-      </c>
-    </row>
-    <row r="225" spans="1:18">
+    </row>
+    <row r="225" spans="1:17">
       <c r="A225">
         <v>224</v>
       </c>
@@ -19946,11 +19373,8 @@
       </c>
       <c r="P225" s="10"/>
       <c r="Q225" s="10"/>
-      <c r="R225" t="s">
-        <v>1812</v>
-      </c>
-    </row>
-    <row r="226" spans="1:18">
+    </row>
+    <row r="226" spans="1:17">
       <c r="A226">
         <v>225</v>
       </c>
@@ -19998,11 +19422,8 @@
       </c>
       <c r="P226" s="10"/>
       <c r="Q226" s="10"/>
-      <c r="R226" t="s">
-        <v>1813</v>
-      </c>
-    </row>
-    <row r="227" spans="1:18" ht="15">
+    </row>
+    <row r="227" spans="1:17" ht="15">
       <c r="A227">
         <v>226</v>
       </c>
@@ -20052,11 +19473,8 @@
         <v>665</v>
       </c>
       <c r="Q227" s="10"/>
-      <c r="R227" t="s">
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="228" spans="1:18">
+    </row>
+    <row r="228" spans="1:17">
       <c r="A228">
         <v>227</v>
       </c>
@@ -20104,11 +19522,8 @@
       </c>
       <c r="P228" s="10"/>
       <c r="Q228" s="10"/>
-      <c r="R228" t="s">
-        <v>1815</v>
-      </c>
-    </row>
-    <row r="229" spans="1:18" ht="15">
+    </row>
+    <row r="229" spans="1:17" ht="15">
       <c r="A229">
         <v>228</v>
       </c>
@@ -20158,11 +19573,8 @@
         <v>670</v>
       </c>
       <c r="Q229" s="10"/>
-      <c r="R229" t="s">
-        <v>1816</v>
-      </c>
-    </row>
-    <row r="230" spans="1:18" ht="15">
+    </row>
+    <row r="230" spans="1:17" ht="15">
       <c r="A230">
         <v>229</v>
       </c>
@@ -20212,11 +19624,8 @@
         <v>673</v>
       </c>
       <c r="Q230" s="10"/>
-      <c r="R230" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="231" spans="1:18" ht="15">
+    </row>
+    <row r="231" spans="1:17" ht="15">
       <c r="A231">
         <v>230</v>
       </c>
@@ -20266,11 +19675,8 @@
         <v>344</v>
       </c>
       <c r="Q231" s="10"/>
-      <c r="R231" t="s">
-        <v>1818</v>
-      </c>
-    </row>
-    <row r="232" spans="1:18" ht="30">
+    </row>
+    <row r="232" spans="1:17" ht="30">
       <c r="A232">
         <v>231</v>
       </c>
@@ -20317,11 +19723,11 @@
         <v>0</v>
       </c>
       <c r="P232" s="10" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="Q232" s="10"/>
     </row>
-    <row r="233" spans="1:18">
+    <row r="233" spans="1:17">
       <c r="A233">
         <v>232</v>
       </c>
@@ -20369,11 +19775,8 @@
       </c>
       <c r="P233" s="10"/>
       <c r="Q233" s="10"/>
-      <c r="R233" t="s">
-        <v>1819</v>
-      </c>
-    </row>
-    <row r="234" spans="1:18" ht="15">
+    </row>
+    <row r="234" spans="1:17" ht="15">
       <c r="A234">
         <v>233</v>
       </c>
@@ -20423,11 +19826,8 @@
         <v>682</v>
       </c>
       <c r="Q234" s="10"/>
-      <c r="R234" t="s">
-        <v>1820</v>
-      </c>
-    </row>
-    <row r="235" spans="1:18">
+    </row>
+    <row r="235" spans="1:17">
       <c r="A235">
         <v>234</v>
       </c>
@@ -20475,11 +19875,8 @@
       </c>
       <c r="P235" s="10"/>
       <c r="Q235" s="10"/>
-      <c r="R235" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="236" spans="1:18" ht="60">
+    </row>
+    <row r="236" spans="1:17" ht="60">
       <c r="A236">
         <v>235</v>
       </c>
@@ -20529,13 +19926,10 @@
         <v>687</v>
       </c>
       <c r="Q236" s="10" t="s">
-        <v>2143</v>
-      </c>
-      <c r="R236" t="s">
-        <v>1822</v>
-      </c>
-    </row>
-    <row r="237" spans="1:18">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="237" spans="1:17">
       <c r="A237">
         <v>236</v>
       </c>
@@ -20583,11 +19977,8 @@
       </c>
       <c r="P237" s="10"/>
       <c r="Q237" s="10"/>
-      <c r="R237" t="s">
-        <v>1823</v>
-      </c>
-    </row>
-    <row r="238" spans="1:18">
+    </row>
+    <row r="238" spans="1:17">
       <c r="A238">
         <v>237</v>
       </c>
@@ -20635,11 +20026,8 @@
       </c>
       <c r="P238" s="10"/>
       <c r="Q238" s="10"/>
-      <c r="R238" t="s">
-        <v>1824</v>
-      </c>
-    </row>
-    <row r="239" spans="1:18" ht="15">
+    </row>
+    <row r="239" spans="1:17" ht="15">
       <c r="A239">
         <v>238</v>
       </c>
@@ -20689,11 +20077,8 @@
         <v>694</v>
       </c>
       <c r="Q239" s="10"/>
-      <c r="R239" t="s">
-        <v>1825</v>
-      </c>
-    </row>
-    <row r="240" spans="1:18">
+    </row>
+    <row r="240" spans="1:17">
       <c r="A240">
         <v>239</v>
       </c>
@@ -20719,7 +20104,7 @@
       <c r="P240" s="10"/>
       <c r="Q240" s="10"/>
     </row>
-    <row r="241" spans="1:18" ht="60">
+    <row r="241" spans="1:17" ht="60">
       <c r="A241">
         <v>240</v>
       </c>
@@ -20769,13 +20154,10 @@
         <v>699</v>
       </c>
       <c r="Q241" s="10" t="s">
-        <v>2144</v>
-      </c>
-      <c r="R241" t="s">
-        <v>1826</v>
-      </c>
-    </row>
-    <row r="242" spans="1:18" ht="60">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="242" spans="1:17" ht="60">
       <c r="A242">
         <v>241</v>
       </c>
@@ -20825,13 +20207,10 @@
         <v>702</v>
       </c>
       <c r="Q242" s="10" t="s">
-        <v>2145</v>
-      </c>
-      <c r="R242" t="s">
-        <v>1827</v>
-      </c>
-    </row>
-    <row r="243" spans="1:18" ht="15">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="243" spans="1:17" ht="15">
       <c r="A243">
         <v>242</v>
       </c>
@@ -20881,11 +20260,8 @@
         <v>389</v>
       </c>
       <c r="Q243" s="10"/>
-      <c r="R243" t="s">
-        <v>1828</v>
-      </c>
-    </row>
-    <row r="244" spans="1:18">
+    </row>
+    <row r="244" spans="1:17">
       <c r="A244">
         <v>243</v>
       </c>
@@ -20933,11 +20309,8 @@
       </c>
       <c r="P244" s="10"/>
       <c r="Q244" s="10"/>
-      <c r="R244" t="s">
-        <v>1829</v>
-      </c>
-    </row>
-    <row r="245" spans="1:18">
+    </row>
+    <row r="245" spans="1:17">
       <c r="A245">
         <v>244</v>
       </c>
@@ -20985,11 +20358,8 @@
       </c>
       <c r="P245" s="10"/>
       <c r="Q245" s="10"/>
-      <c r="R245" t="s">
-        <v>1830</v>
-      </c>
-    </row>
-    <row r="246" spans="1:18">
+    </row>
+    <row r="246" spans="1:17">
       <c r="A246">
         <v>245</v>
       </c>
@@ -21037,11 +20407,8 @@
       </c>
       <c r="P246" s="10"/>
       <c r="Q246" s="10"/>
-      <c r="R246" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="247" spans="1:18" ht="60">
+    </row>
+    <row r="247" spans="1:17" ht="60">
       <c r="A247">
         <v>246</v>
       </c>
@@ -21091,13 +20458,10 @@
         <v>714</v>
       </c>
       <c r="Q247" s="10" t="s">
-        <v>2146</v>
-      </c>
-      <c r="R247" t="s">
-        <v>1832</v>
-      </c>
-    </row>
-    <row r="248" spans="1:18" ht="60">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="248" spans="1:17" ht="60">
       <c r="A248">
         <v>247</v>
       </c>
@@ -21147,13 +20511,10 @@
         <v>717</v>
       </c>
       <c r="Q248" s="10" t="s">
-        <v>2147</v>
-      </c>
-      <c r="R248" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="249" spans="1:18" ht="60">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="249" spans="1:17" ht="60">
       <c r="A249">
         <v>248</v>
       </c>
@@ -21203,13 +20564,10 @@
         <v>720</v>
       </c>
       <c r="Q249" s="10" t="s">
-        <v>2148</v>
-      </c>
-      <c r="R249" t="s">
-        <v>1834</v>
-      </c>
-    </row>
-    <row r="250" spans="1:18" ht="60">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="250" spans="1:17" ht="60">
       <c r="A250">
         <v>249</v>
       </c>
@@ -21259,13 +20617,10 @@
         <v>723</v>
       </c>
       <c r="Q250" s="10" t="s">
-        <v>2149</v>
-      </c>
-      <c r="R250" t="s">
-        <v>1835</v>
-      </c>
-    </row>
-    <row r="251" spans="1:18" ht="60">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="251" spans="1:17" ht="60">
       <c r="A251">
         <v>250</v>
       </c>
@@ -21315,13 +20670,10 @@
         <v>726</v>
       </c>
       <c r="Q251" s="10" t="s">
-        <v>2150</v>
-      </c>
-      <c r="R251" t="s">
-        <v>1836</v>
-      </c>
-    </row>
-    <row r="252" spans="1:18" ht="60">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="252" spans="1:17" ht="60">
       <c r="A252">
         <v>251</v>
       </c>
@@ -21371,13 +20723,10 @@
         <v>729</v>
       </c>
       <c r="Q252" s="10" t="s">
-        <v>2151</v>
-      </c>
-      <c r="R252" t="s">
-        <v>1837</v>
-      </c>
-    </row>
-    <row r="253" spans="1:18" ht="60">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="253" spans="1:17" ht="60">
       <c r="A253">
         <v>252</v>
       </c>
@@ -21427,13 +20776,10 @@
         <v>732</v>
       </c>
       <c r="Q253" s="10" t="s">
-        <v>2152</v>
-      </c>
-      <c r="R253" t="s">
-        <v>1838</v>
-      </c>
-    </row>
-    <row r="254" spans="1:18" ht="60">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="254" spans="1:17" ht="60">
       <c r="A254">
         <v>253</v>
       </c>
@@ -21480,16 +20826,13 @@
         <v>23700</v>
       </c>
       <c r="P254" s="10" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="Q254" s="10" t="s">
-        <v>2153</v>
-      </c>
-      <c r="R254" t="s">
-        <v>1839</v>
-      </c>
-    </row>
-    <row r="255" spans="1:18" ht="60">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="255" spans="1:17" ht="60">
       <c r="A255">
         <v>254</v>
       </c>
@@ -21539,13 +20882,10 @@
         <v>737</v>
       </c>
       <c r="Q255" s="10" t="s">
-        <v>2155</v>
-      </c>
-      <c r="R255" t="s">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="256" spans="1:18">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="256" spans="1:17">
       <c r="A256">
         <v>255</v>
       </c>
@@ -21593,11 +20933,8 @@
       </c>
       <c r="P256" s="10"/>
       <c r="Q256" s="10"/>
-      <c r="R256" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="257" spans="1:18" ht="60">
+    </row>
+    <row r="257" spans="1:17" ht="60">
       <c r="A257">
         <v>256</v>
       </c>
@@ -21649,11 +20986,8 @@
       <c r="Q257" s="10" t="s">
         <v>743</v>
       </c>
-      <c r="R257" t="s">
-        <v>1842</v>
-      </c>
-    </row>
-    <row r="258" spans="1:18" ht="30">
+    </row>
+    <row r="258" spans="1:17" ht="30">
       <c r="A258">
         <v>257</v>
       </c>
@@ -21700,11 +21034,11 @@
         <v>0</v>
       </c>
       <c r="P258" s="10" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="Q258" s="10"/>
     </row>
-    <row r="259" spans="1:18" ht="60">
+    <row r="259" spans="1:17" ht="60">
       <c r="A259">
         <v>258</v>
       </c>
@@ -21754,13 +21088,10 @@
         <v>748</v>
       </c>
       <c r="Q259" s="10" t="s">
-        <v>2156</v>
-      </c>
-      <c r="R259" t="s">
-        <v>1843</v>
-      </c>
-    </row>
-    <row r="260" spans="1:18" ht="60">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="260" spans="1:17" ht="60">
       <c r="A260">
         <v>259</v>
       </c>
@@ -21812,11 +21143,8 @@
       <c r="Q260" s="10" t="s">
         <v>752</v>
       </c>
-      <c r="R260" t="s">
-        <v>1844</v>
-      </c>
-    </row>
-    <row r="261" spans="1:18" ht="60">
+    </row>
+    <row r="261" spans="1:17" ht="60">
       <c r="A261">
         <v>260</v>
       </c>
@@ -21868,11 +21196,8 @@
       <c r="Q261" s="10" t="s">
         <v>756</v>
       </c>
-      <c r="R261" t="s">
-        <v>1845</v>
-      </c>
-    </row>
-    <row r="262" spans="1:18" ht="60">
+    </row>
+    <row r="262" spans="1:17" ht="60">
       <c r="A262">
         <v>261</v>
       </c>
@@ -21924,11 +21249,8 @@
       <c r="Q262" s="10" t="s">
         <v>760</v>
       </c>
-      <c r="R262" t="s">
-        <v>1846</v>
-      </c>
-    </row>
-    <row r="263" spans="1:18" ht="15">
+    </row>
+    <row r="263" spans="1:17" ht="15">
       <c r="A263">
         <v>262</v>
       </c>
@@ -21978,11 +21300,8 @@
         <v>456</v>
       </c>
       <c r="Q263" s="10"/>
-      <c r="R263" t="s">
-        <v>1847</v>
-      </c>
-    </row>
-    <row r="264" spans="1:18" ht="15">
+    </row>
+    <row r="264" spans="1:17" ht="15">
       <c r="A264">
         <v>263</v>
       </c>
@@ -22032,11 +21351,8 @@
         <v>765</v>
       </c>
       <c r="Q264" s="10"/>
-      <c r="R264" t="s">
-        <v>1848</v>
-      </c>
-    </row>
-    <row r="265" spans="1:18" ht="60">
+    </row>
+    <row r="265" spans="1:17" ht="60">
       <c r="A265">
         <v>264</v>
       </c>
@@ -22086,11 +21402,8 @@
         <v>768</v>
       </c>
       <c r="Q265" s="10"/>
-      <c r="R265" t="s">
-        <v>1849</v>
-      </c>
-    </row>
-    <row r="266" spans="1:18" ht="60">
+    </row>
+    <row r="266" spans="1:17" ht="60">
       <c r="A266">
         <v>265</v>
       </c>
@@ -22140,11 +21453,8 @@
         <v>768</v>
       </c>
       <c r="Q266" s="10"/>
-      <c r="R266" t="s">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="267" spans="1:18">
+    </row>
+    <row r="267" spans="1:17">
       <c r="A267">
         <v>266</v>
       </c>
@@ -22192,11 +21502,8 @@
       </c>
       <c r="P267" s="10"/>
       <c r="Q267" s="10"/>
-      <c r="R267" t="s">
-        <v>1851</v>
-      </c>
-    </row>
-    <row r="268" spans="1:18" ht="60">
+    </row>
+    <row r="268" spans="1:17" ht="60">
       <c r="A268">
         <v>267</v>
       </c>
@@ -22248,11 +21555,8 @@
       <c r="Q268" s="10" t="s">
         <v>776</v>
       </c>
-      <c r="R268" t="s">
-        <v>1852</v>
-      </c>
-    </row>
-    <row r="269" spans="1:18" ht="60">
+    </row>
+    <row r="269" spans="1:17" ht="60">
       <c r="A269">
         <v>268</v>
       </c>
@@ -22304,11 +21608,8 @@
       <c r="Q269" s="10" t="s">
         <v>781</v>
       </c>
-      <c r="R269" t="s">
-        <v>1853</v>
-      </c>
-    </row>
-    <row r="270" spans="1:18" ht="60">
+    </row>
+    <row r="270" spans="1:17" ht="60">
       <c r="A270">
         <v>269</v>
       </c>
@@ -22360,11 +21661,8 @@
       <c r="Q270" s="10" t="s">
         <v>785</v>
       </c>
-      <c r="R270" t="s">
-        <v>1854</v>
-      </c>
-    </row>
-    <row r="271" spans="1:18" ht="30">
+    </row>
+    <row r="271" spans="1:17" ht="30">
       <c r="A271">
         <v>270</v>
       </c>
@@ -22414,11 +21712,8 @@
         <v>788</v>
       </c>
       <c r="Q271" s="10"/>
-      <c r="R271" t="s">
-        <v>1855</v>
-      </c>
-    </row>
-    <row r="272" spans="1:18" ht="60">
+    </row>
+    <row r="272" spans="1:17" ht="60">
       <c r="A272">
         <v>271</v>
       </c>
@@ -22470,11 +21765,8 @@
       <c r="Q272" s="10" t="s">
         <v>792</v>
       </c>
-      <c r="R272" t="s">
-        <v>1856</v>
-      </c>
-    </row>
-    <row r="273" spans="1:18" ht="60">
+    </row>
+    <row r="273" spans="1:17" ht="60">
       <c r="A273">
         <v>272</v>
       </c>
@@ -22526,11 +21818,8 @@
       <c r="Q273" s="10" t="s">
         <v>796</v>
       </c>
-      <c r="R273" t="s">
-        <v>1857</v>
-      </c>
-    </row>
-    <row r="274" spans="1:18" ht="60">
+    </row>
+    <row r="274" spans="1:17" ht="60">
       <c r="A274">
         <v>273</v>
       </c>
@@ -22582,11 +21871,8 @@
       <c r="Q274" s="10" t="s">
         <v>801</v>
       </c>
-      <c r="R274" t="s">
-        <v>1858</v>
-      </c>
-    </row>
-    <row r="275" spans="1:18" ht="30">
+    </row>
+    <row r="275" spans="1:17" ht="30">
       <c r="A275">
         <v>274</v>
       </c>
@@ -22636,11 +21922,8 @@
         <v>804</v>
       </c>
       <c r="Q275" s="10"/>
-      <c r="R275" t="s">
-        <v>1859</v>
-      </c>
-    </row>
-    <row r="276" spans="1:18" ht="60">
+    </row>
+    <row r="276" spans="1:17" ht="60">
       <c r="A276">
         <v>275</v>
       </c>
@@ -22692,11 +21975,8 @@
       <c r="Q276" s="10" t="s">
         <v>808</v>
       </c>
-      <c r="R276" t="s">
-        <v>1860</v>
-      </c>
-    </row>
-    <row r="277" spans="1:18" ht="75">
+    </row>
+    <row r="277" spans="1:17" ht="75">
       <c r="A277">
         <v>276</v>
       </c>
@@ -22748,11 +22028,8 @@
       <c r="Q277" s="10" t="s">
         <v>812</v>
       </c>
-      <c r="R277" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="278" spans="1:18" ht="75">
+    </row>
+    <row r="278" spans="1:17" ht="75">
       <c r="A278">
         <v>277</v>
       </c>
@@ -22804,11 +22081,8 @@
       <c r="Q278" s="10" t="s">
         <v>816</v>
       </c>
-      <c r="R278" t="s">
-        <v>1862</v>
-      </c>
-    </row>
-    <row r="279" spans="1:18" ht="60">
+    </row>
+    <row r="279" spans="1:17" ht="60">
       <c r="A279">
         <v>278</v>
       </c>
@@ -22860,11 +22134,8 @@
       <c r="Q279" s="10" t="s">
         <v>820</v>
       </c>
-      <c r="R279" t="s">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="280" spans="1:18" ht="15">
+    </row>
+    <row r="280" spans="1:17" ht="15">
       <c r="A280">
         <v>279</v>
       </c>
@@ -22914,11 +22185,8 @@
         <v>389</v>
       </c>
       <c r="Q280" s="10"/>
-      <c r="R280" t="s">
-        <v>1864</v>
-      </c>
-    </row>
-    <row r="281" spans="1:18" ht="15">
+    </row>
+    <row r="281" spans="1:17" ht="15">
       <c r="A281">
         <v>280</v>
       </c>
@@ -22968,11 +22236,8 @@
         <v>138</v>
       </c>
       <c r="Q281" s="10"/>
-      <c r="R281" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="282" spans="1:18" ht="60">
+    </row>
+    <row r="282" spans="1:17" ht="60">
       <c r="A282">
         <v>281</v>
       </c>
@@ -23024,11 +22289,8 @@
       <c r="Q282" s="10" t="s">
         <v>827</v>
       </c>
-      <c r="R282" t="s">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="283" spans="1:18" ht="60">
+    </row>
+    <row r="283" spans="1:17" ht="60">
       <c r="A283">
         <v>282</v>
       </c>
@@ -23080,11 +22342,8 @@
       <c r="Q283" s="10" t="s">
         <v>831</v>
       </c>
-      <c r="R283" t="s">
-        <v>1867</v>
-      </c>
-    </row>
-    <row r="284" spans="1:18" ht="60">
+    </row>
+    <row r="284" spans="1:17" ht="60">
       <c r="A284">
         <v>283</v>
       </c>
@@ -23134,11 +22393,8 @@
         <v>834</v>
       </c>
       <c r="Q284" s="10"/>
-      <c r="R284" t="s">
-        <v>1868</v>
-      </c>
-    </row>
-    <row r="285" spans="1:18" ht="15">
+    </row>
+    <row r="285" spans="1:17" ht="15">
       <c r="A285">
         <v>284</v>
       </c>
@@ -23188,11 +22444,8 @@
         <v>196</v>
       </c>
       <c r="Q285" s="10"/>
-      <c r="R285" t="s">
-        <v>1869</v>
-      </c>
-    </row>
-    <row r="286" spans="1:18" ht="60">
+    </row>
+    <row r="286" spans="1:17" ht="60">
       <c r="A286">
         <v>285</v>
       </c>
@@ -23244,11 +22497,8 @@
       <c r="Q286" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="R286" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="287" spans="1:18" ht="60">
+    </row>
+    <row r="287" spans="1:17" ht="60">
       <c r="A287">
         <v>286</v>
       </c>
@@ -23300,11 +22550,8 @@
       <c r="Q287" s="10" t="s">
         <v>844</v>
       </c>
-      <c r="R287" t="s">
-        <v>1871</v>
-      </c>
-    </row>
-    <row r="288" spans="1:18" ht="30">
+    </row>
+    <row r="288" spans="1:17" ht="30">
       <c r="A288">
         <v>287</v>
       </c>
@@ -23354,11 +22601,8 @@
         <v>847</v>
       </c>
       <c r="Q288" s="10"/>
-      <c r="R288" t="s">
-        <v>1872</v>
-      </c>
-    </row>
-    <row r="289" spans="1:18" ht="60">
+    </row>
+    <row r="289" spans="1:17" ht="60">
       <c r="A289">
         <v>288</v>
       </c>
@@ -23410,11 +22654,8 @@
       <c r="Q289" s="10" t="s">
         <v>851</v>
       </c>
-      <c r="R289" t="s">
-        <v>1873</v>
-      </c>
-    </row>
-    <row r="290" spans="1:18">
+    </row>
+    <row r="290" spans="1:17">
       <c r="A290">
         <v>289</v>
       </c>
@@ -23460,11 +22701,8 @@
       <c r="O290" s="8"/>
       <c r="P290" s="10"/>
       <c r="Q290" s="10"/>
-      <c r="R290" t="s">
-        <v>1874</v>
-      </c>
-    </row>
-    <row r="291" spans="1:18" ht="15">
+    </row>
+    <row r="291" spans="1:17" ht="15">
       <c r="A291">
         <v>290</v>
       </c>
@@ -23509,14 +22747,11 @@
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="10" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Q291" s="10"/>
-      <c r="R291" t="s">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="292" spans="1:18" ht="15">
+    </row>
+    <row r="292" spans="1:17" ht="15">
       <c r="A292">
         <v>291</v>
       </c>
@@ -23566,11 +22801,8 @@
         <v>858</v>
       </c>
       <c r="Q292" s="10"/>
-      <c r="R292" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="293" spans="1:18">
+    </row>
+    <row r="293" spans="1:17">
       <c r="A293">
         <v>292</v>
       </c>
@@ -23618,11 +22850,8 @@
       </c>
       <c r="P293" s="10"/>
       <c r="Q293" s="10"/>
-      <c r="R293" t="s">
-        <v>1877</v>
-      </c>
-    </row>
-    <row r="294" spans="1:18" ht="30">
+    </row>
+    <row r="294" spans="1:17" ht="30">
       <c r="A294">
         <v>293</v>
       </c>
@@ -23669,11 +22898,11 @@
         <v>0</v>
       </c>
       <c r="P294" s="10" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="Q294" s="10"/>
     </row>
-    <row r="295" spans="1:18">
+    <row r="295" spans="1:17">
       <c r="A295">
         <v>294</v>
       </c>
@@ -23721,11 +22950,8 @@
       </c>
       <c r="P295" s="10"/>
       <c r="Q295" s="10"/>
-      <c r="R295" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="296" spans="1:18" ht="60">
+    </row>
+    <row r="296" spans="1:17" ht="60">
       <c r="A296">
         <v>295</v>
       </c>
@@ -23777,11 +23003,8 @@
       <c r="Q296" s="10" t="s">
         <v>868</v>
       </c>
-      <c r="R296" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="297" spans="1:18">
+    </row>
+    <row r="297" spans="1:17">
       <c r="A297">
         <v>296</v>
       </c>
@@ -23829,11 +23052,8 @@
       </c>
       <c r="P297" s="10"/>
       <c r="Q297" s="10"/>
-      <c r="R297" t="s">
-        <v>1880</v>
-      </c>
-    </row>
-    <row r="298" spans="1:18" ht="105">
+    </row>
+    <row r="298" spans="1:17" ht="105">
       <c r="A298">
         <v>297</v>
       </c>
@@ -23883,11 +23103,8 @@
         <v>874</v>
       </c>
       <c r="Q298" s="10"/>
-      <c r="R298" t="s">
-        <v>1881</v>
-      </c>
-    </row>
-    <row r="299" spans="1:18" ht="30">
+    </row>
+    <row r="299" spans="1:17" ht="30">
       <c r="A299">
         <v>298</v>
       </c>
@@ -23937,11 +23154,8 @@
         <v>877</v>
       </c>
       <c r="Q299" s="10"/>
-      <c r="R299" t="s">
-        <v>1882</v>
-      </c>
-    </row>
-    <row r="300" spans="1:18" ht="60">
+    </row>
+    <row r="300" spans="1:17" ht="60">
       <c r="A300">
         <v>299</v>
       </c>
@@ -23993,11 +23207,8 @@
       <c r="Q300" s="10" t="s">
         <v>881</v>
       </c>
-      <c r="R300" t="s">
-        <v>1883</v>
-      </c>
-    </row>
-    <row r="301" spans="1:18" ht="60">
+    </row>
+    <row r="301" spans="1:17" ht="60">
       <c r="A301">
         <v>300</v>
       </c>
@@ -24049,11 +23260,8 @@
       <c r="Q301" s="10" t="s">
         <v>885</v>
       </c>
-      <c r="R301" t="s">
-        <v>1884</v>
-      </c>
-    </row>
-    <row r="302" spans="1:18" ht="45">
+    </row>
+    <row r="302" spans="1:17" ht="60">
       <c r="A302">
         <v>301</v>
       </c>
@@ -24102,12 +23310,11 @@
       <c r="P302" s="10" t="s">
         <v>888</v>
       </c>
-      <c r="Q302" s="10"/>
-      <c r="R302" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="303" spans="1:18" ht="75">
+      <c r="Q302" s="10" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="303" spans="1:17" ht="75">
       <c r="A303">
         <v>302</v>
       </c>
@@ -24156,12 +23363,11 @@
       <c r="P303" s="10" t="s">
         <v>891</v>
       </c>
-      <c r="Q303" s="10"/>
-      <c r="R303" t="s">
-        <v>1886</v>
-      </c>
-    </row>
-    <row r="304" spans="1:18" ht="45">
+      <c r="Q303" s="10" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="304" spans="1:17" ht="60">
       <c r="A304">
         <v>303</v>
       </c>
@@ -24210,12 +23416,11 @@
       <c r="P304" s="10" t="s">
         <v>895</v>
       </c>
-      <c r="Q304" s="10"/>
-      <c r="R304" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="305" spans="1:18">
+      <c r="Q304" s="10" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="305" spans="1:17">
       <c r="A305">
         <v>304</v>
       </c>
@@ -24263,11 +23468,8 @@
       </c>
       <c r="P305" s="10"/>
       <c r="Q305" s="10"/>
-      <c r="R305" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="306" spans="1:18" ht="60">
+    </row>
+    <row r="306" spans="1:17" ht="60">
       <c r="A306">
         <v>305</v>
       </c>
@@ -24319,11 +23521,8 @@
       <c r="Q306" s="10" t="s">
         <v>901</v>
       </c>
-      <c r="R306" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="307" spans="1:18">
+    </row>
+    <row r="307" spans="1:17">
       <c r="A307">
         <v>306</v>
       </c>
@@ -24371,11 +23570,8 @@
       </c>
       <c r="P307" s="10"/>
       <c r="Q307" s="10"/>
-      <c r="R307" t="s">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="308" spans="1:18" ht="60">
+    </row>
+    <row r="308" spans="1:17" ht="60">
       <c r="A308">
         <v>307</v>
       </c>
@@ -24424,12 +23620,11 @@
       <c r="P308" s="10" t="s">
         <v>906</v>
       </c>
-      <c r="Q308" s="10"/>
-      <c r="R308" t="s">
-        <v>1891</v>
-      </c>
-    </row>
-    <row r="309" spans="1:18" ht="60">
+      <c r="Q308" s="10" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="309" spans="1:17" ht="60">
       <c r="A309">
         <v>308</v>
       </c>
@@ -24481,11 +23676,8 @@
       <c r="Q309" s="10" t="s">
         <v>910</v>
       </c>
-      <c r="R309" t="s">
-        <v>1892</v>
-      </c>
-    </row>
-    <row r="310" spans="1:18" ht="60">
+    </row>
+    <row r="310" spans="1:17" ht="60">
       <c r="A310">
         <v>309</v>
       </c>
@@ -24537,11 +23729,8 @@
       <c r="Q310" s="10" t="s">
         <v>914</v>
       </c>
-      <c r="R310" t="s">
-        <v>1893</v>
-      </c>
-    </row>
-    <row r="311" spans="1:18">
+    </row>
+    <row r="311" spans="1:17">
       <c r="A311">
         <v>310</v>
       </c>
@@ -24584,14 +23773,13 @@
       <c r="N311" t="s">
         <v>21</v>
       </c>
-      <c r="O311" s="8"/>
+      <c r="O311" s="8">
+        <v>4</v>
+      </c>
       <c r="P311" s="10"/>
       <c r="Q311" s="10"/>
-      <c r="R311" t="s">
-        <v>1894</v>
-      </c>
-    </row>
-    <row r="312" spans="1:18" ht="60">
+    </row>
+    <row r="312" spans="1:17" ht="60">
       <c r="A312">
         <v>311</v>
       </c>
@@ -24643,11 +23831,8 @@
       <c r="Q312" s="10" t="s">
         <v>920</v>
       </c>
-      <c r="R312" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="313" spans="1:18">
+    </row>
+    <row r="313" spans="1:17">
       <c r="A313">
         <v>312</v>
       </c>
@@ -24669,14 +23854,34 @@
       <c r="G313">
         <v>100</v>
       </c>
-      <c r="O313" s="8"/>
+      <c r="H313">
+        <v>1</v>
+      </c>
+      <c r="I313">
+        <v>1</v>
+      </c>
+      <c r="J313">
+        <v>50</v>
+      </c>
+      <c r="K313">
+        <v>30</v>
+      </c>
+      <c r="L313">
+        <v>3</v>
+      </c>
+      <c r="M313">
+        <v>110</v>
+      </c>
+      <c r="N313" t="s">
+        <v>31</v>
+      </c>
+      <c r="O313" s="8">
+        <v>27</v>
+      </c>
       <c r="P313" s="10"/>
       <c r="Q313" s="10"/>
-      <c r="R313" t="s">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="314" spans="1:18">
+    </row>
+    <row r="314" spans="1:17" ht="30">
       <c r="A314">
         <v>313</v>
       </c>
@@ -24698,13 +23903,35 @@
       <c r="G314">
         <v>100</v>
       </c>
+      <c r="H314">
+        <v>999999</v>
+      </c>
+      <c r="I314">
+        <v>0</v>
+      </c>
+      <c r="J314">
+        <v>609</v>
+      </c>
+      <c r="K314">
+        <v>10</v>
+      </c>
+      <c r="L314">
+        <v>0</v>
+      </c>
+      <c r="M314">
+        <v>300</v>
+      </c>
+      <c r="N314" t="s">
+        <v>31</v>
+      </c>
       <c r="O314" s="8">
         <v>0</v>
       </c>
-      <c r="P314" s="10"/>
-      <c r="Q314" s="10"/>
-    </row>
-    <row r="315" spans="1:18" ht="60">
+      <c r="P314" s="10" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="315" spans="1:17" ht="60">
       <c r="A315">
         <v>314</v>
       </c>
@@ -24756,11 +23983,8 @@
       <c r="Q315" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="R315" t="s">
-        <v>1897</v>
-      </c>
-    </row>
-    <row r="316" spans="1:18" ht="90">
+    </row>
+    <row r="316" spans="1:17" ht="90">
       <c r="A316">
         <v>315</v>
       </c>
@@ -24809,12 +24033,11 @@
       <c r="P316" s="10" t="s">
         <v>931</v>
       </c>
-      <c r="Q316" s="10"/>
-      <c r="R316" t="s">
-        <v>1898</v>
-      </c>
-    </row>
-    <row r="317" spans="1:18" ht="45">
+      <c r="Q316" s="10" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="317" spans="1:17" ht="60">
       <c r="A317">
         <v>316</v>
       </c>
@@ -24863,12 +24086,11 @@
       <c r="P317" s="10" t="s">
         <v>934</v>
       </c>
-      <c r="Q317" s="10"/>
-      <c r="R317" t="s">
-        <v>1899</v>
-      </c>
-    </row>
-    <row r="318" spans="1:18">
+      <c r="Q317" s="10" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="318" spans="1:17">
       <c r="A318">
         <v>317</v>
       </c>
@@ -24891,10 +24113,10 @@
         <v>100</v>
       </c>
       <c r="H318">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="I318">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J318">
         <v>47</v>
@@ -24903,19 +24125,21 @@
         <v>8</v>
       </c>
       <c r="L318">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="M318">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="N318" t="s">
         <v>21</v>
       </c>
-      <c r="O318" s="8"/>
+      <c r="O318" s="8">
+        <v>150</v>
+      </c>
       <c r="P318" s="10"/>
       <c r="Q318" s="10"/>
     </row>
-    <row r="319" spans="1:18" ht="30">
+    <row r="319" spans="1:17" ht="60">
       <c r="A319">
         <v>318</v>
       </c>
@@ -24964,12 +24188,11 @@
       <c r="P319" s="10" t="s">
         <v>939</v>
       </c>
-      <c r="Q319" s="10"/>
-      <c r="R319" t="s">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="320" spans="1:18" ht="60">
+      <c r="Q319" s="10" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="320" spans="1:17" ht="60">
       <c r="A320">
         <v>319</v>
       </c>
@@ -25021,11 +24244,8 @@
       <c r="Q320" s="10" t="s">
         <v>943</v>
       </c>
-      <c r="R320" t="s">
-        <v>1901</v>
-      </c>
-    </row>
-    <row r="321" spans="1:18" ht="60">
+    </row>
+    <row r="321" spans="1:17" ht="60">
       <c r="A321">
         <v>320</v>
       </c>
@@ -25075,11 +24295,8 @@
       <c r="Q321" s="10" t="s">
         <v>946</v>
       </c>
-      <c r="R321" t="s">
-        <v>1902</v>
-      </c>
-    </row>
-    <row r="322" spans="1:18" ht="60">
+    </row>
+    <row r="322" spans="1:17" ht="60">
       <c r="A322">
         <v>321</v>
       </c>
@@ -25131,11 +24348,8 @@
       <c r="Q322" s="10" t="s">
         <v>950</v>
       </c>
-      <c r="R322" t="s">
-        <v>1903</v>
-      </c>
-    </row>
-    <row r="323" spans="1:18" ht="60">
+    </row>
+    <row r="323" spans="1:17" ht="60">
       <c r="A323">
         <v>322</v>
       </c>
@@ -25187,11 +24401,8 @@
       <c r="Q323" s="10" t="s">
         <v>955</v>
       </c>
-      <c r="R323" t="s">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="324" spans="1:18" ht="75">
+    </row>
+    <row r="324" spans="1:17" ht="75">
       <c r="A324">
         <v>323</v>
       </c>
@@ -25240,12 +24451,11 @@
       <c r="P324" s="10" t="s">
         <v>958</v>
       </c>
-      <c r="Q324" s="10"/>
-      <c r="R324" t="s">
-        <v>1905</v>
-      </c>
-    </row>
-    <row r="325" spans="1:18" ht="60">
+      <c r="Q324" s="10" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="325" spans="1:17" ht="60">
       <c r="A325">
         <v>324</v>
       </c>
@@ -25297,11 +24507,8 @@
       <c r="Q325" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="R325" t="s">
-        <v>1906</v>
-      </c>
-    </row>
-    <row r="326" spans="1:18" ht="60">
+    </row>
+    <row r="326" spans="1:17" ht="60">
       <c r="A326">
         <v>325</v>
       </c>
@@ -25353,11 +24560,8 @@
       <c r="Q326" s="10" t="s">
         <v>967</v>
       </c>
-      <c r="R326" t="s">
-        <v>1907</v>
-      </c>
-    </row>
-    <row r="327" spans="1:18" ht="60">
+    </row>
+    <row r="327" spans="1:17" ht="60">
       <c r="A327">
         <v>326</v>
       </c>
@@ -25409,11 +24613,8 @@
       <c r="Q327" s="10" t="s">
         <v>971</v>
       </c>
-      <c r="R327" t="s">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="328" spans="1:18" ht="60">
+    </row>
+    <row r="328" spans="1:17" ht="60">
       <c r="A328">
         <v>327</v>
       </c>
@@ -25465,11 +24666,8 @@
       <c r="Q328" s="10" t="s">
         <v>975</v>
       </c>
-      <c r="R328" t="s">
-        <v>1909</v>
-      </c>
-    </row>
-    <row r="329" spans="1:18" ht="60">
+    </row>
+    <row r="329" spans="1:17" ht="60">
       <c r="A329">
         <v>328</v>
       </c>
@@ -25521,11 +24719,8 @@
       <c r="Q329" s="10" t="s">
         <v>979</v>
       </c>
-      <c r="R329" t="s">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="330" spans="1:18" ht="60">
+    </row>
+    <row r="330" spans="1:17" ht="60">
       <c r="A330">
         <v>329</v>
       </c>
@@ -25577,11 +24772,8 @@
       <c r="Q330" s="10" t="s">
         <v>984</v>
       </c>
-      <c r="R330" t="s">
-        <v>1911</v>
-      </c>
-    </row>
-    <row r="331" spans="1:18" ht="75">
+    </row>
+    <row r="331" spans="1:17" ht="75">
       <c r="A331">
         <v>330</v>
       </c>
@@ -25633,11 +24825,8 @@
       <c r="Q331" s="10" t="s">
         <v>988</v>
       </c>
-      <c r="R331" t="s">
-        <v>1912</v>
-      </c>
-    </row>
-    <row r="332" spans="1:18" ht="60">
+    </row>
+    <row r="332" spans="1:17" ht="60">
       <c r="A332">
         <v>331</v>
       </c>
@@ -25689,11 +24878,8 @@
       <c r="Q332" s="10" t="s">
         <v>991</v>
       </c>
-      <c r="R332" t="s">
-        <v>1913</v>
-      </c>
-    </row>
-    <row r="333" spans="1:18" ht="60">
+    </row>
+    <row r="333" spans="1:17" ht="60">
       <c r="A333">
         <v>332</v>
       </c>
@@ -25745,11 +24931,8 @@
       <c r="Q333" s="10" t="s">
         <v>996</v>
       </c>
-      <c r="R333" t="s">
-        <v>1914</v>
-      </c>
-    </row>
-    <row r="334" spans="1:18">
+    </row>
+    <row r="334" spans="1:17" ht="60">
       <c r="A334">
         <v>333</v>
       </c>
@@ -25771,13 +24954,36 @@
       <c r="G334">
         <v>3000</v>
       </c>
+      <c r="H334">
+        <v>1</v>
+      </c>
+      <c r="I334">
+        <v>1</v>
+      </c>
+      <c r="J334">
+        <v>451</v>
+      </c>
+      <c r="K334">
+        <v>100</v>
+      </c>
+      <c r="L334">
+        <v>0</v>
+      </c>
+      <c r="M334">
+        <v>2000</v>
+      </c>
+      <c r="N334" t="s">
+        <v>31</v>
+      </c>
       <c r="O334" s="8">
         <v>0</v>
       </c>
-      <c r="P334" s="10"/>
+      <c r="P334" s="10" t="s">
+        <v>2165</v>
+      </c>
       <c r="Q334" s="10"/>
     </row>
-    <row r="335" spans="1:18">
+    <row r="335" spans="1:17">
       <c r="A335">
         <v>334</v>
       </c>
@@ -25799,11 +25005,34 @@
       <c r="G335">
         <v>100</v>
       </c>
-      <c r="O335" s="8"/>
+      <c r="H335">
+        <v>1</v>
+      </c>
+      <c r="I335">
+        <v>1</v>
+      </c>
+      <c r="J335">
+        <v>50</v>
+      </c>
+      <c r="K335">
+        <v>30</v>
+      </c>
+      <c r="L335">
+        <v>3</v>
+      </c>
+      <c r="M335">
+        <v>110</v>
+      </c>
+      <c r="N335" t="s">
+        <v>31</v>
+      </c>
+      <c r="O335" s="8">
+        <v>27</v>
+      </c>
       <c r="P335" s="10"/>
       <c r="Q335" s="10"/>
     </row>
-    <row r="336" spans="1:18">
+    <row r="336" spans="1:17" ht="60">
       <c r="A336">
         <v>335</v>
       </c>
@@ -25825,13 +25054,36 @@
       <c r="G336">
         <v>1500</v>
       </c>
+      <c r="H336">
+        <v>120</v>
+      </c>
+      <c r="I336">
+        <v>1</v>
+      </c>
+      <c r="J336">
+        <v>247</v>
+      </c>
+      <c r="K336">
+        <v>148</v>
+      </c>
+      <c r="L336">
+        <v>0</v>
+      </c>
+      <c r="M336">
+        <v>2000</v>
+      </c>
+      <c r="N336" t="s">
+        <v>21</v>
+      </c>
       <c r="O336" s="8">
         <v>0</v>
       </c>
-      <c r="P336" s="10"/>
+      <c r="P336" s="10" t="s">
+        <v>2166</v>
+      </c>
       <c r="Q336" s="10"/>
     </row>
-    <row r="337" spans="1:18" ht="30">
+    <row r="337" spans="1:17" ht="60">
       <c r="A337">
         <v>336</v>
       </c>
@@ -25880,12 +25132,11 @@
       <c r="P337" s="10" t="s">
         <v>1006</v>
       </c>
-      <c r="Q337" s="10"/>
-      <c r="R337" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="338" spans="1:18" ht="60">
+      <c r="Q337" s="10" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="338" spans="1:17" ht="60">
       <c r="A338">
         <v>337</v>
       </c>
@@ -25937,11 +25188,8 @@
       <c r="Q338" s="10" t="s">
         <v>1010</v>
       </c>
-      <c r="R338" t="s">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="339" spans="1:18" ht="75">
+    </row>
+    <row r="339" spans="1:17" ht="60">
       <c r="A339">
         <v>338</v>
       </c>
@@ -25990,12 +25238,11 @@
       <c r="P339" s="10" t="s">
         <v>1014</v>
       </c>
-      <c r="Q339" s="10"/>
-      <c r="R339" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="340" spans="1:18">
+      <c r="Q339" s="10" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="340" spans="1:17">
       <c r="A340">
         <v>339</v>
       </c>
@@ -26020,11 +25267,8 @@
       <c r="O340" s="8"/>
       <c r="P340" s="10"/>
       <c r="Q340" s="10"/>
-      <c r="R340" t="s">
-        <v>1918</v>
-      </c>
-    </row>
-    <row r="341" spans="1:18">
+    </row>
+    <row r="341" spans="1:17">
       <c r="A341">
         <v>340</v>
       </c>
@@ -26052,7 +25296,7 @@
       <c r="P341" s="10"/>
       <c r="Q341" s="10"/>
     </row>
-    <row r="342" spans="1:18" ht="90">
+    <row r="342" spans="1:17" ht="90">
       <c r="A342">
         <v>341</v>
       </c>
@@ -26104,11 +25348,8 @@
       <c r="Q342" s="10" t="s">
         <v>1022</v>
       </c>
-      <c r="R342" t="s">
-        <v>1919</v>
-      </c>
-    </row>
-    <row r="343" spans="1:18">
+    </row>
+    <row r="343" spans="1:17">
       <c r="A343">
         <v>342</v>
       </c>
@@ -26155,7 +25396,7 @@
       <c r="P343" s="10"/>
       <c r="Q343" s="10"/>
     </row>
-    <row r="344" spans="1:18" ht="60">
+    <row r="344" spans="1:17" ht="60">
       <c r="A344">
         <v>343</v>
       </c>
@@ -26207,11 +25448,8 @@
       <c r="Q344" s="10" t="s">
         <v>1028</v>
       </c>
-      <c r="R344" t="s">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="345" spans="1:18" ht="45">
+    </row>
+    <row r="345" spans="1:17" ht="45">
       <c r="A345">
         <v>344</v>
       </c>
@@ -26261,11 +25499,8 @@
         <v>1031</v>
       </c>
       <c r="Q345" s="10"/>
-      <c r="R345" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="346" spans="1:18" ht="60">
+    </row>
+    <row r="346" spans="1:17" ht="60">
       <c r="A346">
         <v>345</v>
       </c>
@@ -26317,11 +25552,8 @@
       <c r="Q346" s="10" t="s">
         <v>1035</v>
       </c>
-      <c r="R346" t="s">
-        <v>1922</v>
-      </c>
-    </row>
-    <row r="347" spans="1:18" ht="60">
+    </row>
+    <row r="347" spans="1:17" ht="60">
       <c r="A347">
         <v>346</v>
       </c>
@@ -26373,11 +25605,8 @@
       <c r="Q347" s="10" t="s">
         <v>1039</v>
       </c>
-      <c r="R347" t="s">
-        <v>1923</v>
-      </c>
-    </row>
-    <row r="348" spans="1:18" ht="90">
+    </row>
+    <row r="348" spans="1:17" ht="90">
       <c r="A348">
         <v>347</v>
       </c>
@@ -26424,11 +25653,8 @@
         <v>1042</v>
       </c>
       <c r="Q348" s="10"/>
-      <c r="R348" t="s">
-        <v>1924</v>
-      </c>
-    </row>
-    <row r="349" spans="1:18" ht="15">
+    </row>
+    <row r="349" spans="1:17" ht="15">
       <c r="A349">
         <v>348</v>
       </c>
@@ -26478,11 +25704,8 @@
         <v>1046</v>
       </c>
       <c r="Q349" s="10"/>
-      <c r="R349" t="s">
-        <v>1925</v>
-      </c>
-    </row>
-    <row r="350" spans="1:18" ht="105">
+    </row>
+    <row r="350" spans="1:17" ht="105">
       <c r="A350">
         <v>349</v>
       </c>
@@ -26529,11 +25752,8 @@
         <v>1049</v>
       </c>
       <c r="Q350" s="10"/>
-      <c r="R350" t="s">
-        <v>1926</v>
-      </c>
-    </row>
-    <row r="351" spans="1:18" ht="30">
+    </row>
+    <row r="351" spans="1:17" ht="30">
       <c r="A351">
         <v>350</v>
       </c>
@@ -26583,11 +25803,8 @@
         <v>1053</v>
       </c>
       <c r="Q351" s="10"/>
-      <c r="R351" t="s">
-        <v>1927</v>
-      </c>
-    </row>
-    <row r="352" spans="1:18" ht="30">
+    </row>
+    <row r="352" spans="1:17" ht="30">
       <c r="A352">
         <v>351</v>
       </c>
@@ -26637,11 +25854,8 @@
         <v>1056</v>
       </c>
       <c r="Q352" s="10"/>
-      <c r="R352" t="s">
-        <v>1928</v>
-      </c>
-    </row>
-    <row r="353" spans="1:18" ht="15">
+    </row>
+    <row r="353" spans="1:17" ht="15">
       <c r="A353">
         <v>352</v>
       </c>
@@ -26691,11 +25905,8 @@
         <v>1059</v>
       </c>
       <c r="Q353" s="10"/>
-      <c r="R353" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="354" spans="1:18" ht="45">
+    </row>
+    <row r="354" spans="1:17" ht="45">
       <c r="A354">
         <v>353</v>
       </c>
@@ -26745,11 +25956,8 @@
         <v>1062</v>
       </c>
       <c r="Q354" s="10"/>
-      <c r="R354" t="s">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="355" spans="1:18" ht="15">
+    </row>
+    <row r="355" spans="1:17" ht="15">
       <c r="A355">
         <v>354</v>
       </c>
@@ -26799,11 +26007,8 @@
         <v>1065</v>
       </c>
       <c r="Q355" s="10"/>
-      <c r="R355" t="s">
-        <v>1931</v>
-      </c>
-    </row>
-    <row r="356" spans="1:18" ht="45">
+    </row>
+    <row r="356" spans="1:17" ht="45">
       <c r="A356">
         <v>355</v>
       </c>
@@ -26853,11 +26058,8 @@
         <v>1068</v>
       </c>
       <c r="Q356" s="10"/>
-      <c r="R356" t="s">
-        <v>1932</v>
-      </c>
-    </row>
-    <row r="357" spans="1:18" ht="60">
+    </row>
+    <row r="357" spans="1:17" ht="60">
       <c r="A357">
         <v>356</v>
       </c>
@@ -26907,11 +26109,8 @@
         <v>1071</v>
       </c>
       <c r="Q357" s="10"/>
-      <c r="R357" t="s">
-        <v>1933</v>
-      </c>
-    </row>
-    <row r="358" spans="1:18" ht="75">
+    </row>
+    <row r="358" spans="1:17" ht="75">
       <c r="A358">
         <v>357</v>
       </c>
@@ -26961,11 +26160,8 @@
         <v>1074</v>
       </c>
       <c r="Q358" s="10"/>
-      <c r="R358" t="s">
-        <v>1934</v>
-      </c>
-    </row>
-    <row r="359" spans="1:18" ht="30">
+    </row>
+    <row r="359" spans="1:17" ht="30">
       <c r="A359">
         <v>358</v>
       </c>
@@ -27015,11 +26211,8 @@
         <v>1077</v>
       </c>
       <c r="Q359" s="10"/>
-      <c r="R359" t="s">
-        <v>1935</v>
-      </c>
-    </row>
-    <row r="360" spans="1:18" ht="30">
+    </row>
+    <row r="360" spans="1:17" ht="30">
       <c r="A360">
         <v>359</v>
       </c>
@@ -27069,11 +26262,8 @@
         <v>1080</v>
       </c>
       <c r="Q360" s="10"/>
-      <c r="R360" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="361" spans="1:18" ht="30">
+    </row>
+    <row r="361" spans="1:17" ht="30">
       <c r="A361">
         <v>360</v>
       </c>
@@ -27123,11 +26313,8 @@
         <v>1083</v>
       </c>
       <c r="Q361" s="10"/>
-      <c r="R361" t="s">
-        <v>1937</v>
-      </c>
-    </row>
-    <row r="362" spans="1:18" ht="45">
+    </row>
+    <row r="362" spans="1:17" ht="45">
       <c r="A362">
         <v>361</v>
       </c>
@@ -27177,11 +26364,8 @@
         <v>1086</v>
       </c>
       <c r="Q362" s="10"/>
-      <c r="R362" t="s">
-        <v>1938</v>
-      </c>
-    </row>
-    <row r="363" spans="1:18">
+    </row>
+    <row r="363" spans="1:17">
       <c r="A363">
         <v>362</v>
       </c>
@@ -27207,7 +26391,7 @@
       <c r="P363" s="10"/>
       <c r="Q363" s="10"/>
     </row>
-    <row r="364" spans="1:18" ht="45">
+    <row r="364" spans="1:17" ht="45">
       <c r="A364">
         <v>363</v>
       </c>
@@ -27257,11 +26441,8 @@
         <v>1091</v>
       </c>
       <c r="Q364" s="10"/>
-      <c r="R364" t="s">
-        <v>1939</v>
-      </c>
-    </row>
-    <row r="365" spans="1:18" ht="75">
+    </row>
+    <row r="365" spans="1:17" ht="75">
       <c r="A365">
         <v>364</v>
       </c>
@@ -27311,11 +26492,8 @@
         <v>1094</v>
       </c>
       <c r="Q365" s="10"/>
-      <c r="R365" t="s">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="366" spans="1:18" ht="105">
+    </row>
+    <row r="366" spans="1:17" ht="105">
       <c r="A366">
         <v>365</v>
       </c>
@@ -27365,11 +26543,8 @@
         <v>1097</v>
       </c>
       <c r="Q366" s="10"/>
-      <c r="R366" t="s">
-        <v>1941</v>
-      </c>
-    </row>
-    <row r="367" spans="1:18" ht="90">
+    </row>
+    <row r="367" spans="1:17" ht="90">
       <c r="A367">
         <v>366</v>
       </c>
@@ -27419,11 +26594,8 @@
         <v>1100</v>
       </c>
       <c r="Q367" s="10"/>
-      <c r="R367" t="s">
-        <v>1942</v>
-      </c>
-    </row>
-    <row r="368" spans="1:18">
+    </row>
+    <row r="368" spans="1:17">
       <c r="A368">
         <v>367</v>
       </c>
@@ -27451,7 +26623,7 @@
       <c r="P368" s="10"/>
       <c r="Q368" s="10"/>
     </row>
-    <row r="369" spans="1:18">
+    <row r="369" spans="1:17">
       <c r="A369">
         <v>368</v>
       </c>
@@ -27479,7 +26651,7 @@
       <c r="P369" s="10"/>
       <c r="Q369" s="10"/>
     </row>
-    <row r="370" spans="1:18" ht="30">
+    <row r="370" spans="1:17" ht="30">
       <c r="A370">
         <v>369</v>
       </c>
@@ -27529,11 +26701,8 @@
         <v>1107</v>
       </c>
       <c r="Q370" s="10"/>
-      <c r="R370" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="371" spans="1:18" ht="30">
+    </row>
+    <row r="371" spans="1:17" ht="30">
       <c r="A371">
         <v>370</v>
       </c>
@@ -27583,11 +26752,8 @@
         <v>1110</v>
       </c>
       <c r="Q371" s="10"/>
-      <c r="R371" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="372" spans="1:18" ht="30">
+    </row>
+    <row r="372" spans="1:17" ht="30">
       <c r="A372">
         <v>371</v>
       </c>
@@ -27637,11 +26803,8 @@
         <v>1113</v>
       </c>
       <c r="Q372" s="10"/>
-      <c r="R372" t="s">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="373" spans="1:18" ht="45">
+    </row>
+    <row r="373" spans="1:17" ht="45">
       <c r="A373">
         <v>372</v>
       </c>
@@ -27691,11 +26854,8 @@
         <v>1116</v>
       </c>
       <c r="Q373" s="10"/>
-      <c r="R373" t="s">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="374" spans="1:18" ht="45">
+    </row>
+    <row r="374" spans="1:17" ht="45">
       <c r="A374">
         <v>373</v>
       </c>
@@ -27745,11 +26905,8 @@
         <v>1119</v>
       </c>
       <c r="Q374" s="10"/>
-      <c r="R374" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="375" spans="1:18" ht="30">
+    </row>
+    <row r="375" spans="1:17" ht="30">
       <c r="A375">
         <v>374</v>
       </c>
@@ -27799,11 +26956,8 @@
         <v>1122</v>
       </c>
       <c r="Q375" s="10"/>
-      <c r="R375" t="s">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="376" spans="1:18" ht="30">
+    </row>
+    <row r="376" spans="1:17" ht="30">
       <c r="A376">
         <v>375</v>
       </c>
@@ -27853,11 +27007,8 @@
         <v>939</v>
       </c>
       <c r="Q376" s="10"/>
-      <c r="R376" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="377" spans="1:18" ht="45">
+    </row>
+    <row r="377" spans="1:17" ht="45">
       <c r="A377">
         <v>376</v>
       </c>
@@ -27907,11 +27058,8 @@
         <v>1127</v>
       </c>
       <c r="Q377" s="10"/>
-      <c r="R377" t="s">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="378" spans="1:18" ht="30">
+    </row>
+    <row r="378" spans="1:17" ht="30">
       <c r="A378">
         <v>377</v>
       </c>
@@ -27961,11 +27109,8 @@
         <v>1130</v>
       </c>
       <c r="Q378" s="10"/>
-      <c r="R378" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="379" spans="1:18" ht="30">
+    </row>
+    <row r="379" spans="1:17" ht="30">
       <c r="A379">
         <v>378</v>
       </c>
@@ -28015,11 +27160,8 @@
         <v>1133</v>
       </c>
       <c r="Q379" s="10"/>
-      <c r="R379" t="s">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="380" spans="1:18" ht="90">
+    </row>
+    <row r="380" spans="1:17" ht="90">
       <c r="A380">
         <v>379</v>
       </c>
@@ -28069,11 +27211,8 @@
         <v>1136</v>
       </c>
       <c r="Q380" s="10"/>
-      <c r="R380" t="s">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="381" spans="1:18" ht="45">
+    </row>
+    <row r="381" spans="1:17" ht="45">
       <c r="A381">
         <v>380</v>
       </c>
@@ -28123,11 +27262,8 @@
         <v>1139</v>
       </c>
       <c r="Q381" s="10"/>
-      <c r="R381" t="s">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="382" spans="1:18" ht="75">
+    </row>
+    <row r="382" spans="1:17" ht="75">
       <c r="A382">
         <v>381</v>
       </c>
@@ -28177,11 +27313,8 @@
         <v>1142</v>
       </c>
       <c r="Q382" s="10"/>
-      <c r="R382" t="s">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="383" spans="1:18">
+    </row>
+    <row r="383" spans="1:17">
       <c r="A383">
         <v>382</v>
       </c>
@@ -28207,7 +27340,7 @@
       <c r="P383" s="10"/>
       <c r="Q383" s="10"/>
     </row>
-    <row r="384" spans="1:18">
+    <row r="384" spans="1:17">
       <c r="A384">
         <v>383</v>
       </c>
@@ -28235,7 +27368,7 @@
       <c r="P384" s="10"/>
       <c r="Q384" s="10"/>
     </row>
-    <row r="385" spans="1:18" ht="45">
+    <row r="385" spans="1:17" ht="45">
       <c r="A385">
         <v>384</v>
       </c>
@@ -28285,11 +27418,8 @@
         <v>1149</v>
       </c>
       <c r="Q385" s="10"/>
-      <c r="R385" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="386" spans="1:18" ht="60">
+    </row>
+    <row r="386" spans="1:17" ht="60">
       <c r="A386">
         <v>385</v>
       </c>
@@ -28339,11 +27469,8 @@
         <v>1153</v>
       </c>
       <c r="Q386" s="10"/>
-      <c r="R386" t="s">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="387" spans="1:18" ht="75">
+    </row>
+    <row r="387" spans="1:17" ht="75">
       <c r="A387">
         <v>386</v>
       </c>
@@ -28393,11 +27520,8 @@
         <v>1157</v>
       </c>
       <c r="Q387" s="10"/>
-      <c r="R387" t="s">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="388" spans="1:18">
+    </row>
+    <row r="388" spans="1:17">
       <c r="A388">
         <v>387</v>
       </c>
@@ -28423,7 +27547,7 @@
       <c r="P388" s="10"/>
       <c r="Q388" s="10"/>
     </row>
-    <row r="389" spans="1:18" ht="45">
+    <row r="389" spans="1:17" ht="45">
       <c r="A389">
         <v>388</v>
       </c>
@@ -28473,11 +27597,8 @@
         <v>1162</v>
       </c>
       <c r="Q389" s="10"/>
-      <c r="R389" t="s">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="390" spans="1:18" ht="120">
+    </row>
+    <row r="390" spans="1:17" ht="120">
       <c r="A390">
         <v>389</v>
       </c>
@@ -28527,11 +27648,8 @@
         <v>1166</v>
       </c>
       <c r="Q390" s="10"/>
-      <c r="R390" t="s">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="391" spans="1:18" ht="60">
+    </row>
+    <row r="391" spans="1:17" ht="60">
       <c r="A391">
         <v>390</v>
       </c>
@@ -28583,11 +27701,8 @@
       <c r="Q391" s="10" t="s">
         <v>1170</v>
       </c>
-      <c r="R391" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="392" spans="1:18">
+    </row>
+    <row r="392" spans="1:17">
       <c r="A392">
         <v>391</v>
       </c>
@@ -28615,7 +27730,7 @@
       <c r="P392" s="10"/>
       <c r="Q392" s="10"/>
     </row>
-    <row r="393" spans="1:18">
+    <row r="393" spans="1:17">
       <c r="A393">
         <v>392</v>
       </c>
@@ -28643,7 +27758,7 @@
       <c r="P393" s="10"/>
       <c r="Q393" s="10"/>
     </row>
-    <row r="394" spans="1:18" ht="30">
+    <row r="394" spans="1:17" ht="30">
       <c r="A394">
         <v>393</v>
       </c>
@@ -28693,11 +27808,8 @@
         <v>1178</v>
       </c>
       <c r="Q394" s="10"/>
-      <c r="R394" t="s">
-        <v>1962</v>
-      </c>
-    </row>
-    <row r="395" spans="1:18" ht="90">
+    </row>
+    <row r="395" spans="1:17" ht="90">
       <c r="A395">
         <v>394</v>
       </c>
@@ -28747,11 +27859,8 @@
         <v>1182</v>
       </c>
       <c r="Q395" s="10"/>
-      <c r="R395" t="s">
-        <v>1963</v>
-      </c>
-    </row>
-    <row r="396" spans="1:18" ht="60">
+    </row>
+    <row r="396" spans="1:17" ht="60">
       <c r="A396">
         <v>395</v>
       </c>
@@ -28801,11 +27910,8 @@
         <v>1186</v>
       </c>
       <c r="Q396" s="10"/>
-      <c r="R396" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="397" spans="1:18" ht="75">
+    </row>
+    <row r="397" spans="1:17" ht="75">
       <c r="A397">
         <v>396</v>
       </c>
@@ -28855,11 +27961,8 @@
         <v>1190</v>
       </c>
       <c r="Q397" s="10"/>
-      <c r="R397" t="s">
-        <v>1965</v>
-      </c>
-    </row>
-    <row r="398" spans="1:18" ht="60">
+    </row>
+    <row r="398" spans="1:17" ht="60">
       <c r="A398">
         <v>397</v>
       </c>
@@ -28909,11 +28012,8 @@
         <v>1193</v>
       </c>
       <c r="Q398" s="10"/>
-      <c r="R398" t="s">
-        <v>1966</v>
-      </c>
-    </row>
-    <row r="399" spans="1:18" ht="15">
+    </row>
+    <row r="399" spans="1:17" ht="15">
       <c r="A399">
         <v>398</v>
       </c>
@@ -28963,11 +28063,8 @@
         <v>1196</v>
       </c>
       <c r="Q399" s="10"/>
-      <c r="R399" t="s">
-        <v>1967</v>
-      </c>
-    </row>
-    <row r="400" spans="1:18" ht="105">
+    </row>
+    <row r="400" spans="1:17" ht="105">
       <c r="A400">
         <v>399</v>
       </c>
@@ -29017,11 +28114,8 @@
         <v>1199</v>
       </c>
       <c r="Q400" s="10"/>
-      <c r="R400" t="s">
-        <v>1968</v>
-      </c>
-    </row>
-    <row r="401" spans="1:18" ht="120">
+    </row>
+    <row r="401" spans="1:17" ht="120">
       <c r="A401">
         <v>400</v>
       </c>
@@ -29071,11 +28165,8 @@
         <v>1203</v>
       </c>
       <c r="Q401" s="10"/>
-      <c r="R401" t="s">
-        <v>1969</v>
-      </c>
-    </row>
-    <row r="402" spans="1:18" ht="105">
+    </row>
+    <row r="402" spans="1:17" ht="105">
       <c r="A402">
         <v>401</v>
       </c>
@@ -29125,11 +28216,8 @@
         <v>1206</v>
       </c>
       <c r="Q402" s="10"/>
-      <c r="R402" t="s">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="403" spans="1:18" ht="120">
+    </row>
+    <row r="403" spans="1:17" ht="120">
       <c r="A403">
         <v>402</v>
       </c>
@@ -29179,11 +28267,8 @@
         <v>1209</v>
       </c>
       <c r="Q403" s="10"/>
-      <c r="R403" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="404" spans="1:18" ht="45">
+    </row>
+    <row r="404" spans="1:17" ht="45">
       <c r="A404">
         <v>403</v>
       </c>
@@ -29233,11 +28318,8 @@
         <v>1213</v>
       </c>
       <c r="Q404" s="10"/>
-      <c r="R404" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="405" spans="1:18" ht="120">
+    </row>
+    <row r="405" spans="1:17" ht="120">
       <c r="A405">
         <v>404</v>
       </c>
@@ -29287,11 +28369,8 @@
         <v>1217</v>
       </c>
       <c r="Q405" s="10"/>
-      <c r="R405" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="406" spans="1:18" ht="45">
+    </row>
+    <row r="406" spans="1:17" ht="45">
       <c r="A406">
         <v>405</v>
       </c>
@@ -29341,11 +28420,8 @@
         <v>1220</v>
       </c>
       <c r="Q406" s="10"/>
-      <c r="R406" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="407" spans="1:18" ht="75">
+    </row>
+    <row r="407" spans="1:17" ht="75">
       <c r="A407">
         <v>406</v>
       </c>
@@ -29395,11 +28471,8 @@
         <v>1223</v>
       </c>
       <c r="Q407" s="10"/>
-      <c r="R407" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="408" spans="1:18" ht="30">
+    </row>
+    <row r="408" spans="1:17" ht="30">
       <c r="A408">
         <v>407</v>
       </c>
@@ -29449,11 +28522,8 @@
         <v>1226</v>
       </c>
       <c r="Q408" s="10"/>
-      <c r="R408" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="409" spans="1:18">
+    </row>
+    <row r="409" spans="1:17">
       <c r="A409">
         <v>408</v>
       </c>
@@ -29478,11 +28548,8 @@
       <c r="O409" s="8"/>
       <c r="P409" s="10"/>
       <c r="Q409" s="10"/>
-      <c r="R409" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="410" spans="1:18">
+    </row>
+    <row r="410" spans="1:17">
       <c r="A410">
         <v>409</v>
       </c>
@@ -29510,7 +28577,7 @@
       <c r="P410" s="10"/>
       <c r="Q410" s="10"/>
     </row>
-    <row r="411" spans="1:18" ht="135">
+    <row r="411" spans="1:17" ht="135">
       <c r="A411">
         <v>410</v>
       </c>
@@ -29560,11 +28627,8 @@
         <v>1233</v>
       </c>
       <c r="Q411" s="10"/>
-      <c r="R411" t="s">
-        <v>1978</v>
-      </c>
-    </row>
-    <row r="412" spans="1:18" ht="90">
+    </row>
+    <row r="412" spans="1:17" ht="90">
       <c r="A412">
         <v>411</v>
       </c>
@@ -29614,11 +28678,8 @@
         <v>1236</v>
       </c>
       <c r="Q412" s="10"/>
-      <c r="R412" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="413" spans="1:18" ht="105">
+    </row>
+    <row r="413" spans="1:17" ht="105">
       <c r="A413">
         <v>412</v>
       </c>
@@ -29668,11 +28729,8 @@
         <v>1240</v>
       </c>
       <c r="Q413" s="10"/>
-      <c r="R413" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="414" spans="1:18" ht="45">
+    </row>
+    <row r="414" spans="1:17" ht="45">
       <c r="A414">
         <v>413</v>
       </c>
@@ -29722,11 +28780,8 @@
         <v>1243</v>
       </c>
       <c r="Q414" s="10"/>
-      <c r="R414" t="s">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="415" spans="1:18">
+    </row>
+    <row r="415" spans="1:17">
       <c r="A415">
         <v>414</v>
       </c>
@@ -29752,7 +28807,7 @@
       <c r="P415" s="10"/>
       <c r="Q415" s="10"/>
     </row>
-    <row r="416" spans="1:18">
+    <row r="416" spans="1:17">
       <c r="A416">
         <v>415</v>
       </c>
@@ -29780,7 +28835,7 @@
       <c r="P416" s="10"/>
       <c r="Q416" s="10"/>
     </row>
-    <row r="417" spans="1:18">
+    <row r="417" spans="1:17">
       <c r="A417">
         <v>416</v>
       </c>
@@ -29828,11 +28883,8 @@
       </c>
       <c r="P417" s="10"/>
       <c r="Q417" s="10"/>
-      <c r="R417" t="s">
-        <v>1982</v>
-      </c>
-    </row>
-    <row r="418" spans="1:18" ht="90">
+    </row>
+    <row r="418" spans="1:17" ht="90">
       <c r="A418">
         <v>417</v>
       </c>
@@ -29882,11 +28934,8 @@
         <v>1252</v>
       </c>
       <c r="Q418" s="10"/>
-      <c r="R418" t="s">
-        <v>1983</v>
-      </c>
-    </row>
-    <row r="419" spans="1:18" ht="30">
+    </row>
+    <row r="419" spans="1:17" ht="30">
       <c r="A419">
         <v>418</v>
       </c>
@@ -29936,11 +28985,8 @@
         <v>1255</v>
       </c>
       <c r="Q419" s="10"/>
-      <c r="R419" t="s">
-        <v>1984</v>
-      </c>
-    </row>
-    <row r="420" spans="1:18" ht="30">
+    </row>
+    <row r="420" spans="1:17" ht="30">
       <c r="A420">
         <v>419</v>
       </c>
@@ -29990,11 +29036,8 @@
         <v>1258</v>
       </c>
       <c r="Q420" s="10"/>
-      <c r="R420" t="s">
-        <v>1985</v>
-      </c>
-    </row>
-    <row r="421" spans="1:18" ht="75">
+    </row>
+    <row r="421" spans="1:17" ht="75">
       <c r="A421">
         <v>420</v>
       </c>
@@ -30044,11 +29087,8 @@
         <v>1262</v>
       </c>
       <c r="Q421" s="10"/>
-      <c r="R421" t="s">
-        <v>1986</v>
-      </c>
-    </row>
-    <row r="422" spans="1:18">
+    </row>
+    <row r="422" spans="1:17">
       <c r="A422">
         <v>421</v>
       </c>
@@ -30096,11 +29136,8 @@
       </c>
       <c r="P422" s="10"/>
       <c r="Q422" s="10"/>
-      <c r="R422" t="s">
-        <v>1987</v>
-      </c>
-    </row>
-    <row r="423" spans="1:18" ht="60">
+    </row>
+    <row r="423" spans="1:17" ht="60">
       <c r="A423">
         <v>422</v>
       </c>
@@ -30150,11 +29187,8 @@
         <v>1267</v>
       </c>
       <c r="Q423" s="10"/>
-      <c r="R423" t="s">
-        <v>1988</v>
-      </c>
-    </row>
-    <row r="424" spans="1:18" ht="30">
+    </row>
+    <row r="424" spans="1:17" ht="30">
       <c r="A424">
         <v>423</v>
       </c>
@@ -30204,11 +29238,8 @@
         <v>1270</v>
       </c>
       <c r="Q424" s="10"/>
-      <c r="R424" t="s">
-        <v>1989</v>
-      </c>
-    </row>
-    <row r="425" spans="1:18" ht="30">
+    </row>
+    <row r="425" spans="1:17" ht="30">
       <c r="A425">
         <v>424</v>
       </c>
@@ -30258,11 +29289,8 @@
         <v>1122</v>
       </c>
       <c r="Q425" s="10"/>
-      <c r="R425" t="s">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="426" spans="1:18" ht="105">
+    </row>
+    <row r="426" spans="1:17" ht="105">
       <c r="A426">
         <v>425</v>
       </c>
@@ -30312,11 +29340,8 @@
         <v>1275</v>
       </c>
       <c r="Q426" s="10"/>
-      <c r="R426" t="s">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="427" spans="1:18" ht="30">
+    </row>
+    <row r="427" spans="1:17" ht="30">
       <c r="A427">
         <v>426</v>
       </c>
@@ -30366,11 +29391,8 @@
         <v>1278</v>
       </c>
       <c r="Q427" s="10"/>
-      <c r="R427" t="s">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="428" spans="1:18">
+    </row>
+    <row r="428" spans="1:17">
       <c r="A428">
         <v>427</v>
       </c>
@@ -30395,11 +29417,8 @@
       <c r="O428" s="8"/>
       <c r="P428" s="10"/>
       <c r="Q428" s="10"/>
-      <c r="R428" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="429" spans="1:18">
+    </row>
+    <row r="429" spans="1:17">
       <c r="A429">
         <v>428</v>
       </c>
@@ -30427,7 +29446,7 @@
       <c r="P429" s="10"/>
       <c r="Q429" s="10"/>
     </row>
-    <row r="430" spans="1:18" ht="60">
+    <row r="430" spans="1:17" ht="60">
       <c r="A430">
         <v>429</v>
       </c>
@@ -30477,11 +29496,8 @@
         <v>1284</v>
       </c>
       <c r="Q430" s="10"/>
-      <c r="R430" t="s">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="431" spans="1:18" ht="90">
+    </row>
+    <row r="431" spans="1:17" ht="90">
       <c r="A431">
         <v>430</v>
       </c>
@@ -30531,11 +29547,8 @@
         <v>1287</v>
       </c>
       <c r="Q431" s="10"/>
-      <c r="R431" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="432" spans="1:18" ht="60">
+    </row>
+    <row r="432" spans="1:17" ht="60">
       <c r="A432">
         <v>431</v>
       </c>
@@ -30585,11 +29598,8 @@
         <v>1291</v>
       </c>
       <c r="Q432" s="10"/>
-      <c r="R432" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="433" spans="1:18" ht="105">
+    </row>
+    <row r="433" spans="1:17" ht="105">
       <c r="A433">
         <v>432</v>
       </c>
@@ -30639,11 +29649,8 @@
         <v>1294</v>
       </c>
       <c r="Q433" s="10"/>
-      <c r="R433" t="s">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="434" spans="1:18" ht="75">
+    </row>
+    <row r="434" spans="1:17" ht="75">
       <c r="A434">
         <v>433</v>
       </c>
@@ -30693,11 +29700,8 @@
         <v>1298</v>
       </c>
       <c r="Q434" s="10"/>
-      <c r="R434" t="s">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="435" spans="1:18" ht="45">
+    </row>
+    <row r="435" spans="1:17" ht="45">
       <c r="A435">
         <v>434</v>
       </c>
@@ -30747,11 +29751,8 @@
         <v>1301</v>
       </c>
       <c r="Q435" s="10"/>
-      <c r="R435" t="s">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="436" spans="1:18" ht="30">
+    </row>
+    <row r="436" spans="1:17" ht="30">
       <c r="A436">
         <v>435</v>
       </c>
@@ -30801,11 +29802,8 @@
         <v>1304</v>
       </c>
       <c r="Q436" s="10"/>
-      <c r="R436" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="437" spans="1:18" ht="45">
+    </row>
+    <row r="437" spans="1:17" ht="45">
       <c r="A437">
         <v>436</v>
       </c>
@@ -30855,11 +29853,8 @@
         <v>1307</v>
       </c>
       <c r="Q437" s="10"/>
-      <c r="R437" t="s">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="438" spans="1:18" ht="90">
+    </row>
+    <row r="438" spans="1:17" ht="90">
       <c r="A438">
         <v>437</v>
       </c>
@@ -30909,11 +29904,8 @@
         <v>1310</v>
       </c>
       <c r="Q438" s="10"/>
-      <c r="R438" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="439" spans="1:18" ht="60">
+    </row>
+    <row r="439" spans="1:17" ht="60">
       <c r="A439">
         <v>438</v>
       </c>
@@ -30963,11 +29955,8 @@
         <v>1313</v>
       </c>
       <c r="Q439" s="10"/>
-      <c r="R439" t="s">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="440" spans="1:18" ht="105">
+    </row>
+    <row r="440" spans="1:17" ht="105">
       <c r="A440">
         <v>439</v>
       </c>
@@ -31017,11 +30006,8 @@
         <v>1316</v>
       </c>
       <c r="Q440" s="10"/>
-      <c r="R440" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="441" spans="1:18" ht="60">
+    </row>
+    <row r="441" spans="1:17" ht="60">
       <c r="A441">
         <v>440</v>
       </c>
@@ -31071,11 +30057,8 @@
         <v>1319</v>
       </c>
       <c r="Q441" s="10"/>
-      <c r="R441" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="442" spans="1:18" ht="60">
+    </row>
+    <row r="442" spans="1:17" ht="60">
       <c r="A442">
         <v>441</v>
       </c>
@@ -31125,11 +30108,8 @@
         <v>1322</v>
       </c>
       <c r="Q442" s="10"/>
-      <c r="R442" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="443" spans="1:18" ht="90">
+    </row>
+    <row r="443" spans="1:17" ht="90">
       <c r="A443">
         <v>442</v>
       </c>
@@ -31179,11 +30159,8 @@
         <v>1325</v>
       </c>
       <c r="Q443" s="10"/>
-      <c r="R443" t="s">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="444" spans="1:18" ht="60">
+    </row>
+    <row r="444" spans="1:17" ht="60">
       <c r="A444">
         <v>443</v>
       </c>
@@ -31233,11 +30210,8 @@
         <v>1328</v>
       </c>
       <c r="Q444" s="10"/>
-      <c r="R444" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="445" spans="1:18" ht="60">
+    </row>
+    <row r="445" spans="1:17" ht="60">
       <c r="A445">
         <v>444</v>
       </c>
@@ -31287,11 +30261,8 @@
         <v>1331</v>
       </c>
       <c r="Q445" s="10"/>
-      <c r="R445" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="446" spans="1:18" ht="90">
+    </row>
+    <row r="446" spans="1:17" ht="90">
       <c r="A446">
         <v>445</v>
       </c>
@@ -31341,11 +30312,8 @@
         <v>1334</v>
       </c>
       <c r="Q446" s="10"/>
-      <c r="R446" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="447" spans="1:18">
+    </row>
+    <row r="447" spans="1:17">
       <c r="A447">
         <v>446</v>
       </c>
@@ -31373,7 +30341,7 @@
       <c r="P447" s="10"/>
       <c r="Q447" s="10"/>
     </row>
-    <row r="448" spans="1:18" ht="30">
+    <row r="448" spans="1:17" ht="30">
       <c r="A448">
         <v>447</v>
       </c>
@@ -31423,11 +30391,8 @@
         <v>1339</v>
       </c>
       <c r="Q448" s="10"/>
-      <c r="R448" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="449" spans="1:18" ht="15">
+    </row>
+    <row r="449" spans="1:17" ht="15">
       <c r="A449">
         <v>448</v>
       </c>
@@ -31477,11 +30442,8 @@
         <v>1342</v>
       </c>
       <c r="Q449" s="10"/>
-      <c r="R449" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="450" spans="1:18">
+    </row>
+    <row r="450" spans="1:17">
       <c r="A450">
         <v>449</v>
       </c>
@@ -31506,11 +30468,8 @@
       <c r="O450" s="8"/>
       <c r="P450" s="10"/>
       <c r="Q450" s="10"/>
-      <c r="R450" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="451" spans="1:18">
+    </row>
+    <row r="451" spans="1:17">
       <c r="A451">
         <v>450</v>
       </c>
@@ -31538,7 +30497,7 @@
       <c r="P451" s="10"/>
       <c r="Q451" s="10"/>
     </row>
-    <row r="452" spans="1:18" ht="90">
+    <row r="452" spans="1:17" ht="90">
       <c r="A452">
         <v>451</v>
       </c>
@@ -31588,11 +30547,8 @@
         <v>1349</v>
       </c>
       <c r="Q452" s="10"/>
-      <c r="R452" t="s">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="453" spans="1:18">
+    </row>
+    <row r="453" spans="1:17">
       <c r="A453">
         <v>452</v>
       </c>
@@ -31618,7 +30574,7 @@
       <c r="P453" s="10"/>
       <c r="Q453" s="10"/>
     </row>
-    <row r="454" spans="1:18" ht="30">
+    <row r="454" spans="1:17" ht="30">
       <c r="A454">
         <v>453</v>
       </c>
@@ -31668,11 +30624,8 @@
         <v>1355</v>
       </c>
       <c r="Q454" s="10"/>
-      <c r="R454" t="s">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="455" spans="1:18">
+    </row>
+    <row r="455" spans="1:17">
       <c r="A455">
         <v>454</v>
       </c>
@@ -31700,7 +30653,7 @@
       <c r="P455" s="10"/>
       <c r="Q455" s="10"/>
     </row>
-    <row r="456" spans="1:18" ht="15">
+    <row r="456" spans="1:17" ht="15">
       <c r="A456">
         <v>455</v>
       </c>
@@ -31750,11 +30703,8 @@
         <v>1361</v>
       </c>
       <c r="Q456" s="10"/>
-      <c r="R456" t="s">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="457" spans="1:18" ht="30">
+    </row>
+    <row r="457" spans="1:17" ht="30">
       <c r="A457">
         <v>456</v>
       </c>
@@ -31804,11 +30754,8 @@
         <v>1365</v>
       </c>
       <c r="Q457" s="10"/>
-      <c r="R457" t="s">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="458" spans="1:18">
+    </row>
+    <row r="458" spans="1:17">
       <c r="A458">
         <v>457</v>
       </c>
@@ -31836,7 +30783,7 @@
       <c r="P458" s="10"/>
       <c r="Q458" s="10"/>
     </row>
-    <row r="459" spans="1:18" ht="60">
+    <row r="459" spans="1:17" ht="60">
       <c r="A459">
         <v>458</v>
       </c>
@@ -31886,11 +30833,8 @@
         <v>1371</v>
       </c>
       <c r="Q459" s="10"/>
-      <c r="R459" t="s">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="460" spans="1:18" ht="120">
+    </row>
+    <row r="460" spans="1:17" ht="120">
       <c r="A460">
         <v>459</v>
       </c>
@@ -31940,11 +30884,8 @@
         <v>1374</v>
       </c>
       <c r="Q460" s="10"/>
-      <c r="R460" t="s">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="461" spans="1:18" ht="60">
+    </row>
+    <row r="461" spans="1:17" ht="60">
       <c r="A461">
         <v>460</v>
       </c>
@@ -31994,11 +30935,8 @@
         <v>1377</v>
       </c>
       <c r="Q461" s="10"/>
-      <c r="R461" t="s">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="462" spans="1:18" ht="45">
+    </row>
+    <row r="462" spans="1:17" ht="45">
       <c r="A462">
         <v>461</v>
       </c>
@@ -32048,11 +30986,8 @@
         <v>1380</v>
       </c>
       <c r="Q462" s="10"/>
-      <c r="R462" t="s">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="463" spans="1:18" ht="15">
+    </row>
+    <row r="463" spans="1:17" ht="15">
       <c r="A463">
         <v>462</v>
       </c>
@@ -32102,11 +31037,8 @@
         <v>1384</v>
       </c>
       <c r="Q463" s="10"/>
-      <c r="R463" t="s">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="464" spans="1:18">
+    </row>
+    <row r="464" spans="1:17">
       <c r="A464">
         <v>463</v>
       </c>
@@ -32134,7 +31066,7 @@
       <c r="P464" s="10"/>
       <c r="Q464" s="10"/>
     </row>
-    <row r="465" spans="1:18" ht="90">
+    <row r="465" spans="1:17" ht="90">
       <c r="A465">
         <v>464</v>
       </c>
@@ -32184,11 +31116,8 @@
         <v>1390</v>
       </c>
       <c r="Q465" s="10"/>
-      <c r="R465" t="s">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="466" spans="1:18" ht="45">
+    </row>
+    <row r="466" spans="1:17" ht="45">
       <c r="A466">
         <v>465</v>
       </c>
@@ -32238,11 +31167,8 @@
         <v>1393</v>
       </c>
       <c r="Q466" s="10"/>
-      <c r="R466" t="s">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="467" spans="1:18" ht="15">
+    </row>
+    <row r="467" spans="1:17" ht="15">
       <c r="A467">
         <v>466</v>
       </c>
@@ -32292,11 +31218,8 @@
         <v>1396</v>
       </c>
       <c r="Q467" s="10"/>
-      <c r="R467" t="s">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="468" spans="1:18" ht="45">
+    </row>
+    <row r="468" spans="1:17" ht="45">
       <c r="A468">
         <v>467</v>
       </c>
@@ -32346,11 +31269,8 @@
         <v>1400</v>
       </c>
       <c r="Q468" s="10"/>
-      <c r="R468" t="s">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="469" spans="1:18" ht="60">
+    </row>
+    <row r="469" spans="1:17" ht="60">
       <c r="A469">
         <v>468</v>
       </c>
@@ -32400,11 +31320,8 @@
         <v>1404</v>
       </c>
       <c r="Q469" s="10"/>
-      <c r="R469" t="s">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="470" spans="1:18" ht="75">
+    </row>
+    <row r="470" spans="1:17" ht="75">
       <c r="A470">
         <v>469</v>
       </c>
@@ -32454,11 +31371,8 @@
         <v>1408</v>
       </c>
       <c r="Q470" s="10"/>
-      <c r="R470" t="s">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="471" spans="1:18" ht="60">
+    </row>
+    <row r="471" spans="1:17" ht="60">
       <c r="A471">
         <v>470</v>
       </c>
@@ -32508,11 +31422,8 @@
         <v>1411</v>
       </c>
       <c r="Q471" s="10"/>
-      <c r="R471" t="s">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="472" spans="1:18" ht="60">
+    </row>
+    <row r="472" spans="1:17" ht="60">
       <c r="A472">
         <v>471</v>
       </c>
@@ -32562,11 +31473,8 @@
         <v>1414</v>
       </c>
       <c r="Q472" s="10"/>
-      <c r="R472" t="s">
-        <v>2029</v>
-      </c>
-    </row>
-    <row r="473" spans="1:18">
+    </row>
+    <row r="473" spans="1:17">
       <c r="A473">
         <v>472</v>
       </c>
@@ -32614,11 +31522,8 @@
       </c>
       <c r="P473" s="10"/>
       <c r="Q473" s="10"/>
-      <c r="R473" t="s">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="474" spans="1:18">
+    </row>
+    <row r="474" spans="1:17">
       <c r="A474">
         <v>473</v>
       </c>
@@ -32666,11 +31571,8 @@
       </c>
       <c r="P474" s="10"/>
       <c r="Q474" s="10"/>
-      <c r="R474" t="s">
-        <v>2031</v>
-      </c>
-    </row>
-    <row r="475" spans="1:18" ht="15">
+    </row>
+    <row r="475" spans="1:17" ht="15">
       <c r="A475">
         <v>474</v>
       </c>
@@ -32720,11 +31622,8 @@
         <v>138</v>
       </c>
       <c r="Q475" s="10"/>
-      <c r="R475" t="s">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="476" spans="1:18" ht="15">
+    </row>
+    <row r="476" spans="1:17" ht="15">
       <c r="A476">
         <v>475</v>
       </c>
@@ -32774,11 +31673,8 @@
         <v>1423</v>
       </c>
       <c r="Q476" s="10"/>
-      <c r="R476" t="s">
-        <v>2033</v>
-      </c>
-    </row>
-    <row r="477" spans="1:18" ht="15">
+    </row>
+    <row r="477" spans="1:17" ht="15">
       <c r="A477">
         <v>476</v>
       </c>
@@ -32828,11 +31724,8 @@
         <v>1426</v>
       </c>
       <c r="Q477" s="10"/>
-      <c r="R477" t="s">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="478" spans="1:18" ht="75">
+    </row>
+    <row r="478" spans="1:17" ht="75">
       <c r="A478">
         <v>477</v>
       </c>
@@ -32882,11 +31775,8 @@
         <v>1429</v>
       </c>
       <c r="Q478" s="10"/>
-      <c r="R478" t="s">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="479" spans="1:18">
+    </row>
+    <row r="479" spans="1:17">
       <c r="A479">
         <v>478</v>
       </c>
@@ -32911,11 +31801,8 @@
       <c r="O479" s="8"/>
       <c r="P479" s="10"/>
       <c r="Q479" s="10"/>
-      <c r="R479" t="s">
-        <v>2036</v>
-      </c>
-    </row>
-    <row r="480" spans="1:18">
+    </row>
+    <row r="480" spans="1:17">
       <c r="A480">
         <v>479</v>
       </c>
@@ -32943,7 +31830,7 @@
       <c r="P480" s="10"/>
       <c r="Q480" s="10"/>
     </row>
-    <row r="481" spans="1:18">
+    <row r="481" spans="1:17">
       <c r="A481">
         <v>480</v>
       </c>
@@ -32971,7 +31858,7 @@
       <c r="P481" s="10"/>
       <c r="Q481" s="10"/>
     </row>
-    <row r="482" spans="1:18">
+    <row r="482" spans="1:17">
       <c r="A482">
         <v>481</v>
       </c>
@@ -33019,11 +31906,8 @@
       </c>
       <c r="P482" s="10"/>
       <c r="Q482" s="10"/>
-      <c r="R482" t="s">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="483" spans="1:18" ht="15">
+    </row>
+    <row r="483" spans="1:17" ht="15">
       <c r="A483">
         <v>482</v>
       </c>
@@ -33073,11 +31957,8 @@
         <v>560</v>
       </c>
       <c r="Q483" s="10"/>
-      <c r="R483" t="s">
-        <v>2038</v>
-      </c>
-    </row>
-    <row r="484" spans="1:18" ht="30">
+    </row>
+    <row r="484" spans="1:17" ht="30">
       <c r="A484">
         <v>483</v>
       </c>
@@ -33127,11 +32008,8 @@
         <v>1443</v>
       </c>
       <c r="Q484" s="10"/>
-      <c r="R484" t="s">
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="485" spans="1:18" ht="60">
+    </row>
+    <row r="485" spans="1:17" ht="60">
       <c r="A485">
         <v>484</v>
       </c>
@@ -33181,11 +32059,8 @@
         <v>1446</v>
       </c>
       <c r="Q485" s="10"/>
-      <c r="R485" t="s">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="486" spans="1:18" ht="45">
+    </row>
+    <row r="486" spans="1:17" ht="45">
       <c r="A486">
         <v>485</v>
       </c>
@@ -33235,11 +32110,8 @@
         <v>1449</v>
       </c>
       <c r="Q486" s="10"/>
-      <c r="R486" t="s">
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="487" spans="1:18" ht="30">
+    </row>
+    <row r="487" spans="1:17" ht="30">
       <c r="A487">
         <v>486</v>
       </c>
@@ -33289,11 +32161,8 @@
         <v>1452</v>
       </c>
       <c r="Q487" s="10"/>
-      <c r="R487" t="s">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="488" spans="1:18" ht="45">
+    </row>
+    <row r="488" spans="1:17" ht="45">
       <c r="A488">
         <v>487</v>
       </c>
@@ -33343,11 +32212,8 @@
         <v>1455</v>
       </c>
       <c r="Q488" s="10"/>
-      <c r="R488" t="s">
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="489" spans="1:18">
+    </row>
+    <row r="489" spans="1:17">
       <c r="A489">
         <v>488</v>
       </c>
@@ -33395,11 +32261,8 @@
       </c>
       <c r="P489" s="10"/>
       <c r="Q489" s="10"/>
-      <c r="R489" t="s">
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="490" spans="1:18" ht="15">
+    </row>
+    <row r="490" spans="1:17" ht="15">
       <c r="A490">
         <v>489</v>
       </c>
@@ -33449,11 +32312,8 @@
         <v>138</v>
       </c>
       <c r="Q490" s="10"/>
-      <c r="R490" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="491" spans="1:18">
+    </row>
+    <row r="491" spans="1:17">
       <c r="A491">
         <v>490</v>
       </c>
@@ -33481,7 +32341,7 @@
       <c r="P491" s="10"/>
       <c r="Q491" s="10"/>
     </row>
-    <row r="492" spans="1:18" ht="30">
+    <row r="492" spans="1:17" ht="30">
       <c r="A492">
         <v>491</v>
       </c>
@@ -33531,11 +32391,8 @@
         <v>1464</v>
       </c>
       <c r="Q492" s="10"/>
-      <c r="R492" t="s">
-        <v>2046</v>
-      </c>
-    </row>
-    <row r="493" spans="1:18" ht="30">
+    </row>
+    <row r="493" spans="1:17" ht="30">
       <c r="A493">
         <v>492</v>
       </c>
@@ -33585,11 +32442,8 @@
         <v>1467</v>
       </c>
       <c r="Q493" s="10"/>
-      <c r="R493" t="s">
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="494" spans="1:18" ht="30">
+    </row>
+    <row r="494" spans="1:17" ht="30">
       <c r="A494">
         <v>493</v>
       </c>
@@ -33639,11 +32493,8 @@
         <v>1470</v>
       </c>
       <c r="Q494" s="10"/>
-      <c r="R494" t="s">
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="495" spans="1:18" ht="75">
+    </row>
+    <row r="495" spans="1:17" ht="75">
       <c r="A495">
         <v>494</v>
       </c>
@@ -33693,11 +32544,8 @@
         <v>1473</v>
       </c>
       <c r="Q495" s="10"/>
-      <c r="R495" t="s">
-        <v>2049</v>
-      </c>
-    </row>
-    <row r="496" spans="1:18" ht="45">
+    </row>
+    <row r="496" spans="1:17" ht="45">
       <c r="A496">
         <v>495</v>
       </c>
@@ -33747,11 +32595,8 @@
         <v>1476</v>
       </c>
       <c r="Q496" s="10"/>
-      <c r="R496" t="s">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="497" spans="1:18" ht="30">
+    </row>
+    <row r="497" spans="1:17" ht="30">
       <c r="A497">
         <v>496</v>
       </c>
@@ -33801,11 +32646,8 @@
         <v>1479</v>
       </c>
       <c r="Q497" s="10"/>
-      <c r="R497" t="s">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="498" spans="1:18" ht="45">
+    </row>
+    <row r="498" spans="1:17" ht="45">
       <c r="A498">
         <v>497</v>
       </c>
@@ -33855,11 +32697,8 @@
         <v>1482</v>
       </c>
       <c r="Q498" s="10"/>
-      <c r="R498" t="s">
-        <v>2052</v>
-      </c>
-    </row>
-    <row r="499" spans="1:18">
+    </row>
+    <row r="499" spans="1:17">
       <c r="A499">
         <v>498</v>
       </c>
@@ -33887,7 +32726,7 @@
       <c r="P499" s="10"/>
       <c r="Q499" s="10"/>
     </row>
-    <row r="500" spans="1:18">
+    <row r="500" spans="1:17">
       <c r="A500">
         <v>499</v>
       </c>
@@ -33915,7 +32754,7 @@
       <c r="P500" s="10"/>
       <c r="Q500" s="10"/>
     </row>
-    <row r="501" spans="1:18" ht="30">
+    <row r="501" spans="1:17" ht="30">
       <c r="A501">
         <v>500</v>
       </c>
@@ -33965,11 +32804,8 @@
         <v>1489</v>
       </c>
       <c r="Q501" s="10"/>
-      <c r="R501" t="s">
-        <v>2053</v>
-      </c>
-    </row>
-    <row r="502" spans="1:18" ht="45">
+    </row>
+    <row r="502" spans="1:17" ht="45">
       <c r="A502">
         <v>501</v>
       </c>
@@ -34019,11 +32855,8 @@
         <v>1492</v>
       </c>
       <c r="Q502" s="10"/>
-      <c r="R502" t="s">
-        <v>2054</v>
-      </c>
-    </row>
-    <row r="503" spans="1:18" ht="105">
+    </row>
+    <row r="503" spans="1:17" ht="105">
       <c r="A503">
         <v>502</v>
       </c>
@@ -34073,11 +32906,8 @@
         <v>1495</v>
       </c>
       <c r="Q503" s="10"/>
-      <c r="R503" t="s">
-        <v>2055</v>
-      </c>
-    </row>
-    <row r="504" spans="1:18" ht="60">
+    </row>
+    <row r="504" spans="1:17" ht="60">
       <c r="A504">
         <v>503</v>
       </c>
@@ -34127,11 +32957,8 @@
         <v>1498</v>
       </c>
       <c r="Q504" s="10"/>
-      <c r="R504" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="505" spans="1:18" ht="15">
+    </row>
+    <row r="505" spans="1:17" ht="15">
       <c r="A505">
         <v>504</v>
       </c>
@@ -34181,11 +33008,8 @@
         <v>1501</v>
       </c>
       <c r="Q505" s="10"/>
-      <c r="R505" t="s">
-        <v>2057</v>
-      </c>
-    </row>
-    <row r="506" spans="1:18" ht="15">
+    </row>
+    <row r="506" spans="1:17" ht="15">
       <c r="A506">
         <v>505</v>
       </c>
@@ -34235,11 +33059,8 @@
         <v>1504</v>
       </c>
       <c r="Q506" s="10"/>
-      <c r="R506" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="507" spans="1:18">
+    </row>
+    <row r="507" spans="1:17">
       <c r="A507">
         <v>506</v>
       </c>
@@ -34287,11 +33108,8 @@
       </c>
       <c r="P507" s="10"/>
       <c r="Q507" s="10"/>
-      <c r="R507" t="s">
-        <v>2059</v>
-      </c>
-    </row>
-    <row r="508" spans="1:18" ht="60">
+    </row>
+    <row r="508" spans="1:17" ht="60">
       <c r="A508">
         <v>507</v>
       </c>
@@ -34341,11 +33159,8 @@
         <v>1511</v>
       </c>
       <c r="Q508" s="10"/>
-      <c r="R508" t="s">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="509" spans="1:18" ht="30">
+    </row>
+    <row r="509" spans="1:17" ht="30">
       <c r="A509">
         <v>508</v>
       </c>
@@ -34395,11 +33210,8 @@
         <v>1515</v>
       </c>
       <c r="Q509" s="10"/>
-      <c r="R509" t="s">
-        <v>2061</v>
-      </c>
-    </row>
-    <row r="510" spans="1:18">
+    </row>
+    <row r="510" spans="1:17">
       <c r="A510">
         <v>509</v>
       </c>
@@ -34447,11 +33259,8 @@
       </c>
       <c r="P510" s="10"/>
       <c r="Q510" s="10"/>
-      <c r="R510" t="s">
-        <v>2062</v>
-      </c>
-    </row>
-    <row r="511" spans="1:18">
+    </row>
+    <row r="511" spans="1:17">
       <c r="A511">
         <v>510</v>
       </c>
@@ -34499,11 +33308,8 @@
       </c>
       <c r="P511" s="10"/>
       <c r="Q511" s="10"/>
-      <c r="R511" t="s">
-        <v>2063</v>
-      </c>
-    </row>
-    <row r="512" spans="1:18" ht="15">
+    </row>
+    <row r="512" spans="1:17" ht="15">
       <c r="A512">
         <v>511</v>
       </c>
@@ -34553,11 +33359,8 @@
         <v>1523</v>
       </c>
       <c r="Q512" s="10"/>
-      <c r="R512" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="513" spans="1:18" ht="15">
+    </row>
+    <row r="513" spans="1:17" ht="15">
       <c r="A513">
         <v>512</v>
       </c>
@@ -34607,11 +33410,8 @@
         <v>1526</v>
       </c>
       <c r="Q513" s="10"/>
-      <c r="R513" t="s">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="514" spans="1:18" ht="60">
+    </row>
+    <row r="514" spans="1:17" ht="60">
       <c r="A514">
         <v>513</v>
       </c>
@@ -34661,11 +33461,8 @@
         <v>1529</v>
       </c>
       <c r="Q514" s="10"/>
-      <c r="R514" t="s">
-        <v>2066</v>
-      </c>
-    </row>
-    <row r="515" spans="1:18" ht="45">
+    </row>
+    <row r="515" spans="1:17" ht="45">
       <c r="A515">
         <v>514</v>
       </c>
@@ -34715,11 +33512,8 @@
         <v>1532</v>
       </c>
       <c r="Q515" s="10"/>
-      <c r="R515" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="516" spans="1:18">
+    </row>
+    <row r="516" spans="1:17">
       <c r="A516">
         <v>515</v>
       </c>
@@ -34744,11 +33538,8 @@
       <c r="O516" s="8"/>
       <c r="P516" s="10"/>
       <c r="Q516" s="10"/>
-      <c r="R516" t="s">
-        <v>2068</v>
-      </c>
-    </row>
-    <row r="517" spans="1:18">
+    </row>
+    <row r="517" spans="1:17">
       <c r="A517">
         <v>516</v>
       </c>
@@ -34796,11 +33587,8 @@
       </c>
       <c r="P517" s="10"/>
       <c r="Q517" s="10"/>
-      <c r="R517" t="s">
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="518" spans="1:18" ht="45">
+    </row>
+    <row r="518" spans="1:17" ht="45">
       <c r="A518">
         <v>517</v>
       </c>
@@ -34850,11 +33638,8 @@
         <v>1539</v>
       </c>
       <c r="Q518" s="10"/>
-      <c r="R518" t="s">
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="519" spans="1:18" ht="135">
+    </row>
+    <row r="519" spans="1:17" ht="135">
       <c r="A519">
         <v>518</v>
       </c>
@@ -34904,11 +33689,8 @@
         <v>1543</v>
       </c>
       <c r="Q519" s="10"/>
-      <c r="R519" t="s">
-        <v>2071</v>
-      </c>
-    </row>
-    <row r="520" spans="1:18" ht="15">
+    </row>
+    <row r="520" spans="1:17" ht="15">
       <c r="A520">
         <v>519</v>
       </c>
@@ -34958,11 +33740,8 @@
         <v>1546</v>
       </c>
       <c r="Q520" s="10"/>
-      <c r="R520" t="s">
-        <v>2072</v>
-      </c>
-    </row>
-    <row r="521" spans="1:18" ht="15">
+    </row>
+    <row r="521" spans="1:17" ht="15">
       <c r="A521">
         <v>520</v>
       </c>
@@ -35012,11 +33791,8 @@
         <v>1549</v>
       </c>
       <c r="Q521" s="10"/>
-      <c r="R521" t="s">
-        <v>2073</v>
-      </c>
-    </row>
-    <row r="522" spans="1:18" ht="105">
+    </row>
+    <row r="522" spans="1:17" ht="105">
       <c r="A522">
         <v>521</v>
       </c>
@@ -35066,11 +33842,8 @@
         <v>1553</v>
       </c>
       <c r="Q522" s="10"/>
-      <c r="R522" t="s">
-        <v>2074</v>
-      </c>
-    </row>
-    <row r="523" spans="1:18" ht="30">
+    </row>
+    <row r="523" spans="1:17" ht="30">
       <c r="A523">
         <v>522</v>
       </c>
@@ -35120,11 +33893,8 @@
         <v>1556</v>
       </c>
       <c r="Q523" s="10"/>
-      <c r="R523" t="s">
-        <v>2075</v>
-      </c>
-    </row>
-    <row r="524" spans="1:18">
+    </row>
+    <row r="524" spans="1:17">
       <c r="A524">
         <v>523</v>
       </c>
@@ -35152,7 +33922,7 @@
       <c r="P524" s="10"/>
       <c r="Q524" s="10"/>
     </row>
-    <row r="525" spans="1:18" ht="30">
+    <row r="525" spans="1:17" ht="30">
       <c r="A525">
         <v>524</v>
       </c>
@@ -35202,11 +33972,8 @@
         <v>1561</v>
       </c>
       <c r="Q525" s="10"/>
-      <c r="R525" t="s">
-        <v>2076</v>
-      </c>
-    </row>
-    <row r="526" spans="1:18" ht="30">
+    </row>
+    <row r="526" spans="1:17" ht="30">
       <c r="A526">
         <v>525</v>
       </c>
@@ -35256,11 +34023,8 @@
         <v>1564</v>
       </c>
       <c r="Q526" s="10"/>
-      <c r="R526" t="s">
-        <v>2077</v>
-      </c>
-    </row>
-    <row r="527" spans="1:18" ht="60">
+    </row>
+    <row r="527" spans="1:17" ht="60">
       <c r="A527">
         <v>526</v>
       </c>
@@ -35310,11 +34074,8 @@
         <v>1568</v>
       </c>
       <c r="Q527" s="10"/>
-      <c r="R527" t="s">
-        <v>2078</v>
-      </c>
-    </row>
-    <row r="528" spans="1:18">
+    </row>
+    <row r="528" spans="1:17">
       <c r="A528">
         <v>527</v>
       </c>
@@ -35342,7 +34103,7 @@
       <c r="P528" s="10"/>
       <c r="Q528" s="10"/>
     </row>
-    <row r="529" spans="1:18" ht="90">
+    <row r="529" spans="1:17" ht="90">
       <c r="A529">
         <v>528</v>
       </c>
@@ -35392,11 +34153,8 @@
         <v>1573</v>
       </c>
       <c r="Q529" s="10"/>
-      <c r="R529" t="s">
-        <v>2079</v>
-      </c>
-    </row>
-    <row r="530" spans="1:18">
+    </row>
+    <row r="530" spans="1:17">
       <c r="A530">
         <v>529</v>
       </c>
@@ -35424,7 +34182,7 @@
       <c r="P530" s="10"/>
       <c r="Q530" s="10"/>
     </row>
-    <row r="531" spans="1:18">
+    <row r="531" spans="1:17">
       <c r="A531">
         <v>530</v>
       </c>
@@ -35486,9 +34244,6 @@
       <formula1>"単体,範囲"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="R64" r:id="rId1" xr:uid="{312950F6-4C75-A04C-96AC-F1790994E086}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7063624-E115-D94E-80E0-16A08B8F87A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FE3A86-03C1-944E-94BB-5612145789B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7492" uniqueCount="2223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7552" uniqueCount="2267">
   <si>
     <t>id</t>
   </si>
@@ -7825,12 +7825,434 @@
 身動きとれぬままに焼きつくされるという</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>ブタ小屋王国56代目女王のペット豚。
+服を着ての散歩の日課が苦痛で逃亡。
+大自然に飛び出し野ブタとして幸せな
+生活を送っている。服は後に地毛だと判明。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>厳しい野生の世界で片っ端から女性に
+アタックする超肉食系のゾウ。フラれ続け
+傷だらけになった末に、どんな妨害効果も
+無効化する強靭な精神力を手に入れた。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お見合い写真撮影のため、かつてこの世を
+支配した悪の大魔王へと56万年ぶりに
+姿を戻したお年頃のニャンダム。
+高身長、高学歴、高血糖の3高でアピール。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>地底迷宮の奥深くに棲む邪悪な魔導士
+罠で捕らえた勇者たちに延々と
+オチのない長話を聞かせる苦行を科す
+魔界に住む兄貴のドジ話は鉄板ネタ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>10と½周年記念ケーキわんこ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>天界の入国審査官を務めるラッコ
+聖なる祈りを込めた「ただの金塊」で
+天国へ行く資格なき者を地獄へ叩き落とす
+烈波を受けると魔物を召喚する</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>海外からやってきた外来生物の祖
+食の貪欲さから害虫駆除に期待されたが
+制御不能の暴食っぷりで手がつけられず
+今や自然界の脅威となっている</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>10浪目で受験勉強に疲れ果てた浪人生
+ゾンビには学校も試験も無いという噂を聞き
+思い切ってアンデッドデビューを果たしたが
+理想と現実のギャップに早くも後悔している</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>山奥の沼に暮らす所帯持ちの大妖怪
+自家製ゴーヤと強靭な肉体から繰り出す
+恐るべき一撃は外では無敵だが
+家庭ではかかあ天下で肩身が狭い。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>古代研究所の極秘技術でゲノム改造され
+超生命体として巨大化し生まれ変わった羊。
+個性的な姿に一時は満足したが
+もっと鼻筋も高くしたくなってきた。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>巷で流行りのソロキャンプを楽しむうちに
+野生の世界にハマってしまったワニ。
+BBQの炭で黒く染まった強靭な肉体で
+凶暴な王者として原生林に君臨している。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>この世の穢れに触れぬよう育てられた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="Avenir"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>エンジェルサイクロンの箱入り娘。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="Avenir"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>毎晩親が寝静まると家を抜け出して</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="Avenir"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>小烈波で世の中を浄化している。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>かつて善の心を持つ自らの分身に討たれ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="Avenir"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>秘境の奥地に封印されていた伝説の古龍。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="Avenir"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>封印されてなお増幅を続けた瘴気は獣たちを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="Avenir"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE0E0E0"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>超獣化させ、長い歳月を経て封印は解かれた。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>遥か高位の異次元から現世を観測し
+人類に干渉し知恵を与えていた超賢者。
+飽くなき知識欲を満たすため彷徨い続け
+にゃんこ軍団という未知の存在と遭遇。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>3連続攻撃 500 500 500（42F 45F 48F）
+遠方範囲全方位攻撃（1撃目0～500 2撃目750～1250 3撃目1500～2000）
+無効 （波動 ふっとばす 止める 遅くする 攻撃力低下）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>雑誌の最後に載っていた奇跡のお守りを
+肌身離さず身につけている浪人生わんこ。
+お守りパワーで試験問題の裏の裏まで
+読みすぎてしまい今年も浪人が確定。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>度の合わないメガネのせいで転び
+落ちていた石が額にめりこんだメガネザル。
+そのまま天国へ旅立った後は召されてきた
+者たちを見境なく論破している。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>謎の首輪をつける事で音楽に目覚めた犬。
+楽器は弾けないが豊富な音楽知識で
+ゴーストライターに作曲の指示を出し
+自分名義の楽曲として発表している。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>古代研究所が遺跡より発掘しゲノム改造を施す
+ことによって戦闘兵器と化した超巨大ハニワ。
+呪われない体質で数多の妨害波動を放ち
+戦うごとに凶暴性を増す。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>グレた息子に自分の勇姿を見せたくて
+ボクシング界に転身した科学者。
+必勝パワーストーンの効果で賢くなり
+試合で絶対バレないドーピングを開発。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>100％の確率でLv20波動（射程 4267.5）
+無効 （波動 ふっとばす 止める 遅くする 攻撃力低下）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>金目のものに目がない欲深きツバメ。
+妖しく光る石を拾ったことで宝石の
+出張買取ビジネスを閃く。出合い頭に
+受け取った品物の代金は出世払い。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>不死になったことで感情と引き換えに
+あらゆるお笑いの知識を得たピン芸人。
+記憶力の衰えによりライブ中にネタを
+よく飛ばすものの、本人的には無問題。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>人類を超える完全な生命の創造を目指し
+太古の世界へ渡った研究者の成れの果て。
+にゃんこ軍団を異次元へと導いた後、
+研究中の結晶に自我を奪われてしまった。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>検体No.???　状態：不安定　古ノ微生物検出
+戦闘エネルギー値：計測不能
+種ノ保存ヲ優先ニ増殖スル特性アリ
+主ノ悲願タル完全生命ノ誕生ハ近イ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>不思議な角帽を被った途端に裏社会の
+あらゆる知識を注ぎ込まれた博士。
+ディープでスリリングな闇の講義を開き
+純粋な学生達を破滅へと向かわせる。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>体罰が問題視され大自然へ追放された
+危険な先生。自分のテリトリーに踏み入る
+獣は教え子とみなし拳で愛を説いてきた。
+野生の世界では百獣の王と恐れられている。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>獰猛ですごい食欲の古代魚。
+海底で見つけた不思議な石を食べた瞬間
+頭の回転が速くなり、更に漁技術が向上。
+海域の魚が絶滅寸前に陥っている。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>密漁者によって仲間が大量に乱獲され
+怒り狂ったフグ。敵の活動拠点を
+壊滅させるため、単身で転がり込み
+カチコミをかます命知らず。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>遥か彼方の星から侵略にきたダチョウ。
+部下の裏切りによって宇宙船を奪われ
+取り残された。救難信号を送り続けて
+迎えが来るのを首を長くして待つ。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>遥か高位の異次元から現世を観測し
+才を見い出した者に科学の種をもたらしていた
+超賢者。にゃんこ軍団という測定不能な
+存在を徹底的に分析すべく対峙する。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>投打の両方で歴史的な好成績を残した
+野球選手。謎の石のパワーで驚異の
+九刀流によるワンマンチームが可能に
+なったものの、忙しすぎて過労死した。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>嵐を呼ぶパラソル城</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>100％の確率で60F動きを止める
+無効 （波動 烈波 爆波 ふっとばす 止める 遅くする 攻撃力低下）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>100％の確率で150F動きを止める
+無効 （波動 ふっとばす 止める 遅くする 攻撃力低下）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>停止木人城</t>
+  </si>
+  <si>
+    <t>古代研究所の極秘技術でゲノム改造された
+天界の秘密兵器。ステルスで隠せないほど
+巨大化した。姿を目撃してしまった者は
+動きを遅くする波動攻撃で消される。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大好きなおやつの骨を求めてさ迷い歩くゾンビ。
+お腹を貫く骨の存在に気付いてはいるが
+手足が短いせいで抜ける気配がまったくない。
+誰かに手伝ってほしいものの、逃げられてしまう。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>闇の球技大会でボールとすり替わり
+数々の試合の勝敗をコントロール
+してきた陰の立役者。
+サッカーボール役が正直きつい。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エッチなものを見ると真っ赤になって
+取り締まりを行う風紀委員のゾウ。
+本当は興味津々で、没収した戦利品は
+自分の秘蔵コレクションにしている。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>鳥ならトリオを組むべきという
+安直な考えで結成されたトリオ芸人。
+数うちゃ当たるの精神でボケを連発し
+たまに爆笑の渦を巻き起こす。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>遥か高位の異次元より現世を観測し
+生命に淘汰の試練を課す超賢者。
+進化の理を超えるにゃんこ軍団の元へ
+因果の糸を辿り静かに歩み寄る。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>時空の裂け目から魔界に迷い込み
+そこで謎の石を取り込んだ驚異の生命体。
+相手の動きを止めた隙に商品を売る
+悪魔的ビジネスで巨万の富を築き上げた。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>範囲3回攻撃 196000 63000 51000(7F 17F 27F)
+40%でLv2波動(波動の攻撃力は３撃目に対応)
+体力残り25%で攻撃1.5倍</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7885,6 +8307,26 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFE0E0E0"/>
+      <name val="Avenir"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFE0E0E0"/>
+      <name val="MS Mincho"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFE0E0E0"/>
+      <name val="Avenir"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -7912,7 +8354,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7938,6 +8380,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -8177,7 +8623,7 @@
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="3" max="3" width="28" style="6" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="26.1640625" customWidth="1"/>
     <col min="6" max="6" width="14.5" customWidth="1"/>
@@ -8200,7 +8646,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -8253,7 +8699,7 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D2" t="s">
@@ -8305,7 +8751,7 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D3" t="s">
@@ -8356,7 +8802,7 @@
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D4" t="s">
@@ -8407,7 +8853,7 @@
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D5" t="s">
@@ -8458,7 +8904,7 @@
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6" t="s">
         <v>33</v>
       </c>
       <c r="D6" t="s">
@@ -8509,7 +8955,7 @@
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D7" t="s">
@@ -8560,7 +9006,7 @@
       <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D8" t="s">
@@ -8611,7 +9057,7 @@
       <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
         <v>43</v>
       </c>
       <c r="D9" t="s">
@@ -8662,7 +9108,7 @@
       <c r="B10">
         <v>9</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D10" t="s">
@@ -8713,7 +9159,7 @@
       <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D11" t="s">
@@ -8764,7 +9210,7 @@
       <c r="B12">
         <v>11</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D12" t="s">
@@ -8817,7 +9263,7 @@
       <c r="B13">
         <v>12</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="6" t="s">
         <v>56</v>
       </c>
       <c r="D13" t="s">
@@ -8868,7 +9314,7 @@
       <c r="B14">
         <v>13</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>59</v>
       </c>
       <c r="D14" t="s">
@@ -8919,7 +9365,7 @@
       <c r="B15">
         <v>14</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D15" t="s">
@@ -8970,7 +9416,7 @@
       <c r="B16">
         <v>15</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="6" t="s">
         <v>65</v>
       </c>
       <c r="D16" t="s">
@@ -9021,7 +9467,7 @@
       <c r="B17">
         <v>16</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D17" t="s">
@@ -9072,7 +9518,7 @@
       <c r="B18">
         <v>17</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D18" t="s">
@@ -9123,7 +9569,7 @@
       <c r="B19">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="6" t="s">
         <v>75</v>
       </c>
       <c r="D19" t="s">
@@ -9174,7 +9620,7 @@
       <c r="B20">
         <v>19</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="6" t="s">
         <v>79</v>
       </c>
       <c r="D20" t="s">
@@ -9225,7 +9671,7 @@
       <c r="B21">
         <v>20</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="6" t="s">
         <v>83</v>
       </c>
       <c r="D21" t="s">
@@ -9254,7 +9700,7 @@
       <c r="B22">
         <v>21</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="6" t="s">
         <v>85</v>
       </c>
       <c r="D22" t="s">
@@ -9305,7 +9751,7 @@
       <c r="B23">
         <v>22</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="6" t="s">
         <v>88</v>
       </c>
       <c r="D23" t="s">
@@ -9356,7 +9802,7 @@
       <c r="B24">
         <v>23</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="6" t="s">
         <v>91</v>
       </c>
       <c r="D24" t="s">
@@ -9407,7 +9853,7 @@
       <c r="B25">
         <v>24</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="6" t="s">
         <v>94</v>
       </c>
       <c r="D25" t="s">
@@ -9458,7 +9904,7 @@
       <c r="B26">
         <v>25</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="6" t="s">
         <v>97</v>
       </c>
       <c r="D26" t="s">
@@ -9509,7 +9955,7 @@
       <c r="B27">
         <v>26</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="6" t="s">
         <v>100</v>
       </c>
       <c r="D27" t="s">
@@ -9562,7 +10008,7 @@
       <c r="B28">
         <v>27</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="6" t="s">
         <v>104</v>
       </c>
       <c r="D28" t="s">
@@ -9613,7 +10059,7 @@
       <c r="B29">
         <v>28</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="6" t="s">
         <v>107</v>
       </c>
       <c r="D29" t="s">
@@ -9666,7 +10112,7 @@
       <c r="B30">
         <v>29</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="6" t="s">
         <v>111</v>
       </c>
       <c r="D30" t="s">
@@ -9719,7 +10165,7 @@
       <c r="B31">
         <v>30</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="6" t="s">
         <v>115</v>
       </c>
       <c r="D31" t="s">
@@ -9772,7 +10218,7 @@
       <c r="B32">
         <v>31</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="6" t="s">
         <v>119</v>
       </c>
       <c r="D32" t="s">
@@ -9823,7 +10269,7 @@
       <c r="B33">
         <v>32</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="6" t="s">
         <v>122</v>
       </c>
       <c r="D33" t="s">
@@ -9874,7 +10320,7 @@
       <c r="B34">
         <v>33</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="6" t="s">
         <v>125</v>
       </c>
       <c r="D34" t="s">
@@ -9925,7 +10371,7 @@
       <c r="B35">
         <v>34</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="6" t="s">
         <v>128</v>
       </c>
       <c r="D35" t="s">
@@ -9976,7 +10422,7 @@
       <c r="B36">
         <v>35</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="6" t="s">
         <v>131</v>
       </c>
       <c r="D36" t="s">
@@ -10027,7 +10473,7 @@
       <c r="B37">
         <v>36</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="6" t="s">
         <v>134</v>
       </c>
       <c r="D37" t="s">
@@ -10078,7 +10524,7 @@
       <c r="B38">
         <v>37</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="10" t="s">
         <v>137</v>
       </c>
       <c r="D38" t="s">
@@ -10131,7 +10577,7 @@
       <c r="B39">
         <v>38</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="6" t="s">
         <v>141</v>
       </c>
       <c r="D39" t="s">
@@ -10184,7 +10630,7 @@
       <c r="B40">
         <v>39</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="6" t="s">
         <v>145</v>
       </c>
       <c r="D40" t="s">
@@ -10235,7 +10681,7 @@
       <c r="B41">
         <v>40</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="6" t="s">
         <v>148</v>
       </c>
       <c r="D41" t="s">
@@ -10286,7 +10732,7 @@
       <c r="B42">
         <v>41</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="6" t="s">
         <v>151</v>
       </c>
       <c r="D42" t="s">
@@ -10337,7 +10783,7 @@
       <c r="B43">
         <v>42</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="6" t="s">
         <v>155</v>
       </c>
       <c r="D43" t="s">
@@ -10388,7 +10834,7 @@
       <c r="B44">
         <v>43</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="6" t="s">
         <v>158</v>
       </c>
       <c r="D44" t="s">
@@ -10439,7 +10885,7 @@
       <c r="B45">
         <v>44</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="6" t="s">
         <v>162</v>
       </c>
       <c r="D45" t="s">
@@ -10490,7 +10936,7 @@
       <c r="B46">
         <v>45</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="6" t="s">
         <v>166</v>
       </c>
       <c r="D46" t="s">
@@ -10541,7 +10987,7 @@
       <c r="B47">
         <v>46</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="6" t="s">
         <v>169</v>
       </c>
       <c r="D47" t="s">
@@ -10594,7 +11040,7 @@
       <c r="B48">
         <v>47</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="6" t="s">
         <v>173</v>
       </c>
       <c r="D48" t="s">
@@ -10645,7 +11091,7 @@
       <c r="B49">
         <v>48</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="6" t="s">
         <v>176</v>
       </c>
       <c r="D49" t="s">
@@ -10698,7 +11144,7 @@
       <c r="B50">
         <v>49</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="6" t="s">
         <v>179</v>
       </c>
       <c r="D50" t="s">
@@ -10749,7 +11195,7 @@
       <c r="B51">
         <v>50</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="6" t="s">
         <v>182</v>
       </c>
       <c r="D51" t="s">
@@ -10800,7 +11246,7 @@
       <c r="B52">
         <v>51</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="6" t="s">
         <v>185</v>
       </c>
       <c r="D52" t="s">
@@ -10853,7 +11299,7 @@
       <c r="B53">
         <v>52</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="6" t="s">
         <v>189</v>
       </c>
       <c r="D53" t="s">
@@ -10904,7 +11350,7 @@
       <c r="B54">
         <v>53</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="6" t="s">
         <v>192</v>
       </c>
       <c r="D54" t="s">
@@ -10953,7 +11399,7 @@
       <c r="B55">
         <v>54</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="6" t="s">
         <v>194</v>
       </c>
       <c r="D55" t="s">
@@ -11006,7 +11452,7 @@
       <c r="B56">
         <v>55</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="6" t="s">
         <v>199</v>
       </c>
       <c r="D56" t="s">
@@ -11057,7 +11503,7 @@
       <c r="B57">
         <v>56</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="6" t="s">
         <v>202</v>
       </c>
       <c r="D57" t="s">
@@ -11108,7 +11554,7 @@
       <c r="B58">
         <v>57</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="6" t="s">
         <v>205</v>
       </c>
       <c r="D58" t="s">
@@ -11159,7 +11605,7 @@
       <c r="B59">
         <v>58</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="6" t="s">
         <v>207</v>
       </c>
       <c r="D59" t="s">
@@ -11210,7 +11656,7 @@
       <c r="B60">
         <v>59</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="6" t="s">
         <v>209</v>
       </c>
       <c r="D60" t="s">
@@ -11261,7 +11707,7 @@
       <c r="B61">
         <v>60</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="6" t="s">
         <v>212</v>
       </c>
       <c r="D61" t="s">
@@ -11314,7 +11760,7 @@
       <c r="B62">
         <v>61</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="6" t="s">
         <v>215</v>
       </c>
       <c r="D62" t="s">
@@ -11365,7 +11811,7 @@
       <c r="B63">
         <v>62</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="6" t="s">
         <v>218</v>
       </c>
       <c r="D63" t="s">
@@ -11416,7 +11862,7 @@
       <c r="B64">
         <v>63</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="6" t="s">
         <v>220</v>
       </c>
       <c r="D64" t="s">
@@ -11468,7 +11914,7 @@
       <c r="B65">
         <v>64</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="6" t="s">
         <v>223</v>
       </c>
       <c r="D65" t="s">
@@ -11519,7 +11965,7 @@
       <c r="B66">
         <v>65</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="6" t="s">
         <v>226</v>
       </c>
       <c r="D66" t="s">
@@ -11570,7 +12016,7 @@
       <c r="B67">
         <v>66</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="6" t="s">
         <v>228</v>
       </c>
       <c r="D67" t="s">
@@ -11619,7 +12065,7 @@
       <c r="B68">
         <v>67</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D68" t="s">
@@ -11670,7 +12116,7 @@
       <c r="B69">
         <v>68</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="6" t="s">
         <v>233</v>
       </c>
       <c r="D69" t="s">
@@ -11721,7 +12167,7 @@
       <c r="B70">
         <v>69</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="6" t="s">
         <v>236</v>
       </c>
       <c r="D70" t="s">
@@ -11772,7 +12218,7 @@
       <c r="B71">
         <v>70</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="6" t="s">
         <v>239</v>
       </c>
       <c r="D71" t="s">
@@ -11823,7 +12269,7 @@
       <c r="B72">
         <v>71</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="6" t="s">
         <v>241</v>
       </c>
       <c r="D72" t="s">
@@ -11874,7 +12320,7 @@
       <c r="B73">
         <v>72</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="6" t="s">
         <v>243</v>
       </c>
       <c r="D73" t="s">
@@ -11925,7 +12371,7 @@
       <c r="B74">
         <v>73</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="6" t="s">
         <v>246</v>
       </c>
       <c r="D74" t="s">
@@ -11974,7 +12420,7 @@
       <c r="B75">
         <v>74</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="6" t="s">
         <v>248</v>
       </c>
       <c r="D75" t="s">
@@ -12025,7 +12471,7 @@
       <c r="B76">
         <v>75</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="6" t="s">
         <v>250</v>
       </c>
       <c r="D76" t="s">
@@ -12074,7 +12520,7 @@
       <c r="B77">
         <v>76</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="6" t="s">
         <v>252</v>
       </c>
       <c r="D77" t="s">
@@ -12123,7 +12569,7 @@
       <c r="B78">
         <v>77</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="6" t="s">
         <v>254</v>
       </c>
       <c r="D78" t="s">
@@ -12172,7 +12618,7 @@
       <c r="B79">
         <v>78</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="6" t="s">
         <v>256</v>
       </c>
       <c r="D79" t="s">
@@ -12221,7 +12667,7 @@
       <c r="B80">
         <v>79</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="6" t="s">
         <v>258</v>
       </c>
       <c r="D80" t="s">
@@ -12270,7 +12716,7 @@
       <c r="B81">
         <v>80</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="6" t="s">
         <v>260</v>
       </c>
       <c r="D81" t="s">
@@ -12319,7 +12765,7 @@
       <c r="B82">
         <v>81</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="6" t="s">
         <v>262</v>
       </c>
       <c r="D82" t="s">
@@ -12368,7 +12814,7 @@
       <c r="B83">
         <v>82</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="6" t="s">
         <v>264</v>
       </c>
       <c r="D83" t="s">
@@ -12417,7 +12863,7 @@
       <c r="B84">
         <v>83</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="6" t="s">
         <v>266</v>
       </c>
       <c r="D84" t="s">
@@ -12466,7 +12912,7 @@
       <c r="B85">
         <v>84</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="6" t="s">
         <v>268</v>
       </c>
       <c r="D85" t="s">
@@ -12515,7 +12961,7 @@
       <c r="B86">
         <v>85</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="6" t="s">
         <v>270</v>
       </c>
       <c r="D86" t="s">
@@ -12564,7 +13010,7 @@
       <c r="B87">
         <v>86</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="6" t="s">
         <v>272</v>
       </c>
       <c r="D87" t="s">
@@ -12613,7 +13059,7 @@
       <c r="B88">
         <v>87</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="6" t="s">
         <v>274</v>
       </c>
       <c r="D88" t="s">
@@ -12662,7 +13108,7 @@
       <c r="B89">
         <v>88</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="6" t="s">
         <v>276</v>
       </c>
       <c r="D89" t="s">
@@ -12713,7 +13159,7 @@
       <c r="B90">
         <v>89</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="6" t="s">
         <v>280</v>
       </c>
       <c r="D90" t="s">
@@ -12764,7 +13210,7 @@
       <c r="B91">
         <v>90</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="6" t="s">
         <v>283</v>
       </c>
       <c r="D91" t="s">
@@ -12815,7 +13261,7 @@
       <c r="B92">
         <v>91</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="6" t="s">
         <v>286</v>
       </c>
       <c r="D92" t="s">
@@ -12866,7 +13312,7 @@
       <c r="B93">
         <v>92</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="6" t="s">
         <v>289</v>
       </c>
       <c r="D93" t="s">
@@ -12917,7 +13363,7 @@
       <c r="B94">
         <v>93</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="6" t="s">
         <v>292</v>
       </c>
       <c r="D94" t="s">
@@ -12968,7 +13414,7 @@
       <c r="B95">
         <v>94</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="6" t="s">
         <v>295</v>
       </c>
       <c r="D95" t="s">
@@ -13019,7 +13465,7 @@
       <c r="B96">
         <v>95</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="6" t="s">
         <v>298</v>
       </c>
       <c r="D96" t="s">
@@ -13072,7 +13518,7 @@
       <c r="B97">
         <v>96</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="6" t="s">
         <v>302</v>
       </c>
       <c r="D97" t="s">
@@ -13098,7 +13544,7 @@
       <c r="B98">
         <v>97</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="6" t="s">
         <v>304</v>
       </c>
       <c r="D98" t="s">
@@ -13151,7 +13597,7 @@
       <c r="B99">
         <v>98</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="6" t="s">
         <v>308</v>
       </c>
       <c r="D99" t="s">
@@ -13202,7 +13648,7 @@
       <c r="B100">
         <v>99</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="6" t="s">
         <v>311</v>
       </c>
       <c r="D100" t="s">
@@ -13255,7 +13701,7 @@
       <c r="B101">
         <v>100</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="6" t="s">
         <v>315</v>
       </c>
       <c r="D101" t="s">
@@ -13306,7 +13752,7 @@
       <c r="B102">
         <v>101</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="6" t="s">
         <v>318</v>
       </c>
       <c r="D102" t="s">
@@ -13355,7 +13801,7 @@
       <c r="B103">
         <v>102</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="6" t="s">
         <v>320</v>
       </c>
       <c r="D103" t="s">
@@ -13404,7 +13850,7 @@
       <c r="B104">
         <v>103</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="6" t="s">
         <v>322</v>
       </c>
       <c r="D104" t="s">
@@ -13453,7 +13899,7 @@
       <c r="B105">
         <v>104</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="6" t="s">
         <v>324</v>
       </c>
       <c r="D105" t="s">
@@ -13502,7 +13948,7 @@
       <c r="B106">
         <v>105</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="6" t="s">
         <v>326</v>
       </c>
       <c r="D106" t="s">
@@ -13551,7 +13997,7 @@
       <c r="B107">
         <v>106</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="6" t="s">
         <v>328</v>
       </c>
       <c r="D107" t="s">
@@ -13600,7 +14046,7 @@
       <c r="B108">
         <v>107</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="6" t="s">
         <v>330</v>
       </c>
       <c r="D108" t="s">
@@ -13649,7 +14095,7 @@
       <c r="B109">
         <v>108</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="6" t="s">
         <v>332</v>
       </c>
       <c r="D109" t="s">
@@ -13698,7 +14144,7 @@
       <c r="B110">
         <v>109</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="6" t="s">
         <v>334</v>
       </c>
       <c r="D110" t="s">
@@ -13747,7 +14193,7 @@
       <c r="B111">
         <v>110</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="6" t="s">
         <v>336</v>
       </c>
       <c r="D111" t="s">
@@ -13796,7 +14242,7 @@
       <c r="B112">
         <v>111</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="6" t="s">
         <v>338</v>
       </c>
       <c r="D112" t="s">
@@ -13847,7 +14293,7 @@
       <c r="B113">
         <v>112</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="6" t="s">
         <v>341</v>
       </c>
       <c r="D113" t="s">
@@ -13898,7 +14344,7 @@
       <c r="B114">
         <v>113</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D114" t="s">
@@ -13949,7 +14395,7 @@
       <c r="B115">
         <v>114</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="6" t="s">
         <v>347</v>
       </c>
       <c r="D115" t="s">
@@ -13998,7 +14444,7 @@
       <c r="B116">
         <v>115</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="6" t="s">
         <v>349</v>
       </c>
       <c r="D116" t="s">
@@ -14051,7 +14497,7 @@
       <c r="B117">
         <v>116</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="6" t="s">
         <v>352</v>
       </c>
       <c r="D117" t="s">
@@ -14102,7 +14548,7 @@
       <c r="B118">
         <v>117</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="6" t="s">
         <v>355</v>
       </c>
       <c r="D118" t="s">
@@ -14153,7 +14599,7 @@
       <c r="B119">
         <v>118</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="6" t="s">
         <v>358</v>
       </c>
       <c r="D119" t="s">
@@ -14204,7 +14650,7 @@
       <c r="B120">
         <v>119</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="6" t="s">
         <v>361</v>
       </c>
       <c r="D120" t="s">
@@ -14253,7 +14699,7 @@
       <c r="B121">
         <v>120</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="6" t="s">
         <v>363</v>
       </c>
       <c r="D121" t="s">
@@ -14306,7 +14752,7 @@
       <c r="B122">
         <v>121</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="6" t="s">
         <v>367</v>
       </c>
       <c r="D122" t="s">
@@ -14357,7 +14803,7 @@
       <c r="B123">
         <v>122</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="6" t="s">
         <v>371</v>
       </c>
       <c r="D123" t="s">
@@ -14408,7 +14854,7 @@
       <c r="B124">
         <v>123</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="6" t="s">
         <v>374</v>
       </c>
       <c r="D124" t="s">
@@ -14459,7 +14905,7 @@
       <c r="B125">
         <v>124</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="6" t="s">
         <v>377</v>
       </c>
       <c r="D125" t="s">
@@ -14512,7 +14958,7 @@
       <c r="B126">
         <v>125</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="6" t="s">
         <v>382</v>
       </c>
       <c r="D126" t="s">
@@ -14565,7 +15011,7 @@
       <c r="B127">
         <v>126</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="6" t="s">
         <v>386</v>
       </c>
       <c r="D127" t="s">
@@ -14618,7 +15064,7 @@
       <c r="B128">
         <v>127</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="6" t="s">
         <v>390</v>
       </c>
       <c r="D128" t="s">
@@ -14671,7 +15117,7 @@
       <c r="B129">
         <v>128</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="6" t="s">
         <v>394</v>
       </c>
       <c r="D129" t="s">
@@ -14724,7 +15170,7 @@
       <c r="B130">
         <v>129</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="6" t="s">
         <v>397</v>
       </c>
       <c r="D130" t="s">
@@ -14777,7 +15223,7 @@
       <c r="B131">
         <v>130</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="6" t="s">
         <v>401</v>
       </c>
       <c r="D131" t="s">
@@ -14830,7 +15276,7 @@
       <c r="B132">
         <v>131</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="6" t="s">
         <v>405</v>
       </c>
       <c r="D132" t="s">
@@ -14883,7 +15329,7 @@
       <c r="B133">
         <v>132</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="6" t="s">
         <v>408</v>
       </c>
       <c r="D133" t="s">
@@ -14936,7 +15382,7 @@
       <c r="B134">
         <v>133</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="6" t="s">
         <v>411</v>
       </c>
       <c r="D134" t="s">
@@ -14989,7 +15435,7 @@
       <c r="B135">
         <v>134</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="6" t="s">
         <v>415</v>
       </c>
       <c r="D135" t="s">
@@ -15042,7 +15488,7 @@
       <c r="B136">
         <v>135</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" s="6" t="s">
         <v>419</v>
       </c>
       <c r="D136" t="s">
@@ -15095,7 +15541,7 @@
       <c r="B137">
         <v>136</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="6" t="s">
         <v>423</v>
       </c>
       <c r="D137" t="s">
@@ -15148,7 +15594,7 @@
       <c r="B138">
         <v>137</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="6" t="s">
         <v>426</v>
       </c>
       <c r="D138" t="s">
@@ -15199,7 +15645,7 @@
       <c r="B139">
         <v>138</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="6" t="s">
         <v>429</v>
       </c>
       <c r="D139" t="s">
@@ -15252,7 +15698,7 @@
       <c r="B140">
         <v>139</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="6" t="s">
         <v>433</v>
       </c>
       <c r="D140" t="s">
@@ -15351,7 +15797,7 @@
       <c r="B142">
         <v>141</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C142" s="6" t="s">
         <v>438</v>
       </c>
       <c r="D142" t="s">
@@ -15400,7 +15846,7 @@
       <c r="B143">
         <v>142</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C143" s="6" t="s">
         <v>440</v>
       </c>
       <c r="D143" t="s">
@@ -15451,7 +15897,7 @@
       <c r="B144">
         <v>143</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C144" s="6" t="s">
         <v>443</v>
       </c>
       <c r="D144" t="s">
@@ -15500,7 +15946,7 @@
       <c r="B145">
         <v>144</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C145" s="6" t="s">
         <v>445</v>
       </c>
       <c r="D145" t="s">
@@ -15553,7 +15999,7 @@
       <c r="B146">
         <v>145</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="6" t="s">
         <v>449</v>
       </c>
       <c r="D146" t="s">
@@ -15606,7 +16052,7 @@
       <c r="B147">
         <v>146</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="6" t="s">
         <v>453</v>
       </c>
       <c r="D147" t="s">
@@ -15657,7 +16103,7 @@
       <c r="B148">
         <v>147</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C148" s="6" t="s">
         <v>456</v>
       </c>
       <c r="D148" t="s">
@@ -15710,7 +16156,7 @@
       <c r="B149">
         <v>148</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="6" t="s">
         <v>460</v>
       </c>
       <c r="D149" t="s">
@@ -15763,7 +16209,7 @@
       <c r="B150">
         <v>149</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C150" s="6" t="s">
         <v>464</v>
       </c>
       <c r="D150" t="s">
@@ -15816,7 +16262,7 @@
       <c r="B151">
         <v>150</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="6" t="s">
         <v>467</v>
       </c>
       <c r="D151" t="s">
@@ -15869,7 +16315,7 @@
       <c r="B152">
         <v>151</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C152" s="6" t="s">
         <v>471</v>
       </c>
       <c r="D152" t="s">
@@ -15922,7 +16368,7 @@
       <c r="B153">
         <v>152</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C153" s="6" t="s">
         <v>475</v>
       </c>
       <c r="D153" t="s">
@@ -15973,7 +16419,7 @@
       <c r="B154">
         <v>153</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C154" s="6" t="s">
         <v>478</v>
       </c>
       <c r="D154" t="s">
@@ -16024,7 +16470,7 @@
       <c r="B155">
         <v>154</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C155" s="6" t="s">
         <v>481</v>
       </c>
       <c r="D155" t="s">
@@ -16075,7 +16521,7 @@
       <c r="B156">
         <v>155</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C156" s="6" t="s">
         <v>484</v>
       </c>
       <c r="D156" t="s">
@@ -16128,7 +16574,7 @@
       <c r="B157">
         <v>156</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C157" s="6" t="s">
         <v>488</v>
       </c>
       <c r="D157" t="s">
@@ -16179,7 +16625,7 @@
       <c r="B158">
         <v>157</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C158" s="6" t="s">
         <v>490</v>
       </c>
       <c r="D158" t="s">
@@ -16228,7 +16674,7 @@
       <c r="B159">
         <v>158</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C159" s="6" t="s">
         <v>492</v>
       </c>
       <c r="D159" t="s">
@@ -16281,7 +16727,7 @@
       <c r="B160">
         <v>159</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C160" s="6" t="s">
         <v>496</v>
       </c>
       <c r="D160" t="s">
@@ -16334,7 +16780,7 @@
       <c r="B161">
         <v>160</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C161" s="6" t="s">
         <v>500</v>
       </c>
       <c r="D161" t="s">
@@ -16383,7 +16829,7 @@
       <c r="B162">
         <v>161</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C162" s="6" t="s">
         <v>502</v>
       </c>
       <c r="D162" t="s">
@@ -16434,7 +16880,7 @@
       <c r="B163">
         <v>162</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C163" s="6" t="s">
         <v>504</v>
       </c>
       <c r="D163" t="s">
@@ -16485,7 +16931,7 @@
       <c r="B164">
         <v>163</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C164" s="6" t="s">
         <v>507</v>
       </c>
       <c r="D164" t="s">
@@ -16536,7 +16982,7 @@
       <c r="B165">
         <v>164</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C165" s="6" t="s">
         <v>510</v>
       </c>
       <c r="D165" t="s">
@@ -16585,7 +17031,7 @@
       <c r="B166">
         <v>165</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C166" s="6" t="s">
         <v>512</v>
       </c>
       <c r="D166" t="s">
@@ -16634,7 +17080,7 @@
       <c r="B167">
         <v>166</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C167" s="6" t="s">
         <v>514</v>
       </c>
       <c r="D167" t="s">
@@ -16685,7 +17131,7 @@
       <c r="B168">
         <v>167</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C168" s="6" t="s">
         <v>516</v>
       </c>
       <c r="D168" t="s">
@@ -16734,7 +17180,7 @@
       <c r="B169">
         <v>168</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C169" s="6" t="s">
         <v>518</v>
       </c>
       <c r="D169" t="s">
@@ -16785,7 +17231,7 @@
       <c r="B170">
         <v>169</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C170" s="6" t="s">
         <v>521</v>
       </c>
       <c r="D170" t="s">
@@ -16834,7 +17280,7 @@
       <c r="B171">
         <v>170</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="6" t="s">
         <v>523</v>
       </c>
       <c r="D171" t="s">
@@ -16885,7 +17331,7 @@
       <c r="B172">
         <v>171</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C172" s="6" t="s">
         <v>526</v>
       </c>
       <c r="D172" t="s">
@@ -16936,7 +17382,7 @@
       <c r="B173">
         <v>172</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C173" s="6" t="s">
         <v>528</v>
       </c>
       <c r="D173" t="s">
@@ -16989,7 +17435,7 @@
       <c r="B174">
         <v>173</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C174" s="6" t="s">
         <v>532</v>
       </c>
       <c r="D174" t="s">
@@ -17042,7 +17488,7 @@
       <c r="B175">
         <v>174</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C175" s="6" t="s">
         <v>536</v>
       </c>
       <c r="D175" t="s">
@@ -17095,7 +17541,7 @@
       <c r="B176">
         <v>175</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C176" s="6" t="s">
         <v>540</v>
       </c>
       <c r="D176" t="s">
@@ -17148,7 +17594,7 @@
       <c r="B177">
         <v>176</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C177" s="6" t="s">
         <v>544</v>
       </c>
       <c r="D177" t="s">
@@ -17201,7 +17647,7 @@
       <c r="B178">
         <v>177</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C178" s="6" t="s">
         <v>548</v>
       </c>
       <c r="D178" t="s">
@@ -17252,7 +17698,7 @@
       <c r="B179">
         <v>178</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C179" s="6" t="s">
         <v>551</v>
       </c>
       <c r="D179" t="s">
@@ -17303,7 +17749,7 @@
       <c r="B180">
         <v>179</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C180" s="6" t="s">
         <v>554</v>
       </c>
       <c r="D180" t="s">
@@ -17354,7 +17800,7 @@
       <c r="B181">
         <v>180</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C181" s="6" t="s">
         <v>557</v>
       </c>
       <c r="D181" t="s">
@@ -17405,7 +17851,7 @@
       <c r="B182">
         <v>181</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C182" s="6" t="s">
         <v>559</v>
       </c>
       <c r="D182" t="s">
@@ -17456,7 +17902,7 @@
       <c r="B183">
         <v>182</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C183" s="6" t="s">
         <v>562</v>
       </c>
       <c r="D183" t="s">
@@ -17509,7 +17955,7 @@
       <c r="B184">
         <v>183</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C184" s="6" t="s">
         <v>566</v>
       </c>
       <c r="D184" t="s">
@@ -17562,7 +18008,7 @@
       <c r="B185">
         <v>184</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C185" s="6" t="s">
         <v>570</v>
       </c>
       <c r="D185" t="s">
@@ -17611,7 +18057,7 @@
       <c r="B186">
         <v>185</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C186" s="6" t="s">
         <v>572</v>
       </c>
       <c r="D186" t="s">
@@ -17660,7 +18106,7 @@
       <c r="B187">
         <v>186</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C187" s="6" t="s">
         <v>574</v>
       </c>
       <c r="D187" t="s">
@@ -17713,7 +18159,7 @@
       <c r="B188">
         <v>187</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C188" s="6" t="s">
         <v>578</v>
       </c>
       <c r="D188" t="s">
@@ -17764,7 +18210,7 @@
       <c r="B189">
         <v>188</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C189" s="6" t="s">
         <v>581</v>
       </c>
       <c r="D189" t="s">
@@ -17815,7 +18261,7 @@
       <c r="B190">
         <v>189</v>
       </c>
-      <c r="C190" t="s">
+      <c r="C190" s="6" t="s">
         <v>583</v>
       </c>
       <c r="D190" t="s">
@@ -17868,7 +18314,7 @@
       <c r="B191">
         <v>190</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C191" s="6" t="s">
         <v>587</v>
       </c>
       <c r="D191" t="s">
@@ -17917,7 +18363,7 @@
       <c r="B192">
         <v>191</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C192" s="6" t="s">
         <v>589</v>
       </c>
       <c r="D192" t="s">
@@ -17968,7 +18414,7 @@
       <c r="B193">
         <v>192</v>
       </c>
-      <c r="C193" t="s">
+      <c r="C193" s="6" t="s">
         <v>592</v>
       </c>
       <c r="D193" t="s">
@@ -18019,7 +18465,7 @@
       <c r="B194">
         <v>193</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C194" s="6" t="s">
         <v>595</v>
       </c>
       <c r="D194" t="s">
@@ -18072,7 +18518,7 @@
       <c r="B195">
         <v>194</v>
       </c>
-      <c r="C195" t="s">
+      <c r="C195" s="6" t="s">
         <v>600</v>
       </c>
       <c r="D195" t="s">
@@ -18125,7 +18571,7 @@
       <c r="B196">
         <v>195</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C196" s="6" t="s">
         <v>604</v>
       </c>
       <c r="D196" t="s">
@@ -18178,7 +18624,7 @@
       <c r="B197">
         <v>196</v>
       </c>
-      <c r="C197" t="s">
+      <c r="C197" s="6" t="s">
         <v>608</v>
       </c>
       <c r="D197" t="s">
@@ -18231,7 +18677,7 @@
       <c r="B198">
         <v>197</v>
       </c>
-      <c r="C198" t="s">
+      <c r="C198" s="6" t="s">
         <v>612</v>
       </c>
       <c r="D198" t="s">
@@ -18284,7 +18730,7 @@
       <c r="B199">
         <v>198</v>
       </c>
-      <c r="C199" t="s">
+      <c r="C199" s="6" t="s">
         <v>616</v>
       </c>
       <c r="D199" t="s">
@@ -18337,7 +18783,7 @@
       <c r="B200">
         <v>199</v>
       </c>
-      <c r="C200" t="s">
+      <c r="C200" s="6" t="s">
         <v>620</v>
       </c>
       <c r="D200" t="s">
@@ -18390,7 +18836,7 @@
       <c r="B201">
         <v>200</v>
       </c>
-      <c r="C201" t="s">
+      <c r="C201" s="6" t="s">
         <v>624</v>
       </c>
       <c r="D201" t="s">
@@ -18443,7 +18889,7 @@
       <c r="B202">
         <v>201</v>
       </c>
-      <c r="C202" t="s">
+      <c r="C202" s="6" t="s">
         <v>628</v>
       </c>
       <c r="D202" t="s">
@@ -18496,7 +18942,7 @@
       <c r="B203">
         <v>202</v>
       </c>
-      <c r="C203" t="s">
+      <c r="C203" s="6" t="s">
         <v>632</v>
       </c>
       <c r="D203" t="s">
@@ -18549,7 +18995,7 @@
       <c r="B204">
         <v>203</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C204" s="6" t="s">
         <v>636</v>
       </c>
       <c r="D204" t="s">
@@ -18602,7 +19048,7 @@
       <c r="B205">
         <v>204</v>
       </c>
-      <c r="C205" t="s">
+      <c r="C205" s="6" t="s">
         <v>640</v>
       </c>
       <c r="D205" t="s">
@@ -18651,7 +19097,7 @@
       <c r="B206">
         <v>205</v>
       </c>
-      <c r="C206" t="s">
+      <c r="C206" s="6" t="s">
         <v>642</v>
       </c>
       <c r="D206" t="s">
@@ -18700,7 +19146,7 @@
       <c r="B207">
         <v>206</v>
       </c>
-      <c r="C207" t="s">
+      <c r="C207" s="6" t="s">
         <v>644</v>
       </c>
       <c r="D207" t="s">
@@ -18749,7 +19195,7 @@
       <c r="B208">
         <v>207</v>
       </c>
-      <c r="C208" t="s">
+      <c r="C208" s="6" t="s">
         <v>646</v>
       </c>
       <c r="D208" t="s">
@@ -18802,7 +19248,7 @@
       <c r="B209">
         <v>208</v>
       </c>
-      <c r="C209" t="s">
+      <c r="C209" s="6" t="s">
         <v>650</v>
       </c>
       <c r="D209" t="s">
@@ -18855,7 +19301,7 @@
       <c r="B210">
         <v>209</v>
       </c>
-      <c r="C210" t="s">
+      <c r="C210" s="6" t="s">
         <v>654</v>
       </c>
       <c r="D210" t="s">
@@ -18906,7 +19352,7 @@
       <c r="B211">
         <v>210</v>
       </c>
-      <c r="C211" t="s">
+      <c r="C211" s="6" t="s">
         <v>656</v>
       </c>
       <c r="D211" t="s">
@@ -18955,7 +19401,7 @@
       <c r="B212">
         <v>211</v>
       </c>
-      <c r="C212" t="s">
+      <c r="C212" s="6" t="s">
         <v>658</v>
       </c>
       <c r="D212" t="s">
@@ -19004,7 +19450,7 @@
       <c r="B213">
         <v>212</v>
       </c>
-      <c r="C213" t="s">
+      <c r="C213" s="6" t="s">
         <v>660</v>
       </c>
       <c r="D213" t="s">
@@ -19057,7 +19503,7 @@
       <c r="B214">
         <v>213</v>
       </c>
-      <c r="C214" t="s">
+      <c r="C214" s="6" t="s">
         <v>664</v>
       </c>
       <c r="D214" t="s">
@@ -19110,7 +19556,7 @@
       <c r="B215">
         <v>214</v>
       </c>
-      <c r="C215" t="s">
+      <c r="C215" s="6" t="s">
         <v>668</v>
       </c>
       <c r="D215" t="s">
@@ -19159,7 +19605,7 @@
       <c r="B216">
         <v>215</v>
       </c>
-      <c r="C216" t="s">
+      <c r="C216" s="6" t="s">
         <v>670</v>
       </c>
       <c r="D216" t="s">
@@ -19210,7 +19656,7 @@
       <c r="B217">
         <v>216</v>
       </c>
-      <c r="C217" t="s">
+      <c r="C217" s="6" t="s">
         <v>673</v>
       </c>
       <c r="D217" t="s">
@@ -19261,7 +19707,7 @@
       <c r="B218">
         <v>217</v>
       </c>
-      <c r="C218" t="s">
+      <c r="C218" s="6" t="s">
         <v>675</v>
       </c>
       <c r="D218" t="s">
@@ -19314,7 +19760,7 @@
       <c r="B219">
         <v>218</v>
       </c>
-      <c r="C219" t="s">
+      <c r="C219" s="6" t="s">
         <v>679</v>
       </c>
       <c r="D219" t="s">
@@ -19367,7 +19813,7 @@
       <c r="B220">
         <v>219</v>
       </c>
-      <c r="C220" t="s">
+      <c r="C220" s="6" t="s">
         <v>683</v>
       </c>
       <c r="D220" t="s">
@@ -19420,7 +19866,7 @@
       <c r="B221">
         <v>220</v>
       </c>
-      <c r="C221" t="s">
+      <c r="C221" s="6" t="s">
         <v>687</v>
       </c>
       <c r="D221" t="s">
@@ -19469,7 +19915,7 @@
       <c r="B222">
         <v>221</v>
       </c>
-      <c r="C222" t="s">
+      <c r="C222" s="6" t="s">
         <v>689</v>
       </c>
       <c r="D222" t="s">
@@ -19518,7 +19964,7 @@
       <c r="B223">
         <v>222</v>
       </c>
-      <c r="C223" t="s">
+      <c r="C223" s="6" t="s">
         <v>691</v>
       </c>
       <c r="D223" t="s">
@@ -19569,7 +20015,7 @@
       <c r="B224">
         <v>223</v>
       </c>
-      <c r="C224" t="s">
+      <c r="C224" s="6" t="s">
         <v>694</v>
       </c>
       <c r="D224" t="s">
@@ -19620,7 +20066,7 @@
       <c r="B225">
         <v>224</v>
       </c>
-      <c r="C225" t="s">
+      <c r="C225" s="6" t="s">
         <v>696</v>
       </c>
       <c r="D225" t="s">
@@ -19669,7 +20115,7 @@
       <c r="B226">
         <v>225</v>
       </c>
-      <c r="C226" t="s">
+      <c r="C226" s="6" t="s">
         <v>698</v>
       </c>
       <c r="D226" t="s">
@@ -19718,7 +20164,7 @@
       <c r="B227">
         <v>226</v>
       </c>
-      <c r="C227" t="s">
+      <c r="C227" s="6" t="s">
         <v>700</v>
       </c>
       <c r="D227" t="s">
@@ -19769,7 +20215,7 @@
       <c r="B228">
         <v>227</v>
       </c>
-      <c r="C228" t="s">
+      <c r="C228" s="6" t="s">
         <v>703</v>
       </c>
       <c r="D228" t="s">
@@ -19818,7 +20264,7 @@
       <c r="B229">
         <v>228</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C229" s="6" t="s">
         <v>705</v>
       </c>
       <c r="D229" t="s">
@@ -19869,7 +20315,7 @@
       <c r="B230">
         <v>229</v>
       </c>
-      <c r="C230" t="s">
+      <c r="C230" s="6" t="s">
         <v>708</v>
       </c>
       <c r="D230" t="s">
@@ -19920,7 +20366,7 @@
       <c r="B231">
         <v>230</v>
       </c>
-      <c r="C231" t="s">
+      <c r="C231" s="6" t="s">
         <v>711</v>
       </c>
       <c r="D231" t="s">
@@ -19971,7 +20417,7 @@
       <c r="B232">
         <v>231</v>
       </c>
-      <c r="C232" t="s">
+      <c r="C232" s="6" t="s">
         <v>713</v>
       </c>
       <c r="D232" t="s">
@@ -20022,7 +20468,7 @@
       <c r="B233">
         <v>232</v>
       </c>
-      <c r="C233" t="s">
+      <c r="C233" s="6" t="s">
         <v>715</v>
       </c>
       <c r="D233" t="s">
@@ -20071,7 +20517,7 @@
       <c r="B234">
         <v>233</v>
       </c>
-      <c r="C234" t="s">
+      <c r="C234" s="6" t="s">
         <v>717</v>
       </c>
       <c r="D234" t="s">
@@ -20122,7 +20568,7 @@
       <c r="B235">
         <v>234</v>
       </c>
-      <c r="C235" t="s">
+      <c r="C235" s="6" t="s">
         <v>720</v>
       </c>
       <c r="D235" t="s">
@@ -20171,7 +20617,7 @@
       <c r="B236">
         <v>235</v>
       </c>
-      <c r="C236" t="s">
+      <c r="C236" s="6" t="s">
         <v>722</v>
       </c>
       <c r="D236" t="s">
@@ -20224,7 +20670,7 @@
       <c r="B237">
         <v>236</v>
       </c>
-      <c r="C237" t="s">
+      <c r="C237" s="6" t="s">
         <v>726</v>
       </c>
       <c r="D237" t="s">
@@ -20273,7 +20719,7 @@
       <c r="B238">
         <v>237</v>
       </c>
-      <c r="C238" t="s">
+      <c r="C238" s="6" t="s">
         <v>728</v>
       </c>
       <c r="D238" t="s">
@@ -20322,7 +20768,7 @@
       <c r="B239">
         <v>238</v>
       </c>
-      <c r="C239" t="s">
+      <c r="C239" s="6" t="s">
         <v>730</v>
       </c>
       <c r="D239" t="s">
@@ -20373,7 +20819,7 @@
       <c r="B240">
         <v>239</v>
       </c>
-      <c r="C240" t="s">
+      <c r="C240" s="6" t="s">
         <v>733</v>
       </c>
       <c r="D240" t="s">
@@ -20399,7 +20845,7 @@
       <c r="B241">
         <v>240</v>
       </c>
-      <c r="C241" t="s">
+      <c r="C241" s="6" t="s">
         <v>735</v>
       </c>
       <c r="D241" t="s">
@@ -20452,7 +20898,7 @@
       <c r="B242">
         <v>241</v>
       </c>
-      <c r="C242" t="s">
+      <c r="C242" s="6" t="s">
         <v>739</v>
       </c>
       <c r="D242" t="s">
@@ -20505,7 +20951,7 @@
       <c r="B243">
         <v>242</v>
       </c>
-      <c r="C243" t="s">
+      <c r="C243" s="6" t="s">
         <v>743</v>
       </c>
       <c r="D243" t="s">
@@ -20556,7 +21002,7 @@
       <c r="B244">
         <v>243</v>
       </c>
-      <c r="C244" t="s">
+      <c r="C244" s="6" t="s">
         <v>745</v>
       </c>
       <c r="D244" t="s">
@@ -20605,7 +21051,7 @@
       <c r="B245">
         <v>244</v>
       </c>
-      <c r="C245" t="s">
+      <c r="C245" s="6" t="s">
         <v>747</v>
       </c>
       <c r="D245" t="s">
@@ -20654,7 +21100,7 @@
       <c r="B246">
         <v>245</v>
       </c>
-      <c r="C246" t="s">
+      <c r="C246" s="6" t="s">
         <v>749</v>
       </c>
       <c r="D246" t="s">
@@ -20703,7 +21149,7 @@
       <c r="B247">
         <v>246</v>
       </c>
-      <c r="C247" t="s">
+      <c r="C247" s="6" t="s">
         <v>751</v>
       </c>
       <c r="D247" t="s">
@@ -20756,7 +21202,7 @@
       <c r="B248">
         <v>247</v>
       </c>
-      <c r="C248" t="s">
+      <c r="C248" s="6" t="s">
         <v>756</v>
       </c>
       <c r="D248" t="s">
@@ -20809,7 +21255,7 @@
       <c r="B249">
         <v>248</v>
       </c>
-      <c r="C249" t="s">
+      <c r="C249" s="6" t="s">
         <v>760</v>
       </c>
       <c r="D249" t="s">
@@ -20862,7 +21308,7 @@
       <c r="B250">
         <v>249</v>
       </c>
-      <c r="C250" t="s">
+      <c r="C250" s="6" t="s">
         <v>763</v>
       </c>
       <c r="D250" t="s">
@@ -20915,7 +21361,7 @@
       <c r="B251">
         <v>250</v>
       </c>
-      <c r="C251" t="s">
+      <c r="C251" s="6" t="s">
         <v>766</v>
       </c>
       <c r="D251" t="s">
@@ -20968,7 +21414,7 @@
       <c r="B252">
         <v>251</v>
       </c>
-      <c r="C252" t="s">
+      <c r="C252" s="6" t="s">
         <v>770</v>
       </c>
       <c r="D252" t="s">
@@ -21021,7 +21467,7 @@
       <c r="B253">
         <v>252</v>
       </c>
-      <c r="C253" t="s">
+      <c r="C253" s="6" t="s">
         <v>773</v>
       </c>
       <c r="D253" t="s">
@@ -21074,7 +21520,7 @@
       <c r="B254">
         <v>253</v>
       </c>
-      <c r="C254" t="s">
+      <c r="C254" s="6" t="s">
         <v>776</v>
       </c>
       <c r="D254" t="s">
@@ -21127,7 +21573,7 @@
       <c r="B255">
         <v>254</v>
       </c>
-      <c r="C255" t="s">
+      <c r="C255" s="6" t="s">
         <v>780</v>
       </c>
       <c r="D255" t="s">
@@ -21180,7 +21626,7 @@
       <c r="B256">
         <v>255</v>
       </c>
-      <c r="C256" t="s">
+      <c r="C256" s="6" t="s">
         <v>783</v>
       </c>
       <c r="D256" t="s">
@@ -21229,7 +21675,7 @@
       <c r="B257">
         <v>256</v>
       </c>
-      <c r="C257" t="s">
+      <c r="C257" s="6" t="s">
         <v>785</v>
       </c>
       <c r="D257" t="s">
@@ -21282,7 +21728,7 @@
       <c r="B258">
         <v>257</v>
       </c>
-      <c r="C258" t="s">
+      <c r="C258" s="6" t="s">
         <v>789</v>
       </c>
       <c r="D258" t="s">
@@ -21333,7 +21779,7 @@
       <c r="B259">
         <v>258</v>
       </c>
-      <c r="C259" t="s">
+      <c r="C259" s="6" t="s">
         <v>791</v>
       </c>
       <c r="D259" t="s">
@@ -21386,7 +21832,7 @@
       <c r="B260">
         <v>259</v>
       </c>
-      <c r="C260" t="s">
+      <c r="C260" s="6" t="s">
         <v>795</v>
       </c>
       <c r="D260" t="s">
@@ -21439,7 +21885,7 @@
       <c r="B261">
         <v>260</v>
       </c>
-      <c r="C261" t="s">
+      <c r="C261" s="6" t="s">
         <v>799</v>
       </c>
       <c r="D261" t="s">
@@ -21492,7 +21938,7 @@
       <c r="B262">
         <v>261</v>
       </c>
-      <c r="C262" t="s">
+      <c r="C262" s="6" t="s">
         <v>803</v>
       </c>
       <c r="D262" t="s">
@@ -21545,7 +21991,7 @@
       <c r="B263">
         <v>262</v>
       </c>
-      <c r="C263" t="s">
+      <c r="C263" s="6" t="s">
         <v>806</v>
       </c>
       <c r="D263" t="s">
@@ -21596,7 +22042,7 @@
       <c r="B264">
         <v>263</v>
       </c>
-      <c r="C264" t="s">
+      <c r="C264" s="6" t="s">
         <v>808</v>
       </c>
       <c r="D264" t="s">
@@ -21647,7 +22093,7 @@
       <c r="B265">
         <v>264</v>
       </c>
-      <c r="C265" t="s">
+      <c r="C265" s="6" t="s">
         <v>811</v>
       </c>
       <c r="D265" t="s">
@@ -21698,7 +22144,7 @@
       <c r="B266">
         <v>265</v>
       </c>
-      <c r="C266" t="s">
+      <c r="C266" s="6" t="s">
         <v>814</v>
       </c>
       <c r="D266" t="s">
@@ -21749,7 +22195,7 @@
       <c r="B267">
         <v>266</v>
       </c>
-      <c r="C267" t="s">
+      <c r="C267" s="6" t="s">
         <v>816</v>
       </c>
       <c r="D267" t="s">
@@ -21798,7 +22244,7 @@
       <c r="B268">
         <v>267</v>
       </c>
-      <c r="C268" t="s">
+      <c r="C268" s="6" t="s">
         <v>818</v>
       </c>
       <c r="D268" t="s">
@@ -21851,7 +22297,7 @@
       <c r="B269">
         <v>268</v>
       </c>
-      <c r="C269" t="s">
+      <c r="C269" s="6" t="s">
         <v>822</v>
       </c>
       <c r="D269" t="s">
@@ -21904,7 +22350,7 @@
       <c r="B270">
         <v>269</v>
       </c>
-      <c r="C270" t="s">
+      <c r="C270" s="6" t="s">
         <v>827</v>
       </c>
       <c r="D270" t="s">
@@ -21957,7 +22403,7 @@
       <c r="B271">
         <v>270</v>
       </c>
-      <c r="C271" t="s">
+      <c r="C271" s="6" t="s">
         <v>831</v>
       </c>
       <c r="D271" t="s">
@@ -22008,7 +22454,7 @@
       <c r="B272">
         <v>271</v>
       </c>
-      <c r="C272" t="s">
+      <c r="C272" s="6" t="s">
         <v>834</v>
       </c>
       <c r="D272" t="s">
@@ -22061,7 +22507,7 @@
       <c r="B273">
         <v>272</v>
       </c>
-      <c r="C273" t="s">
+      <c r="C273" s="6" t="s">
         <v>838</v>
       </c>
       <c r="D273" t="s">
@@ -22114,7 +22560,7 @@
       <c r="B274">
         <v>273</v>
       </c>
-      <c r="C274" t="s">
+      <c r="C274" s="6" t="s">
         <v>842</v>
       </c>
       <c r="D274" t="s">
@@ -22167,7 +22613,7 @@
       <c r="B275">
         <v>274</v>
       </c>
-      <c r="C275" t="s">
+      <c r="C275" s="6" t="s">
         <v>847</v>
       </c>
       <c r="D275" t="s">
@@ -22218,7 +22664,7 @@
       <c r="B276">
         <v>275</v>
       </c>
-      <c r="C276" t="s">
+      <c r="C276" s="6" t="s">
         <v>850</v>
       </c>
       <c r="D276" t="s">
@@ -22271,7 +22717,7 @@
       <c r="B277">
         <v>276</v>
       </c>
-      <c r="C277" t="s">
+      <c r="C277" s="6" t="s">
         <v>853</v>
       </c>
       <c r="D277" t="s">
@@ -22324,7 +22770,7 @@
       <c r="B278">
         <v>277</v>
       </c>
-      <c r="C278" t="s">
+      <c r="C278" s="6" t="s">
         <v>856</v>
       </c>
       <c r="D278" t="s">
@@ -22377,7 +22823,7 @@
       <c r="B279">
         <v>278</v>
       </c>
-      <c r="C279" t="s">
+      <c r="C279" s="6" t="s">
         <v>860</v>
       </c>
       <c r="D279" t="s">
@@ -22430,7 +22876,7 @@
       <c r="B280">
         <v>279</v>
       </c>
-      <c r="C280" t="s">
+      <c r="C280" s="6" t="s">
         <v>864</v>
       </c>
       <c r="D280" t="s">
@@ -22481,7 +22927,7 @@
       <c r="B281">
         <v>280</v>
       </c>
-      <c r="C281" t="s">
+      <c r="C281" s="6" t="s">
         <v>866</v>
       </c>
       <c r="D281" t="s">
@@ -22532,7 +22978,7 @@
       <c r="B282">
         <v>281</v>
       </c>
-      <c r="C282" t="s">
+      <c r="C282" s="6" t="s">
         <v>868</v>
       </c>
       <c r="D282" t="s">
@@ -22585,7 +23031,7 @@
       <c r="B283">
         <v>282</v>
       </c>
-      <c r="C283" t="s">
+      <c r="C283" s="6" t="s">
         <v>871</v>
       </c>
       <c r="D283" t="s">
@@ -22638,7 +23084,7 @@
       <c r="B284">
         <v>283</v>
       </c>
-      <c r="C284" t="s">
+      <c r="C284" s="6" t="s">
         <v>875</v>
       </c>
       <c r="D284" t="s">
@@ -22689,7 +23135,7 @@
       <c r="B285">
         <v>284</v>
       </c>
-      <c r="C285" t="s">
+      <c r="C285" s="6" t="s">
         <v>878</v>
       </c>
       <c r="D285" t="s">
@@ -22740,7 +23186,7 @@
       <c r="B286">
         <v>285</v>
       </c>
-      <c r="C286" t="s">
+      <c r="C286" s="6" t="s">
         <v>880</v>
       </c>
       <c r="D286" t="s">
@@ -22793,7 +23239,7 @@
       <c r="B287">
         <v>286</v>
       </c>
-      <c r="C287" t="s">
+      <c r="C287" s="6" t="s">
         <v>884</v>
       </c>
       <c r="D287" t="s">
@@ -22846,7 +23292,7 @@
       <c r="B288">
         <v>287</v>
       </c>
-      <c r="C288" t="s">
+      <c r="C288" s="6" t="s">
         <v>888</v>
       </c>
       <c r="D288" t="s">
@@ -22897,7 +23343,7 @@
       <c r="B289">
         <v>288</v>
       </c>
-      <c r="C289" t="s">
+      <c r="C289" s="6" t="s">
         <v>891</v>
       </c>
       <c r="D289" t="s">
@@ -22950,7 +23396,7 @@
       <c r="B290">
         <v>289</v>
       </c>
-      <c r="C290" t="s">
+      <c r="C290" s="6" t="s">
         <v>895</v>
       </c>
       <c r="D290" t="s">
@@ -22997,7 +23443,7 @@
       <c r="B291">
         <v>290</v>
       </c>
-      <c r="C291" t="s">
+      <c r="C291" s="6" t="s">
         <v>897</v>
       </c>
       <c r="D291" t="s">
@@ -23046,7 +23492,7 @@
       <c r="B292">
         <v>291</v>
       </c>
-      <c r="C292" t="s">
+      <c r="C292" s="6" t="s">
         <v>900</v>
       </c>
       <c r="D292" t="s">
@@ -23097,7 +23543,7 @@
       <c r="B293">
         <v>292</v>
       </c>
-      <c r="C293" t="s">
+      <c r="C293" s="6" t="s">
         <v>903</v>
       </c>
       <c r="D293" t="s">
@@ -23146,7 +23592,7 @@
       <c r="B294">
         <v>293</v>
       </c>
-      <c r="C294" t="s">
+      <c r="C294" s="6" t="s">
         <v>905</v>
       </c>
       <c r="D294" t="s">
@@ -23197,7 +23643,7 @@
       <c r="B295">
         <v>294</v>
       </c>
-      <c r="C295" t="s">
+      <c r="C295" s="6" t="s">
         <v>907</v>
       </c>
       <c r="D295" t="s">
@@ -23246,7 +23692,7 @@
       <c r="B296">
         <v>295</v>
       </c>
-      <c r="C296" t="s">
+      <c r="C296" s="6" t="s">
         <v>909</v>
       </c>
       <c r="D296" t="s">
@@ -23299,7 +23745,7 @@
       <c r="B297">
         <v>296</v>
       </c>
-      <c r="C297" t="s">
+      <c r="C297" s="6" t="s">
         <v>913</v>
       </c>
       <c r="D297" t="s">
@@ -23348,7 +23794,7 @@
       <c r="B298">
         <v>297</v>
       </c>
-      <c r="C298" t="s">
+      <c r="C298" s="6" t="s">
         <v>915</v>
       </c>
       <c r="D298" t="s">
@@ -23399,7 +23845,7 @@
       <c r="B299">
         <v>298</v>
       </c>
-      <c r="C299" t="s">
+      <c r="C299" s="6" t="s">
         <v>919</v>
       </c>
       <c r="D299" t="s">
@@ -23450,7 +23896,7 @@
       <c r="B300">
         <v>299</v>
       </c>
-      <c r="C300" t="s">
+      <c r="C300" s="6" t="s">
         <v>922</v>
       </c>
       <c r="D300" t="s">
@@ -23503,7 +23949,7 @@
       <c r="B301">
         <v>300</v>
       </c>
-      <c r="C301" t="s">
+      <c r="C301" s="6" t="s">
         <v>926</v>
       </c>
       <c r="D301" t="s">
@@ -23556,7 +24002,7 @@
       <c r="B302">
         <v>301</v>
       </c>
-      <c r="C302" t="s">
+      <c r="C302" s="6" t="s">
         <v>930</v>
       </c>
       <c r="D302" t="s">
@@ -23609,7 +24055,7 @@
       <c r="B303">
         <v>302</v>
       </c>
-      <c r="C303" t="s">
+      <c r="C303" s="6" t="s">
         <v>933</v>
       </c>
       <c r="D303" t="s">
@@ -23662,7 +24108,7 @@
       <c r="B304">
         <v>303</v>
       </c>
-      <c r="C304" t="s">
+      <c r="C304" s="6" t="s">
         <v>937</v>
       </c>
       <c r="D304" t="s">
@@ -23715,7 +24161,7 @@
       <c r="B305">
         <v>304</v>
       </c>
-      <c r="C305" t="s">
+      <c r="C305" s="6" t="s">
         <v>942</v>
       </c>
       <c r="D305" t="s">
@@ -23764,7 +24210,7 @@
       <c r="B306">
         <v>305</v>
       </c>
-      <c r="C306" t="s">
+      <c r="C306" s="6" t="s">
         <v>944</v>
       </c>
       <c r="D306" t="s">
@@ -23817,7 +24263,7 @@
       <c r="B307">
         <v>306</v>
       </c>
-      <c r="C307" t="s">
+      <c r="C307" s="6" t="s">
         <v>948</v>
       </c>
       <c r="D307" t="s">
@@ -23866,7 +24312,7 @@
       <c r="B308">
         <v>307</v>
       </c>
-      <c r="C308" t="s">
+      <c r="C308" s="6" t="s">
         <v>950</v>
       </c>
       <c r="D308" t="s">
@@ -23919,7 +24365,7 @@
       <c r="B309">
         <v>308</v>
       </c>
-      <c r="C309" t="s">
+      <c r="C309" s="6" t="s">
         <v>954</v>
       </c>
       <c r="D309" t="s">
@@ -23972,7 +24418,7 @@
       <c r="B310">
         <v>309</v>
       </c>
-      <c r="C310" t="s">
+      <c r="C310" s="6" t="s">
         <v>958</v>
       </c>
       <c r="D310" t="s">
@@ -24025,7 +24471,7 @@
       <c r="B311">
         <v>310</v>
       </c>
-      <c r="C311" t="s">
+      <c r="C311" s="6" t="s">
         <v>962</v>
       </c>
       <c r="D311" t="s">
@@ -24074,7 +24520,7 @@
       <c r="B312">
         <v>311</v>
       </c>
-      <c r="C312" t="s">
+      <c r="C312" s="6" t="s">
         <v>964</v>
       </c>
       <c r="D312" t="s">
@@ -24127,7 +24573,7 @@
       <c r="B313">
         <v>312</v>
       </c>
-      <c r="C313" t="s">
+      <c r="C313" s="6" t="s">
         <v>968</v>
       </c>
       <c r="D313" t="s">
@@ -24176,7 +24622,7 @@
       <c r="B314">
         <v>313</v>
       </c>
-      <c r="C314" t="s">
+      <c r="C314" s="6" t="s">
         <v>970</v>
       </c>
       <c r="D314" t="s">
@@ -24226,7 +24672,7 @@
       <c r="B315">
         <v>314</v>
       </c>
-      <c r="C315" t="s">
+      <c r="C315" s="6" t="s">
         <v>972</v>
       </c>
       <c r="D315" t="s">
@@ -24279,7 +24725,7 @@
       <c r="B316">
         <v>315</v>
       </c>
-      <c r="C316" t="s">
+      <c r="C316" s="6" t="s">
         <v>976</v>
       </c>
       <c r="D316" t="s">
@@ -24332,7 +24778,7 @@
       <c r="B317">
         <v>316</v>
       </c>
-      <c r="C317" t="s">
+      <c r="C317" s="6" t="s">
         <v>980</v>
       </c>
       <c r="D317" t="s">
@@ -24385,7 +24831,7 @@
       <c r="B318">
         <v>317</v>
       </c>
-      <c r="C318" t="s">
+      <c r="C318" s="6" t="s">
         <v>984</v>
       </c>
       <c r="D318" t="s">
@@ -24434,7 +24880,7 @@
       <c r="B319">
         <v>318</v>
       </c>
-      <c r="C319" t="s">
+      <c r="C319" s="6" t="s">
         <v>986</v>
       </c>
       <c r="D319" t="s">
@@ -24487,7 +24933,7 @@
       <c r="B320">
         <v>319</v>
       </c>
-      <c r="C320" t="s">
+      <c r="C320" s="6" t="s">
         <v>990</v>
       </c>
       <c r="D320" t="s">
@@ -24540,7 +24986,7 @@
       <c r="B321">
         <v>320</v>
       </c>
-      <c r="C321" t="s">
+      <c r="C321" s="6" t="s">
         <v>994</v>
       </c>
       <c r="D321" t="s">
@@ -24591,7 +25037,7 @@
       <c r="B322">
         <v>321</v>
       </c>
-      <c r="C322" t="s">
+      <c r="C322" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D322" t="s">
@@ -24644,7 +25090,7 @@
       <c r="B323">
         <v>322</v>
       </c>
-      <c r="C323" t="s">
+      <c r="C323" s="6" t="s">
         <v>1001</v>
       </c>
       <c r="D323" t="s">
@@ -24697,7 +25143,7 @@
       <c r="B324">
         <v>323</v>
       </c>
-      <c r="C324" t="s">
+      <c r="C324" s="6" t="s">
         <v>1006</v>
       </c>
       <c r="D324" t="s">
@@ -24750,7 +25196,7 @@
       <c r="B325">
         <v>324</v>
       </c>
-      <c r="C325" t="s">
+      <c r="C325" s="6" t="s">
         <v>1010</v>
       </c>
       <c r="D325" t="s">
@@ -24803,7 +25249,7 @@
       <c r="B326">
         <v>325</v>
       </c>
-      <c r="C326" t="s">
+      <c r="C326" s="6" t="s">
         <v>1015</v>
       </c>
       <c r="D326" t="s">
@@ -24856,7 +25302,7 @@
       <c r="B327">
         <v>326</v>
       </c>
-      <c r="C327" t="s">
+      <c r="C327" s="6" t="s">
         <v>1019</v>
       </c>
       <c r="D327" t="s">
@@ -24909,7 +25355,7 @@
       <c r="B328">
         <v>327</v>
       </c>
-      <c r="C328" t="s">
+      <c r="C328" s="6" t="s">
         <v>1023</v>
       </c>
       <c r="D328" t="s">
@@ -24962,7 +25408,7 @@
       <c r="B329">
         <v>328</v>
       </c>
-      <c r="C329" t="s">
+      <c r="C329" s="6" t="s">
         <v>1027</v>
       </c>
       <c r="D329" t="s">
@@ -25015,7 +25461,7 @@
       <c r="B330">
         <v>329</v>
       </c>
-      <c r="C330" t="s">
+      <c r="C330" s="6" t="s">
         <v>1031</v>
       </c>
       <c r="D330" t="s">
@@ -25068,7 +25514,7 @@
       <c r="B331">
         <v>330</v>
       </c>
-      <c r="C331" t="s">
+      <c r="C331" s="6" t="s">
         <v>1036</v>
       </c>
       <c r="D331" t="s">
@@ -25121,7 +25567,7 @@
       <c r="B332">
         <v>331</v>
       </c>
-      <c r="C332" t="s">
+      <c r="C332" s="6" t="s">
         <v>1040</v>
       </c>
       <c r="D332" t="s">
@@ -25174,7 +25620,7 @@
       <c r="B333">
         <v>332</v>
       </c>
-      <c r="C333" t="s">
+      <c r="C333" s="6" t="s">
         <v>1043</v>
       </c>
       <c r="D333" t="s">
@@ -25227,7 +25673,7 @@
       <c r="B334">
         <v>333</v>
       </c>
-      <c r="C334" t="s">
+      <c r="C334" s="6" t="s">
         <v>1048</v>
       </c>
       <c r="D334" t="s">
@@ -25278,7 +25724,7 @@
       <c r="B335">
         <v>334</v>
       </c>
-      <c r="C335" t="s">
+      <c r="C335" s="6" t="s">
         <v>1051</v>
       </c>
       <c r="D335" t="s">
@@ -25327,7 +25773,7 @@
       <c r="B336">
         <v>335</v>
       </c>
-      <c r="C336" t="s">
+      <c r="C336" s="6" t="s">
         <v>1053</v>
       </c>
       <c r="D336" t="s">
@@ -25378,7 +25824,7 @@
       <c r="B337">
         <v>336</v>
       </c>
-      <c r="C337" t="s">
+      <c r="C337" s="6" t="s">
         <v>1056</v>
       </c>
       <c r="D337" t="s">
@@ -25431,7 +25877,7 @@
       <c r="B338">
         <v>337</v>
       </c>
-      <c r="C338" t="s">
+      <c r="C338" s="6" t="s">
         <v>1061</v>
       </c>
       <c r="D338" t="s">
@@ -25484,7 +25930,7 @@
       <c r="B339">
         <v>338</v>
       </c>
-      <c r="C339" t="s">
+      <c r="C339" s="6" t="s">
         <v>1065</v>
       </c>
       <c r="D339" t="s">
@@ -25537,7 +25983,7 @@
       <c r="B340">
         <v>339</v>
       </c>
-      <c r="C340" t="s">
+      <c r="C340" s="6" t="s">
         <v>1070</v>
       </c>
       <c r="D340" t="s">
@@ -25586,7 +26032,7 @@
       <c r="B341">
         <v>340</v>
       </c>
-      <c r="C341" t="s">
+      <c r="C341" s="6" t="s">
         <v>1072</v>
       </c>
       <c r="D341" t="s">
@@ -25637,7 +26083,7 @@
       <c r="B342">
         <v>341</v>
       </c>
-      <c r="C342" t="s">
+      <c r="C342" s="6" t="s">
         <v>1074</v>
       </c>
       <c r="D342" t="s">
@@ -25690,7 +26136,7 @@
       <c r="B343">
         <v>342</v>
       </c>
-      <c r="C343" t="s">
+      <c r="C343" s="6" t="s">
         <v>1078</v>
       </c>
       <c r="D343" t="s">
@@ -25739,7 +26185,7 @@
       <c r="B344">
         <v>343</v>
       </c>
-      <c r="C344" t="s">
+      <c r="C344" s="6" t="s">
         <v>1080</v>
       </c>
       <c r="D344" t="s">
@@ -25792,7 +26238,7 @@
       <c r="B345">
         <v>344</v>
       </c>
-      <c r="C345" t="s">
+      <c r="C345" s="6" t="s">
         <v>1084</v>
       </c>
       <c r="D345" t="s">
@@ -25843,7 +26289,7 @@
       <c r="B346">
         <v>345</v>
       </c>
-      <c r="C346" t="s">
+      <c r="C346" s="6" t="s">
         <v>1087</v>
       </c>
       <c r="D346" t="s">
@@ -25896,7 +26342,7 @@
       <c r="B347">
         <v>346</v>
       </c>
-      <c r="C347" t="s">
+      <c r="C347" s="6" t="s">
         <v>1091</v>
       </c>
       <c r="D347" t="s">
@@ -25949,7 +26395,7 @@
       <c r="B348">
         <v>347</v>
       </c>
-      <c r="C348" t="s">
+      <c r="C348" s="6" t="s">
         <v>1095</v>
       </c>
       <c r="D348" t="s">
@@ -25997,7 +26443,7 @@
       <c r="B349">
         <v>348</v>
       </c>
-      <c r="C349" t="s">
+      <c r="C349" s="6" t="s">
         <v>1098</v>
       </c>
       <c r="D349" t="s">
@@ -26050,7 +26496,7 @@
       <c r="B350">
         <v>349</v>
       </c>
-      <c r="C350" t="s">
+      <c r="C350" s="6" t="s">
         <v>1103</v>
       </c>
       <c r="D350" t="s">
@@ -26100,7 +26546,7 @@
       <c r="B351">
         <v>350</v>
       </c>
-      <c r="C351" t="s">
+      <c r="C351" s="6" t="s">
         <v>1107</v>
       </c>
       <c r="D351" t="s">
@@ -26153,7 +26599,7 @@
       <c r="B352">
         <v>351</v>
       </c>
-      <c r="C352" t="s">
+      <c r="C352" s="6" t="s">
         <v>1112</v>
       </c>
       <c r="D352" t="s">
@@ -26206,7 +26652,7 @@
       <c r="B353">
         <v>352</v>
       </c>
-      <c r="C353" t="s">
+      <c r="C353" s="6" t="s">
         <v>1116</v>
       </c>
       <c r="D353" t="s">
@@ -26259,7 +26705,7 @@
       <c r="B354">
         <v>353</v>
       </c>
-      <c r="C354" t="s">
+      <c r="C354" s="6" t="s">
         <v>1120</v>
       </c>
       <c r="D354" t="s">
@@ -26312,7 +26758,7 @@
       <c r="B355">
         <v>354</v>
       </c>
-      <c r="C355" t="s">
+      <c r="C355" s="6" t="s">
         <v>1124</v>
       </c>
       <c r="D355" t="s">
@@ -26365,7 +26811,7 @@
       <c r="B356">
         <v>355</v>
       </c>
-      <c r="C356" t="s">
+      <c r="C356" s="6" t="s">
         <v>1128</v>
       </c>
       <c r="D356" t="s">
@@ -26418,7 +26864,7 @@
       <c r="B357">
         <v>356</v>
       </c>
-      <c r="C357" t="s">
+      <c r="C357" s="6" t="s">
         <v>1132</v>
       </c>
       <c r="D357" t="s">
@@ -26471,7 +26917,7 @@
       <c r="B358">
         <v>357</v>
       </c>
-      <c r="C358" t="s">
+      <c r="C358" s="6" t="s">
         <v>1136</v>
       </c>
       <c r="D358" t="s">
@@ -26524,7 +26970,7 @@
       <c r="B359">
         <v>358</v>
       </c>
-      <c r="C359" t="s">
+      <c r="C359" s="6" t="s">
         <v>1139</v>
       </c>
       <c r="D359" t="s">
@@ -26577,7 +27023,7 @@
       <c r="B360">
         <v>359</v>
       </c>
-      <c r="C360" t="s">
+      <c r="C360" s="6" t="s">
         <v>1142</v>
       </c>
       <c r="D360" t="s">
@@ -26628,7 +27074,7 @@
       <c r="B361">
         <v>360</v>
       </c>
-      <c r="C361" t="s">
+      <c r="C361" s="6" t="s">
         <v>1145</v>
       </c>
       <c r="D361" t="s">
@@ -26679,7 +27125,7 @@
       <c r="B362">
         <v>361</v>
       </c>
-      <c r="C362" t="s">
+      <c r="C362" s="6" t="s">
         <v>1148</v>
       </c>
       <c r="D362" t="s">
@@ -26730,7 +27176,7 @@
       <c r="B363">
         <v>362</v>
       </c>
-      <c r="C363" t="s">
+      <c r="C363" s="6" t="s">
         <v>1151</v>
       </c>
       <c r="D363" t="s">
@@ -26756,7 +27202,7 @@
       <c r="B364">
         <v>363</v>
       </c>
-      <c r="C364" t="s">
+      <c r="C364" s="6" t="s">
         <v>1153</v>
       </c>
       <c r="D364" t="s">
@@ -26809,7 +27255,7 @@
       <c r="B365">
         <v>364</v>
       </c>
-      <c r="C365" t="s">
+      <c r="C365" s="6" t="s">
         <v>1156</v>
       </c>
       <c r="D365" t="s">
@@ -26862,7 +27308,7 @@
       <c r="B366">
         <v>365</v>
       </c>
-      <c r="C366" t="s">
+      <c r="C366" s="6" t="s">
         <v>1159</v>
       </c>
       <c r="D366" t="s">
@@ -26915,7 +27361,7 @@
       <c r="B367">
         <v>366</v>
       </c>
-      <c r="C367" t="s">
+      <c r="C367" s="6" t="s">
         <v>1162</v>
       </c>
       <c r="D367" t="s">
@@ -26968,7 +27414,7 @@
       <c r="B368">
         <v>367</v>
       </c>
-      <c r="C368" t="s">
+      <c r="C368" s="6" t="s">
         <v>1165</v>
       </c>
       <c r="D368" t="s">
@@ -27017,7 +27463,7 @@
       <c r="B369">
         <v>368</v>
       </c>
-      <c r="C369" t="s">
+      <c r="C369" s="6" t="s">
         <v>1167</v>
       </c>
       <c r="D369" t="s">
@@ -27066,7 +27512,7 @@
       <c r="B370">
         <v>369</v>
       </c>
-      <c r="C370" t="s">
+      <c r="C370" s="6" t="s">
         <v>1169</v>
       </c>
       <c r="D370" t="s">
@@ -27117,7 +27563,7 @@
       <c r="B371">
         <v>370</v>
       </c>
-      <c r="C371" t="s">
+      <c r="C371" s="6" t="s">
         <v>1172</v>
       </c>
       <c r="D371" t="s">
@@ -27168,7 +27614,7 @@
       <c r="B372">
         <v>371</v>
       </c>
-      <c r="C372" t="s">
+      <c r="C372" s="6" t="s">
         <v>1175</v>
       </c>
       <c r="D372" t="s">
@@ -27219,7 +27665,7 @@
       <c r="B373">
         <v>372</v>
       </c>
-      <c r="C373" t="s">
+      <c r="C373" s="6" t="s">
         <v>1178</v>
       </c>
       <c r="D373" t="s">
@@ -27270,7 +27716,7 @@
       <c r="B374">
         <v>373</v>
       </c>
-      <c r="C374" t="s">
+      <c r="C374" s="6" t="s">
         <v>1181</v>
       </c>
       <c r="D374" t="s">
@@ -27321,7 +27767,7 @@
       <c r="B375">
         <v>374</v>
       </c>
-      <c r="C375" t="s">
+      <c r="C375" s="6" t="s">
         <v>1184</v>
       </c>
       <c r="D375" t="s">
@@ -27372,7 +27818,7 @@
       <c r="B376">
         <v>375</v>
       </c>
-      <c r="C376" t="s">
+      <c r="C376" s="6" t="s">
         <v>1187</v>
       </c>
       <c r="D376" t="s">
@@ -27425,7 +27871,7 @@
       <c r="B377">
         <v>376</v>
       </c>
-      <c r="C377" t="s">
+      <c r="C377" s="6" t="s">
         <v>1189</v>
       </c>
       <c r="D377" t="s">
@@ -27478,7 +27924,7 @@
       <c r="B378">
         <v>377</v>
       </c>
-      <c r="C378" t="s">
+      <c r="C378" s="6" t="s">
         <v>1192</v>
       </c>
       <c r="D378" t="s">
@@ -27531,7 +27977,7 @@
       <c r="B379">
         <v>378</v>
       </c>
-      <c r="C379" t="s">
+      <c r="C379" s="6" t="s">
         <v>1195</v>
       </c>
       <c r="D379" t="s">
@@ -27584,7 +28030,7 @@
       <c r="B380">
         <v>379</v>
       </c>
-      <c r="C380" t="s">
+      <c r="C380" s="6" t="s">
         <v>1198</v>
       </c>
       <c r="D380" t="s">
@@ -27637,7 +28083,7 @@
       <c r="B381">
         <v>380</v>
       </c>
-      <c r="C381" t="s">
+      <c r="C381" s="6" t="s">
         <v>1201</v>
       </c>
       <c r="D381" t="s">
@@ -27690,7 +28136,7 @@
       <c r="B382">
         <v>381</v>
       </c>
-      <c r="C382" t="s">
+      <c r="C382" s="6" t="s">
         <v>1204</v>
       </c>
       <c r="D382" t="s">
@@ -27839,7 +28285,7 @@
       <c r="B385">
         <v>384</v>
       </c>
-      <c r="C385" t="s">
+      <c r="C385" s="6" t="s">
         <v>1211</v>
       </c>
       <c r="D385" t="s">
@@ -27892,7 +28338,7 @@
       <c r="B386">
         <v>385</v>
       </c>
-      <c r="C386" t="s">
+      <c r="C386" s="6" t="s">
         <v>1214</v>
       </c>
       <c r="D386" t="s">
@@ -27945,7 +28391,7 @@
       <c r="B387">
         <v>386</v>
       </c>
-      <c r="C387" t="s">
+      <c r="C387" s="6" t="s">
         <v>1218</v>
       </c>
       <c r="D387" t="s">
@@ -27998,7 +28444,7 @@
       <c r="B388">
         <v>387</v>
       </c>
-      <c r="C388" t="s">
+      <c r="C388" s="6" t="s">
         <v>1222</v>
       </c>
       <c r="D388" t="s">
@@ -28047,7 +28493,7 @@
       <c r="B389">
         <v>388</v>
       </c>
-      <c r="C389" t="s">
+      <c r="C389" s="6" t="s">
         <v>1224</v>
       </c>
       <c r="D389" t="s">
@@ -28098,7 +28544,7 @@
       <c r="B390">
         <v>389</v>
       </c>
-      <c r="C390" t="s">
+      <c r="C390" s="6" t="s">
         <v>1227</v>
       </c>
       <c r="D390" t="s">
@@ -28151,7 +28597,7 @@
       <c r="B391">
         <v>390</v>
       </c>
-      <c r="C391" t="s">
+      <c r="C391" s="6" t="s">
         <v>1231</v>
       </c>
       <c r="D391" t="s">
@@ -28204,7 +28650,7 @@
       <c r="B392">
         <v>391</v>
       </c>
-      <c r="C392" t="s">
+      <c r="C392" s="6" t="s">
         <v>1235</v>
       </c>
       <c r="D392" t="s">
@@ -28255,7 +28701,7 @@
       <c r="B393">
         <v>392</v>
       </c>
-      <c r="C393" t="s">
+      <c r="C393" s="6" t="s">
         <v>1237</v>
       </c>
       <c r="D393" t="s">
@@ -28306,7 +28752,7 @@
       <c r="B394">
         <v>393</v>
       </c>
-      <c r="C394" t="s">
+      <c r="C394" s="6" t="s">
         <v>1239</v>
       </c>
       <c r="D394" t="s">
@@ -28359,7 +28805,7 @@
       <c r="B395">
         <v>394</v>
       </c>
-      <c r="C395" t="s">
+      <c r="C395" s="6" t="s">
         <v>1243</v>
       </c>
       <c r="D395" t="s">
@@ -28412,7 +28858,7 @@
       <c r="B396">
         <v>395</v>
       </c>
-      <c r="C396" t="s">
+      <c r="C396" s="6" t="s">
         <v>1247</v>
       </c>
       <c r="D396" t="s">
@@ -28465,7 +28911,7 @@
       <c r="B397">
         <v>396</v>
       </c>
-      <c r="C397" t="s">
+      <c r="C397" s="6" t="s">
         <v>1251</v>
       </c>
       <c r="D397" t="s">
@@ -28518,7 +28964,7 @@
       <c r="B398">
         <v>397</v>
       </c>
-      <c r="C398" t="s">
+      <c r="C398" s="6" t="s">
         <v>1255</v>
       </c>
       <c r="D398" t="s">
@@ -28571,7 +29017,7 @@
       <c r="B399">
         <v>398</v>
       </c>
-      <c r="C399" t="s">
+      <c r="C399" s="6" t="s">
         <v>1258</v>
       </c>
       <c r="D399" t="s">
@@ -28624,7 +29070,7 @@
       <c r="B400">
         <v>399</v>
       </c>
-      <c r="C400" t="s">
+      <c r="C400" s="6" t="s">
         <v>1261</v>
       </c>
       <c r="D400" t="s">
@@ -28677,7 +29123,7 @@
       <c r="B401">
         <v>400</v>
       </c>
-      <c r="C401" t="s">
+      <c r="C401" s="6" t="s">
         <v>1264</v>
       </c>
       <c r="D401" t="s">
@@ -28730,7 +29176,7 @@
       <c r="B402">
         <v>401</v>
       </c>
-      <c r="C402" t="s">
+      <c r="C402" s="6" t="s">
         <v>1268</v>
       </c>
       <c r="D402" t="s">
@@ -28783,7 +29229,7 @@
       <c r="B403">
         <v>402</v>
       </c>
-      <c r="C403" t="s">
+      <c r="C403" s="6" t="s">
         <v>1271</v>
       </c>
       <c r="D403" t="s">
@@ -28836,7 +29282,7 @@
       <c r="B404">
         <v>403</v>
       </c>
-      <c r="C404" t="s">
+      <c r="C404" s="6" t="s">
         <v>1274</v>
       </c>
       <c r="D404" t="s">
@@ -28889,7 +29335,7 @@
       <c r="B405">
         <v>404</v>
       </c>
-      <c r="C405" t="s">
+      <c r="C405" s="6" t="s">
         <v>1278</v>
       </c>
       <c r="D405" t="s">
@@ -28942,7 +29388,7 @@
       <c r="B406">
         <v>405</v>
       </c>
-      <c r="C406" t="s">
+      <c r="C406" s="6" t="s">
         <v>1281</v>
       </c>
       <c r="D406" t="s">
@@ -28995,7 +29441,7 @@
       <c r="B407">
         <v>406</v>
       </c>
-      <c r="C407" t="s">
+      <c r="C407" s="6" t="s">
         <v>1284</v>
       </c>
       <c r="D407" t="s">
@@ -29046,7 +29492,7 @@
       <c r="B408">
         <v>407</v>
       </c>
-      <c r="C408" t="s">
+      <c r="C408" s="6" t="s">
         <v>1287</v>
       </c>
       <c r="D408" t="s">
@@ -29099,7 +29545,7 @@
       <c r="B409">
         <v>408</v>
       </c>
-      <c r="C409" t="s">
+      <c r="C409" s="6" t="s">
         <v>1290</v>
       </c>
       <c r="D409" t="s">
@@ -29148,7 +29594,7 @@
       <c r="B410">
         <v>409</v>
       </c>
-      <c r="C410" t="s">
+      <c r="C410" s="6" t="s">
         <v>1292</v>
       </c>
       <c r="D410" t="s">
@@ -29197,7 +29643,7 @@
       <c r="B411">
         <v>410</v>
       </c>
-      <c r="C411" t="s">
+      <c r="C411" s="6" t="s">
         <v>1294</v>
       </c>
       <c r="D411" t="s">
@@ -29250,7 +29696,7 @@
       <c r="B412">
         <v>411</v>
       </c>
-      <c r="C412" t="s">
+      <c r="C412" s="6" t="s">
         <v>1296</v>
       </c>
       <c r="D412" t="s">
@@ -29303,7 +29749,7 @@
       <c r="B413">
         <v>412</v>
       </c>
-      <c r="C413" t="s">
+      <c r="C413" s="6" t="s">
         <v>1298</v>
       </c>
       <c r="D413" t="s">
@@ -29356,7 +29802,7 @@
       <c r="B414">
         <v>413</v>
       </c>
-      <c r="C414" t="s">
+      <c r="C414" s="6" t="s">
         <v>1301</v>
       </c>
       <c r="D414" t="s">
@@ -29409,7 +29855,7 @@
       <c r="B415">
         <v>414</v>
       </c>
-      <c r="C415" t="s">
+      <c r="C415" s="6" t="s">
         <v>1304</v>
       </c>
       <c r="D415" t="s">
@@ -29458,7 +29904,7 @@
       <c r="B416">
         <v>415</v>
       </c>
-      <c r="C416" t="s">
+      <c r="C416" s="6" t="s">
         <v>1306</v>
       </c>
       <c r="D416" t="s">
@@ -29509,7 +29955,7 @@
       <c r="B417">
         <v>416</v>
       </c>
-      <c r="C417" t="s">
+      <c r="C417" s="6" t="s">
         <v>1308</v>
       </c>
       <c r="D417" t="s">
@@ -29558,7 +30004,7 @@
       <c r="B418">
         <v>417</v>
       </c>
-      <c r="C418" t="s">
+      <c r="C418" s="6" t="s">
         <v>1310</v>
       </c>
       <c r="D418" t="s">
@@ -29611,7 +30057,7 @@
       <c r="B419">
         <v>418</v>
       </c>
-      <c r="C419" t="s">
+      <c r="C419" s="6" t="s">
         <v>1312</v>
       </c>
       <c r="D419" t="s">
@@ -29662,7 +30108,7 @@
       <c r="B420">
         <v>419</v>
       </c>
-      <c r="C420" t="s">
+      <c r="C420" s="6" t="s">
         <v>1315</v>
       </c>
       <c r="D420" t="s">
@@ -29715,7 +30161,7 @@
       <c r="B421">
         <v>420</v>
       </c>
-      <c r="C421" t="s">
+      <c r="C421" s="6" t="s">
         <v>1318</v>
       </c>
       <c r="D421" t="s">
@@ -29768,7 +30214,7 @@
       <c r="B422">
         <v>421</v>
       </c>
-      <c r="C422" t="s">
+      <c r="C422" s="6" t="s">
         <v>1321</v>
       </c>
       <c r="D422" t="s">
@@ -29819,7 +30265,7 @@
       <c r="B423">
         <v>422</v>
       </c>
-      <c r="C423" t="s">
+      <c r="C423" s="6" t="s">
         <v>1323</v>
       </c>
       <c r="D423" t="s">
@@ -29865,14 +30311,14 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="424" spans="1:17" ht="30">
+    <row r="424" spans="1:17" ht="60">
       <c r="A424">
         <v>423</v>
       </c>
       <c r="B424">
         <v>423</v>
       </c>
-      <c r="C424" t="s">
+      <c r="C424" s="6" t="s">
         <v>1326</v>
       </c>
       <c r="D424" t="s">
@@ -29914,16 +30360,18 @@
       <c r="P424" s="10" t="s">
         <v>1328</v>
       </c>
-      <c r="Q424" s="10"/>
-    </row>
-    <row r="425" spans="1:17" ht="30">
+      <c r="Q424" s="10" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="425" spans="1:17" ht="60">
       <c r="A425">
         <v>424</v>
       </c>
       <c r="B425">
         <v>424</v>
       </c>
-      <c r="C425" t="s">
+      <c r="C425" s="6" t="s">
         <v>1329</v>
       </c>
       <c r="D425" t="s">
@@ -29965,7 +30413,9 @@
       <c r="P425" s="10" t="s">
         <v>1186</v>
       </c>
-      <c r="Q425" s="10"/>
+      <c r="Q425" s="10" t="s">
+        <v>2224</v>
+      </c>
     </row>
     <row r="426" spans="1:17" ht="105">
       <c r="A426">
@@ -29974,7 +30424,7 @@
       <c r="B426">
         <v>425</v>
       </c>
-      <c r="C426" t="s">
+      <c r="C426" s="6" t="s">
         <v>1331</v>
       </c>
       <c r="D426" t="s">
@@ -30016,16 +30466,18 @@
       <c r="P426" s="10" t="s">
         <v>2170</v>
       </c>
-      <c r="Q426" s="10"/>
-    </row>
-    <row r="427" spans="1:17" ht="30">
+      <c r="Q426" s="10" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="427" spans="1:17" ht="60">
       <c r="A427">
         <v>426</v>
       </c>
       <c r="B427">
         <v>426</v>
       </c>
-      <c r="C427" t="s">
+      <c r="C427" s="6" t="s">
         <v>1333</v>
       </c>
       <c r="D427" t="s">
@@ -30067,7 +30519,9 @@
       <c r="P427" s="10" t="s">
         <v>1335</v>
       </c>
-      <c r="Q427" s="10"/>
+      <c r="Q427" s="10" t="s">
+        <v>2226</v>
+      </c>
     </row>
     <row r="428" spans="1:17">
       <c r="A428">
@@ -30076,8 +30530,8 @@
       <c r="B428">
         <v>427</v>
       </c>
-      <c r="C428" t="s">
-        <v>1290</v>
+      <c r="C428" s="6" t="s">
+        <v>2227</v>
       </c>
       <c r="D428" t="s">
         <v>18</v>
@@ -30091,18 +30545,41 @@
       <c r="G428">
         <v>100</v>
       </c>
-      <c r="O428" s="8"/>
+      <c r="H428">
+        <v>1</v>
+      </c>
+      <c r="I428">
+        <v>1</v>
+      </c>
+      <c r="J428">
+        <v>50</v>
+      </c>
+      <c r="K428">
+        <v>30</v>
+      </c>
+      <c r="L428">
+        <v>3</v>
+      </c>
+      <c r="M428">
+        <v>110</v>
+      </c>
+      <c r="N428" t="s">
+        <v>31</v>
+      </c>
+      <c r="O428" s="8">
+        <v>27</v>
+      </c>
       <c r="P428" s="10"/>
       <c r="Q428" s="10"/>
     </row>
-    <row r="429" spans="1:17">
+    <row r="429" spans="1:17" ht="30">
       <c r="A429">
         <v>428</v>
       </c>
       <c r="B429">
         <v>428</v>
       </c>
-      <c r="C429" t="s">
+      <c r="C429" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="D429" t="s">
@@ -30117,10 +30594,33 @@
       <c r="G429">
         <v>10</v>
       </c>
+      <c r="H429">
+        <v>0</v>
+      </c>
+      <c r="I429">
+        <v>1</v>
+      </c>
+      <c r="J429">
+        <v>1000</v>
+      </c>
+      <c r="K429">
+        <v>1</v>
+      </c>
+      <c r="L429">
+        <v>0</v>
+      </c>
+      <c r="M429">
+        <v>50</v>
+      </c>
+      <c r="N429" t="s">
+        <v>21</v>
+      </c>
       <c r="O429" s="8">
         <v>0</v>
       </c>
-      <c r="P429" s="10"/>
+      <c r="P429" s="10" t="s">
+        <v>2193</v>
+      </c>
       <c r="Q429" s="10"/>
     </row>
     <row r="430" spans="1:17" ht="60">
@@ -30130,7 +30630,7 @@
       <c r="B430">
         <v>429</v>
       </c>
-      <c r="C430" t="s">
+      <c r="C430" s="6" t="s">
         <v>1339</v>
       </c>
       <c r="D430" t="s">
@@ -30172,7 +30672,9 @@
       <c r="P430" s="10" t="s">
         <v>1341</v>
       </c>
-      <c r="Q430" s="10"/>
+      <c r="Q430" s="10" t="s">
+        <v>2228</v>
+      </c>
     </row>
     <row r="431" spans="1:17" ht="90">
       <c r="A431">
@@ -30181,7 +30683,7 @@
       <c r="B431">
         <v>430</v>
       </c>
-      <c r="C431" t="s">
+      <c r="C431" s="6" t="s">
         <v>1342</v>
       </c>
       <c r="D431" t="s">
@@ -30223,7 +30725,9 @@
       <c r="P431" s="10" t="s">
         <v>1344</v>
       </c>
-      <c r="Q431" s="10"/>
+      <c r="Q431" s="10" t="s">
+        <v>2229</v>
+      </c>
     </row>
     <row r="432" spans="1:17" ht="60">
       <c r="A432">
@@ -30232,7 +30736,7 @@
       <c r="B432">
         <v>431</v>
       </c>
-      <c r="C432" t="s">
+      <c r="C432" s="6" t="s">
         <v>1345</v>
       </c>
       <c r="D432" t="s">
@@ -30274,7 +30778,9 @@
       <c r="P432" s="10" t="s">
         <v>1348</v>
       </c>
-      <c r="Q432" s="10"/>
+      <c r="Q432" s="10" t="s">
+        <v>2230</v>
+      </c>
     </row>
     <row r="433" spans="1:17" ht="105">
       <c r="A433">
@@ -30283,7 +30789,7 @@
       <c r="B433">
         <v>432</v>
       </c>
-      <c r="C433" t="s">
+      <c r="C433" s="6" t="s">
         <v>1349</v>
       </c>
       <c r="D433" t="s">
@@ -30325,7 +30831,9 @@
       <c r="P433" s="10" t="s">
         <v>2171</v>
       </c>
-      <c r="Q433" s="10"/>
+      <c r="Q433" s="10" t="s">
+        <v>2231</v>
+      </c>
     </row>
     <row r="434" spans="1:17" ht="75">
       <c r="A434">
@@ -30334,7 +30842,7 @@
       <c r="B434">
         <v>433</v>
       </c>
-      <c r="C434" t="s">
+      <c r="C434" s="6" t="s">
         <v>1351</v>
       </c>
       <c r="D434" t="s">
@@ -30376,16 +30884,18 @@
       <c r="P434" s="10" t="s">
         <v>2172</v>
       </c>
-      <c r="Q434" s="10"/>
-    </row>
-    <row r="435" spans="1:17" ht="45">
+      <c r="Q434" s="10" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="435" spans="1:17" ht="60">
       <c r="A435">
         <v>434</v>
       </c>
       <c r="B435">
         <v>434</v>
       </c>
-      <c r="C435" t="s">
+      <c r="C435" s="6" t="s">
         <v>1354</v>
       </c>
       <c r="D435" t="s">
@@ -30427,16 +30937,18 @@
       <c r="P435" s="10" t="s">
         <v>1356</v>
       </c>
-      <c r="Q435" s="10"/>
-    </row>
-    <row r="436" spans="1:17" ht="30">
+      <c r="Q435" s="10" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="436" spans="1:17" ht="70">
       <c r="A436">
         <v>435</v>
       </c>
       <c r="B436">
         <v>435</v>
       </c>
-      <c r="C436" t="s">
+      <c r="C436" s="6" t="s">
         <v>1357</v>
       </c>
       <c r="D436" t="s">
@@ -30478,16 +30990,18 @@
       <c r="P436" s="10" t="s">
         <v>1359</v>
       </c>
-      <c r="Q436" s="10"/>
-    </row>
-    <row r="437" spans="1:17" ht="45">
+      <c r="Q436" s="14" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="437" spans="1:17" ht="70">
       <c r="A437">
         <v>436</v>
       </c>
       <c r="B437">
         <v>436</v>
       </c>
-      <c r="C437" t="s">
+      <c r="C437" s="6" t="s">
         <v>1360</v>
       </c>
       <c r="D437" t="s">
@@ -30529,16 +31043,18 @@
       <c r="P437" s="10" t="s">
         <v>1362</v>
       </c>
-      <c r="Q437" s="10"/>
-    </row>
-    <row r="438" spans="1:17" ht="90">
+      <c r="Q437" s="14" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="438" spans="1:17" ht="92">
       <c r="A438">
         <v>437</v>
       </c>
       <c r="B438">
         <v>437</v>
       </c>
-      <c r="C438" t="s">
+      <c r="C438" s="6" t="s">
         <v>1363</v>
       </c>
       <c r="D438" t="s">
@@ -30580,16 +31096,16 @@
       <c r="P438" s="10" t="s">
         <v>1365</v>
       </c>
-      <c r="Q438" s="10"/>
-    </row>
-    <row r="439" spans="1:17" ht="60">
+      <c r="Q438" s="13"/>
+    </row>
+    <row r="439" spans="1:17" ht="62">
       <c r="A439">
         <v>438</v>
       </c>
       <c r="B439">
         <v>438</v>
       </c>
-      <c r="C439" t="s">
+      <c r="C439" s="6" t="s">
         <v>1366</v>
       </c>
       <c r="D439" t="s">
@@ -30631,7 +31147,7 @@
       <c r="P439" s="10" t="s">
         <v>1368</v>
       </c>
-      <c r="Q439" s="10"/>
+      <c r="Q439" s="13"/>
     </row>
     <row r="440" spans="1:17" ht="105">
       <c r="A440">
@@ -30640,7 +31156,7 @@
       <c r="B440">
         <v>439</v>
       </c>
-      <c r="C440" t="s">
+      <c r="C440" s="6" t="s">
         <v>1369</v>
       </c>
       <c r="D440" t="s">
@@ -30691,7 +31207,7 @@
       <c r="B441">
         <v>440</v>
       </c>
-      <c r="C441" t="s">
+      <c r="C441" s="6" t="s">
         <v>1372</v>
       </c>
       <c r="D441" t="s">
@@ -30742,7 +31258,7 @@
       <c r="B442">
         <v>441</v>
       </c>
-      <c r="C442" t="s">
+      <c r="C442" s="6" t="s">
         <v>1375</v>
       </c>
       <c r="D442" t="s">
@@ -30793,7 +31309,7 @@
       <c r="B443">
         <v>442</v>
       </c>
-      <c r="C443" t="s">
+      <c r="C443" s="6" t="s">
         <v>1378</v>
       </c>
       <c r="D443" t="s">
@@ -30844,7 +31360,7 @@
       <c r="B444">
         <v>443</v>
       </c>
-      <c r="C444" t="s">
+      <c r="C444" s="6" t="s">
         <v>1381</v>
       </c>
       <c r="D444" t="s">
@@ -30895,7 +31411,7 @@
       <c r="B445">
         <v>444</v>
       </c>
-      <c r="C445" t="s">
+      <c r="C445" s="6" t="s">
         <v>1384</v>
       </c>
       <c r="D445" t="s">
@@ -30946,7 +31462,7 @@
       <c r="B446">
         <v>445</v>
       </c>
-      <c r="C446" t="s">
+      <c r="C446" s="6" t="s">
         <v>1387</v>
       </c>
       <c r="D446" t="s">
@@ -30990,14 +31506,14 @@
       </c>
       <c r="Q446" s="10"/>
     </row>
-    <row r="447" spans="1:17">
+    <row r="447" spans="1:17" ht="30">
       <c r="A447">
         <v>446</v>
       </c>
       <c r="B447">
         <v>446</v>
       </c>
-      <c r="C447" t="s">
+      <c r="C447" s="6" t="s">
         <v>1390</v>
       </c>
       <c r="D447" t="s">
@@ -31012,10 +31528,33 @@
       <c r="G447">
         <v>1000</v>
       </c>
+      <c r="H447">
+        <v>0</v>
+      </c>
+      <c r="I447">
+        <v>0</v>
+      </c>
+      <c r="J447">
+        <v>0</v>
+      </c>
+      <c r="K447">
+        <v>1</v>
+      </c>
+      <c r="L447">
+        <v>0</v>
+      </c>
+      <c r="M447">
+        <v>0</v>
+      </c>
+      <c r="N447" t="s">
+        <v>31</v>
+      </c>
       <c r="O447" s="8">
         <v>0</v>
       </c>
-      <c r="P447" s="10"/>
+      <c r="P447" s="10" t="s">
+        <v>2193</v>
+      </c>
       <c r="Q447" s="10"/>
     </row>
     <row r="448" spans="1:17" ht="30">
@@ -31025,7 +31564,7 @@
       <c r="B448">
         <v>447</v>
       </c>
-      <c r="C448" t="s">
+      <c r="C448" s="6" t="s">
         <v>1392</v>
       </c>
       <c r="D448" t="s">
@@ -31076,7 +31615,7 @@
       <c r="B449">
         <v>448</v>
       </c>
-      <c r="C449" t="s">
+      <c r="C449" s="6" t="s">
         <v>1395</v>
       </c>
       <c r="D449" t="s">
@@ -31127,7 +31666,7 @@
       <c r="B450">
         <v>449</v>
       </c>
-      <c r="C450" t="s">
+      <c r="C450" s="6" t="s">
         <v>1398</v>
       </c>
       <c r="D450" t="s">
@@ -31176,7 +31715,7 @@
       <c r="B451">
         <v>450</v>
       </c>
-      <c r="C451" t="s">
+      <c r="C451" s="6" t="s">
         <v>1400</v>
       </c>
       <c r="D451" t="s">
@@ -31225,7 +31764,7 @@
       <c r="B452">
         <v>451</v>
       </c>
-      <c r="C452" t="s">
+      <c r="C452" s="6" t="s">
         <v>1402</v>
       </c>
       <c r="D452" t="s">
@@ -31276,7 +31815,7 @@
       <c r="B453">
         <v>452</v>
       </c>
-      <c r="C453" t="s">
+      <c r="C453" s="6" t="s">
         <v>1405</v>
       </c>
       <c r="D453" t="s">
@@ -31291,18 +31830,41 @@
       <c r="G453">
         <v>3000</v>
       </c>
-      <c r="O453" s="8"/>
+      <c r="H453">
+        <v>600</v>
+      </c>
+      <c r="I453">
+        <v>3</v>
+      </c>
+      <c r="J453">
+        <v>18</v>
+      </c>
+      <c r="K453">
+        <v>4</v>
+      </c>
+      <c r="L453">
+        <v>25</v>
+      </c>
+      <c r="M453">
+        <v>110</v>
+      </c>
+      <c r="N453" t="s">
+        <v>21</v>
+      </c>
+      <c r="O453" s="8">
+        <v>150</v>
+      </c>
       <c r="P453" s="10"/>
       <c r="Q453" s="10"/>
     </row>
-    <row r="454" spans="1:17" ht="30">
+    <row r="454" spans="1:17" ht="60">
       <c r="A454">
         <v>453</v>
       </c>
       <c r="B454">
         <v>453</v>
       </c>
-      <c r="C454" t="s">
+      <c r="C454" s="6" t="s">
         <v>1407</v>
       </c>
       <c r="D454" t="s">
@@ -31344,16 +31906,18 @@
       <c r="P454" s="10" t="s">
         <v>1410</v>
       </c>
-      <c r="Q454" s="10"/>
-    </row>
-    <row r="455" spans="1:17">
+      <c r="Q454" s="10" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="455" spans="1:17" ht="75">
       <c r="A455">
         <v>454</v>
       </c>
       <c r="B455">
         <v>454</v>
       </c>
-      <c r="C455" t="s">
+      <c r="C455" s="6" t="s">
         <v>1411</v>
       </c>
       <c r="D455" t="s">
@@ -31368,20 +31932,43 @@
       <c r="G455">
         <v>30000</v>
       </c>
+      <c r="H455">
+        <v>1500</v>
+      </c>
+      <c r="I455">
+        <v>1</v>
+      </c>
+      <c r="J455">
+        <v>559</v>
+      </c>
+      <c r="K455">
+        <v>42</v>
+      </c>
+      <c r="L455">
+        <v>0</v>
+      </c>
+      <c r="M455">
+        <v>2000</v>
+      </c>
+      <c r="N455" t="s">
+        <v>31</v>
+      </c>
       <c r="O455" s="8">
         <v>0</v>
       </c>
-      <c r="P455" s="10"/>
+      <c r="P455" s="10" t="s">
+        <v>2237</v>
+      </c>
       <c r="Q455" s="10"/>
     </row>
-    <row r="456" spans="1:17" ht="15">
+    <row r="456" spans="1:17" ht="60">
       <c r="A456">
         <v>455</v>
       </c>
       <c r="B456">
         <v>455</v>
       </c>
-      <c r="C456" t="s">
+      <c r="C456" s="6" t="s">
         <v>1413</v>
       </c>
       <c r="D456" t="s">
@@ -31423,16 +32010,18 @@
       <c r="P456" s="10" t="s">
         <v>1416</v>
       </c>
-      <c r="Q456" s="10"/>
-    </row>
-    <row r="457" spans="1:17" ht="30">
+      <c r="Q456" s="10" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="457" spans="1:17" ht="60">
       <c r="A457">
         <v>456</v>
       </c>
       <c r="B457">
         <v>456</v>
       </c>
-      <c r="C457" t="s">
+      <c r="C457" s="6" t="s">
         <v>1417</v>
       </c>
       <c r="D457" t="s">
@@ -31474,16 +32063,18 @@
       <c r="P457" s="10" t="s">
         <v>1420</v>
       </c>
-      <c r="Q457" s="10"/>
-    </row>
-    <row r="458" spans="1:17">
+      <c r="Q457" s="10" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="458" spans="1:17" ht="30">
       <c r="A458">
         <v>457</v>
       </c>
       <c r="B458">
         <v>457</v>
       </c>
-      <c r="C458" t="s">
+      <c r="C458" s="6" t="s">
         <v>1421</v>
       </c>
       <c r="D458" t="s">
@@ -31498,11 +32089,33 @@
       <c r="G458">
         <v>100</v>
       </c>
+      <c r="H458">
+        <v>999999</v>
+      </c>
+      <c r="I458">
+        <v>0</v>
+      </c>
+      <c r="J458">
+        <v>209</v>
+      </c>
+      <c r="K458">
+        <v>10</v>
+      </c>
+      <c r="L458">
+        <v>0</v>
+      </c>
+      <c r="M458">
+        <v>450</v>
+      </c>
+      <c r="N458" t="s">
+        <v>31</v>
+      </c>
       <c r="O458" s="8">
         <v>0</v>
       </c>
-      <c r="P458" s="10"/>
-      <c r="Q458" s="10"/>
+      <c r="P458" s="10" t="s">
+        <v>2193</v>
+      </c>
     </row>
     <row r="459" spans="1:17" ht="60">
       <c r="A459">
@@ -31511,7 +32124,7 @@
       <c r="B459">
         <v>458</v>
       </c>
-      <c r="C459" t="s">
+      <c r="C459" s="6" t="s">
         <v>1423</v>
       </c>
       <c r="D459" t="s">
@@ -31553,7 +32166,9 @@
       <c r="P459" s="10" t="s">
         <v>1426</v>
       </c>
-      <c r="Q459" s="10"/>
+      <c r="Q459" s="10" t="s">
+        <v>2240</v>
+      </c>
     </row>
     <row r="460" spans="1:17" ht="120">
       <c r="A460">
@@ -31562,7 +32177,7 @@
       <c r="B460">
         <v>459</v>
       </c>
-      <c r="C460" t="s">
+      <c r="C460" s="6" t="s">
         <v>1427</v>
       </c>
       <c r="D460" t="s">
@@ -31604,7 +32219,9 @@
       <c r="P460" s="10" t="s">
         <v>1429</v>
       </c>
-      <c r="Q460" s="10"/>
+      <c r="Q460" s="10" t="s">
+        <v>2241</v>
+      </c>
     </row>
     <row r="461" spans="1:17" ht="60">
       <c r="A461">
@@ -31613,7 +32230,7 @@
       <c r="B461">
         <v>460</v>
       </c>
-      <c r="C461" t="s">
+      <c r="C461" s="6" t="s">
         <v>1430</v>
       </c>
       <c r="D461" t="s">
@@ -31664,7 +32281,7 @@
       <c r="B462">
         <v>461</v>
       </c>
-      <c r="C462" t="s">
+      <c r="C462" s="6" t="s">
         <v>1433</v>
       </c>
       <c r="D462" t="s">
@@ -31708,14 +32325,14 @@
       </c>
       <c r="Q462" s="10"/>
     </row>
-    <row r="463" spans="1:17" ht="15">
+    <row r="463" spans="1:17" ht="60">
       <c r="A463">
         <v>462</v>
       </c>
       <c r="B463">
         <v>462</v>
       </c>
-      <c r="C463" t="s">
+      <c r="C463" s="6" t="s">
         <v>1435</v>
       </c>
       <c r="D463" t="s">
@@ -31757,16 +32374,18 @@
       <c r="P463" s="10" t="s">
         <v>2174</v>
       </c>
-      <c r="Q463" s="10"/>
-    </row>
-    <row r="464" spans="1:17">
+      <c r="Q463" s="10" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="464" spans="1:17" ht="45">
       <c r="A464">
         <v>463</v>
       </c>
       <c r="B464">
         <v>463</v>
       </c>
-      <c r="C464" t="s">
+      <c r="C464" s="6" t="s">
         <v>1438</v>
       </c>
       <c r="D464" t="s">
@@ -31781,10 +32400,33 @@
       <c r="G464">
         <v>100</v>
       </c>
+      <c r="H464">
+        <v>999999</v>
+      </c>
+      <c r="I464">
+        <v>0</v>
+      </c>
+      <c r="J464">
+        <v>709</v>
+      </c>
+      <c r="K464">
+        <v>10</v>
+      </c>
+      <c r="L464">
+        <v>0</v>
+      </c>
+      <c r="M464">
+        <v>300</v>
+      </c>
+      <c r="N464" t="s">
+        <v>31</v>
+      </c>
       <c r="O464" s="8">
         <v>0</v>
       </c>
-      <c r="P464" s="10"/>
+      <c r="P464" s="10" t="s">
+        <v>2243</v>
+      </c>
       <c r="Q464" s="10"/>
     </row>
     <row r="465" spans="1:17" ht="90">
@@ -31794,7 +32436,7 @@
       <c r="B465">
         <v>464</v>
       </c>
-      <c r="C465" t="s">
+      <c r="C465" s="6" t="s">
         <v>1440</v>
       </c>
       <c r="D465" t="s">
@@ -31845,7 +32487,7 @@
       <c r="B466">
         <v>465</v>
       </c>
-      <c r="C466" t="s">
+      <c r="C466" s="6" t="s">
         <v>1444</v>
       </c>
       <c r="D466" t="s">
@@ -31896,7 +32538,7 @@
       <c r="B467">
         <v>466</v>
       </c>
-      <c r="C467" t="s">
+      <c r="C467" s="6" t="s">
         <v>1447</v>
       </c>
       <c r="D467" t="s">
@@ -31940,14 +32582,14 @@
       </c>
       <c r="Q467" s="10"/>
     </row>
-    <row r="468" spans="1:17" ht="45">
+    <row r="468" spans="1:17" ht="60">
       <c r="A468">
         <v>467</v>
       </c>
       <c r="B468">
         <v>467</v>
       </c>
-      <c r="C468" t="s">
+      <c r="C468" s="6" t="s">
         <v>1450</v>
       </c>
       <c r="D468" t="s">
@@ -31989,16 +32631,18 @@
       <c r="P468" s="10" t="s">
         <v>1453</v>
       </c>
-      <c r="Q468" s="10"/>
-    </row>
-    <row r="469" spans="1:17" ht="45">
+      <c r="Q468" s="10" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="469" spans="1:17" ht="60">
       <c r="A469">
         <v>468</v>
       </c>
       <c r="B469">
         <v>468</v>
       </c>
-      <c r="C469" t="s">
+      <c r="C469" s="6" t="s">
         <v>1454</v>
       </c>
       <c r="D469" t="s">
@@ -32040,7 +32684,9 @@
       <c r="P469" s="10" t="s">
         <v>1457</v>
       </c>
-      <c r="Q469" s="10"/>
+      <c r="Q469" s="10" t="s">
+        <v>2245</v>
+      </c>
     </row>
     <row r="470" spans="1:17" ht="75">
       <c r="A470">
@@ -32049,7 +32695,7 @@
       <c r="B470">
         <v>469</v>
       </c>
-      <c r="C470" t="s">
+      <c r="C470" s="6" t="s">
         <v>1458</v>
       </c>
       <c r="D470" t="s">
@@ -32091,7 +32737,9 @@
       <c r="P470" s="10" t="s">
         <v>1461</v>
       </c>
-      <c r="Q470" s="10"/>
+      <c r="Q470" s="10" t="s">
+        <v>2246</v>
+      </c>
     </row>
     <row r="471" spans="1:17" ht="60">
       <c r="A471">
@@ -32100,7 +32748,7 @@
       <c r="B471">
         <v>470</v>
       </c>
-      <c r="C471" t="s">
+      <c r="C471" s="6" t="s">
         <v>1462</v>
       </c>
       <c r="D471" t="s">
@@ -32142,7 +32790,9 @@
       <c r="P471" s="10" t="s">
         <v>1464</v>
       </c>
-      <c r="Q471" s="10"/>
+      <c r="Q471" s="10" t="s">
+        <v>2247</v>
+      </c>
     </row>
     <row r="472" spans="1:17" ht="60">
       <c r="A472">
@@ -32151,7 +32801,7 @@
       <c r="B472">
         <v>471</v>
       </c>
-      <c r="C472" t="s">
+      <c r="C472" s="6" t="s">
         <v>1465</v>
       </c>
       <c r="D472" t="s">
@@ -32202,7 +32852,7 @@
       <c r="B473">
         <v>472</v>
       </c>
-      <c r="C473" t="s">
+      <c r="C473" s="6" t="s">
         <v>1468</v>
       </c>
       <c r="D473" t="s">
@@ -32251,7 +32901,7 @@
       <c r="B474">
         <v>473</v>
       </c>
-      <c r="C474" t="s">
+      <c r="C474" s="6" t="s">
         <v>1470</v>
       </c>
       <c r="D474" t="s">
@@ -32300,7 +32950,7 @@
       <c r="B475">
         <v>474</v>
       </c>
-      <c r="C475" t="s">
+      <c r="C475" s="6" t="s">
         <v>1472</v>
       </c>
       <c r="D475" t="s">
@@ -32351,7 +33001,7 @@
       <c r="B476">
         <v>475</v>
       </c>
-      <c r="C476" t="s">
+      <c r="C476" s="6" t="s">
         <v>1474</v>
       </c>
       <c r="D476" t="s">
@@ -32402,7 +33052,7 @@
       <c r="B477">
         <v>476</v>
       </c>
-      <c r="C477" t="s">
+      <c r="C477" s="6" t="s">
         <v>1477</v>
       </c>
       <c r="D477" t="s">
@@ -32453,7 +33103,7 @@
       <c r="B478">
         <v>477</v>
       </c>
-      <c r="C478" t="s">
+      <c r="C478" s="6" t="s">
         <v>1480</v>
       </c>
       <c r="D478" t="s">
@@ -32504,7 +33154,7 @@
       <c r="B479">
         <v>478</v>
       </c>
-      <c r="C479" t="s">
+      <c r="C479" s="6" t="s">
         <v>1483</v>
       </c>
       <c r="D479" t="s">
@@ -32553,7 +33203,7 @@
       <c r="B480">
         <v>479</v>
       </c>
-      <c r="C480" t="s">
+      <c r="C480" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="D480" t="s">
@@ -32592,17 +33242,16 @@
       <c r="O480" s="8">
         <v>0</v>
       </c>
-      <c r="P480" s="10"/>
       <c r="Q480" s="10"/>
     </row>
-    <row r="481" spans="1:17">
+    <row r="481" spans="1:17" ht="30">
       <c r="A481">
         <v>480</v>
       </c>
       <c r="B481">
         <v>480</v>
       </c>
-      <c r="C481" t="s">
+      <c r="C481" s="6" t="s">
         <v>1487</v>
       </c>
       <c r="D481" t="s">
@@ -32617,10 +33266,33 @@
       <c r="G481">
         <v>10</v>
       </c>
+      <c r="H481">
+        <v>1</v>
+      </c>
+      <c r="I481">
+        <v>1</v>
+      </c>
+      <c r="J481">
+        <v>1000</v>
+      </c>
+      <c r="K481">
+        <v>1</v>
+      </c>
+      <c r="L481">
+        <v>0</v>
+      </c>
+      <c r="M481">
+        <v>50</v>
+      </c>
+      <c r="N481" t="s">
+        <v>21</v>
+      </c>
       <c r="O481" s="8">
         <v>0</v>
       </c>
-      <c r="P481" s="10"/>
+      <c r="P481" s="10" t="s">
+        <v>2193</v>
+      </c>
       <c r="Q481" s="10"/>
     </row>
     <row r="482" spans="1:17">
@@ -32630,7 +33302,7 @@
       <c r="B482">
         <v>481</v>
       </c>
-      <c r="C482" t="s">
+      <c r="C482" s="6" t="s">
         <v>1489</v>
       </c>
       <c r="D482" t="s">
@@ -32667,7 +33339,7 @@
         <v>21</v>
       </c>
       <c r="O482" s="8">
-        <v>592</v>
+        <v>150</v>
       </c>
       <c r="P482" s="10"/>
       <c r="Q482" s="10"/>
@@ -32679,7 +33351,7 @@
       <c r="B483">
         <v>482</v>
       </c>
-      <c r="C483" t="s">
+      <c r="C483" s="6" t="s">
         <v>1491</v>
       </c>
       <c r="D483" t="s">
@@ -32723,14 +33395,14 @@
       </c>
       <c r="Q483" s="10"/>
     </row>
-    <row r="484" spans="1:17" ht="30">
+    <row r="484" spans="1:17" ht="60">
       <c r="A484">
         <v>483</v>
       </c>
       <c r="B484">
         <v>483</v>
       </c>
-      <c r="C484" t="s">
+      <c r="C484" s="6" t="s">
         <v>1493</v>
       </c>
       <c r="D484" t="s">
@@ -32772,7 +33444,9 @@
       <c r="P484" s="10" t="s">
         <v>1496</v>
       </c>
-      <c r="Q484" s="10"/>
+      <c r="Q484" s="10" t="s">
+        <v>2248</v>
+      </c>
     </row>
     <row r="485" spans="1:17" ht="60">
       <c r="A485">
@@ -32781,7 +33455,7 @@
       <c r="B485">
         <v>484</v>
       </c>
-      <c r="C485" t="s">
+      <c r="C485" s="6" t="s">
         <v>1497</v>
       </c>
       <c r="D485" t="s">
@@ -32823,16 +33497,18 @@
       <c r="P485" s="10" t="s">
         <v>1499</v>
       </c>
-      <c r="Q485" s="10"/>
-    </row>
-    <row r="486" spans="1:17" ht="45">
+      <c r="Q485" s="10" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="486" spans="1:17" ht="60">
       <c r="A486">
         <v>485</v>
       </c>
       <c r="B486">
         <v>485</v>
       </c>
-      <c r="C486" t="s">
+      <c r="C486" s="6" t="s">
         <v>1500</v>
       </c>
       <c r="D486" t="s">
@@ -32874,7 +33550,9 @@
       <c r="P486" s="10" t="s">
         <v>1502</v>
       </c>
-      <c r="Q486" s="10"/>
+      <c r="Q486" s="10" t="s">
+        <v>2250</v>
+      </c>
     </row>
     <row r="487" spans="1:17" ht="30">
       <c r="A487">
@@ -32883,7 +33561,7 @@
       <c r="B487">
         <v>486</v>
       </c>
-      <c r="C487" t="s">
+      <c r="C487" s="6" t="s">
         <v>1503</v>
       </c>
       <c r="D487" t="s">
@@ -32934,7 +33612,7 @@
       <c r="B488">
         <v>487</v>
       </c>
-      <c r="C488" t="s">
+      <c r="C488" s="6" t="s">
         <v>1506</v>
       </c>
       <c r="D488" t="s">
@@ -32985,7 +33663,7 @@
       <c r="B489">
         <v>488</v>
       </c>
-      <c r="C489" t="s">
+      <c r="C489" s="6" t="s">
         <v>1508</v>
       </c>
       <c r="D489" t="s">
@@ -33034,7 +33712,7 @@
       <c r="B490">
         <v>489</v>
       </c>
-      <c r="C490" t="s">
+      <c r="C490" s="6" t="s">
         <v>1510</v>
       </c>
       <c r="D490" t="s">
@@ -33078,14 +33756,14 @@
       </c>
       <c r="Q490" s="10"/>
     </row>
-    <row r="491" spans="1:17">
+    <row r="491" spans="1:17" ht="30">
       <c r="A491">
         <v>490</v>
       </c>
       <c r="B491">
         <v>490</v>
       </c>
-      <c r="C491" t="s">
+      <c r="C491" s="6" t="s">
         <v>1512</v>
       </c>
       <c r="D491" t="s">
@@ -33100,10 +33778,33 @@
       <c r="G491">
         <v>10</v>
       </c>
+      <c r="H491">
+        <v>1</v>
+      </c>
+      <c r="I491">
+        <v>1</v>
+      </c>
+      <c r="J491">
+        <v>1000</v>
+      </c>
+      <c r="K491">
+        <v>1</v>
+      </c>
+      <c r="L491">
+        <v>0</v>
+      </c>
+      <c r="M491">
+        <v>10</v>
+      </c>
+      <c r="N491" t="s">
+        <v>21</v>
+      </c>
       <c r="O491" s="8">
         <v>0</v>
       </c>
-      <c r="P491" s="10"/>
+      <c r="P491" s="10" t="s">
+        <v>2193</v>
+      </c>
       <c r="Q491" s="10"/>
     </row>
     <row r="492" spans="1:17" ht="30">
@@ -33113,7 +33814,7 @@
       <c r="B492">
         <v>491</v>
       </c>
-      <c r="C492" t="s">
+      <c r="C492" s="6" t="s">
         <v>1514</v>
       </c>
       <c r="D492" t="s">
@@ -33157,14 +33858,14 @@
       </c>
       <c r="Q492" s="10"/>
     </row>
-    <row r="493" spans="1:17" ht="30">
+    <row r="493" spans="1:17" ht="60">
       <c r="A493">
         <v>492</v>
       </c>
       <c r="B493">
         <v>492</v>
       </c>
-      <c r="C493" t="s">
+      <c r="C493" s="6" t="s">
         <v>1517</v>
       </c>
       <c r="D493" t="s">
@@ -33206,16 +33907,18 @@
       <c r="P493" s="10" t="s">
         <v>1519</v>
       </c>
-      <c r="Q493" s="10"/>
-    </row>
-    <row r="494" spans="1:17" ht="30">
+      <c r="Q493" s="10" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="494" spans="1:17" ht="60">
       <c r="A494">
         <v>493</v>
       </c>
       <c r="B494">
         <v>493</v>
       </c>
-      <c r="C494" t="s">
+      <c r="C494" s="6" t="s">
         <v>1520</v>
       </c>
       <c r="D494" t="s">
@@ -33257,7 +33960,9 @@
       <c r="P494" s="10" t="s">
         <v>1522</v>
       </c>
-      <c r="Q494" s="10"/>
+      <c r="Q494" s="10" t="s">
+        <v>2252</v>
+      </c>
     </row>
     <row r="495" spans="1:17" ht="75">
       <c r="A495">
@@ -33266,7 +33971,7 @@
       <c r="B495">
         <v>494</v>
       </c>
-      <c r="C495" t="s">
+      <c r="C495" s="6" t="s">
         <v>1523</v>
       </c>
       <c r="D495" t="s">
@@ -33308,16 +34013,18 @@
       <c r="P495" s="10" t="s">
         <v>1525</v>
       </c>
-      <c r="Q495" s="10"/>
-    </row>
-    <row r="496" spans="1:17" ht="45">
+      <c r="Q495" s="10" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="496" spans="1:17" ht="60">
       <c r="A496">
         <v>495</v>
       </c>
       <c r="B496">
         <v>495</v>
       </c>
-      <c r="C496" t="s">
+      <c r="C496" s="6" t="s">
         <v>1526</v>
       </c>
       <c r="D496" t="s">
@@ -33359,7 +34066,9 @@
       <c r="P496" s="10" t="s">
         <v>1528</v>
       </c>
-      <c r="Q496" s="10"/>
+      <c r="Q496" s="10" t="s">
+        <v>2254</v>
+      </c>
     </row>
     <row r="497" spans="1:17" ht="30">
       <c r="A497">
@@ -33368,7 +34077,7 @@
       <c r="B497">
         <v>496</v>
       </c>
-      <c r="C497" t="s">
+      <c r="C497" s="6" t="s">
         <v>1529</v>
       </c>
       <c r="D497" t="s">
@@ -33419,7 +34128,7 @@
       <c r="B498">
         <v>497</v>
       </c>
-      <c r="C498" t="s">
+      <c r="C498" s="6" t="s">
         <v>1532</v>
       </c>
       <c r="D498" t="s">
@@ -33463,15 +34172,15 @@
       </c>
       <c r="Q498" s="10"/>
     </row>
-    <row r="499" spans="1:17">
+    <row r="499" spans="1:17" ht="45">
       <c r="A499">
         <v>498</v>
       </c>
       <c r="B499">
         <v>498</v>
       </c>
-      <c r="C499" t="s">
-        <v>1535</v>
+      <c r="C499" s="6" t="s">
+        <v>2255</v>
       </c>
       <c r="D499" t="s">
         <v>18</v>
@@ -33485,21 +34194,44 @@
       <c r="G499">
         <v>10</v>
       </c>
+      <c r="H499">
+        <v>1</v>
+      </c>
+      <c r="I499">
+        <v>1</v>
+      </c>
+      <c r="J499">
+        <v>439</v>
+      </c>
+      <c r="K499">
+        <v>60</v>
+      </c>
+      <c r="L499">
+        <v>0</v>
+      </c>
+      <c r="M499">
+        <v>2950</v>
+      </c>
+      <c r="N499" t="s">
+        <v>31</v>
+      </c>
       <c r="O499" s="8">
         <v>0</v>
       </c>
-      <c r="P499" s="10"/>
+      <c r="P499" s="10" t="s">
+        <v>2256</v>
+      </c>
       <c r="Q499" s="10"/>
     </row>
-    <row r="500" spans="1:17">
+    <row r="500" spans="1:17" ht="45">
       <c r="A500">
         <v>499</v>
       </c>
       <c r="B500">
         <v>499</v>
       </c>
-      <c r="C500" t="s">
-        <v>1537</v>
+      <c r="C500" s="6" t="s">
+        <v>2258</v>
       </c>
       <c r="D500" t="s">
         <v>18</v>
@@ -33513,10 +34245,33 @@
       <c r="G500">
         <v>100</v>
       </c>
+      <c r="H500">
+        <v>5000</v>
+      </c>
+      <c r="I500">
+        <v>0</v>
+      </c>
+      <c r="J500">
+        <v>309</v>
+      </c>
+      <c r="K500">
+        <v>10</v>
+      </c>
+      <c r="L500">
+        <v>0</v>
+      </c>
+      <c r="M500">
+        <v>800</v>
+      </c>
+      <c r="N500" t="s">
+        <v>31</v>
+      </c>
       <c r="O500" s="8">
         <v>0</v>
       </c>
-      <c r="P500" s="10"/>
+      <c r="P500" s="10" t="s">
+        <v>2257</v>
+      </c>
       <c r="Q500" s="10"/>
     </row>
     <row r="501" spans="1:17" ht="30">
@@ -33526,7 +34281,7 @@
       <c r="B501">
         <v>500</v>
       </c>
-      <c r="C501" t="s">
+      <c r="C501" s="6" t="s">
         <v>1539</v>
       </c>
       <c r="D501" t="s">
@@ -33577,7 +34332,7 @@
       <c r="B502">
         <v>501</v>
       </c>
-      <c r="C502" t="s">
+      <c r="C502" s="6" t="s">
         <v>1542</v>
       </c>
       <c r="D502" t="s">
@@ -33628,7 +34383,7 @@
       <c r="B503">
         <v>502</v>
       </c>
-      <c r="C503" t="s">
+      <c r="C503" s="6" t="s">
         <v>1545</v>
       </c>
       <c r="D503" t="s">
@@ -33670,16 +34425,18 @@
       <c r="P503" s="10" t="s">
         <v>2176</v>
       </c>
-      <c r="Q503" s="10"/>
-    </row>
-    <row r="504" spans="1:17" ht="45">
+      <c r="Q503" s="10" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="504" spans="1:17" ht="60">
       <c r="A504">
         <v>503</v>
       </c>
       <c r="B504">
         <v>503</v>
       </c>
-      <c r="C504" t="s">
+      <c r="C504" s="6" t="s">
         <v>1547</v>
       </c>
       <c r="D504" t="s">
@@ -33721,16 +34478,18 @@
       <c r="P504" s="10" t="s">
         <v>1549</v>
       </c>
-      <c r="Q504" s="10"/>
-    </row>
-    <row r="505" spans="1:17" ht="15">
+      <c r="Q504" s="10" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="505" spans="1:17" ht="60">
       <c r="A505">
         <v>504</v>
       </c>
       <c r="B505">
         <v>504</v>
       </c>
-      <c r="C505" t="s">
+      <c r="C505" s="6" t="s">
         <v>1550</v>
       </c>
       <c r="D505" t="s">
@@ -33772,7 +34531,9 @@
       <c r="P505" s="10" t="s">
         <v>1552</v>
       </c>
-      <c r="Q505" s="10"/>
+      <c r="Q505" s="10" t="s">
+        <v>2261</v>
+      </c>
     </row>
     <row r="506" spans="1:17" ht="15">
       <c r="A506">
@@ -33781,7 +34542,7 @@
       <c r="B506">
         <v>505</v>
       </c>
-      <c r="C506" t="s">
+      <c r="C506" s="6" t="s">
         <v>1553</v>
       </c>
       <c r="D506" t="s">
@@ -33832,7 +34593,7 @@
       <c r="B507">
         <v>506</v>
       </c>
-      <c r="C507" t="s">
+      <c r="C507" s="6" t="s">
         <v>1556</v>
       </c>
       <c r="D507" t="s">
@@ -33881,7 +34642,7 @@
       <c r="B508">
         <v>507</v>
       </c>
-      <c r="C508" t="s">
+      <c r="C508" s="6" t="s">
         <v>1559</v>
       </c>
       <c r="D508" t="s">
@@ -33932,7 +34693,7 @@
       <c r="B509">
         <v>508</v>
       </c>
-      <c r="C509" t="s">
+      <c r="C509" s="6" t="s">
         <v>1563</v>
       </c>
       <c r="D509" t="s">
@@ -33983,7 +34744,7 @@
       <c r="B510">
         <v>509</v>
       </c>
-      <c r="C510" t="s">
+      <c r="C510" s="6" t="s">
         <v>1567</v>
       </c>
       <c r="D510" t="s">
@@ -34032,7 +34793,7 @@
       <c r="B511">
         <v>510</v>
       </c>
-      <c r="C511" t="s">
+      <c r="C511" s="6" t="s">
         <v>1570</v>
       </c>
       <c r="D511" t="s">
@@ -34081,7 +34842,7 @@
       <c r="B512">
         <v>511</v>
       </c>
-      <c r="C512" t="s">
+      <c r="C512" s="6" t="s">
         <v>1572</v>
       </c>
       <c r="D512" t="s">
@@ -34132,7 +34893,7 @@
       <c r="B513">
         <v>512</v>
       </c>
-      <c r="C513" t="s">
+      <c r="C513" s="6" t="s">
         <v>1575</v>
       </c>
       <c r="D513" t="s">
@@ -34183,7 +34944,7 @@
       <c r="B514">
         <v>513</v>
       </c>
-      <c r="C514" t="s">
+      <c r="C514" s="6" t="s">
         <v>1578</v>
       </c>
       <c r="D514" t="s">
@@ -34234,7 +34995,7 @@
       <c r="B515">
         <v>514</v>
       </c>
-      <c r="C515" t="s">
+      <c r="C515" s="6" t="s">
         <v>1581</v>
       </c>
       <c r="D515" t="s">
@@ -34285,7 +35046,7 @@
       <c r="B516">
         <v>515</v>
       </c>
-      <c r="C516" t="s">
+      <c r="C516" s="6" t="s">
         <v>1584</v>
       </c>
       <c r="D516" t="s">
@@ -34300,7 +35061,30 @@
       <c r="G516">
         <v>30</v>
       </c>
-      <c r="O516" s="8"/>
+      <c r="H516">
+        <v>1</v>
+      </c>
+      <c r="I516">
+        <v>1</v>
+      </c>
+      <c r="J516">
+        <v>50</v>
+      </c>
+      <c r="K516">
+        <v>30</v>
+      </c>
+      <c r="L516">
+        <v>3</v>
+      </c>
+      <c r="M516">
+        <v>110</v>
+      </c>
+      <c r="N516" t="s">
+        <v>31</v>
+      </c>
+      <c r="O516" s="8">
+        <v>27</v>
+      </c>
       <c r="P516" s="10"/>
       <c r="Q516" s="10"/>
     </row>
@@ -34311,7 +35095,7 @@
       <c r="B517">
         <v>516</v>
       </c>
-      <c r="C517" t="s">
+      <c r="C517" s="6" t="s">
         <v>1586</v>
       </c>
       <c r="D517" t="s">
@@ -34353,14 +35137,14 @@
       <c r="P517" s="10"/>
       <c r="Q517" s="10"/>
     </row>
-    <row r="518" spans="1:17" ht="45">
+    <row r="518" spans="1:17" ht="60">
       <c r="A518">
         <v>517</v>
       </c>
       <c r="B518">
         <v>517</v>
       </c>
-      <c r="C518" t="s">
+      <c r="C518" s="6" t="s">
         <v>1588</v>
       </c>
       <c r="D518" t="s">
@@ -34402,7 +35186,9 @@
       <c r="P518" s="10" t="s">
         <v>1590</v>
       </c>
-      <c r="Q518" s="10"/>
+      <c r="Q518" s="10" t="s">
+        <v>2262</v>
+      </c>
     </row>
     <row r="519" spans="1:17" ht="120">
       <c r="A519">
@@ -34411,7 +35197,7 @@
       <c r="B519">
         <v>518</v>
       </c>
-      <c r="C519" t="s">
+      <c r="C519" s="6" t="s">
         <v>1591</v>
       </c>
       <c r="D519" t="s">
@@ -34453,7 +35239,9 @@
       <c r="P519" s="10" t="s">
         <v>2177</v>
       </c>
-      <c r="Q519" s="10"/>
+      <c r="Q519" s="10" t="s">
+        <v>2263</v>
+      </c>
     </row>
     <row r="520" spans="1:17" ht="15">
       <c r="A520">
@@ -34462,7 +35250,7 @@
       <c r="B520">
         <v>519</v>
       </c>
-      <c r="C520" t="s">
+      <c r="C520" s="6" t="s">
         <v>1594</v>
       </c>
       <c r="D520" t="s">
@@ -34513,7 +35301,7 @@
       <c r="B521">
         <v>520</v>
       </c>
-      <c r="C521" t="s">
+      <c r="C521" s="6" t="s">
         <v>1597</v>
       </c>
       <c r="D521" t="s">
@@ -34564,7 +35352,7 @@
       <c r="B522">
         <v>521</v>
       </c>
-      <c r="C522" t="s">
+      <c r="C522" s="6" t="s">
         <v>1600</v>
       </c>
       <c r="D522" t="s">
@@ -34606,7 +35394,9 @@
       <c r="P522" s="10" t="s">
         <v>2178</v>
       </c>
-      <c r="Q522" s="10"/>
+      <c r="Q522" s="10" t="s">
+        <v>2264</v>
+      </c>
     </row>
     <row r="523" spans="1:17" ht="30">
       <c r="A523">
@@ -34615,7 +35405,7 @@
       <c r="B523">
         <v>522</v>
       </c>
-      <c r="C523" t="s">
+      <c r="C523" s="6" t="s">
         <v>1603</v>
       </c>
       <c r="D523" t="s">
@@ -34694,7 +35484,7 @@
       <c r="B525">
         <v>524</v>
       </c>
-      <c r="C525" t="s">
+      <c r="C525" s="6" t="s">
         <v>1608</v>
       </c>
       <c r="D525" t="s">
@@ -34745,7 +35535,7 @@
       <c r="B526">
         <v>525</v>
       </c>
-      <c r="C526" t="s">
+      <c r="C526" s="6" t="s">
         <v>1611</v>
       </c>
       <c r="D526" t="s">
@@ -34796,7 +35586,7 @@
       <c r="B527">
         <v>526</v>
       </c>
-      <c r="C527" t="s">
+      <c r="C527" s="6" t="s">
         <v>1614</v>
       </c>
       <c r="D527" t="s">
@@ -34847,7 +35637,7 @@
       <c r="B528">
         <v>527</v>
       </c>
-      <c r="C528" t="s">
+      <c r="C528" s="6" t="s">
         <v>1618</v>
       </c>
       <c r="D528" t="s">
@@ -34861,6 +35651,27 @@
       </c>
       <c r="G528">
         <v>10000</v>
+      </c>
+      <c r="H528">
+        <v>0</v>
+      </c>
+      <c r="I528">
+        <v>1</v>
+      </c>
+      <c r="J528">
+        <v>0</v>
+      </c>
+      <c r="K528">
+        <v>1</v>
+      </c>
+      <c r="L528">
+        <v>0</v>
+      </c>
+      <c r="M528">
+        <v>0</v>
+      </c>
+      <c r="N528" t="s">
+        <v>21</v>
       </c>
       <c r="O528" s="8">
         <v>0</v>
@@ -34875,7 +35686,7 @@
       <c r="B529">
         <v>528</v>
       </c>
-      <c r="C529" t="s">
+      <c r="C529" s="6" t="s">
         <v>1620</v>
       </c>
       <c r="D529" t="s">
@@ -34917,16 +35728,15 @@
       <c r="P529" s="10" t="s">
         <v>1622</v>
       </c>
-      <c r="Q529" s="10"/>
+      <c r="Q529" s="10" t="s">
+        <v>2265</v>
+      </c>
     </row>
     <row r="530" spans="1:17">
-      <c r="A530">
-        <v>529</v>
-      </c>
       <c r="B530">
         <v>529</v>
       </c>
-      <c r="C530" t="s">
+      <c r="C530" s="6" t="s">
         <v>1623</v>
       </c>
       <c r="D530" t="s">
@@ -34941,13 +35751,34 @@
       <c r="G530">
         <v>10</v>
       </c>
+      <c r="H530">
+        <v>1</v>
+      </c>
+      <c r="I530">
+        <v>1</v>
+      </c>
+      <c r="J530">
+        <v>1000</v>
+      </c>
+      <c r="K530">
+        <v>1</v>
+      </c>
+      <c r="L530">
+        <v>0</v>
+      </c>
+      <c r="M530">
+        <v>10</v>
+      </c>
+      <c r="N530" t="s">
+        <v>21</v>
+      </c>
       <c r="O530" s="8">
         <v>0</v>
       </c>
       <c r="P530" s="10"/>
       <c r="Q530" s="10"/>
     </row>
-    <row r="531" spans="1:17">
+    <row r="531" spans="1:17" ht="75">
       <c r="A531">
         <v>530</v>
       </c>
@@ -34993,7 +35824,9 @@
       <c r="O531" s="8">
         <v>18900</v>
       </c>
-      <c r="P531" s="10"/>
+      <c r="P531" s="10" t="s">
+        <v>2266</v>
+      </c>
       <c r="Q531" s="10"/>
     </row>
   </sheetData>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FE3A86-03C1-944E-94BB-5612145789B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F507712-1FE1-6240-BF3F-147C63CC6138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7552" uniqueCount="2267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7558" uniqueCount="2274">
   <si>
     <t>id</t>
   </si>
@@ -7900,152 +7900,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="MS Mincho"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>この世の穢れに触れぬよう育てられた</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="Avenir"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="MS Mincho"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>エンジェルサイクロンの箱入り娘。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="Avenir"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="MS Mincho"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>毎晩親が寝静まると家を抜け出して</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="Avenir"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="MS Mincho"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>小烈波で世の中を浄化している。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="MS Mincho"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>かつて善の心を持つ自らの分身に討たれ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="Avenir"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="MS Mincho"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>秘境の奥地に封印されていた伝説の古龍。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="Avenir"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="MS Mincho"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>封印されてなお増幅を続けた瘴気は獣たちを</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="Avenir"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE0E0E0"/>
-        <rFont val="MS Mincho"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>超獣化させ、長い歳月を経て封印は解かれた。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>遥か高位の異次元から現世を観測し
 人類に干渉し知恵を与えていた超賢者。
 飽くなき知識欲を満たすため彷徨い続け
@@ -8247,12 +8101,59 @@
 体力残り25%で攻撃1.5倍</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>この世の穢れに触れぬよう育てられた
+エンジェルサイクロンの箱入り娘。
+毎晩親が寝静まると家を抜け出して
+小烈波で世の中を浄化している。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>かつて善の心を持つ自らの分身に討たれ
+秘境の奥地に封印されていた伝説の古龍。
+封印されてなお増幅を続けた瘴気は獣たちを
+超獣化させ、長い歳月を経て封印は解かれた。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>image</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>聡慧の覇者ゼロムート</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>enemy_images/enemy_531.jpg</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>25%で小波動Lv2   
+10%でクリティカル
+城破壊が得意(×4倍ダメージ)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>軽量化により浮くことが可能に
+なったメタルサイクロンの改良版。
+本当は制作費のコストカットによって仕方なく
+軽量化が行われただけということを本人は知らない。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ミニメタルサイクロン</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>metal,floating,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8307,26 +8208,6 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFE0E0E0"/>
-      <name val="Avenir"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFE0E0E0"/>
-      <name val="MS Mincho"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFE0E0E0"/>
-      <name val="Avenir"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -8354,7 +8235,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8380,10 +8261,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -8618,25 +8495,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R531"/>
+  <dimension ref="A1:AG531"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="28" style="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="26.1640625" customWidth="1"/>
-    <col min="6" max="6" width="14.5" customWidth="1"/>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="11" width="20" customWidth="1"/>
-    <col min="12" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="35.6640625" style="6" customWidth="1"/>
-    <col min="17" max="17" width="44.5" style="6" customWidth="1"/>
+    <col min="16" max="16" width="63.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="45" style="6" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="38.83203125" customWidth="1"/>
+    <col min="22" max="22" width="26.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -8653,7 +8533,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>2267</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -30941,7 +30821,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="436" spans="1:17" ht="70">
+    <row r="436" spans="1:17" ht="60">
       <c r="A436">
         <v>435</v>
       </c>
@@ -30990,11 +30870,11 @@
       <c r="P436" s="10" t="s">
         <v>1359</v>
       </c>
-      <c r="Q436" s="14" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="437" spans="1:17" ht="70">
+      <c r="Q436" s="10" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="437" spans="1:17" ht="60">
       <c r="A437">
         <v>436</v>
       </c>
@@ -31043,11 +30923,11 @@
       <c r="P437" s="10" t="s">
         <v>1362</v>
       </c>
-      <c r="Q437" s="14" t="s">
-        <v>2235</v>
-      </c>
-    </row>
-    <row r="438" spans="1:17" ht="92">
+      <c r="Q437" s="10" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="438" spans="1:17" ht="90">
       <c r="A438">
         <v>437</v>
       </c>
@@ -31096,9 +30976,8 @@
       <c r="P438" s="10" t="s">
         <v>1365</v>
       </c>
-      <c r="Q438" s="13"/>
-    </row>
-    <row r="439" spans="1:17" ht="62">
+    </row>
+    <row r="439" spans="1:17" ht="60">
       <c r="A439">
         <v>438</v>
       </c>
@@ -31147,7 +31026,6 @@
       <c r="P439" s="10" t="s">
         <v>1368</v>
       </c>
-      <c r="Q439" s="13"/>
     </row>
     <row r="440" spans="1:17" ht="105">
       <c r="A440">
@@ -31907,7 +31785,7 @@
         <v>1410</v>
       </c>
       <c r="Q454" s="10" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="455" spans="1:17" ht="75">
@@ -31957,7 +31835,7 @@
         <v>0</v>
       </c>
       <c r="P455" s="10" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="Q455" s="10"/>
     </row>
@@ -32011,7 +31889,7 @@
         <v>1416</v>
       </c>
       <c r="Q456" s="10" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="457" spans="1:17" ht="60">
@@ -32064,7 +31942,7 @@
         <v>1420</v>
       </c>
       <c r="Q457" s="10" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="458" spans="1:17" ht="30">
@@ -32167,7 +32045,7 @@
         <v>1426</v>
       </c>
       <c r="Q459" s="10" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="460" spans="1:17" ht="120">
@@ -32220,7 +32098,7 @@
         <v>1429</v>
       </c>
       <c r="Q460" s="10" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="461" spans="1:17" ht="60">
@@ -32375,7 +32253,7 @@
         <v>2174</v>
       </c>
       <c r="Q463" s="10" t="s">
-        <v>2242</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="464" spans="1:17" ht="45">
@@ -32425,7 +32303,7 @@
         <v>0</v>
       </c>
       <c r="P464" s="10" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="Q464" s="10"/>
     </row>
@@ -32632,7 +32510,7 @@
         <v>1453</v>
       </c>
       <c r="Q468" s="10" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="469" spans="1:17" ht="60">
@@ -32685,7 +32563,7 @@
         <v>1457</v>
       </c>
       <c r="Q469" s="10" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="470" spans="1:17" ht="75">
@@ -32738,7 +32616,7 @@
         <v>1461</v>
       </c>
       <c r="Q470" s="10" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="471" spans="1:17" ht="60">
@@ -32791,7 +32669,7 @@
         <v>1464</v>
       </c>
       <c r="Q471" s="10" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="472" spans="1:17" ht="60">
@@ -33445,7 +33323,7 @@
         <v>1496</v>
       </c>
       <c r="Q484" s="10" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="485" spans="1:17" ht="60">
@@ -33498,7 +33376,7 @@
         <v>1499</v>
       </c>
       <c r="Q485" s="10" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="486" spans="1:17" ht="60">
@@ -33551,7 +33429,7 @@
         <v>1502</v>
       </c>
       <c r="Q486" s="10" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="487" spans="1:17" ht="30">
@@ -33908,7 +33786,7 @@
         <v>1519</v>
       </c>
       <c r="Q493" s="10" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="494" spans="1:17" ht="60">
@@ -33961,7 +33839,7 @@
         <v>1522</v>
       </c>
       <c r="Q494" s="10" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="495" spans="1:17" ht="75">
@@ -34014,7 +33892,7 @@
         <v>1525</v>
       </c>
       <c r="Q495" s="10" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="496" spans="1:17" ht="60">
@@ -34067,7 +33945,7 @@
         <v>1528</v>
       </c>
       <c r="Q496" s="10" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="497" spans="1:17" ht="30">
@@ -34180,7 +34058,7 @@
         <v>498</v>
       </c>
       <c r="C499" s="6" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="D499" t="s">
         <v>18</v>
@@ -34219,7 +34097,7 @@
         <v>0</v>
       </c>
       <c r="P499" s="10" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="Q499" s="10"/>
     </row>
@@ -34231,7 +34109,7 @@
         <v>499</v>
       </c>
       <c r="C500" s="6" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="D500" t="s">
         <v>18</v>
@@ -34270,7 +34148,7 @@
         <v>0</v>
       </c>
       <c r="P500" s="10" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="Q500" s="10"/>
     </row>
@@ -34426,7 +34304,7 @@
         <v>2176</v>
       </c>
       <c r="Q503" s="10" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="504" spans="1:17" ht="60">
@@ -34479,7 +34357,7 @@
         <v>1549</v>
       </c>
       <c r="Q504" s="10" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="505" spans="1:17" ht="60">
@@ -34532,7 +34410,7 @@
         <v>1552</v>
       </c>
       <c r="Q505" s="10" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="506" spans="1:17" ht="15">
@@ -35187,7 +35065,7 @@
         <v>1590</v>
       </c>
       <c r="Q518" s="10" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="519" spans="1:17" ht="120">
@@ -35240,7 +35118,7 @@
         <v>2177</v>
       </c>
       <c r="Q519" s="10" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="520" spans="1:17" ht="15">
@@ -35395,7 +35273,7 @@
         <v>2178</v>
       </c>
       <c r="Q522" s="10" t="s">
-        <v>2264</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="523" spans="1:17" ht="30">
@@ -35679,7 +35557,7 @@
       <c r="P528" s="10"/>
       <c r="Q528" s="10"/>
     </row>
-    <row r="529" spans="1:17" ht="90">
+    <row r="529" spans="1:33" ht="75">
       <c r="A529">
         <v>528</v>
       </c>
@@ -35729,56 +35607,106 @@
         <v>1622</v>
       </c>
       <c r="Q529" s="10" t="s">
-        <v>2265</v>
-      </c>
-    </row>
-    <row r="530" spans="1:17">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="530" spans="1:33" ht="60">
+      <c r="A530">
+        <v>529</v>
+      </c>
       <c r="B530">
         <v>529</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>1623</v>
-      </c>
-      <c r="D530" t="s">
-        <v>18</v>
+        <v>2272</v>
       </c>
       <c r="E530" t="s">
         <v>1624</v>
       </c>
-      <c r="F530" t="s">
-        <v>20</v>
+      <c r="F530" s="6" t="s">
+        <v>2273</v>
       </c>
       <c r="G530">
-        <v>10</v>
+        <v>3200</v>
       </c>
       <c r="H530">
-        <v>1</v>
+        <v>2400</v>
       </c>
       <c r="I530">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J530">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="K530">
         <v>1</v>
       </c>
       <c r="L530">
+        <v>45</v>
+      </c>
+      <c r="M530">
+        <v>180</v>
+      </c>
+      <c r="N530" t="s">
+        <v>31</v>
+      </c>
+      <c r="O530">
+        <v>4500</v>
+      </c>
+      <c r="P530" s="10" t="s">
+        <v>2270</v>
+      </c>
+      <c r="Q530" s="10" t="s">
+        <v>2271</v>
+      </c>
+      <c r="R530">
+        <v>529</v>
+      </c>
+      <c r="S530">
+        <v>529</v>
+      </c>
+      <c r="T530" s="6" t="s">
+        <v>1623</v>
+      </c>
+      <c r="U530" t="s">
+        <v>18</v>
+      </c>
+      <c r="V530" s="6" t="s">
+        <v>2269</v>
+      </c>
+      <c r="W530" t="s">
+        <v>20</v>
+      </c>
+      <c r="X530">
+        <v>10</v>
+      </c>
+      <c r="Y530">
+        <v>1</v>
+      </c>
+      <c r="Z530">
+        <v>1</v>
+      </c>
+      <c r="AA530">
+        <v>1000</v>
+      </c>
+      <c r="AB530">
+        <v>1</v>
+      </c>
+      <c r="AC530">
         <v>0</v>
       </c>
-      <c r="M530">
+      <c r="AD530">
         <v>10</v>
       </c>
-      <c r="N530" t="s">
+      <c r="AE530" t="s">
         <v>21</v>
       </c>
-      <c r="O530" s="8">
+      <c r="AF530" s="8">
         <v>0</v>
       </c>
-      <c r="P530" s="10"/>
-      <c r="Q530" s="10"/>
-    </row>
-    <row r="531" spans="1:17" ht="75">
+      <c r="AG530" s="10"/>
+    </row>
+    <row r="531" spans="1:33" ht="45">
       <c r="A531">
         <v>530</v>
       </c>
@@ -35786,7 +35714,7 @@
         <v>530</v>
       </c>
       <c r="C531" s="6" t="s">
-        <v>1625</v>
+        <v>2268</v>
       </c>
       <c r="D531" t="s">
         <v>1626</v>
@@ -35825,20 +35753,20 @@
         <v>18900</v>
       </c>
       <c r="P531" s="10" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="Q531" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="D2:D1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="D2:D1000 U530" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"official,custom"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F1000" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F1000 W530" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"none,red,floating,black,metal,angel,alien,zombie,ancient,devil,witch,apostle,starAlien,superLife,beast,sage,villain,custom"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N1000" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N1000 AE530" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"単体,範囲"</formula1>
     </dataValidation>
   </dataValidations>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F507712-1FE1-6240-BF3F-147C63CC6138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB729154-8CD4-A349-82CD-E77413FE1B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7558" uniqueCount="2274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7559" uniqueCount="2275">
   <si>
     <t>id</t>
   </si>
@@ -8146,6 +8146,12 @@
   </si>
   <si>
     <t>metal,floating,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>世界を滅ぼし去った太古のネコムート。
+覚醒をはじめた強大な力は自らの制御も
+不能にし破壊の限りを尽くす。</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -35755,7 +35761,9 @@
       <c r="P531" s="10" t="s">
         <v>2264</v>
       </c>
-      <c r="Q531" s="10"/>
+      <c r="Q531" s="10" t="s">
+        <v>2274</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB729154-8CD4-A349-82CD-E77413FE1B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51E69FF-9DA6-5442-940F-995B88FE522F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8096,12 +8096,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>範囲3回攻撃 196000 63000 51000(7F 17F 27F)
-40%でLv2波動(波動の攻撃力は３撃目に対応)
-体力残り25%で攻撃1.5倍</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>この世の穢れに触れぬよう育てられた
 エンジェルサイクロンの箱入り娘。
 毎晩親が寝静まると家を抜け出して
@@ -8152,6 +8146,15 @@
     <t>世界を滅ぼし去った太古のネコムート。
 覚醒をはじめた強大な力は自らの制御も
 不能にし破壊の限りを尽くす。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>範囲3連続攻撃 196000 63000 51000(7F 17F 27F)
+40%でLv2波動(波動の攻撃力は３撃目に対応)
+体力残り25%で攻撃1.5倍</t>
+    <rPh sb="3" eb="5">
+      <t>レンゾク</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -8539,7 +8542,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -30877,7 +30880,7 @@
         <v>1359</v>
       </c>
       <c r="Q436" s="10" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="437" spans="1:17" ht="60">
@@ -30930,7 +30933,7 @@
         <v>1362</v>
       </c>
       <c r="Q437" s="10" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="438" spans="1:17" ht="90">
@@ -35624,13 +35627,13 @@
         <v>529</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="E530" t="s">
         <v>1624</v>
       </c>
       <c r="F530" s="6" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="G530">
         <v>3200</v>
@@ -35660,10 +35663,10 @@
         <v>4500</v>
       </c>
       <c r="P530" s="10" t="s">
+        <v>2269</v>
+      </c>
+      <c r="Q530" s="10" t="s">
         <v>2270</v>
-      </c>
-      <c r="Q530" s="10" t="s">
-        <v>2271</v>
       </c>
       <c r="R530">
         <v>529</v>
@@ -35678,7 +35681,7 @@
         <v>18</v>
       </c>
       <c r="V530" s="6" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="W530" t="s">
         <v>20</v>
@@ -35720,7 +35723,7 @@
         <v>530</v>
       </c>
       <c r="C531" s="6" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="D531" t="s">
         <v>1626</v>
@@ -35759,10 +35762,10 @@
         <v>18900</v>
       </c>
       <c r="P531" s="10" t="s">
-        <v>2264</v>
+        <v>2274</v>
       </c>
       <c r="Q531" s="10" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
     </row>
   </sheetData>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51E69FF-9DA6-5442-940F-995B88FE522F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7616A4A9-FAAC-E043-AABB-4ADFD09C8431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7616A4A9-FAAC-E043-AABB-4ADFD09C8431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54488B67-7277-DC44-97DE-80D4654BEFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7526,13 +7526,6 @@
 悪魔シールド（HP60000 KB時、悪魔シールドHP60000再生回復）</t>
   </si>
   <si>
-    <t>2連続攻撃 40000 20000（62F 81F）
-遠方範囲攻撃（1撃目1～401 2撃目401～651）
-古代の呪い（100％の確率で90F特殊能力封印）
-100％の確率で再生産時間50％遅延
-無効 （呪い）</t>
-  </si>
-  <si>
     <t>近づくことも許されない魔界最強の悪魔。
 と本人が豪語する頭でっかちな嫌われ者。
 悪魔研究家によると魔界に生息するばい菌
@@ -8155,6 +8148,14 @@
     <rPh sb="3" eb="5">
       <t>レンゾク</t>
     </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>2連続攻撃 40000 20000（62F 81F）
+遠方範囲攻撃（1撃目1～401 2撃目401～651）
+古代の呪い（100％の確率で90F特殊能力封印）
+100％の確率で再生産時間50％遅延
+無効 （呪い）</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -8542,7 +8543,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -13583,7 +13584,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="45">
+    <row r="101" spans="1:17" ht="30">
       <c r="A101">
         <v>100</v>
       </c>
@@ -18296,7 +18297,7 @@
       </c>
       <c r="Q192" s="10"/>
     </row>
-    <row r="193" spans="1:17" ht="30">
+    <row r="193" spans="1:17" ht="15">
       <c r="A193">
         <v>192</v>
       </c>
@@ -19487,7 +19488,7 @@
       <c r="P215" s="10"/>
       <c r="Q215" s="10"/>
     </row>
-    <row r="216" spans="1:17" ht="45">
+    <row r="216" spans="1:17" ht="30">
       <c r="A216">
         <v>215</v>
       </c>
@@ -19538,7 +19539,7 @@
       </c>
       <c r="Q216" s="10"/>
     </row>
-    <row r="217" spans="1:17" ht="45">
+    <row r="217" spans="1:17" ht="30">
       <c r="A217">
         <v>216</v>
       </c>
@@ -19642,7 +19643,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="219" spans="1:17" ht="75">
+    <row r="219" spans="1:17" ht="60">
       <c r="A219">
         <v>218</v>
       </c>
@@ -20299,7 +20300,7 @@
       </c>
       <c r="Q231" s="10"/>
     </row>
-    <row r="232" spans="1:17" ht="30">
+    <row r="232" spans="1:17" ht="15">
       <c r="A232">
         <v>231</v>
       </c>
@@ -21610,7 +21611,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="258" spans="1:17" ht="30">
+    <row r="258" spans="1:17" ht="15">
       <c r="A258">
         <v>257</v>
       </c>
@@ -21975,7 +21976,7 @@
       </c>
       <c r="Q264" s="10"/>
     </row>
-    <row r="265" spans="1:17" ht="60">
+    <row r="265" spans="1:17" ht="45">
       <c r="A265">
         <v>264</v>
       </c>
@@ -22026,7 +22027,7 @@
       </c>
       <c r="Q265" s="10"/>
     </row>
-    <row r="266" spans="1:17" ht="60">
+    <row r="266" spans="1:17" ht="45">
       <c r="A266">
         <v>265</v>
       </c>
@@ -22599,7 +22600,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="277" spans="1:17" ht="75">
+    <row r="277" spans="1:17" ht="60">
       <c r="A277">
         <v>276</v>
       </c>
@@ -22652,7 +22653,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="278" spans="1:17" ht="75">
+    <row r="278" spans="1:17" ht="60">
       <c r="A278">
         <v>277</v>
       </c>
@@ -23174,7 +23175,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="288" spans="1:17" ht="30">
+    <row r="288" spans="1:17" ht="15">
       <c r="A288">
         <v>287</v>
       </c>
@@ -23474,7 +23475,7 @@
       <c r="P293" s="10"/>
       <c r="Q293" s="10"/>
     </row>
-    <row r="294" spans="1:17" ht="30">
+    <row r="294" spans="1:17" ht="15">
       <c r="A294">
         <v>293</v>
       </c>
@@ -23937,7 +23938,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="303" spans="1:17" ht="75">
+    <row r="303" spans="1:17" ht="60">
       <c r="A303">
         <v>302</v>
       </c>
@@ -24504,7 +24505,7 @@
       <c r="P313" s="10"/>
       <c r="Q313" s="10"/>
     </row>
-    <row r="314" spans="1:17" ht="30">
+    <row r="314" spans="1:17" ht="15">
       <c r="A314">
         <v>313</v>
       </c>
@@ -24607,7 +24608,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="316" spans="1:17" ht="90">
+    <row r="316" spans="1:17" ht="60">
       <c r="A316">
         <v>315</v>
       </c>
@@ -25025,7 +25026,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="324" spans="1:17" ht="75">
+    <row r="324" spans="1:17" ht="60">
       <c r="A324">
         <v>323</v>
       </c>
@@ -25396,7 +25397,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="331" spans="1:17" ht="75">
+    <row r="331" spans="1:17" ht="60">
       <c r="A331">
         <v>330</v>
       </c>
@@ -25555,7 +25556,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="334" spans="1:17" ht="60">
+    <row r="334" spans="1:17" ht="30">
       <c r="A334">
         <v>333</v>
       </c>
@@ -25655,7 +25656,7 @@
       <c r="P335" s="10"/>
       <c r="Q335" s="10"/>
     </row>
-    <row r="336" spans="1:17" ht="60">
+    <row r="336" spans="1:17" ht="30">
       <c r="A336">
         <v>335</v>
       </c>
@@ -25914,7 +25915,7 @@
       <c r="P340" s="10"/>
       <c r="Q340" s="10"/>
     </row>
-    <row r="341" spans="1:17" ht="30">
+    <row r="341" spans="1:17" ht="15">
       <c r="A341">
         <v>340</v>
       </c>
@@ -25965,7 +25966,7 @@
       </c>
       <c r="Q341" s="10"/>
     </row>
-    <row r="342" spans="1:17" ht="90">
+    <row r="342" spans="1:17" ht="60">
       <c r="A342">
         <v>341</v>
       </c>
@@ -26120,7 +26121,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="345" spans="1:17" ht="45">
+    <row r="345" spans="1:17" ht="30">
       <c r="A345">
         <v>344</v>
       </c>
@@ -26277,7 +26278,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="348" spans="1:17" ht="90">
+    <row r="348" spans="1:17" ht="75">
       <c r="A348">
         <v>347</v>
       </c>
@@ -26378,7 +26379,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="350" spans="1:17" ht="105">
+    <row r="350" spans="1:17" ht="75">
       <c r="A350">
         <v>349</v>
       </c>
@@ -26799,7 +26800,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="358" spans="1:17" ht="75">
+    <row r="358" spans="1:17" ht="60">
       <c r="A358">
         <v>357</v>
       </c>
@@ -26849,7 +26850,7 @@
         <v>1138</v>
       </c>
       <c r="Q358" s="10" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="359" spans="1:17" ht="60">
@@ -26902,10 +26903,10 @@
         <v>1141</v>
       </c>
       <c r="Q359" s="10" t="s">
-        <v>2180</v>
-      </c>
-    </row>
-    <row r="360" spans="1:17" ht="30">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="360" spans="1:17" ht="15">
       <c r="A360">
         <v>359</v>
       </c>
@@ -26956,7 +26957,7 @@
       </c>
       <c r="Q360" s="10"/>
     </row>
-    <row r="361" spans="1:17" ht="30">
+    <row r="361" spans="1:17" ht="15">
       <c r="A361">
         <v>360</v>
       </c>
@@ -27007,7 +27008,7 @@
       </c>
       <c r="Q361" s="10"/>
     </row>
-    <row r="362" spans="1:17" ht="45">
+    <row r="362" spans="1:17" ht="30">
       <c r="A362">
         <v>361</v>
       </c>
@@ -27134,10 +27135,10 @@
         <v>1155</v>
       </c>
       <c r="Q364" s="10" t="s">
-        <v>2181</v>
-      </c>
-    </row>
-    <row r="365" spans="1:17" ht="75">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="365" spans="1:17" ht="60">
       <c r="A365">
         <v>364</v>
       </c>
@@ -27187,10 +27188,10 @@
         <v>1158</v>
       </c>
       <c r="Q365" s="10" t="s">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="366" spans="1:17" ht="105">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="366" spans="1:17" ht="60">
       <c r="A366">
         <v>365</v>
       </c>
@@ -27240,10 +27241,10 @@
         <v>1161</v>
       </c>
       <c r="Q366" s="10" t="s">
-        <v>2183</v>
-      </c>
-    </row>
-    <row r="367" spans="1:17" ht="90">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="367" spans="1:17" ht="60">
       <c r="A367">
         <v>366</v>
       </c>
@@ -27293,7 +27294,7 @@
         <v>1164</v>
       </c>
       <c r="Q367" s="10" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="368" spans="1:17">
@@ -27547,7 +27548,7 @@
       </c>
       <c r="Q372" s="10"/>
     </row>
-    <row r="373" spans="1:17" ht="45">
+    <row r="373" spans="1:17" ht="30">
       <c r="A373">
         <v>372</v>
       </c>
@@ -27598,7 +27599,7 @@
       </c>
       <c r="Q373" s="10"/>
     </row>
-    <row r="374" spans="1:17" ht="45">
+    <row r="374" spans="1:17" ht="30">
       <c r="A374">
         <v>373</v>
       </c>
@@ -27649,7 +27650,7 @@
       </c>
       <c r="Q374" s="10"/>
     </row>
-    <row r="375" spans="1:17" ht="30">
+    <row r="375" spans="1:17" ht="15">
       <c r="A375">
         <v>374</v>
       </c>
@@ -27750,7 +27751,7 @@
         <v>988</v>
       </c>
       <c r="Q376" s="10" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="377" spans="1:17" ht="60">
@@ -27803,7 +27804,7 @@
         <v>1191</v>
       </c>
       <c r="Q377" s="10" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="378" spans="1:17" ht="60">
@@ -27856,7 +27857,7 @@
         <v>1194</v>
       </c>
       <c r="Q378" s="10" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="379" spans="1:17" ht="60">
@@ -27909,10 +27910,10 @@
         <v>1197</v>
       </c>
       <c r="Q379" s="10" t="s">
-        <v>2187</v>
-      </c>
-    </row>
-    <row r="380" spans="1:17" ht="90">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="380" spans="1:17" ht="60">
       <c r="A380">
         <v>379</v>
       </c>
@@ -27962,7 +27963,7 @@
         <v>1200</v>
       </c>
       <c r="Q380" s="10" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="381" spans="1:17" ht="60">
@@ -28015,10 +28016,10 @@
         <v>1203</v>
       </c>
       <c r="Q381" s="10" t="s">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="382" spans="1:17" ht="75">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="382" spans="1:17" ht="45">
       <c r="A382">
         <v>381</v>
       </c>
@@ -28076,7 +28077,7 @@
         <v>382</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="D383" t="s">
         <v>18</v>
@@ -28116,7 +28117,7 @@
       </c>
       <c r="Q383" s="10"/>
     </row>
-    <row r="384" spans="1:17" ht="30">
+    <row r="384" spans="1:17" ht="15">
       <c r="A384">
         <v>383</v>
       </c>
@@ -28124,7 +28125,7 @@
         <v>383</v>
       </c>
       <c r="C384" s="6" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="D384" t="s">
         <v>18</v>
@@ -28163,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="P384" s="10" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="Q384" s="10"/>
     </row>
@@ -28217,7 +28218,7 @@
         <v>1213</v>
       </c>
       <c r="Q385" s="10" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="386" spans="1:17" ht="60">
@@ -28270,7 +28271,7 @@
         <v>1217</v>
       </c>
       <c r="Q386" s="10" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="387" spans="1:17" ht="60">
@@ -28323,7 +28324,7 @@
         <v>1221</v>
       </c>
       <c r="Q387" s="10" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="388" spans="1:17">
@@ -28426,7 +28427,7 @@
       </c>
       <c r="Q389" s="10"/>
     </row>
-    <row r="390" spans="1:17" ht="120">
+    <row r="390" spans="1:17" ht="75">
       <c r="A390">
         <v>389</v>
       </c>
@@ -28476,7 +28477,7 @@
         <v>1230</v>
       </c>
       <c r="Q390" s="10" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="391" spans="1:17" ht="60">
@@ -28532,7 +28533,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="392" spans="1:17" ht="30">
+    <row r="392" spans="1:17" ht="15">
       <c r="A392">
         <v>391</v>
       </c>
@@ -28579,11 +28580,11 @@
         <v>0</v>
       </c>
       <c r="P392" s="10" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="Q392" s="10"/>
     </row>
-    <row r="393" spans="1:17" ht="30">
+    <row r="393" spans="1:17" ht="15">
       <c r="A393">
         <v>392</v>
       </c>
@@ -28630,7 +28631,7 @@
         <v>0</v>
       </c>
       <c r="P393" s="10" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="Q393" s="10"/>
     </row>
@@ -28684,10 +28685,10 @@
         <v>1242</v>
       </c>
       <c r="Q394" s="10" t="s">
-        <v>2198</v>
-      </c>
-    </row>
-    <row r="395" spans="1:17" ht="75">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="395" spans="1:17" ht="60">
       <c r="A395">
         <v>394</v>
       </c>
@@ -28737,7 +28738,7 @@
         <v>1246</v>
       </c>
       <c r="Q395" s="10" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="396" spans="1:17" ht="60">
@@ -28790,7 +28791,7 @@
         <v>1250</v>
       </c>
       <c r="Q396" s="10" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="397" spans="1:17" ht="60">
@@ -28843,7 +28844,7 @@
         <v>1254</v>
       </c>
       <c r="Q397" s="10" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="398" spans="1:17" ht="60">
@@ -28896,7 +28897,7 @@
         <v>1257</v>
       </c>
       <c r="Q398" s="10" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="399" spans="1:17" ht="60">
@@ -28949,10 +28950,10 @@
         <v>1260</v>
       </c>
       <c r="Q399" s="10" t="s">
-        <v>2203</v>
-      </c>
-    </row>
-    <row r="400" spans="1:17" ht="105">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="400" spans="1:17" ht="60">
       <c r="A400">
         <v>399</v>
       </c>
@@ -29002,10 +29003,10 @@
         <v>1263</v>
       </c>
       <c r="Q400" s="10" t="s">
-        <v>2204</v>
-      </c>
-    </row>
-    <row r="401" spans="1:17" ht="120">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="401" spans="1:17" ht="75">
       <c r="A401">
         <v>400</v>
       </c>
@@ -29055,10 +29056,10 @@
         <v>1267</v>
       </c>
       <c r="Q401" s="10" t="s">
-        <v>2205</v>
-      </c>
-    </row>
-    <row r="402" spans="1:17" ht="90">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="402" spans="1:17" ht="60">
       <c r="A402">
         <v>401</v>
       </c>
@@ -29108,10 +29109,10 @@
         <v>1270</v>
       </c>
       <c r="Q402" s="10" t="s">
-        <v>2206</v>
-      </c>
-    </row>
-    <row r="403" spans="1:17" ht="120">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="403" spans="1:17" ht="90">
       <c r="A403">
         <v>402</v>
       </c>
@@ -29161,7 +29162,7 @@
         <v>1273</v>
       </c>
       <c r="Q403" s="10" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="404" spans="1:17" ht="60">
@@ -29214,10 +29215,10 @@
         <v>1277</v>
       </c>
       <c r="Q404" s="10" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="405" spans="1:17" ht="105">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="405" spans="1:17" ht="75">
       <c r="A405">
         <v>404</v>
       </c>
@@ -29267,7 +29268,7 @@
         <v>2164</v>
       </c>
       <c r="Q405" s="10" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="406" spans="1:17" ht="60">
@@ -29320,10 +29321,10 @@
         <v>1283</v>
       </c>
       <c r="Q406" s="10" t="s">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="407" spans="1:17" ht="75">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="407" spans="1:17" ht="45">
       <c r="A407">
         <v>406</v>
       </c>
@@ -29424,7 +29425,7 @@
         <v>1289</v>
       </c>
       <c r="Q408" s="10" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="409" spans="1:17">
@@ -29525,7 +29526,7 @@
       <c r="P410" s="10"/>
       <c r="Q410" s="10"/>
     </row>
-    <row r="411" spans="1:17" ht="135">
+    <row r="411" spans="1:17" ht="75">
       <c r="A411">
         <v>410</v>
       </c>
@@ -29575,10 +29576,10 @@
         <v>2165</v>
       </c>
       <c r="Q411" s="10" t="s">
-        <v>2212</v>
-      </c>
-    </row>
-    <row r="412" spans="1:17" ht="90">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="412" spans="1:17" ht="60">
       <c r="A412">
         <v>411</v>
       </c>
@@ -29628,10 +29629,10 @@
         <v>2166</v>
       </c>
       <c r="Q412" s="10" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="413" spans="1:17" ht="105">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="413" spans="1:17" ht="75">
       <c r="A413">
         <v>412</v>
       </c>
@@ -29681,7 +29682,7 @@
         <v>2167</v>
       </c>
       <c r="Q413" s="10" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="414" spans="1:17" ht="60">
@@ -29734,7 +29735,7 @@
         <v>1303</v>
       </c>
       <c r="Q414" s="10" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="415" spans="1:17">
@@ -29786,7 +29787,7 @@
       <c r="P415" s="10"/>
       <c r="Q415" s="10"/>
     </row>
-    <row r="416" spans="1:17" ht="30">
+    <row r="416" spans="1:17" ht="15">
       <c r="A416">
         <v>415</v>
       </c>
@@ -29833,7 +29834,7 @@
         <v>0</v>
       </c>
       <c r="P416" s="10" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="Q416" s="10"/>
     </row>
@@ -29886,7 +29887,7 @@
       <c r="P417" s="10"/>
       <c r="Q417" s="10"/>
     </row>
-    <row r="418" spans="1:17" ht="90">
+    <row r="418" spans="1:17" ht="60">
       <c r="A418">
         <v>417</v>
       </c>
@@ -29936,7 +29937,7 @@
         <v>2168</v>
       </c>
       <c r="Q418" s="10" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="419" spans="1:17" ht="30">
@@ -30040,7 +30041,7 @@
         <v>1317</v>
       </c>
       <c r="Q420" s="10" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="421" spans="1:17" ht="60">
@@ -30093,7 +30094,7 @@
         <v>2169</v>
       </c>
       <c r="Q421" s="10" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="422" spans="1:17" ht="60">
@@ -30144,7 +30145,7 @@
       </c>
       <c r="P422" s="10"/>
       <c r="Q422" s="10" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="423" spans="1:17" ht="60">
@@ -30197,7 +30198,7 @@
         <v>1325</v>
       </c>
       <c r="Q423" s="10" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="424" spans="1:17" ht="60">
@@ -30250,7 +30251,7 @@
         <v>1328</v>
       </c>
       <c r="Q424" s="10" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="425" spans="1:17" ht="60">
@@ -30303,10 +30304,10 @@
         <v>1186</v>
       </c>
       <c r="Q425" s="10" t="s">
-        <v>2224</v>
-      </c>
-    </row>
-    <row r="426" spans="1:17" ht="105">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="426" spans="1:17" ht="60">
       <c r="A426">
         <v>425</v>
       </c>
@@ -30356,7 +30357,7 @@
         <v>2170</v>
       </c>
       <c r="Q426" s="10" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="427" spans="1:17" ht="60">
@@ -30409,7 +30410,7 @@
         <v>1335</v>
       </c>
       <c r="Q427" s="10" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="428" spans="1:17">
@@ -30420,7 +30421,7 @@
         <v>427</v>
       </c>
       <c r="C428" s="6" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="D428" t="s">
         <v>18</v>
@@ -30461,7 +30462,7 @@
       <c r="P428" s="10"/>
       <c r="Q428" s="10"/>
     </row>
-    <row r="429" spans="1:17" ht="30">
+    <row r="429" spans="1:17" ht="15">
       <c r="A429">
         <v>428</v>
       </c>
@@ -30508,7 +30509,7 @@
         <v>0</v>
       </c>
       <c r="P429" s="10" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="Q429" s="10"/>
     </row>
@@ -30562,10 +30563,10 @@
         <v>1341</v>
       </c>
       <c r="Q430" s="10" t="s">
-        <v>2228</v>
-      </c>
-    </row>
-    <row r="431" spans="1:17" ht="90">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="431" spans="1:17" ht="60">
       <c r="A431">
         <v>430</v>
       </c>
@@ -30615,7 +30616,7 @@
         <v>1344</v>
       </c>
       <c r="Q431" s="10" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="432" spans="1:17" ht="60">
@@ -30668,10 +30669,10 @@
         <v>1348</v>
       </c>
       <c r="Q432" s="10" t="s">
-        <v>2230</v>
-      </c>
-    </row>
-    <row r="433" spans="1:17" ht="105">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="433" spans="1:17" ht="60">
       <c r="A433">
         <v>432</v>
       </c>
@@ -30721,10 +30722,10 @@
         <v>2171</v>
       </c>
       <c r="Q433" s="10" t="s">
-        <v>2231</v>
-      </c>
-    </row>
-    <row r="434" spans="1:17" ht="75">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="434" spans="1:17" ht="60">
       <c r="A434">
         <v>433</v>
       </c>
@@ -30774,7 +30775,7 @@
         <v>2172</v>
       </c>
       <c r="Q434" s="10" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="435" spans="1:17" ht="60">
@@ -30827,7 +30828,7 @@
         <v>1356</v>
       </c>
       <c r="Q435" s="10" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="436" spans="1:17" ht="60">
@@ -30880,7 +30881,7 @@
         <v>1359</v>
       </c>
       <c r="Q436" s="10" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="437" spans="1:17" ht="60">
@@ -30933,10 +30934,10 @@
         <v>1362</v>
       </c>
       <c r="Q437" s="10" t="s">
-        <v>2265</v>
-      </c>
-    </row>
-    <row r="438" spans="1:17" ht="90">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="438" spans="1:17" ht="45">
       <c r="A438">
         <v>437</v>
       </c>
@@ -30986,7 +30987,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="439" spans="1:17" ht="60">
+    <row r="439" spans="1:17" ht="30">
       <c r="A439">
         <v>438</v>
       </c>
@@ -31036,7 +31037,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="440" spans="1:17" ht="105">
+    <row r="440" spans="1:17" ht="60">
       <c r="A440">
         <v>439</v>
       </c>
@@ -31087,7 +31088,7 @@
       </c>
       <c r="Q440" s="10"/>
     </row>
-    <row r="441" spans="1:17" ht="60">
+    <row r="441" spans="1:17" ht="30">
       <c r="A441">
         <v>440</v>
       </c>
@@ -31138,7 +31139,7 @@
       </c>
       <c r="Q441" s="10"/>
     </row>
-    <row r="442" spans="1:17" ht="60">
+    <row r="442" spans="1:17" ht="30">
       <c r="A442">
         <v>441</v>
       </c>
@@ -31189,7 +31190,7 @@
       </c>
       <c r="Q442" s="10"/>
     </row>
-    <row r="443" spans="1:17" ht="90">
+    <row r="443" spans="1:17" ht="45">
       <c r="A443">
         <v>442</v>
       </c>
@@ -31240,7 +31241,7 @@
       </c>
       <c r="Q443" s="10"/>
     </row>
-    <row r="444" spans="1:17" ht="60">
+    <row r="444" spans="1:17" ht="30">
       <c r="A444">
         <v>443</v>
       </c>
@@ -31291,7 +31292,7 @@
       </c>
       <c r="Q444" s="10"/>
     </row>
-    <row r="445" spans="1:17" ht="60">
+    <row r="445" spans="1:17" ht="30">
       <c r="A445">
         <v>444</v>
       </c>
@@ -31342,7 +31343,7 @@
       </c>
       <c r="Q445" s="10"/>
     </row>
-    <row r="446" spans="1:17" ht="90">
+    <row r="446" spans="1:17" ht="60">
       <c r="A446">
         <v>445</v>
       </c>
@@ -31393,7 +31394,7 @@
       </c>
       <c r="Q446" s="10"/>
     </row>
-    <row r="447" spans="1:17" ht="30">
+    <row r="447" spans="1:17" ht="15">
       <c r="A447">
         <v>446</v>
       </c>
@@ -31440,7 +31441,7 @@
         <v>0</v>
       </c>
       <c r="P447" s="10" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="Q447" s="10"/>
     </row>
@@ -31644,7 +31645,7 @@
       <c r="P451" s="10"/>
       <c r="Q451" s="10"/>
     </row>
-    <row r="452" spans="1:17" ht="90">
+    <row r="452" spans="1:17" ht="60">
       <c r="A452">
         <v>451</v>
       </c>
@@ -31794,10 +31795,10 @@
         <v>1410</v>
       </c>
       <c r="Q454" s="10" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="455" spans="1:17" ht="75">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="455" spans="1:17" ht="45">
       <c r="A455">
         <v>454</v>
       </c>
@@ -31844,7 +31845,7 @@
         <v>0</v>
       </c>
       <c r="P455" s="10" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="Q455" s="10"/>
     </row>
@@ -31898,7 +31899,7 @@
         <v>1416</v>
       </c>
       <c r="Q456" s="10" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="457" spans="1:17" ht="60">
@@ -31951,10 +31952,10 @@
         <v>1420</v>
       </c>
       <c r="Q457" s="10" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="458" spans="1:17" ht="30">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="458" spans="1:17" ht="15">
       <c r="A458">
         <v>457</v>
       </c>
@@ -32001,7 +32002,7 @@
         <v>0</v>
       </c>
       <c r="P458" s="10" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="459" spans="1:17" ht="60">
@@ -32054,10 +32055,10 @@
         <v>1426</v>
       </c>
       <c r="Q459" s="10" t="s">
-        <v>2238</v>
-      </c>
-    </row>
-    <row r="460" spans="1:17" ht="120">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="460" spans="1:17" ht="105">
       <c r="A460">
         <v>459</v>
       </c>
@@ -32107,7 +32108,7 @@
         <v>1429</v>
       </c>
       <c r="Q460" s="10" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="461" spans="1:17" ht="60">
@@ -32161,7 +32162,7 @@
       </c>
       <c r="Q461" s="10"/>
     </row>
-    <row r="462" spans="1:17" ht="45">
+    <row r="462" spans="1:17" ht="30">
       <c r="A462">
         <v>461</v>
       </c>
@@ -32262,10 +32263,10 @@
         <v>2174</v>
       </c>
       <c r="Q463" s="10" t="s">
-        <v>2240</v>
-      </c>
-    </row>
-    <row r="464" spans="1:17" ht="45">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="464" spans="1:17" ht="30">
       <c r="A464">
         <v>463</v>
       </c>
@@ -32312,11 +32313,11 @@
         <v>0</v>
       </c>
       <c r="P464" s="10" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="Q464" s="10"/>
     </row>
-    <row r="465" spans="1:17" ht="90">
+    <row r="465" spans="1:17" ht="60">
       <c r="A465">
         <v>464</v>
       </c>
@@ -32519,7 +32520,7 @@
         <v>1453</v>
       </c>
       <c r="Q468" s="10" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="469" spans="1:17" ht="60">
@@ -32572,10 +32573,10 @@
         <v>1457</v>
       </c>
       <c r="Q469" s="10" t="s">
-        <v>2243</v>
-      </c>
-    </row>
-    <row r="470" spans="1:17" ht="75">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="470" spans="1:17" ht="60">
       <c r="A470">
         <v>469</v>
       </c>
@@ -32625,7 +32626,7 @@
         <v>1461</v>
       </c>
       <c r="Q470" s="10" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="471" spans="1:17" ht="60">
@@ -32678,10 +32679,10 @@
         <v>1464</v>
       </c>
       <c r="Q471" s="10" t="s">
-        <v>2245</v>
-      </c>
-    </row>
-    <row r="472" spans="1:17" ht="60">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="472" spans="1:17" ht="45">
       <c r="A472">
         <v>471</v>
       </c>
@@ -32983,7 +32984,7 @@
       </c>
       <c r="Q477" s="10"/>
     </row>
-    <row r="478" spans="1:17" ht="75">
+    <row r="478" spans="1:17" ht="60">
       <c r="A478">
         <v>477</v>
       </c>
@@ -33131,7 +33132,7 @@
       </c>
       <c r="Q480" s="10"/>
     </row>
-    <row r="481" spans="1:17" ht="30">
+    <row r="481" spans="1:17" ht="15">
       <c r="A481">
         <v>480</v>
       </c>
@@ -33178,7 +33179,7 @@
         <v>0</v>
       </c>
       <c r="P481" s="10" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="Q481" s="10"/>
     </row>
@@ -33332,7 +33333,7 @@
         <v>1496</v>
       </c>
       <c r="Q484" s="10" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="485" spans="1:17" ht="60">
@@ -33385,7 +33386,7 @@
         <v>1499</v>
       </c>
       <c r="Q485" s="10" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="486" spans="1:17" ht="60">
@@ -33438,7 +33439,7 @@
         <v>1502</v>
       </c>
       <c r="Q486" s="10" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="487" spans="1:17" ht="30">
@@ -33492,7 +33493,7 @@
       </c>
       <c r="Q487" s="10"/>
     </row>
-    <row r="488" spans="1:17" ht="45">
+    <row r="488" spans="1:17" ht="30">
       <c r="A488">
         <v>487</v>
       </c>
@@ -33643,7 +33644,7 @@
       </c>
       <c r="Q490" s="10"/>
     </row>
-    <row r="491" spans="1:17" ht="30">
+    <row r="491" spans="1:17" ht="15">
       <c r="A491">
         <v>490</v>
       </c>
@@ -33690,7 +33691,7 @@
         <v>0</v>
       </c>
       <c r="P491" s="10" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="Q491" s="10"/>
     </row>
@@ -33795,7 +33796,7 @@
         <v>1519</v>
       </c>
       <c r="Q493" s="10" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="494" spans="1:17" ht="60">
@@ -33848,10 +33849,10 @@
         <v>1522</v>
       </c>
       <c r="Q494" s="10" t="s">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="495" spans="1:17" ht="75">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="495" spans="1:17" ht="60">
       <c r="A495">
         <v>494</v>
       </c>
@@ -33901,7 +33902,7 @@
         <v>1525</v>
       </c>
       <c r="Q495" s="10" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="496" spans="1:17" ht="60">
@@ -33954,7 +33955,7 @@
         <v>1528</v>
       </c>
       <c r="Q496" s="10" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="497" spans="1:17" ht="30">
@@ -34008,7 +34009,7 @@
       </c>
       <c r="Q497" s="10"/>
     </row>
-    <row r="498" spans="1:17" ht="45">
+    <row r="498" spans="1:17" ht="30">
       <c r="A498">
         <v>497</v>
       </c>
@@ -34059,7 +34060,7 @@
       </c>
       <c r="Q498" s="10"/>
     </row>
-    <row r="499" spans="1:17" ht="45">
+    <row r="499" spans="1:17" ht="30">
       <c r="A499">
         <v>498</v>
       </c>
@@ -34067,7 +34068,7 @@
         <v>498</v>
       </c>
       <c r="C499" s="6" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="D499" t="s">
         <v>18</v>
@@ -34106,11 +34107,11 @@
         <v>0</v>
       </c>
       <c r="P499" s="10" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="Q499" s="10"/>
     </row>
-    <row r="500" spans="1:17" ht="45">
+    <row r="500" spans="1:17" ht="30">
       <c r="A500">
         <v>499</v>
       </c>
@@ -34118,7 +34119,7 @@
         <v>499</v>
       </c>
       <c r="C500" s="6" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="D500" t="s">
         <v>18</v>
@@ -34157,7 +34158,7 @@
         <v>0</v>
       </c>
       <c r="P500" s="10" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="Q500" s="10"/>
     </row>
@@ -34212,7 +34213,7 @@
       </c>
       <c r="Q501" s="10"/>
     </row>
-    <row r="502" spans="1:17" ht="45">
+    <row r="502" spans="1:17" ht="30">
       <c r="A502">
         <v>501</v>
       </c>
@@ -34263,7 +34264,7 @@
       </c>
       <c r="Q502" s="10"/>
     </row>
-    <row r="503" spans="1:17" ht="105">
+    <row r="503" spans="1:17" ht="75">
       <c r="A503">
         <v>502</v>
       </c>
@@ -34313,7 +34314,7 @@
         <v>2176</v>
       </c>
       <c r="Q503" s="10" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="504" spans="1:17" ht="60">
@@ -34366,7 +34367,7 @@
         <v>1549</v>
       </c>
       <c r="Q504" s="10" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="505" spans="1:17" ht="60">
@@ -34419,7 +34420,7 @@
         <v>1552</v>
       </c>
       <c r="Q505" s="10" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="506" spans="1:17" ht="15">
@@ -34522,7 +34523,7 @@
       <c r="P507" s="10"/>
       <c r="Q507" s="10"/>
     </row>
-    <row r="508" spans="1:17" ht="60">
+    <row r="508" spans="1:17" ht="30">
       <c r="A508">
         <v>507</v>
       </c>
@@ -34824,7 +34825,7 @@
       </c>
       <c r="Q513" s="10"/>
     </row>
-    <row r="514" spans="1:17" ht="60">
+    <row r="514" spans="1:17" ht="45">
       <c r="A514">
         <v>513</v>
       </c>
@@ -35074,10 +35075,10 @@
         <v>1590</v>
       </c>
       <c r="Q518" s="10" t="s">
-        <v>2260</v>
-      </c>
-    </row>
-    <row r="519" spans="1:17" ht="120">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="519" spans="1:17" ht="90">
       <c r="A519">
         <v>518</v>
       </c>
@@ -35127,7 +35128,7 @@
         <v>2177</v>
       </c>
       <c r="Q519" s="10" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="520" spans="1:17" ht="15">
@@ -35232,7 +35233,7 @@
       </c>
       <c r="Q521" s="10"/>
     </row>
-    <row r="522" spans="1:17" ht="105">
+    <row r="522" spans="1:17" ht="75">
       <c r="A522">
         <v>521</v>
       </c>
@@ -35279,10 +35280,10 @@
         <v>27650</v>
       </c>
       <c r="P522" s="10" t="s">
-        <v>2178</v>
+        <v>2274</v>
       </c>
       <c r="Q522" s="10" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="523" spans="1:17" ht="30">
@@ -35344,7 +35345,7 @@
         <v>523</v>
       </c>
       <c r="C524" s="6" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="D524" t="s">
         <v>18</v>
@@ -35466,7 +35467,7 @@
       </c>
       <c r="Q526" s="10"/>
     </row>
-    <row r="527" spans="1:17" ht="60">
+    <row r="527" spans="1:17" ht="45">
       <c r="A527">
         <v>526</v>
       </c>
@@ -35616,7 +35617,7 @@
         <v>1622</v>
       </c>
       <c r="Q529" s="10" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="530" spans="1:33" ht="60">
@@ -35627,13 +35628,13 @@
         <v>529</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="E530" t="s">
         <v>1624</v>
       </c>
       <c r="F530" s="6" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="G530">
         <v>3200</v>
@@ -35663,10 +35664,10 @@
         <v>4500</v>
       </c>
       <c r="P530" s="10" t="s">
+        <v>2268</v>
+      </c>
+      <c r="Q530" s="10" t="s">
         <v>2269</v>
-      </c>
-      <c r="Q530" s="10" t="s">
-        <v>2270</v>
       </c>
       <c r="R530">
         <v>529</v>
@@ -35681,7 +35682,7 @@
         <v>18</v>
       </c>
       <c r="V530" s="6" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="W530" t="s">
         <v>20</v>
@@ -35723,7 +35724,7 @@
         <v>530</v>
       </c>
       <c r="C531" s="6" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="D531" t="s">
         <v>1626</v>
@@ -35762,10 +35763,10 @@
         <v>18900</v>
       </c>
       <c r="P531" s="10" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="Q531" s="10" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
     </row>
   </sheetData>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54488B67-7277-DC44-97DE-80D4654BEFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C65118-9B32-CB48-B201-922E1FF6094C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7559" uniqueCount="2275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7559" uniqueCount="2277">
   <si>
     <t>id</t>
   </si>
@@ -8115,12 +8115,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>25%で小波動Lv2   
-10%でクリティカル
-城破壊が得意(×4倍ダメージ)</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>軽量化により浮くことが可能に
 なったメタルサイクロンの改良版。
 本当は制作費のコストカットによって仕方なく
@@ -8142,20 +8136,43 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>範囲3連続攻撃 196000 63000 51000(7F 17F 27F)
-40%でLv2波動(波動の攻撃力は３撃目に対応)
-体力残り25%で攻撃1.5倍</t>
-    <rPh sb="3" eb="5">
-      <t>レンゾク</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>2連続攻撃 40000 20000（62F 81F）
 遠方範囲攻撃（1撃目1～401 2撃目401～651）
 古代の呪い（100％の確率で90F特殊能力封印）
 100％の確率で再生産時間50％遅延
 無効 （呪い）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>残り体力50％以下で攻撃力50％上昇</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>対 お城 与ダメx4</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>範囲3連続攻撃 196000 63000 51000(7F 17F 27F)
+40%の確率でLv2波動(波動の攻撃力は３撃目に対応)
+体力残り25%以下で攻撃力50％上昇</t>
+    <rPh sb="3" eb="5">
+      <t>レンゾク</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>25%の確率でLv2小波動   
+10%の確率でクリティカル
+対 お城 与ダメx4</t>
+    <rPh sb="10" eb="11">
+      <t>ショウハドウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハドウヤッテ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -10042,7 +10059,7 @@
         <v>3555</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>113</v>
+        <v>2274</v>
       </c>
       <c r="Q30" s="10" t="s">
         <v>114</v>
@@ -18191,7 +18208,7 @@
         <v>7900</v>
       </c>
       <c r="P190" s="10" t="s">
-        <v>585</v>
+        <v>2273</v>
       </c>
       <c r="Q190" s="10" t="s">
         <v>586</v>
@@ -35280,7 +35297,7 @@
         <v>27650</v>
       </c>
       <c r="P522" s="10" t="s">
-        <v>2274</v>
+        <v>2272</v>
       </c>
       <c r="Q522" s="10" t="s">
         <v>2261</v>
@@ -35628,13 +35645,13 @@
         <v>529</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="E530" t="s">
         <v>1624</v>
       </c>
       <c r="F530" s="6" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="G530">
         <v>3200</v>
@@ -35664,10 +35681,10 @@
         <v>4500</v>
       </c>
       <c r="P530" s="10" t="s">
+        <v>2276</v>
+      </c>
+      <c r="Q530" s="10" t="s">
         <v>2268</v>
-      </c>
-      <c r="Q530" s="10" t="s">
-        <v>2269</v>
       </c>
       <c r="R530">
         <v>529</v>
@@ -35763,10 +35780,10 @@
         <v>18900</v>
       </c>
       <c r="P531" s="10" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="Q531" s="10" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
     </row>
   </sheetData>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C65118-9B32-CB48-B201-922E1FF6094C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CB7892-B4B9-C64E-A885-3F0DFEE70327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7559" uniqueCount="2277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7556" uniqueCount="2278">
   <si>
     <t>id</t>
   </si>
@@ -8173,6 +8173,10 @@
     <rPh sb="11" eb="13">
       <t>ハドウヤッテ</t>
     </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>3％の確率でクリティカル</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -11762,7 +11766,7 @@
       </c>
       <c r="Q63" s="10"/>
     </row>
-    <row r="64" spans="1:18" ht="15">
+    <row r="64" spans="1:18">
       <c r="A64">
         <v>63</v>
       </c>
@@ -11807,9 +11811,6 @@
       </c>
       <c r="O64" s="8">
         <v>9361</v>
-      </c>
-      <c r="P64" s="10" t="s">
-        <v>222</v>
       </c>
       <c r="Q64" s="10"/>
       <c r="R64" s="12"/>
@@ -11861,7 +11862,7 @@
         <v>7900</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Q65" s="10"/>
     </row>
@@ -11965,7 +11966,7 @@
       <c r="P67" s="10"/>
       <c r="Q67" s="10"/>
     </row>
-    <row r="68" spans="1:17" ht="15">
+    <row r="68" spans="1:17">
       <c r="A68">
         <v>67</v>
       </c>
@@ -12011,12 +12012,10 @@
       <c r="O68" s="8">
         <v>7896</v>
       </c>
-      <c r="P68" s="10" t="s">
-        <v>232</v>
-      </c>
+      <c r="P68" s="10"/>
       <c r="Q68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="45">
+    <row r="69" spans="1:17">
       <c r="A69">
         <v>68</v>
       </c>
@@ -12062,12 +12061,12 @@
       <c r="O69" s="8">
         <v>2449</v>
       </c>
-      <c r="P69" s="10" t="s">
-        <v>235</v>
+      <c r="P69" s="6" t="s">
+        <v>2277</v>
       </c>
       <c r="Q69" s="10"/>
     </row>
-    <row r="70" spans="1:17" ht="15">
+    <row r="70" spans="1:17">
       <c r="A70">
         <v>69</v>
       </c>
@@ -12113,12 +12112,9 @@
       <c r="O70" s="8">
         <v>5332</v>
       </c>
-      <c r="P70" s="10" t="s">
-        <v>238</v>
-      </c>
       <c r="Q70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15">
+    <row r="71" spans="1:17" ht="45">
       <c r="A71">
         <v>70</v>
       </c>
@@ -12165,7 +12161,7 @@
         <v>8393</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>139</v>
+        <v>235</v>
       </c>
       <c r="Q71" s="10"/>
     </row>
@@ -12317,7 +12313,6 @@
       <c r="O74" s="8">
         <v>39496</v>
       </c>
-      <c r="P74" s="10"/>
       <c r="Q74" s="10"/>
     </row>
     <row r="75" spans="1:17" ht="15">
@@ -12515,7 +12510,6 @@
       <c r="O78" s="8">
         <v>18130</v>
       </c>
-      <c r="P78" s="10"/>
       <c r="Q78" s="10"/>
     </row>
     <row r="79" spans="1:17">

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CB7892-B4B9-C64E-A885-3F0DFEE70327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B3BC90-6545-5640-8FDD-1E814DAEA1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17293,7 +17293,7 @@
         <v>529</v>
       </c>
       <c r="F173" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
       <c r="G173">
         <v>13500</v>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B3BC90-6545-5640-8FDD-1E814DAEA1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E10D19-E5CE-AF4C-AFA6-C127A2DFDA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7556" uniqueCount="2278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7611" uniqueCount="2305">
   <si>
     <t>id</t>
   </si>
@@ -8178,6 +8178,87 @@
   <si>
     <t>3％の確率でクリティカル</t>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>enemy_images/enemy_531.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_532.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_533.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_534.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_535.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_536.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_537.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_538.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_539.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_540.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_541.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_542.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_543.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_544.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_545.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_546.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_547.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_548.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_549.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_550.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_551.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_552.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_553.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_554.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_555.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_556.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_557.jpg</t>
   </si>
 </sst>
 </file>
@@ -8526,7 +8607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG531"/>
+  <dimension ref="A1:AG558"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -35641,6 +35722,9 @@
       <c r="C530" s="6" t="s">
         <v>2269</v>
       </c>
+      <c r="D530" t="s">
+        <v>1626</v>
+      </c>
       <c r="E530" t="s">
         <v>1624</v>
       </c>
@@ -35780,10 +35864,388 @@
         <v>2271</v>
       </c>
     </row>
+    <row r="532" spans="1:33">
+      <c r="A532">
+        <v>531</v>
+      </c>
+      <c r="B532">
+        <v>531</v>
+      </c>
+      <c r="D532" t="s">
+        <v>18</v>
+      </c>
+      <c r="E532" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="533" spans="1:33">
+      <c r="A533">
+        <v>532</v>
+      </c>
+      <c r="B533">
+        <v>532</v>
+      </c>
+      <c r="D533" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E533" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="534" spans="1:33">
+      <c r="A534">
+        <v>533</v>
+      </c>
+      <c r="B534">
+        <v>533</v>
+      </c>
+      <c r="D534" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E534" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="535" spans="1:33">
+      <c r="A535">
+        <v>534</v>
+      </c>
+      <c r="B535">
+        <v>534</v>
+      </c>
+      <c r="D535" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E535" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="536" spans="1:33">
+      <c r="A536">
+        <v>535</v>
+      </c>
+      <c r="B536">
+        <v>535</v>
+      </c>
+      <c r="D536" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E536" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="537" spans="1:33">
+      <c r="A537">
+        <v>536</v>
+      </c>
+      <c r="B537">
+        <v>536</v>
+      </c>
+      <c r="D537" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E537" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="538" spans="1:33">
+      <c r="A538">
+        <v>537</v>
+      </c>
+      <c r="B538">
+        <v>537</v>
+      </c>
+      <c r="D538" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E538" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="539" spans="1:33">
+      <c r="A539">
+        <v>538</v>
+      </c>
+      <c r="B539">
+        <v>538</v>
+      </c>
+      <c r="D539" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E539" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="540" spans="1:33">
+      <c r="A540">
+        <v>539</v>
+      </c>
+      <c r="B540">
+        <v>539</v>
+      </c>
+      <c r="D540" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E540" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="541" spans="1:33">
+      <c r="A541">
+        <v>540</v>
+      </c>
+      <c r="B541">
+        <v>540</v>
+      </c>
+      <c r="D541" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E541" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="542" spans="1:33">
+      <c r="A542">
+        <v>541</v>
+      </c>
+      <c r="B542">
+        <v>541</v>
+      </c>
+      <c r="D542" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E542" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="543" spans="1:33">
+      <c r="A543">
+        <v>542</v>
+      </c>
+      <c r="B543">
+        <v>542</v>
+      </c>
+      <c r="D543" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E543" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="544" spans="1:33">
+      <c r="A544">
+        <v>543</v>
+      </c>
+      <c r="B544">
+        <v>543</v>
+      </c>
+      <c r="D544" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E544" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5">
+      <c r="A545">
+        <v>544</v>
+      </c>
+      <c r="B545">
+        <v>544</v>
+      </c>
+      <c r="D545" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E545" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5">
+      <c r="A546">
+        <v>545</v>
+      </c>
+      <c r="B546">
+        <v>545</v>
+      </c>
+      <c r="D546" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E546" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5">
+      <c r="A547">
+        <v>546</v>
+      </c>
+      <c r="B547">
+        <v>546</v>
+      </c>
+      <c r="D547" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E547" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5">
+      <c r="A548">
+        <v>547</v>
+      </c>
+      <c r="B548">
+        <v>547</v>
+      </c>
+      <c r="D548" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E548" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5">
+      <c r="A549">
+        <v>548</v>
+      </c>
+      <c r="B549">
+        <v>548</v>
+      </c>
+      <c r="D549" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E549" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5">
+      <c r="A550">
+        <v>549</v>
+      </c>
+      <c r="B550">
+        <v>549</v>
+      </c>
+      <c r="D550" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E550" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5">
+      <c r="A551">
+        <v>550</v>
+      </c>
+      <c r="B551">
+        <v>550</v>
+      </c>
+      <c r="D551" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E551" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5">
+      <c r="A552">
+        <v>551</v>
+      </c>
+      <c r="B552">
+        <v>551</v>
+      </c>
+      <c r="D552" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E552" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5">
+      <c r="A553">
+        <v>552</v>
+      </c>
+      <c r="B553">
+        <v>552</v>
+      </c>
+      <c r="D553" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E553" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5">
+      <c r="A554">
+        <v>553</v>
+      </c>
+      <c r="B554">
+        <v>553</v>
+      </c>
+      <c r="D554" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E554" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5">
+      <c r="A555">
+        <v>554</v>
+      </c>
+      <c r="B555">
+        <v>554</v>
+      </c>
+      <c r="D555" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E555" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5">
+      <c r="A556">
+        <v>555</v>
+      </c>
+      <c r="B556">
+        <v>555</v>
+      </c>
+      <c r="D556" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E556" t="s">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5">
+      <c r="A557">
+        <v>556</v>
+      </c>
+      <c r="B557">
+        <v>556</v>
+      </c>
+      <c r="D557" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E557" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5">
+      <c r="A558">
+        <v>557</v>
+      </c>
+      <c r="B558">
+        <v>557</v>
+      </c>
+      <c r="D558" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E558" t="s">
+        <v>2304</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4"/>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="D2:D1000 U530" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="U530 D2:D1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"official,custom"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="F2:F1000 W530" xr:uid="{00000000-0002-0000-0000-000001000000}">

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E10D19-E5CE-AF4C-AFA6-C127A2DFDA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8824AB56-5125-9740-A0ED-C35D510AE8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7611" uniqueCount="2305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7652" uniqueCount="2344">
   <si>
     <t>id</t>
   </si>
@@ -8259,6 +8259,137 @@
   </si>
   <si>
     <t>enemy_images/enemy_557.jpg</t>
+  </si>
+  <si>
+    <t>マリックス</t>
+  </si>
+  <si>
+    <t>大悪魔デビネル</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>赤井ブン君</t>
+  </si>
+  <si>
+    <t>ダーク・エナジー</t>
+  </si>
+  <si>
+    <t>幹事</t>
+  </si>
+  <si>
+    <t>古代兵器クオリネス</t>
+  </si>
+  <si>
+    <t>デット・ブル</t>
+  </si>
+  <si>
+    <t>デカヲル様</t>
+  </si>
+  <si>
+    <t>金仮面マネラー</t>
+  </si>
+  <si>
+    <t>譜の賢者ヴェトーヴン</t>
+  </si>
+  <si>
+    <t>クラーケ博士</t>
+  </si>
+  <si>
+    <t>アポロール</t>
+  </si>
+  <si>
+    <t>ゲコー&amp;ケロークス</t>
+  </si>
+  <si>
+    <t>アイ・ディア</t>
+  </si>
+  <si>
+    <t>ペリカニウム</t>
+  </si>
+  <si>
+    <t>どん兵衛</t>
+  </si>
+  <si>
+    <t>怪鳥七面相</t>
+  </si>
+  <si>
+    <t>サイボーグ‐弐式</t>
+  </si>
+  <si>
+    <t>プロミネリス</t>
+  </si>
+  <si>
+    <t>超海獣マナバール</t>
+  </si>
+  <si>
+    <t>トリミアンヌ</t>
+  </si>
+  <si>
+    <t>イカリケモルル</t>
+  </si>
+  <si>
+    <t>イノシェント</t>
+  </si>
+  <si>
+    <t>ダークヴィルニール</t>
+  </si>
+  <si>
+    <t>星野我王</t>
+  </si>
+  <si>
+    <t>超飛獣トリトブレス</t>
+  </si>
+  <si>
+    <t>こねこライブ城</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>starAlien,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>devil,superLife,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>red,floating,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>black,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>zombie,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>floating,ancient,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>superLife,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>none,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>floating,zombie,sage,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>angel,sage,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>black,sage,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>starAlien,none,custom</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -35871,11 +36002,17 @@
       <c r="B532">
         <v>531</v>
       </c>
+      <c r="C532" s="6" t="s">
+        <v>2331</v>
+      </c>
       <c r="D532" t="s">
         <v>18</v>
       </c>
       <c r="E532" t="s">
         <v>2278</v>
+      </c>
+      <c r="F532" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="533" spans="1:33">
@@ -35885,11 +36022,17 @@
       <c r="B533">
         <v>532</v>
       </c>
+      <c r="C533" s="6" t="s">
+        <v>2305</v>
+      </c>
       <c r="D533" t="s">
         <v>1626</v>
       </c>
       <c r="E533" t="s">
         <v>2279</v>
+      </c>
+      <c r="F533" s="6" t="s">
+        <v>2332</v>
       </c>
     </row>
     <row r="534" spans="1:33">
@@ -35899,11 +36042,17 @@
       <c r="B534">
         <v>533</v>
       </c>
+      <c r="C534" s="6" t="s">
+        <v>2306</v>
+      </c>
       <c r="D534" t="s">
         <v>1626</v>
       </c>
       <c r="E534" t="s">
         <v>2280</v>
+      </c>
+      <c r="F534" s="6" t="s">
+        <v>2333</v>
       </c>
     </row>
     <row r="535" spans="1:33">
@@ -35913,11 +36062,17 @@
       <c r="B535">
         <v>534</v>
       </c>
+      <c r="C535" s="6" t="s">
+        <v>2307</v>
+      </c>
       <c r="D535" t="s">
         <v>1626</v>
       </c>
       <c r="E535" t="s">
         <v>2281</v>
+      </c>
+      <c r="F535" s="6" t="s">
+        <v>2334</v>
       </c>
     </row>
     <row r="536" spans="1:33">
@@ -35927,11 +36082,17 @@
       <c r="B536">
         <v>535</v>
       </c>
+      <c r="C536" s="6" t="s">
+        <v>2308</v>
+      </c>
       <c r="D536" t="s">
         <v>1626</v>
       </c>
       <c r="E536" t="s">
         <v>2282</v>
+      </c>
+      <c r="F536" s="6" t="s">
+        <v>2335</v>
       </c>
     </row>
     <row r="537" spans="1:33">
@@ -35941,11 +36102,17 @@
       <c r="B537">
         <v>536</v>
       </c>
+      <c r="C537" s="6" t="s">
+        <v>2309</v>
+      </c>
       <c r="D537" t="s">
         <v>1626</v>
       </c>
       <c r="E537" t="s">
         <v>2283</v>
+      </c>
+      <c r="F537" s="6" t="s">
+        <v>2336</v>
       </c>
     </row>
     <row r="538" spans="1:33">
@@ -35955,11 +36122,17 @@
       <c r="B538">
         <v>537</v>
       </c>
+      <c r="C538" s="6" t="s">
+        <v>2310</v>
+      </c>
       <c r="D538" t="s">
         <v>1626</v>
       </c>
       <c r="E538" t="s">
         <v>2284</v>
+      </c>
+      <c r="F538" s="6" t="s">
+        <v>2337</v>
       </c>
     </row>
     <row r="539" spans="1:33">
@@ -35969,11 +36142,17 @@
       <c r="B539">
         <v>538</v>
       </c>
+      <c r="C539" s="6" t="s">
+        <v>2311</v>
+      </c>
       <c r="D539" t="s">
         <v>1626</v>
       </c>
       <c r="E539" t="s">
         <v>2285</v>
+      </c>
+      <c r="F539" s="6" t="s">
+        <v>2336</v>
       </c>
     </row>
     <row r="540" spans="1:33">
@@ -35983,11 +36162,17 @@
       <c r="B540">
         <v>539</v>
       </c>
+      <c r="C540" s="6" t="s">
+        <v>2312</v>
+      </c>
       <c r="D540" t="s">
         <v>1626</v>
       </c>
       <c r="E540" t="s">
         <v>2286</v>
+      </c>
+      <c r="F540" s="6" t="s">
+        <v>2338</v>
       </c>
     </row>
     <row r="541" spans="1:33">
@@ -35997,11 +36182,17 @@
       <c r="B541">
         <v>540</v>
       </c>
+      <c r="C541" s="6" t="s">
+        <v>2313</v>
+      </c>
       <c r="D541" t="s">
         <v>1626</v>
       </c>
       <c r="E541" t="s">
         <v>2287</v>
+      </c>
+      <c r="F541" s="6" t="s">
+        <v>2339</v>
       </c>
     </row>
     <row r="542" spans="1:33">
@@ -36011,11 +36202,17 @@
       <c r="B542">
         <v>541</v>
       </c>
+      <c r="C542" s="6" t="s">
+        <v>2315</v>
+      </c>
       <c r="D542" t="s">
         <v>1626</v>
       </c>
       <c r="E542" t="s">
         <v>2288</v>
+      </c>
+      <c r="F542" s="6" t="s">
+        <v>2340</v>
       </c>
     </row>
     <row r="543" spans="1:33">
@@ -36025,11 +36222,17 @@
       <c r="B543">
         <v>542</v>
       </c>
+      <c r="C543" s="6" t="s">
+        <v>2314</v>
+      </c>
       <c r="D543" t="s">
         <v>1626</v>
       </c>
       <c r="E543" t="s">
         <v>2289</v>
+      </c>
+      <c r="F543" s="6" t="s">
+        <v>2341</v>
       </c>
     </row>
     <row r="544" spans="1:33">
@@ -36039,34 +36242,49 @@
       <c r="B544">
         <v>543</v>
       </c>
+      <c r="C544" s="6" t="s">
+        <v>2316</v>
+      </c>
       <c r="D544" t="s">
         <v>1626</v>
       </c>
       <c r="E544" t="s">
         <v>2290</v>
       </c>
-    </row>
-    <row r="545" spans="1:5">
+      <c r="F544" s="6" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6">
       <c r="A545">
         <v>544</v>
       </c>
       <c r="B545">
         <v>544</v>
       </c>
+      <c r="C545" s="6" t="s">
+        <v>2317</v>
+      </c>
       <c r="D545" t="s">
         <v>1626</v>
       </c>
       <c r="E545" t="s">
         <v>2291</v>
       </c>
-    </row>
-    <row r="546" spans="1:5">
+      <c r="F545" s="6" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6">
       <c r="A546">
         <v>545</v>
       </c>
       <c r="B546">
         <v>545</v>
       </c>
+      <c r="C546" s="6" t="s">
+        <v>2318</v>
+      </c>
       <c r="D546" t="s">
         <v>1626</v>
       </c>
@@ -36074,13 +36292,16 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="547" spans="1:5">
+    <row r="547" spans="1:6">
       <c r="A547">
         <v>546</v>
       </c>
       <c r="B547">
         <v>546</v>
       </c>
+      <c r="C547" s="6" t="s">
+        <v>2319</v>
+      </c>
       <c r="D547" t="s">
         <v>1626</v>
       </c>
@@ -36088,13 +36309,16 @@
         <v>2293</v>
       </c>
     </row>
-    <row r="548" spans="1:5">
+    <row r="548" spans="1:6">
       <c r="A548">
         <v>547</v>
       </c>
       <c r="B548">
         <v>547</v>
       </c>
+      <c r="C548" s="6" t="s">
+        <v>2320</v>
+      </c>
       <c r="D548" t="s">
         <v>1626</v>
       </c>
@@ -36102,13 +36326,16 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="549" spans="1:5">
+    <row r="549" spans="1:6">
       <c r="A549">
         <v>548</v>
       </c>
       <c r="B549">
         <v>548</v>
       </c>
+      <c r="C549" s="6" t="s">
+        <v>2321</v>
+      </c>
       <c r="D549" t="s">
         <v>1626</v>
       </c>
@@ -36116,13 +36343,16 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="550" spans="1:5">
+    <row r="550" spans="1:6">
       <c r="A550">
         <v>549</v>
       </c>
       <c r="B550">
         <v>549</v>
       </c>
+      <c r="C550" s="6" t="s">
+        <v>2322</v>
+      </c>
       <c r="D550" t="s">
         <v>1626</v>
       </c>
@@ -36130,13 +36360,16 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="551" spans="1:5">
+    <row r="551" spans="1:6">
       <c r="A551">
         <v>550</v>
       </c>
       <c r="B551">
         <v>550</v>
       </c>
+      <c r="C551" s="6" t="s">
+        <v>2323</v>
+      </c>
       <c r="D551" t="s">
         <v>1626</v>
       </c>
@@ -36144,13 +36377,16 @@
         <v>2297</v>
       </c>
     </row>
-    <row r="552" spans="1:5">
+    <row r="552" spans="1:6">
       <c r="A552">
         <v>551</v>
       </c>
       <c r="B552">
         <v>551</v>
       </c>
+      <c r="C552" s="6" t="s">
+        <v>2324</v>
+      </c>
       <c r="D552" t="s">
         <v>1626</v>
       </c>
@@ -36158,13 +36394,16 @@
         <v>2298</v>
       </c>
     </row>
-    <row r="553" spans="1:5">
+    <row r="553" spans="1:6">
       <c r="A553">
         <v>552</v>
       </c>
       <c r="B553">
         <v>552</v>
       </c>
+      <c r="C553" s="6" t="s">
+        <v>2325</v>
+      </c>
       <c r="D553" t="s">
         <v>1626</v>
       </c>
@@ -36172,13 +36411,16 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="554" spans="1:5">
+    <row r="554" spans="1:6">
       <c r="A554">
         <v>553</v>
       </c>
       <c r="B554">
         <v>553</v>
       </c>
+      <c r="C554" s="6" t="s">
+        <v>2326</v>
+      </c>
       <c r="D554" t="s">
         <v>1626</v>
       </c>
@@ -36186,13 +36428,16 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="555" spans="1:5">
+    <row r="555" spans="1:6">
       <c r="A555">
         <v>554</v>
       </c>
       <c r="B555">
         <v>554</v>
       </c>
+      <c r="C555" s="6" t="s">
+        <v>2327</v>
+      </c>
       <c r="D555" t="s">
         <v>1626</v>
       </c>
@@ -36200,13 +36445,16 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="556" spans="1:5">
+    <row r="556" spans="1:6">
       <c r="A556">
         <v>555</v>
       </c>
       <c r="B556">
         <v>555</v>
       </c>
+      <c r="C556" s="6" t="s">
+        <v>2328</v>
+      </c>
       <c r="D556" t="s">
         <v>1626</v>
       </c>
@@ -36214,13 +36462,16 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="557" spans="1:5">
+    <row r="557" spans="1:6">
       <c r="A557">
         <v>556</v>
       </c>
       <c r="B557">
         <v>556</v>
       </c>
+      <c r="C557" s="6" t="s">
+        <v>2329</v>
+      </c>
       <c r="D557" t="s">
         <v>1626</v>
       </c>
@@ -36228,12 +36479,15 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="558" spans="1:5">
+    <row r="558" spans="1:6">
       <c r="A558">
         <v>557</v>
       </c>
       <c r="B558">
         <v>557</v>
+      </c>
+      <c r="C558" s="6" t="s">
+        <v>2330</v>
       </c>
       <c r="D558" t="s">
         <v>1626</v>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8824AB56-5125-9740-A0ED-C35D510AE8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDB1E7B-8883-FF4A-9712-1BF9D769C179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7652" uniqueCount="2344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7663" uniqueCount="2354">
   <si>
     <t>id</t>
   </si>
@@ -8108,10 +8108,6 @@
   </si>
   <si>
     <t>聡慧の覇者ゼロムート</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>enemy_images/enemy_531.jpg</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -8380,6 +8376,10 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
+    <t>angel,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
     <t>angel,sage,custom</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -8389,6 +8389,49 @@
   </si>
   <si>
     <t>starAlien,none,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>starAlien,sage,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>metal,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>devil,sage,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>floating,metal,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>red,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>starAlien,beast,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ancient,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>angel,starAlian,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>floating,beast,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>未来組織の採用担当をしているキツネ。
+採用面接では度重なる激務により基準が
+適当であり、顔が恐ろしいかどうかで
+採用、不採用を決めている。</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -10275,7 +10318,7 @@
         <v>3555</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="Q30" s="10" t="s">
         <v>114</v>
@@ -12274,7 +12317,7 @@
         <v>2449</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="Q69" s="10"/>
     </row>
@@ -18414,7 +18457,7 @@
         <v>7900</v>
       </c>
       <c r="P190" s="10" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="Q190" s="10" t="s">
         <v>586</v>
@@ -35503,7 +35546,7 @@
         <v>27650</v>
       </c>
       <c r="P522" s="10" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="Q522" s="10" t="s">
         <v>2261</v>
@@ -35851,7 +35894,7 @@
         <v>529</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="D530" t="s">
         <v>1626</v>
@@ -35860,7 +35903,7 @@
         <v>1624</v>
       </c>
       <c r="F530" s="6" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="G530">
         <v>3200</v>
@@ -35890,56 +35933,14 @@
         <v>4500</v>
       </c>
       <c r="P530" s="10" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="Q530" s="10" t="s">
-        <v>2268</v>
-      </c>
-      <c r="R530">
-        <v>529</v>
-      </c>
-      <c r="S530">
-        <v>529</v>
-      </c>
-      <c r="T530" s="6" t="s">
-        <v>1623</v>
-      </c>
-      <c r="U530" t="s">
-        <v>18</v>
-      </c>
-      <c r="V530" s="6" t="s">
         <v>2267</v>
       </c>
-      <c r="W530" t="s">
-        <v>20</v>
-      </c>
-      <c r="X530">
-        <v>10</v>
-      </c>
-      <c r="Y530">
-        <v>1</v>
-      </c>
-      <c r="Z530">
-        <v>1</v>
-      </c>
-      <c r="AA530">
-        <v>1000</v>
-      </c>
-      <c r="AB530">
-        <v>1</v>
-      </c>
-      <c r="AC530">
-        <v>0</v>
-      </c>
-      <c r="AD530">
-        <v>10</v>
-      </c>
-      <c r="AE530" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF530" s="8">
-        <v>0</v>
-      </c>
+      <c r="T530" s="6"/>
+      <c r="U530" s="6"/>
+      <c r="V530" s="6"/>
       <c r="AG530" s="10"/>
     </row>
     <row r="531" spans="1:33" ht="45">
@@ -35989,10 +35990,10 @@
         <v>18900</v>
       </c>
       <c r="P531" s="10" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="Q531" s="10" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="532" spans="1:33">
@@ -36003,19 +36004,46 @@
         <v>531</v>
       </c>
       <c r="C532" s="6" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="D532" t="s">
         <v>18</v>
       </c>
       <c r="E532" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="F532" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="533" spans="1:33">
+      <c r="G532">
+        <v>10</v>
+      </c>
+      <c r="H532">
+        <v>1</v>
+      </c>
+      <c r="I532">
+        <v>1</v>
+      </c>
+      <c r="J532">
+        <v>1000</v>
+      </c>
+      <c r="K532">
+        <v>1</v>
+      </c>
+      <c r="L532">
+        <v>0</v>
+      </c>
+      <c r="M532">
+        <v>10</v>
+      </c>
+      <c r="N532" t="s">
+        <v>21</v>
+      </c>
+      <c r="O532" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:33" ht="60">
       <c r="A533">
         <v>532</v>
       </c>
@@ -36023,16 +36051,46 @@
         <v>532</v>
       </c>
       <c r="C533" s="6" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="D533" t="s">
         <v>1626</v>
       </c>
       <c r="E533" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="F533" s="6" t="s">
-        <v>2332</v>
+        <v>2331</v>
+      </c>
+      <c r="G533">
+        <v>52000</v>
+      </c>
+      <c r="H533">
+        <v>9200</v>
+      </c>
+      <c r="I533">
+        <v>1</v>
+      </c>
+      <c r="J533">
+        <v>378</v>
+      </c>
+      <c r="K533">
+        <v>90</v>
+      </c>
+      <c r="L533">
+        <v>6</v>
+      </c>
+      <c r="M533">
+        <v>1500</v>
+      </c>
+      <c r="N533" t="s">
+        <v>31</v>
+      </c>
+      <c r="O533" s="8">
+        <v>400</v>
+      </c>
+      <c r="Q533" s="10" t="s">
+        <v>2353</v>
       </c>
     </row>
     <row r="534" spans="1:33">
@@ -36043,16 +36101,16 @@
         <v>533</v>
       </c>
       <c r="C534" s="6" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="D534" t="s">
         <v>1626</v>
       </c>
       <c r="E534" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="F534" s="6" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="535" spans="1:33">
@@ -36063,16 +36121,16 @@
         <v>534</v>
       </c>
       <c r="C535" s="6" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="D535" t="s">
         <v>1626</v>
       </c>
       <c r="E535" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="F535" s="6" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="536" spans="1:33">
@@ -36083,16 +36141,16 @@
         <v>535</v>
       </c>
       <c r="C536" s="6" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="D536" t="s">
         <v>1626</v>
       </c>
       <c r="E536" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="F536" s="6" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="537" spans="1:33">
@@ -36103,16 +36161,16 @@
         <v>536</v>
       </c>
       <c r="C537" s="6" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="D537" t="s">
         <v>1626</v>
       </c>
       <c r="E537" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="F537" s="6" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="538" spans="1:33">
@@ -36123,16 +36181,16 @@
         <v>537</v>
       </c>
       <c r="C538" s="6" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="D538" t="s">
         <v>1626</v>
       </c>
       <c r="E538" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F538" s="6" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="539" spans="1:33">
@@ -36143,16 +36201,16 @@
         <v>538</v>
       </c>
       <c r="C539" s="6" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="D539" t="s">
         <v>1626</v>
       </c>
       <c r="E539" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="F539" s="6" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="540" spans="1:33">
@@ -36163,16 +36221,16 @@
         <v>539</v>
       </c>
       <c r="C540" s="6" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="D540" t="s">
         <v>1626</v>
       </c>
       <c r="E540" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="F540" s="6" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="541" spans="1:33">
@@ -36183,16 +36241,16 @@
         <v>540</v>
       </c>
       <c r="C541" s="6" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="D541" t="s">
         <v>1626</v>
       </c>
       <c r="E541" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="F541" s="6" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="542" spans="1:33">
@@ -36203,16 +36261,16 @@
         <v>541</v>
       </c>
       <c r="C542" s="6" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="D542" t="s">
         <v>1626</v>
       </c>
       <c r="E542" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="F542" s="6" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="543" spans="1:33">
@@ -36223,13 +36281,13 @@
         <v>542</v>
       </c>
       <c r="C543" s="6" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="D543" t="s">
         <v>1626</v>
       </c>
       <c r="E543" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="F543" s="6" t="s">
         <v>2341</v>
@@ -36243,13 +36301,13 @@
         <v>543</v>
       </c>
       <c r="C544" s="6" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="D544" t="s">
         <v>1626</v>
       </c>
       <c r="E544" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="F544" s="6" t="s">
         <v>2342</v>
@@ -36263,13 +36321,13 @@
         <v>544</v>
       </c>
       <c r="C545" s="6" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="D545" t="s">
         <v>1626</v>
       </c>
       <c r="E545" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="F545" s="6" t="s">
         <v>2343</v>
@@ -36283,13 +36341,16 @@
         <v>545</v>
       </c>
       <c r="C546" s="6" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="D546" t="s">
         <v>1626</v>
       </c>
       <c r="E546" t="s">
-        <v>2292</v>
+        <v>2291</v>
+      </c>
+      <c r="F546" s="6" t="s">
+        <v>2344</v>
       </c>
     </row>
     <row r="547" spans="1:6">
@@ -36300,13 +36361,16 @@
         <v>546</v>
       </c>
       <c r="C547" s="6" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="D547" t="s">
         <v>1626</v>
       </c>
       <c r="E547" t="s">
-        <v>2293</v>
+        <v>2292</v>
+      </c>
+      <c r="F547" s="6" t="s">
+        <v>2345</v>
       </c>
     </row>
     <row r="548" spans="1:6">
@@ -36317,13 +36381,16 @@
         <v>547</v>
       </c>
       <c r="C548" s="6" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="D548" t="s">
         <v>1626</v>
       </c>
       <c r="E548" t="s">
-        <v>2294</v>
+        <v>2293</v>
+      </c>
+      <c r="F548" s="6" t="s">
+        <v>2334</v>
       </c>
     </row>
     <row r="549" spans="1:6">
@@ -36334,13 +36401,16 @@
         <v>548</v>
       </c>
       <c r="C549" s="6" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="D549" t="s">
         <v>1626</v>
       </c>
       <c r="E549" t="s">
-        <v>2295</v>
+        <v>2294</v>
+      </c>
+      <c r="F549" s="6" t="s">
+        <v>2346</v>
       </c>
     </row>
     <row r="550" spans="1:6">
@@ -36351,13 +36421,16 @@
         <v>549</v>
       </c>
       <c r="C550" s="6" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="D550" t="s">
         <v>1626</v>
       </c>
       <c r="E550" t="s">
-        <v>2296</v>
+        <v>2295</v>
+      </c>
+      <c r="F550" s="6" t="s">
+        <v>2347</v>
       </c>
     </row>
     <row r="551" spans="1:6">
@@ -36368,13 +36441,16 @@
         <v>550</v>
       </c>
       <c r="C551" s="6" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="D551" t="s">
         <v>1626</v>
       </c>
       <c r="E551" t="s">
-        <v>2297</v>
+        <v>2296</v>
+      </c>
+      <c r="F551" s="6" t="s">
+        <v>2348</v>
       </c>
     </row>
     <row r="552" spans="1:6">
@@ -36385,13 +36461,16 @@
         <v>551</v>
       </c>
       <c r="C552" s="6" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="D552" t="s">
         <v>1626</v>
       </c>
       <c r="E552" t="s">
-        <v>2298</v>
+        <v>2297</v>
+      </c>
+      <c r="F552" s="6" t="s">
+        <v>2349</v>
       </c>
     </row>
     <row r="553" spans="1:6">
@@ -36402,13 +36481,16 @@
         <v>552</v>
       </c>
       <c r="C553" s="6" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="D553" t="s">
         <v>1626</v>
       </c>
       <c r="E553" t="s">
-        <v>2299</v>
+        <v>2298</v>
+      </c>
+      <c r="F553" s="6" t="s">
+        <v>2340</v>
       </c>
     </row>
     <row r="554" spans="1:6">
@@ -36419,13 +36501,16 @@
         <v>553</v>
       </c>
       <c r="C554" s="6" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="D554" t="s">
         <v>1626</v>
       </c>
       <c r="E554" t="s">
-        <v>2300</v>
+        <v>2299</v>
+      </c>
+      <c r="F554" s="6" t="s">
+        <v>2348</v>
       </c>
     </row>
     <row r="555" spans="1:6">
@@ -36436,13 +36521,16 @@
         <v>554</v>
       </c>
       <c r="C555" s="6" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="D555" t="s">
         <v>1626</v>
       </c>
       <c r="E555" t="s">
-        <v>2301</v>
+        <v>2300</v>
+      </c>
+      <c r="F555" s="6" t="s">
+        <v>2350</v>
       </c>
     </row>
     <row r="556" spans="1:6">
@@ -36453,13 +36541,16 @@
         <v>555</v>
       </c>
       <c r="C556" s="6" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="D556" t="s">
         <v>1626</v>
       </c>
       <c r="E556" t="s">
-        <v>2302</v>
+        <v>2301</v>
+      </c>
+      <c r="F556" s="6" t="s">
+        <v>2334</v>
       </c>
     </row>
     <row r="557" spans="1:6">
@@ -36470,13 +36561,16 @@
         <v>556</v>
       </c>
       <c r="C557" s="6" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="D557" t="s">
         <v>1626</v>
       </c>
       <c r="E557" t="s">
-        <v>2303</v>
+        <v>2302</v>
+      </c>
+      <c r="F557" s="6" t="s">
+        <v>2351</v>
       </c>
     </row>
     <row r="558" spans="1:6">
@@ -36487,13 +36581,16 @@
         <v>557</v>
       </c>
       <c r="C558" s="6" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="D558" t="s">
         <v>1626</v>
       </c>
       <c r="E558" t="s">
-        <v>2304</v>
+        <v>2303</v>
+      </c>
+      <c r="F558" s="6" t="s">
+        <v>2352</v>
       </c>
     </row>
   </sheetData>
@@ -36505,7 +36602,7 @@
     <dataValidation type="list" allowBlank="1" sqref="F2:F1000 W530" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"none,red,floating,black,metal,angel,alien,zombie,ancient,devil,witch,apostle,starAlien,superLife,beast,sage,villain,custom"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N1000 AE530" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N1000 N532" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"単体,範囲"</formula1>
     </dataValidation>
   </dataValidations>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDB1E7B-8883-FF4A-9712-1BF9D769C179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDB8C6B-D008-A34E-ABEF-70D5F425AEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8420,10 +8420,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>angel,starAlian,custom</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>floating,beast,custom</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -8432,6 +8428,10 @@
 採用面接では度重なる激務により基準が
 適当であり、顔が恐ろしいかどうかで
 採用、不採用を決めている。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>angel,starAlien,custom</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -36090,7 +36090,7 @@
         <v>400</v>
       </c>
       <c r="Q533" s="10" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="534" spans="1:33">
@@ -36570,7 +36570,7 @@
         <v>2302</v>
       </c>
       <c r="F557" s="6" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="558" spans="1:6">
@@ -36590,7 +36590,7 @@
         <v>2303</v>
       </c>
       <c r="F558" s="6" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
     </row>
   </sheetData>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDB8C6B-D008-A34E-ABEF-70D5F425AEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAE3813-25A3-A349-B2BF-E5A9250D5CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7663" uniqueCount="2354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7666" uniqueCount="2356">
   <si>
     <t>id</t>
   </si>
@@ -8432,6 +8432,20 @@
   </si>
   <si>
     <t>angel,starAlien,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>遠方範囲攻撃 (-210～290)
+範囲3連続攻撃 15000 15000 15000(6F  12F  18F) 
+100%の確率でLv5小烈波(射程 150～200  450～500 750～800)
+無効(動きを止める、ふっとばす)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>自分は何類なのか？という問を追及するた
+め宇宙からやってきた海のいきもの。問の
+答えを道行く人に宇宙語で尋ねては答えら
+れなかった人に小烈波を放つあぶないやつ</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -36313,7 +36327,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="545" spans="1:6">
+    <row r="545" spans="1:17">
       <c r="A545">
         <v>544</v>
       </c>
@@ -36333,7 +36347,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="546" spans="1:6">
+    <row r="546" spans="1:17">
       <c r="A546">
         <v>545</v>
       </c>
@@ -36353,7 +36367,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="547" spans="1:6">
+    <row r="547" spans="1:17">
       <c r="A547">
         <v>546</v>
       </c>
@@ -36373,7 +36387,7 @@
         <v>2345</v>
       </c>
     </row>
-    <row r="548" spans="1:6">
+    <row r="548" spans="1:17">
       <c r="A548">
         <v>547</v>
       </c>
@@ -36393,7 +36407,7 @@
         <v>2334</v>
       </c>
     </row>
-    <row r="549" spans="1:6">
+    <row r="549" spans="1:17">
       <c r="A549">
         <v>548</v>
       </c>
@@ -36413,7 +36427,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="550" spans="1:6">
+    <row r="550" spans="1:17">
       <c r="A550">
         <v>549</v>
       </c>
@@ -36433,7 +36447,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="551" spans="1:6">
+    <row r="551" spans="1:17">
       <c r="A551">
         <v>550</v>
       </c>
@@ -36453,7 +36467,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="552" spans="1:6">
+    <row r="552" spans="1:17" ht="60">
       <c r="A552">
         <v>551</v>
       </c>
@@ -36472,8 +36486,41 @@
       <c r="F552" s="6" t="s">
         <v>2349</v>
       </c>
-    </row>
-    <row r="553" spans="1:6">
+      <c r="G552">
+        <v>1898000</v>
+      </c>
+      <c r="H552">
+        <v>38000</v>
+      </c>
+      <c r="I552">
+        <v>3</v>
+      </c>
+      <c r="J552">
+        <v>108</v>
+      </c>
+      <c r="K552">
+        <v>18</v>
+      </c>
+      <c r="L552">
+        <v>5</v>
+      </c>
+      <c r="M552">
+        <v>190</v>
+      </c>
+      <c r="N552" t="s">
+        <v>31</v>
+      </c>
+      <c r="O552">
+        <v>7700</v>
+      </c>
+      <c r="P552" s="10" t="s">
+        <v>2354</v>
+      </c>
+      <c r="Q552" s="10" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="553" spans="1:17">
       <c r="A553">
         <v>552</v>
       </c>
@@ -36493,7 +36540,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="554" spans="1:6">
+    <row r="554" spans="1:17">
       <c r="A554">
         <v>553</v>
       </c>
@@ -36513,7 +36560,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="555" spans="1:6">
+    <row r="555" spans="1:17">
       <c r="A555">
         <v>554</v>
       </c>
@@ -36533,7 +36580,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="556" spans="1:6">
+    <row r="556" spans="1:17">
       <c r="A556">
         <v>555</v>
       </c>
@@ -36553,7 +36600,7 @@
         <v>2334</v>
       </c>
     </row>
-    <row r="557" spans="1:6">
+    <row r="557" spans="1:17">
       <c r="A557">
         <v>556</v>
       </c>
@@ -36573,7 +36620,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="558" spans="1:6">
+    <row r="558" spans="1:17">
       <c r="A558">
         <v>557</v>
       </c>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAE3813-25A3-A349-B2BF-E5A9250D5CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310A705F-1D27-F34B-8D33-4DAD92588F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36490,7 +36490,7 @@
         <v>1898000</v>
       </c>
       <c r="H552">
-        <v>38000</v>
+        <v>45000</v>
       </c>
       <c r="I552">
         <v>3</v>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310A705F-1D27-F34B-8D33-4DAD92588F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356E022E-30F0-3E45-A8A6-0EF38DE8306D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7666" uniqueCount="2356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7676" uniqueCount="2363">
   <si>
     <t>id</t>
   </si>
@@ -8446,6 +8446,52 @@
 め宇宙からやってきた海のいきもの。問の
 答えを道行く人に宇宙語で尋ねては答えら
 れなかった人に小烈波を放つあぶないやつ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>遠方範囲攻撃 (300～1700)
+バリア (60000)
+100%の確率で再生産時間100%遅延</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>100%の確率で再生産時間30%遅延
+無効(吹っ飛ばし、呪い、ワープ)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>オレは最強の暗殺者だ………と語る、
+依頼成功30%の新人ハイエナ。最
+近鍛え直そうと思い立ち、落ちて
+たネコ缶で咬合力トレーニング中。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>全方位範囲攻撃(-100～300)
+20%の確率で再生産時間40%遅延
+10%の確率でLv3波動(射程 867.5)
+1%の確率で渾身の一撃(与ダメ ×30)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>競馬界において伝説を残したとされている
+青毛の馬。歩幅が小さく高速で足を動かす
+ことによって速く動いているため、走り方
+のせいで人気はない。意外とインドア派</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>全方位範囲攻撃 (-200〜800)
+30%の確率でふっとばす
+30%の確率で90F動きを遅くする
+30%の確率で90F攻撃力50%に低下</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>星の神殿に住む星のお面を被った天使。どれを答え
+ても不正解の選択クイズを投げかけ、理不尽なこと
+を言いまくり、相手を泣かした過去があるため、全
+にゃんこ軍、全わんこ軍からとても嫌われている。</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -36103,6 +36149,9 @@
       <c r="O533" s="8">
         <v>400</v>
       </c>
+      <c r="P533" s="10" t="s">
+        <v>2356</v>
+      </c>
       <c r="Q533" s="10" t="s">
         <v>2352</v>
       </c>
@@ -36147,7 +36196,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="536" spans="1:33">
+    <row r="536" spans="1:33" ht="60">
       <c r="A536">
         <v>535</v>
       </c>
@@ -36165,6 +36214,39 @@
       </c>
       <c r="F536" s="6" t="s">
         <v>2334</v>
+      </c>
+      <c r="G536">
+        <v>780000</v>
+      </c>
+      <c r="H536">
+        <v>28600</v>
+      </c>
+      <c r="I536">
+        <v>3</v>
+      </c>
+      <c r="J536">
+        <v>60</v>
+      </c>
+      <c r="K536">
+        <v>30</v>
+      </c>
+      <c r="L536">
+        <v>20</v>
+      </c>
+      <c r="M536">
+        <v>370</v>
+      </c>
+      <c r="N536" t="s">
+        <v>31</v>
+      </c>
+      <c r="O536" s="8">
+        <v>2480</v>
+      </c>
+      <c r="P536" s="10" t="s">
+        <v>2357</v>
+      </c>
+      <c r="Q536" s="10" t="s">
+        <v>2358</v>
       </c>
     </row>
     <row r="537" spans="1:33">
@@ -36580,7 +36662,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="556" spans="1:17">
+    <row r="556" spans="1:17" ht="60">
       <c r="A556">
         <v>555</v>
       </c>
@@ -36599,8 +36681,41 @@
       <c r="F556" s="6" t="s">
         <v>2334</v>
       </c>
-    </row>
-    <row r="557" spans="1:17">
+      <c r="G556">
+        <v>1926000</v>
+      </c>
+      <c r="H556">
+        <v>3980</v>
+      </c>
+      <c r="I556">
+        <v>4</v>
+      </c>
+      <c r="J556">
+        <v>15</v>
+      </c>
+      <c r="K556">
+        <v>9</v>
+      </c>
+      <c r="L556">
+        <v>35</v>
+      </c>
+      <c r="M556">
+        <v>250</v>
+      </c>
+      <c r="N556" t="s">
+        <v>31</v>
+      </c>
+      <c r="O556">
+        <v>6980</v>
+      </c>
+      <c r="P556" s="10" t="s">
+        <v>2359</v>
+      </c>
+      <c r="Q556" s="10" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="557" spans="1:17" ht="60">
       <c r="A557">
         <v>556</v>
       </c>
@@ -36618,6 +36733,39 @@
       </c>
       <c r="F557" s="6" t="s">
         <v>2353</v>
+      </c>
+      <c r="G557">
+        <v>2600000</v>
+      </c>
+      <c r="H557">
+        <v>26000</v>
+      </c>
+      <c r="I557">
+        <v>2</v>
+      </c>
+      <c r="J557">
+        <v>63</v>
+      </c>
+      <c r="K557">
+        <v>24</v>
+      </c>
+      <c r="L557">
+        <v>1</v>
+      </c>
+      <c r="M557">
+        <v>320</v>
+      </c>
+      <c r="N557" t="s">
+        <v>31</v>
+      </c>
+      <c r="O557">
+        <v>7900</v>
+      </c>
+      <c r="P557" s="10" t="s">
+        <v>2361</v>
+      </c>
+      <c r="Q557" s="10" t="s">
+        <v>2362</v>
       </c>
     </row>
     <row r="558" spans="1:17">

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356E022E-30F0-3E45-A8A6-0EF38DE8306D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C351844-1546-9743-A2D4-DFFE1A065939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7676" uniqueCount="2363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7679" uniqueCount="2365">
   <si>
     <t>id</t>
   </si>
@@ -8492,6 +8492,17 @@
 ても不正解の選択クイズを投げかけ、理不尽なこと
 を言いまくり、相手を泣かした過去があるため、全
 にゃんこ軍、全わんこ軍からとても嫌われている。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>60%の確率で渾身の一撃(与ダメ ×3)
+20%の確率でLv2小波動 (射程 667.5 与ダメ×0.2)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>父親の執筆する小説をこまめに読んで
+いる文学少年。この見た目なのに運動
+会で白組にされたことに不満げ。</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -36176,7 +36187,7 @@
         <v>2332</v>
       </c>
     </row>
-    <row r="535" spans="1:33">
+    <row r="535" spans="1:33" ht="45">
       <c r="A535">
         <v>534</v>
       </c>
@@ -36194,6 +36205,39 @@
       </c>
       <c r="F535" s="6" t="s">
         <v>2333</v>
+      </c>
+      <c r="G535">
+        <v>32000</v>
+      </c>
+      <c r="H535">
+        <v>2600</v>
+      </c>
+      <c r="I535">
+        <v>3</v>
+      </c>
+      <c r="J535">
+        <v>31</v>
+      </c>
+      <c r="K535">
+        <v>20</v>
+      </c>
+      <c r="L535">
+        <v>36</v>
+      </c>
+      <c r="M535">
+        <v>145</v>
+      </c>
+      <c r="N535" t="s">
+        <v>31</v>
+      </c>
+      <c r="O535" s="8">
+        <v>1540</v>
+      </c>
+      <c r="P535" s="10" t="s">
+        <v>2363</v>
+      </c>
+      <c r="Q535" s="10" t="s">
+        <v>2364</v>
       </c>
     </row>
     <row r="536" spans="1:33" ht="60">

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C351844-1546-9743-A2D4-DFFE1A065939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF20590-3EEF-AC49-A8A5-B7DF882E4991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12041,7 +12041,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15">
+    <row r="63" spans="1:18">
       <c r="A63">
         <v>62</v>
       </c>
@@ -12087,12 +12087,9 @@
       <c r="O63" s="8">
         <v>7821</v>
       </c>
-      <c r="P63" s="10" t="s">
-        <v>113</v>
-      </c>
       <c r="Q63" s="10"/>
     </row>
-    <row r="64" spans="1:18">
+    <row r="64" spans="1:18" ht="15">
       <c r="A64">
         <v>63</v>
       </c>
@@ -12137,6 +12134,9 @@
       </c>
       <c r="O64" s="8">
         <v>9361</v>
+      </c>
+      <c r="P64" s="10" t="s">
+        <v>113</v>
       </c>
       <c r="Q64" s="10"/>
       <c r="R64" s="12"/>
@@ -36001,7 +36001,7 @@
         <v>31</v>
       </c>
       <c r="O530">
-        <v>4500</v>
+        <v>6500</v>
       </c>
       <c r="P530" s="10" t="s">
         <v>2275</v>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF20590-3EEF-AC49-A8A5-B7DF882E4991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE49F59-C72A-234E-A9B9-D050BB1FBBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7679" uniqueCount="2365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7682" uniqueCount="2367">
   <si>
     <t>id</t>
   </si>
@@ -8503,6 +8503,19 @@
     <t>父親の執筆する小説をこまめに読んで
 いる文学少年。この見た目なのに運動
 会で白組にされたことに不満げ。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>古代の波動に目覚めたイノシシ。文明を捨
+てて原始に戻る素晴らしさを説いて回ってい
+る。まずは食事から始めようと、ファスト
+フードを捨て木の実中心の食生活に挑戦中。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>全方位攻撃 (-200～350)
+古代の呪い (100％の確率で60F特殊能力封印)
+対 お城 与ダメ×4</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -36686,7 +36699,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="555" spans="1:17">
+    <row r="555" spans="1:17" ht="60">
       <c r="A555">
         <v>554</v>
       </c>
@@ -36704,6 +36717,39 @@
       </c>
       <c r="F555" s="6" t="s">
         <v>2350</v>
+      </c>
+      <c r="G555">
+        <v>1000000</v>
+      </c>
+      <c r="H555">
+        <v>9999</v>
+      </c>
+      <c r="I555">
+        <v>2</v>
+      </c>
+      <c r="J555">
+        <v>12</v>
+      </c>
+      <c r="K555">
+        <v>9</v>
+      </c>
+      <c r="L555">
+        <v>15</v>
+      </c>
+      <c r="M555">
+        <v>130</v>
+      </c>
+      <c r="N555" t="s">
+        <v>31</v>
+      </c>
+      <c r="O555">
+        <v>4000</v>
+      </c>
+      <c r="P555" s="10" t="s">
+        <v>2366</v>
+      </c>
+      <c r="Q555" s="10" t="s">
+        <v>2365</v>
       </c>
     </row>
     <row r="556" spans="1:17" ht="60">

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE49F59-C72A-234E-A9B9-D050BB1FBBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E4EFC5-6B00-234C-A699-120C224B4CBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7682" uniqueCount="2367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7700" uniqueCount="2380">
   <si>
     <t>id</t>
   </si>
@@ -8412,10 +8412,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>starAlien,beast,custom</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>ancient,custom</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -8435,13 +8431,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>遠方範囲攻撃 (-210～290)
-範囲3連続攻撃 15000 15000 15000(6F  12F  18F) 
-100%の確率でLv5小烈波(射程 150～200  450～500 750～800)
-無効(動きを止める、ふっとばす)</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>自分は何類なのか？という問を追及するた
 め宇宙からやってきた海のいきもの。問の
 答えを道行く人に宇宙語で尋ねては答えら
@@ -8516,6 +8505,83 @@
     <t>全方位攻撃 (-200～350)
 古代の呪い (100％の確率で60F特殊能力封印)
 対 お城 与ダメ×4</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>enemy_images/enemy_558.jpg</t>
+  </si>
+  <si>
+    <t>enemy_images/enemy_559.jpg</t>
+  </si>
+  <si>
+    <t>alien,beast,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>floating,alien,beast,custom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>遠方範囲攻撃 (-210～290)
+範囲3連続攻撃 15000 15000 15000(6F  12F  18F) 
+100%の確率でLv5小烈波(射程 150～200  450～500 750～800)
+無効(止める、ふっとばす)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>全方位範囲攻撃(-100～420)
+10%の確率でクリティカル
+無効 (ふっとばす、止める、遅くする、攻撃力低下、ワープ)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>無効 (波動、烈波、爆波)</t>
+  </si>
+  <si>
+    <t>5%の確率でクリティカル
+無効 (クリティカル、メタルキラー、止める)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>硬さと顔の恐さを追求した結果作られた生
+命体のゴリラ。外付けの脳みそで頭脳を保
+管しているが物忘れが激しいため大人の脳
+トレをさせることで補完している。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>まだ見ぬ宇宙を目指して群れから離れ野生
+化したツバメ。しかしこのゲームでは横に
+しか移動できないため大気圏突破が叶うこ
+とはない。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大学デビューで無理にイメチェンしたこ
+とにより周りからも物理的にも浮き始め
+たダチョウ同好会。広く浅く所属してい
+るコミュニティを端から端まで飛び回る。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ゴリリウム</t>
+  </si>
+  <si>
+    <t>超空獣スワロケット</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>全方位範囲攻撃(-400～590)
+100%の確率で360F動きを遅くする
+100%の確率でふっとばす
+無効(止める、遅くする、ふっとばす、攻撃力低下、呪い)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>怒りの炎に燃えるナマルケモルル。かつて
+ないスピードと攻撃範囲、さらに全てを焼
+き尽くす超火力を誇る。彼の動きはもう誰
+にも止められない。</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -8865,7 +8931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG558"/>
+  <dimension ref="A1:AG560"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -36174,10 +36240,10 @@
         <v>400</v>
       </c>
       <c r="P533" s="10" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
       <c r="Q533" s="10" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="534" spans="1:33">
@@ -36247,10 +36313,10 @@
         <v>1540</v>
       </c>
       <c r="P535" s="10" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="Q535" s="10" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="536" spans="1:33" ht="60">
@@ -36300,10 +36366,10 @@
         <v>2480</v>
       </c>
       <c r="P536" s="10" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="Q536" s="10" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="537" spans="1:33">
@@ -36623,7 +36689,7 @@
         <v>2297</v>
       </c>
       <c r="F552" s="6" t="s">
-        <v>2349</v>
+        <v>2367</v>
       </c>
       <c r="G552">
         <v>1898000</v>
@@ -36653,10 +36719,10 @@
         <v>7700</v>
       </c>
       <c r="P552" s="10" t="s">
-        <v>2354</v>
+        <v>2369</v>
       </c>
       <c r="Q552" s="10" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="553" spans="1:17">
@@ -36679,7 +36745,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="554" spans="1:17">
+    <row r="554" spans="1:17" ht="60">
       <c r="A554">
         <v>553</v>
       </c>
@@ -36697,6 +36763,39 @@
       </c>
       <c r="F554" s="6" t="s">
         <v>2348</v>
+      </c>
+      <c r="G554">
+        <v>2250000</v>
+      </c>
+      <c r="H554">
+        <v>188000</v>
+      </c>
+      <c r="I554">
+        <v>3</v>
+      </c>
+      <c r="J554">
+        <v>420</v>
+      </c>
+      <c r="K554">
+        <v>128</v>
+      </c>
+      <c r="L554">
+        <v>36</v>
+      </c>
+      <c r="M554">
+        <v>400</v>
+      </c>
+      <c r="N554" t="s">
+        <v>31</v>
+      </c>
+      <c r="O554">
+        <v>11800</v>
+      </c>
+      <c r="P554" s="10" t="s">
+        <v>2378</v>
+      </c>
+      <c r="Q554" s="10" t="s">
+        <v>2379</v>
       </c>
     </row>
     <row r="555" spans="1:17" ht="60">
@@ -36716,7 +36815,7 @@
         <v>2300</v>
       </c>
       <c r="F555" s="6" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="G555">
         <v>1000000</v>
@@ -36746,10 +36845,10 @@
         <v>4000</v>
       </c>
       <c r="P555" s="10" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="Q555" s="10" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="556" spans="1:17" ht="60">
@@ -36799,10 +36898,10 @@
         <v>6980</v>
       </c>
       <c r="P556" s="10" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="Q556" s="10" t="s">
-        <v>2360</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="557" spans="1:17" ht="60">
@@ -36822,7 +36921,7 @@
         <v>2302</v>
       </c>
       <c r="F557" s="6" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="G557">
         <v>2600000</v>
@@ -36852,13 +36951,13 @@
         <v>7900</v>
       </c>
       <c r="P557" s="10" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="Q557" s="10" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="558" spans="1:17">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="558" spans="1:17" ht="60">
       <c r="A558">
         <v>557</v>
       </c>
@@ -36875,7 +36974,140 @@
         <v>2303</v>
       </c>
       <c r="F558" s="6" t="s">
-        <v>2351</v>
+        <v>2350</v>
+      </c>
+      <c r="G558">
+        <v>2100000</v>
+      </c>
+      <c r="H558">
+        <v>18000</v>
+      </c>
+      <c r="I558">
+        <v>4</v>
+      </c>
+      <c r="J558">
+        <v>21</v>
+      </c>
+      <c r="K558">
+        <v>4</v>
+      </c>
+      <c r="L558">
+        <v>32</v>
+      </c>
+      <c r="M558">
+        <v>380</v>
+      </c>
+      <c r="N558" t="s">
+        <v>31</v>
+      </c>
+      <c r="O558">
+        <v>948</v>
+      </c>
+      <c r="P558" s="10" t="s">
+        <v>2370</v>
+      </c>
+      <c r="Q558" s="10" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="559" spans="1:17" ht="60">
+      <c r="A559">
+        <v>558</v>
+      </c>
+      <c r="B559">
+        <v>558</v>
+      </c>
+      <c r="C559" s="6" t="s">
+        <v>2377</v>
+      </c>
+      <c r="E559" t="s">
+        <v>2365</v>
+      </c>
+      <c r="F559" s="6" t="s">
+        <v>2368</v>
+      </c>
+      <c r="G559">
+        <v>66000</v>
+      </c>
+      <c r="H559">
+        <v>37500</v>
+      </c>
+      <c r="I559">
+        <v>10</v>
+      </c>
+      <c r="J559">
+        <v>137</v>
+      </c>
+      <c r="K559">
+        <v>1</v>
+      </c>
+      <c r="L559">
+        <v>86</v>
+      </c>
+      <c r="M559">
+        <v>140</v>
+      </c>
+      <c r="N559" t="s">
+        <v>31</v>
+      </c>
+      <c r="O559">
+        <v>7500</v>
+      </c>
+      <c r="P559" s="6" t="s">
+        <v>2371</v>
+      </c>
+      <c r="Q559" s="10" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="560" spans="1:17" ht="60">
+      <c r="A560">
+        <v>559</v>
+      </c>
+      <c r="B560">
+        <v>559</v>
+      </c>
+      <c r="C560" s="6" t="s">
+        <v>2376</v>
+      </c>
+      <c r="E560" t="s">
+        <v>2366</v>
+      </c>
+      <c r="F560" s="6" t="s">
+        <v>2345</v>
+      </c>
+      <c r="G560">
+        <v>35</v>
+      </c>
+      <c r="H560">
+        <v>19000</v>
+      </c>
+      <c r="I560">
+        <v>7</v>
+      </c>
+      <c r="J560">
+        <v>11</v>
+      </c>
+      <c r="K560">
+        <v>6</v>
+      </c>
+      <c r="L560">
+        <v>15</v>
+      </c>
+      <c r="M560">
+        <v>155</v>
+      </c>
+      <c r="N560" t="s">
+        <v>31</v>
+      </c>
+      <c r="O560">
+        <v>1800</v>
+      </c>
+      <c r="P560" s="10" t="s">
+        <v>2372</v>
+      </c>
+      <c r="Q560" s="10" t="s">
+        <v>2373</v>
       </c>
     </row>
   </sheetData>
@@ -36887,7 +37119,7 @@
     <dataValidation type="list" allowBlank="1" sqref="F2:F1000 W530" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"none,red,floating,black,metal,angel,alien,zombie,ancient,devil,witch,apostle,starAlien,superLife,beast,sage,villain,custom"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N1000 N532" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N1000" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"単体,範囲"</formula1>
     </dataValidation>
   </dataValidations>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D6D4FC-C77F-D949-BE90-8FFEB63647B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547B4626-87B9-5841-B2B3-82E254974598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7700" uniqueCount="2380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7700" uniqueCount="2381">
   <si>
     <t>id</t>
   </si>
@@ -8612,6 +8612,10 @@
     <t>100％の確率で爆波（射程 420）
 悪魔シールド（HP2500 KB時 悪魔シールドHP1250再生回復）
 無効 （ふっとばす 遅くする）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>angel,starAlien</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -17728,7 +17732,7 @@
         <v>529</v>
       </c>
       <c r="F173" t="s">
-        <v>369</v>
+        <v>278</v>
       </c>
       <c r="G173">
         <v>13500</v>
@@ -21918,8 +21922,8 @@
       <c r="E255" t="s">
         <v>781</v>
       </c>
-      <c r="F255" t="s">
-        <v>20</v>
+      <c r="F255" s="6" t="s">
+        <v>2380</v>
       </c>
       <c r="G255">
         <v>50000</v>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547B4626-87B9-5841-B2B3-82E254974598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16561E32-2A8B-A04F-8AD5-9AB6F5FB1362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14494,7 +14494,7 @@
         <v>335</v>
       </c>
       <c r="F110" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="G110">
         <v>1000000</v>
@@ -16196,7 +16196,7 @@
         <v>441</v>
       </c>
       <c r="F143" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="G143">
         <v>166000</v>
@@ -16247,7 +16247,7 @@
         <v>444</v>
       </c>
       <c r="F144" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="G144">
         <v>6300</v>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16561E32-2A8B-A04F-8AD5-9AB6F5FB1362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7A62B9-9E97-B142-849B-46BEC55FF20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10162,7 +10162,7 @@
         <v>92</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G24">
         <v>99999</v>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7A62B9-9E97-B142-849B-46BEC55FF20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484C15CE-2419-604D-9EE4-2F68199DAFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21870,7 +21870,7 @@
         <v>777</v>
       </c>
       <c r="F254" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="G254">
         <v>1399999</v>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484C15CE-2419-604D-9EE4-2F68199DAFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7369DD66-E3DC-A645-AD6E-D38D59BCB79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7369DD66-E3DC-A645-AD6E-D38D59BCB79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE2D530-0F01-BC48-9CE7-1D9DC928C5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22025,7 +22025,7 @@
         <v>786</v>
       </c>
       <c r="F257" t="s">
-        <v>379</v>
+        <v>753</v>
       </c>
       <c r="G257">
         <v>666666</v>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE2D530-0F01-BC48-9CE7-1D9DC928C5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867840CD-7833-C749-9181-EC86F998EB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7700" uniqueCount="2381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7700" uniqueCount="2382">
   <si>
     <t>id</t>
   </si>
@@ -8616,6 +8616,16 @@
   </si>
   <si>
     <t>angel,starAlien</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>超突撃部隊コンボーイズ</t>
+    <rPh sb="0" eb="3">
+      <t>チョウトツゲキブタイコンボーイズ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ブタイ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -10022,7 +10032,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>83</v>
+        <v>2381</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -10032,12 +10042,6 @@
       </c>
       <c r="F21" t="s">
         <v>20</v>
-      </c>
-      <c r="G21">
-        <v>80</v>
-      </c>
-      <c r="I21">
-        <v>3</v>
       </c>
       <c r="O21" s="8"/>
       <c r="P21" s="10"/>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867840CD-7833-C749-9181-EC86F998EB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B585029-5AAD-FF46-88D0-733DB2266966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12020,7 +12020,7 @@
         <v>210</v>
       </c>
       <c r="F60" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="G60">
         <v>999999</v>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B585029-5AAD-FF46-88D0-733DB2266966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A10AA0D-8446-4C49-B37F-85E2CC4AF40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7700" uniqueCount="2382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7700" uniqueCount="2383">
   <si>
     <t>id</t>
   </si>
@@ -8626,6 +8626,10 @@
     <rPh sb="3" eb="5">
       <t>ブタイ</t>
     </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>floating,alien</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -15735,8 +15739,8 @@
       <c r="E134" t="s">
         <v>412</v>
       </c>
-      <c r="F134" t="s">
-        <v>369</v>
+      <c r="F134" s="6" t="s">
+        <v>2382</v>
       </c>
       <c r="G134">
         <v>1499999</v>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masya2/Library/Mobile Documents/com~apple~CloudDocs/Documents/BattleCatsDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A10AA0D-8446-4C49-B37F-85E2CC4AF40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEB1F84-92B9-214B-BFEE-E08593D8D767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18366,7 +18366,7 @@
         <v>571</v>
       </c>
       <c r="F185" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="G185">
         <v>100</v>
@@ -19455,7 +19455,7 @@
         <v>643</v>
       </c>
       <c r="F206" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="G206">
         <v>297</v>
@@ -19504,7 +19504,7 @@
         <v>645</v>
       </c>
       <c r="F207" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="G207">
         <v>50</v>
